--- a/Stats For Rush.xlsx
+++ b/Stats For Rush.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurtl\Desktop\statstreaks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25DAF3C-5C27-4812-8CE0-80CB41EB2BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26321694-BA01-4D50-BEBE-92204E36464B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="866" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" tabRatio="866" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PL assists" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2683" uniqueCount="1203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2686" uniqueCount="1208">
   <si>
     <t>Rank</t>
   </si>
@@ -3643,6 +3643,21 @@
   </si>
   <si>
     <t>Mário Jardel</t>
+  </si>
+  <si>
+    <t>Ilkay Gundogan</t>
+  </si>
+  <si>
+    <t>Robbie Earle</t>
+  </si>
+  <si>
+    <t>Ayoze Perez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Pablo Angel </t>
+  </si>
+  <si>
+    <t>Cesar Azpilicueta</t>
   </si>
 </sst>
 </file>
@@ -3816,7 +3831,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3891,6 +3906,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6196,158 +6212,500 @@
       </c>
     </row>
     <row r="122" spans="1:5">
-      <c r="A122" s="14"/>
-      <c r="B122" s="15"/>
+      <c r="A122" s="8">
+        <v>120</v>
+      </c>
+      <c r="B122" s="12" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C122" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D122" s="9"/>
+      <c r="E122" s="8">
+        <v>35</v>
+      </c>
     </row>
     <row r="123" spans="1:5">
-      <c r="A123" s="14"/>
-      <c r="B123" s="15"/>
+      <c r="A123" s="10">
+        <v>120</v>
+      </c>
+      <c r="B123" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="C123" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D123" s="11"/>
+      <c r="E123" s="10">
+        <v>35</v>
+      </c>
     </row>
     <row r="124" spans="1:5">
-      <c r="A124" s="14"/>
-      <c r="B124" s="15"/>
+      <c r="A124" s="8">
+        <v>120</v>
+      </c>
+      <c r="B124" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="C124" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D124" s="9"/>
+      <c r="E124" s="8">
+        <v>35</v>
+      </c>
     </row>
     <row r="125" spans="1:5" ht="29" customHeight="1">
-      <c r="A125" s="14"/>
-      <c r="B125" s="15"/>
+      <c r="A125" s="10">
+        <v>120</v>
+      </c>
+      <c r="B125" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="C125" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D125" s="11"/>
+      <c r="E125" s="10">
+        <v>35</v>
+      </c>
     </row>
     <row r="126" spans="1:5">
-      <c r="A126" s="14"/>
-      <c r="B126" s="15"/>
+      <c r="A126" s="8">
+        <v>120</v>
+      </c>
+      <c r="B126" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C126" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D126" s="9"/>
+      <c r="E126" s="8">
+        <v>35</v>
+      </c>
     </row>
     <row r="127" spans="1:5">
-      <c r="A127" s="14"/>
-      <c r="B127" s="15"/>
+      <c r="A127" s="10">
+        <v>120</v>
+      </c>
+      <c r="B127" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="C127" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D127" s="11"/>
+      <c r="E127" s="10">
+        <v>35</v>
+      </c>
     </row>
     <row r="128" spans="1:5">
-      <c r="A128" s="14"/>
-      <c r="B128" s="15"/>
-    </row>
-    <row r="129" spans="1:2" ht="43.5" customHeight="1">
-      <c r="A129" s="14"/>
-      <c r="B129" s="15"/>
-    </row>
-    <row r="130" spans="1:2">
-      <c r="A130" s="14"/>
-      <c r="B130" s="15"/>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" s="14"/>
-      <c r="B131" s="15"/>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" s="14"/>
-      <c r="B132" s="15"/>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" s="14"/>
-      <c r="B133" s="15"/>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" s="14"/>
-      <c r="B134" s="15"/>
-    </row>
-    <row r="135" spans="1:2" ht="43.5" customHeight="1">
-      <c r="A135" s="14"/>
-      <c r="B135" s="15"/>
-    </row>
-    <row r="136" spans="1:2">
-      <c r="A136" s="14"/>
-      <c r="B136" s="15"/>
-    </row>
-    <row r="137" spans="1:2">
-      <c r="A137" s="14"/>
-      <c r="B137" s="15"/>
-    </row>
-    <row r="138" spans="1:2">
-      <c r="A138" s="14"/>
-      <c r="B138" s="15"/>
-    </row>
-    <row r="139" spans="1:2" ht="29" customHeight="1">
-      <c r="A139" s="14"/>
-      <c r="B139" s="15"/>
-    </row>
-    <row r="140" spans="1:2">
-      <c r="A140" s="14"/>
-      <c r="B140" s="15"/>
-    </row>
-    <row r="141" spans="1:2">
-      <c r="A141" s="14"/>
-      <c r="B141" s="15"/>
-    </row>
-    <row r="142" spans="1:2">
-      <c r="A142" s="14"/>
-      <c r="B142" s="15"/>
-    </row>
-    <row r="143" spans="1:2" ht="58" customHeight="1">
-      <c r="A143" s="14"/>
-      <c r="B143" s="15"/>
-    </row>
-    <row r="144" spans="1:2" ht="29" customHeight="1">
-      <c r="A144" s="14"/>
-      <c r="B144" s="15"/>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="14"/>
-      <c r="B145" s="15"/>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="A146" s="14"/>
-      <c r="B146" s="15"/>
-    </row>
-    <row r="147" spans="1:2" ht="43.5" customHeight="1">
-      <c r="A147" s="14"/>
-      <c r="B147" s="15"/>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" s="14"/>
-      <c r="B148" s="15"/>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" s="14"/>
-      <c r="B149" s="15"/>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" s="14"/>
-      <c r="B150" s="15"/>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="A151" s="14"/>
-      <c r="B151" s="15"/>
-    </row>
-    <row r="152" spans="1:2">
+      <c r="A128" s="8">
+        <v>120</v>
+      </c>
+      <c r="B128" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C128" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D128" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E128" s="8">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="43.5" customHeight="1">
+      <c r="A129" s="10">
+        <v>120</v>
+      </c>
+      <c r="B129" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="C129" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D129" s="11"/>
+      <c r="E129" s="10">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="8">
+        <v>129</v>
+      </c>
+      <c r="B130" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C130" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D130" s="9"/>
+      <c r="E130" s="8">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="10">
+        <v>129</v>
+      </c>
+      <c r="B131" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="C131" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D131" s="11"/>
+      <c r="E131" s="10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" s="8">
+        <v>129</v>
+      </c>
+      <c r="B132" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C132" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D132" s="9"/>
+      <c r="E132" s="8">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" s="10">
+        <v>129</v>
+      </c>
+      <c r="B133" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="C133" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D133" s="11"/>
+      <c r="E133" s="10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="8">
+        <v>129</v>
+      </c>
+      <c r="B134" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="C134" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D134" s="9"/>
+      <c r="E134" s="8">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="43.5" customHeight="1">
+      <c r="A135" s="10">
+        <v>129</v>
+      </c>
+      <c r="B135" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C135" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D135" s="11"/>
+      <c r="E135" s="10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" s="8">
+        <v>129</v>
+      </c>
+      <c r="B136" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="C136" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D136" s="9"/>
+      <c r="E136" s="8">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="10">
+        <v>129</v>
+      </c>
+      <c r="B137" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="C137" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D137" s="11"/>
+      <c r="E137" s="10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="8">
+        <v>129</v>
+      </c>
+      <c r="B138" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="C138" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D138" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E138" s="8">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="29" customHeight="1">
+      <c r="A139" s="10">
+        <v>129</v>
+      </c>
+      <c r="B139" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="C139" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D139" s="11"/>
+      <c r="E139" s="10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="8">
+        <v>139</v>
+      </c>
+      <c r="B140" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="C140" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D140" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E140" s="8">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="10">
+        <v>139</v>
+      </c>
+      <c r="B141" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="C141" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D141" s="11"/>
+      <c r="E141" s="10">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="8">
+        <v>139</v>
+      </c>
+      <c r="B142" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C142" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D142" s="9"/>
+      <c r="E142" s="8">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="58" customHeight="1">
+      <c r="A143" s="10">
+        <v>139</v>
+      </c>
+      <c r="B143" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="C143" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="D143" s="11"/>
+      <c r="E143" s="10">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="29" customHeight="1">
+      <c r="A144" s="8">
+        <v>139</v>
+      </c>
+      <c r="B144" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="C144" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="D144" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E144" s="8">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="10">
+        <v>139</v>
+      </c>
+      <c r="B145" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="C145" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D145" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E145" s="10">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="8">
+        <v>139</v>
+      </c>
+      <c r="B146" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C146" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="D146" s="9"/>
+      <c r="E146" s="8">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="43.5" customHeight="1">
+      <c r="A147" s="10">
+        <v>139</v>
+      </c>
+      <c r="B147" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="C147" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D147" s="11"/>
+      <c r="E147" s="10">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="8">
+        <v>139</v>
+      </c>
+      <c r="B148" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="C148" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D148" s="9"/>
+      <c r="E148" s="8">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="10">
+        <v>139</v>
+      </c>
+      <c r="B149" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="C149" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D149" s="11"/>
+      <c r="E149" s="10">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="8">
+        <v>139</v>
+      </c>
+      <c r="B150" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="C150" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="D150" s="9"/>
+      <c r="E150" s="8">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="10">
+        <v>139</v>
+      </c>
+      <c r="B151" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="C151" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D151" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E151" s="10">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
       <c r="A152" s="14"/>
       <c r="B152" s="15"/>
     </row>
-    <row r="153" spans="1:2" ht="29" customHeight="1">
+    <row r="153" spans="1:5" ht="29" customHeight="1">
       <c r="A153" s="14"/>
       <c r="B153" s="15"/>
     </row>
-    <row r="154" spans="1:2">
+    <row r="154" spans="1:5">
       <c r="A154" s="14"/>
       <c r="B154" s="15"/>
     </row>
-    <row r="155" spans="1:2">
+    <row r="155" spans="1:5">
       <c r="A155" s="14"/>
       <c r="B155" s="15"/>
     </row>
-    <row r="156" spans="1:2">
+    <row r="156" spans="1:5">
       <c r="A156" s="14"/>
       <c r="B156" s="15"/>
     </row>
-    <row r="157" spans="1:2" ht="29" customHeight="1">
+    <row r="157" spans="1:5" ht="29" customHeight="1">
       <c r="A157" s="14"/>
       <c r="B157" s="15"/>
     </row>
-    <row r="158" spans="1:2">
+    <row r="158" spans="1:5">
       <c r="A158" s="14"/>
       <c r="B158" s="15"/>
     </row>
-    <row r="159" spans="1:2">
+    <row r="159" spans="1:5">
       <c r="A159" s="14"/>
       <c r="B159" s="15"/>
     </row>
-    <row r="160" spans="1:2">
+    <row r="160" spans="1:5">
       <c r="A160" s="14"/>
       <c r="B160" s="15"/>
     </row>
@@ -7985,6 +8343,36 @@
     <hyperlink ref="B119" r:id="rId114" display="https://www.premierleague.com/en/players/1921/matthew-le-tissier/overview" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
     <hyperlink ref="B120" r:id="rId115" display="https://www.premierleague.com/en/players/1860/nolberto-solano/overview" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
     <hyperlink ref="B121" r:id="rId116" display="https://www.premierleague.com/en/players/1860/nolberto-solano/overview" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="B151" r:id="rId117" display="https://www.premierleague.com/en/players/60689/chris-wood/overview" xr:uid="{00000000-0004-0000-0100-0000B7000000}"/>
+    <hyperlink ref="B150" r:id="rId118" display="https://www.premierleague.com/en/players/60689/chris-wood/overview" xr:uid="{00000000-0004-0000-0100-0000B6000000}"/>
+    <hyperlink ref="B149" r:id="rId119" display="https://www.premierleague.com/en/players/60689/chris-wood/overview" xr:uid="{00000000-0004-0000-0100-0000B5000000}"/>
+    <hyperlink ref="B148" r:id="rId120" display="https://www.premierleague.com/en/players/60689/chris-wood/overview" xr:uid="{00000000-0004-0000-0100-0000B4000000}"/>
+    <hyperlink ref="B147" r:id="rId121" display="https://www.premierleague.com/en/players/60689/chris-wood/overview" xr:uid="{00000000-0004-0000-0100-0000B3000000}"/>
+    <hyperlink ref="B146" r:id="rId122" display="https://www.premierleague.com/en/players/60689/chris-wood/overview" xr:uid="{00000000-0004-0000-0100-0000B2000000}"/>
+    <hyperlink ref="B145" r:id="rId123" display="https://www.premierleague.com/en/players/1972/kevin-phillips/overview" xr:uid="{00000000-0004-0000-0100-0000B1000000}"/>
+    <hyperlink ref="B144" r:id="rId124" display="https://www.premierleague.com/en/players/1972/kevin-phillips/overview" xr:uid="{00000000-0004-0000-0100-0000B0000000}"/>
+    <hyperlink ref="B143" r:id="rId125" display="https://www.premierleague.com/en/players/1972/kevin-phillips/overview" xr:uid="{00000000-0004-0000-0100-0000AF000000}"/>
+    <hyperlink ref="B142" r:id="rId126" display="https://www.premierleague.com/en/players/1972/kevin-phillips/overview" xr:uid="{00000000-0004-0000-0100-0000AE000000}"/>
+    <hyperlink ref="B141" r:id="rId127" display="https://www.premierleague.com/en/players/2183/mark-viduka/overview" xr:uid="{00000000-0004-0000-0100-0000AD000000}"/>
+    <hyperlink ref="B140" r:id="rId128" display="https://www.premierleague.com/en/players/2183/mark-viduka/overview" xr:uid="{00000000-0004-0000-0100-0000AC000000}"/>
+    <hyperlink ref="B139" r:id="rId129" display="https://www.premierleague.com/en/players/2183/mark-viduka/overview" xr:uid="{00000000-0004-0000-0100-0000AB000000}"/>
+    <hyperlink ref="B138" r:id="rId130" display="https://www.premierleague.com/en/players/2183/mark-viduka/overview" xr:uid="{00000000-0004-0000-0100-0000AA000000}"/>
+    <hyperlink ref="B137" r:id="rId131" display="https://www.premierleague.com/en/players/75115/callum-wilson/overview" xr:uid="{00000000-0004-0000-0100-0000A9000000}"/>
+    <hyperlink ref="B136" r:id="rId132" display="https://www.premierleague.com/en/players/75115/callum-wilson/overview" xr:uid="{00000000-0004-0000-0100-0000A8000000}"/>
+    <hyperlink ref="B135" r:id="rId133" display="https://www.premierleague.com/en/players/75115/callum-wilson/overview" xr:uid="{00000000-0004-0000-0100-0000A7000000}"/>
+    <hyperlink ref="B134" r:id="rId134" display="https://www.premierleague.com/en/players/75115/callum-wilson/overview" xr:uid="{00000000-0004-0000-0100-0000A6000000}"/>
+    <hyperlink ref="B133" r:id="rId135" display="https://www.premierleague.com/en/players/75115/callum-wilson/overview" xr:uid="{00000000-0004-0000-0100-0000A5000000}"/>
+    <hyperlink ref="B132" r:id="rId136" display="https://www.premierleague.com/en/players/75115/callum-wilson/overview" xr:uid="{00000000-0004-0000-0100-0000A4000000}"/>
+    <hyperlink ref="B131" r:id="rId137" display="https://www.premierleague.com/en/players/8595/dimitar-berbatov/overview" xr:uid="{00000000-0004-0000-0100-0000A3000000}"/>
+    <hyperlink ref="B130" r:id="rId138" display="https://www.premierleague.com/en/players/8595/dimitar-berbatov/overview" xr:uid="{00000000-0004-0000-0100-0000A2000000}"/>
+    <hyperlink ref="B129" r:id="rId139" display="https://www.premierleague.com/en/players/8595/dimitar-berbatov/overview" xr:uid="{00000000-0004-0000-0100-0000A1000000}"/>
+    <hyperlink ref="B128" r:id="rId140" display="https://www.premierleague.com/en/players/8595/dimitar-berbatov/overview" xr:uid="{00000000-0004-0000-0100-0000A0000000}"/>
+    <hyperlink ref="B127" r:id="rId141" display="https://www.premierleague.com/en/players/13239/yakubu/overview" xr:uid="{00000000-0004-0000-0100-00009F000000}"/>
+    <hyperlink ref="B126" r:id="rId142" display="https://www.premierleague.com/en/players/13239/yakubu/overview" xr:uid="{00000000-0004-0000-0100-00009E000000}"/>
+    <hyperlink ref="B125" r:id="rId143" display="https://www.premierleague.com/en/players/13239/yakubu/overview" xr:uid="{00000000-0004-0000-0100-00009D000000}"/>
+    <hyperlink ref="B124" r:id="rId144" display="https://www.premierleague.com/en/players/13239/yakubu/overview" xr:uid="{00000000-0004-0000-0100-00009C000000}"/>
+    <hyperlink ref="B123" r:id="rId145" display="https://www.premierleague.com/en/players/4857/ruud-van-nistelrooy/overview" xr:uid="{00000000-0004-0000-0100-00009B000000}"/>
+    <hyperlink ref="B122" r:id="rId146" display="https://www.premierleague.com/en/players/4857/ruud-van-nistelrooy/overview" xr:uid="{00000000-0004-0000-0100-00009A000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8007,13 +8395,13 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:E858"/>
+  <dimension ref="A1:E863"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="4" max="4" width="10.453125" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8093,7 +8481,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="10">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
@@ -10494,7 +10882,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="13" t="s">
-        <v>265</v>
+        <v>1203</v>
       </c>
       <c r="C161" s="11" t="s">
         <v>13</v>
@@ -10504,493 +10892,92 @@
         <v>45</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="18" customHeight="1">
-      <c r="A162" s="8">
-        <v>120</v>
-      </c>
-      <c r="B162" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="C162" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D162" s="9"/>
-      <c r="E162" s="8">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" ht="18" customHeight="1">
+    <row r="162" spans="1:5" s="28" customFormat="1" ht="18" customHeight="1">
+      <c r="A162" s="10">
+        <v>160</v>
+      </c>
+      <c r="B162" s="13" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C162" s="11"/>
+      <c r="D162" s="11"/>
+      <c r="E162" s="10">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" s="28" customFormat="1" ht="18" customHeight="1">
       <c r="A163" s="10">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="B163" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="C163" s="11" t="s">
-        <v>39</v>
-      </c>
+        <v>1205</v>
+      </c>
+      <c r="C163" s="11"/>
       <c r="D163" s="11"/>
       <c r="E163" s="10">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" ht="18" customHeight="1">
-      <c r="A164" s="8">
-        <v>120</v>
-      </c>
-      <c r="B164" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="C164" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D164" s="9"/>
-      <c r="E164" s="8">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" ht="18" customHeight="1">
-      <c r="A165" s="10">
-        <v>120</v>
-      </c>
-      <c r="B165" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="C165" s="11" t="s">
-        <v>11</v>
-      </c>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" s="28" customFormat="1" ht="18" customHeight="1">
+      <c r="A164" s="10"/>
+      <c r="B164" s="13" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C164" s="11"/>
+      <c r="D164" s="11"/>
+      <c r="E164" s="10">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" s="28" customFormat="1" ht="18" customHeight="1">
+      <c r="A165" s="10"/>
+      <c r="B165" s="13"/>
+      <c r="C165" s="11"/>
       <c r="D165" s="11"/>
-      <c r="E165" s="10">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" ht="18" customHeight="1">
-      <c r="A166" s="8">
-        <v>120</v>
-      </c>
-      <c r="B166" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="C166" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D166" s="9"/>
-      <c r="E166" s="8">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" ht="18" customHeight="1">
-      <c r="A167" s="10">
-        <v>120</v>
-      </c>
-      <c r="B167" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="C167" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D167" s="11"/>
-      <c r="E167" s="10">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" ht="18" customHeight="1">
-      <c r="A168" s="8">
-        <v>120</v>
-      </c>
-      <c r="B168" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="C168" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D168" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="E168" s="8">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" ht="18" customHeight="1">
-      <c r="A169" s="10">
-        <v>120</v>
-      </c>
-      <c r="B169" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="C169" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D169" s="11"/>
-      <c r="E169" s="10">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" ht="18" customHeight="1">
-      <c r="A170" s="8">
-        <v>129</v>
-      </c>
-      <c r="B170" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="C170" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D170" s="9"/>
-      <c r="E170" s="8">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" ht="18" customHeight="1">
-      <c r="A171" s="10">
-        <v>129</v>
-      </c>
-      <c r="B171" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="C171" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D171" s="11"/>
-      <c r="E171" s="10">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" ht="18" customHeight="1">
-      <c r="A172" s="8">
-        <v>129</v>
-      </c>
-      <c r="B172" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="C172" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D172" s="9"/>
-      <c r="E172" s="8">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" ht="18" customHeight="1">
-      <c r="A173" s="10">
-        <v>129</v>
-      </c>
-      <c r="B173" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="C173" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D173" s="11"/>
-      <c r="E173" s="10">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" ht="18" customHeight="1">
-      <c r="A174" s="8">
-        <v>129</v>
-      </c>
-      <c r="B174" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="C174" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D174" s="9"/>
-      <c r="E174" s="8">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" ht="18" customHeight="1">
-      <c r="A175" s="10">
-        <v>129</v>
-      </c>
-      <c r="B175" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="C175" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D175" s="11"/>
-      <c r="E175" s="10">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" ht="18" customHeight="1">
-      <c r="A176" s="8">
-        <v>129</v>
-      </c>
-      <c r="B176" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="C176" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D176" s="9"/>
-      <c r="E176" s="8">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" ht="18" customHeight="1">
-      <c r="A177" s="10">
-        <v>129</v>
-      </c>
-      <c r="B177" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="C177" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D177" s="11"/>
-      <c r="E177" s="10">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" ht="18" customHeight="1">
-      <c r="A178" s="8">
-        <v>129</v>
-      </c>
-      <c r="B178" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="C178" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D178" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E178" s="8">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" ht="18" customHeight="1">
-      <c r="A179" s="10">
-        <v>129</v>
-      </c>
-      <c r="B179" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="C179" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D179" s="11"/>
-      <c r="E179" s="10">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" ht="18" customHeight="1">
-      <c r="A180" s="8">
-        <v>139</v>
-      </c>
-      <c r="B180" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="C180" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D180" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="E180" s="8">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" ht="18" customHeight="1">
-      <c r="A181" s="10">
-        <v>139</v>
-      </c>
-      <c r="B181" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="C181" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D181" s="11"/>
-      <c r="E181" s="10">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" ht="18" customHeight="1">
-      <c r="A182" s="8">
-        <v>139</v>
-      </c>
-      <c r="B182" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="C182" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D182" s="9"/>
-      <c r="E182" s="8">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" ht="18" customHeight="1">
-      <c r="A183" s="10">
-        <v>139</v>
-      </c>
-      <c r="B183" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="C183" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="D183" s="11"/>
-      <c r="E183" s="10">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" ht="18" customHeight="1">
-      <c r="A184" s="8">
-        <v>139</v>
-      </c>
-      <c r="B184" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="C184" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="D184" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="E184" s="8">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" ht="18" customHeight="1">
-      <c r="A185" s="10">
-        <v>139</v>
-      </c>
-      <c r="B185" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="C185" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D185" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E185" s="10">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" ht="18" customHeight="1">
-      <c r="A186" s="8">
-        <v>139</v>
-      </c>
-      <c r="B186" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="C186" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="D186" s="9"/>
-      <c r="E186" s="8">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" ht="18" customHeight="1">
-      <c r="A187" s="10">
-        <v>139</v>
-      </c>
-      <c r="B187" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="C187" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D187" s="11"/>
-      <c r="E187" s="10">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" ht="18" customHeight="1">
-      <c r="A188" s="8">
-        <v>139</v>
-      </c>
-      <c r="B188" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="C188" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D188" s="9"/>
-      <c r="E188" s="8">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" ht="18" customHeight="1">
-      <c r="A189" s="10">
-        <v>139</v>
-      </c>
-      <c r="B189" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="C189" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D189" s="11"/>
-      <c r="E189" s="10">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" ht="18" customHeight="1">
-      <c r="A190" s="8">
-        <v>139</v>
-      </c>
-      <c r="B190" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="C190" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="D190" s="9"/>
-      <c r="E190" s="8">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" ht="18" customHeight="1">
-      <c r="A191" s="10">
-        <v>139</v>
-      </c>
-      <c r="B191" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="C191" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D191" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="E191" s="10">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5">
-      <c r="A192" s="14"/>
-      <c r="B192" s="15"/>
-    </row>
-    <row r="193" spans="1:2" ht="29" customHeight="1">
-      <c r="A193" s="14"/>
-      <c r="B193" s="15"/>
-    </row>
-    <row r="194" spans="1:2">
-      <c r="A194" s="14"/>
-      <c r="B194" s="15"/>
-    </row>
-    <row r="195" spans="1:2">
-      <c r="A195" s="14"/>
-      <c r="B195" s="15"/>
-    </row>
-    <row r="196" spans="1:2">
-      <c r="A196" s="14"/>
-      <c r="B196" s="15"/>
-    </row>
-    <row r="197" spans="1:2" ht="43.5" customHeight="1">
+      <c r="E165" s="10"/>
+    </row>
+    <row r="166" spans="1:5" s="28" customFormat="1" ht="18" customHeight="1">
+      <c r="A166" s="10"/>
+      <c r="B166" s="13"/>
+      <c r="C166" s="11"/>
+      <c r="D166" s="11"/>
+      <c r="E166" s="10"/>
+    </row>
+    <row r="167" spans="1:5" ht="18" customHeight="1"/>
+    <row r="168" spans="1:5" ht="18" customHeight="1"/>
+    <row r="169" spans="1:5" ht="18" customHeight="1"/>
+    <row r="170" spans="1:5" ht="18" customHeight="1"/>
+    <row r="171" spans="1:5" ht="18" customHeight="1"/>
+    <row r="172" spans="1:5" ht="18" customHeight="1"/>
+    <row r="173" spans="1:5" ht="18" customHeight="1"/>
+    <row r="174" spans="1:5" ht="18" customHeight="1"/>
+    <row r="175" spans="1:5" ht="18" customHeight="1"/>
+    <row r="176" spans="1:5" ht="18" customHeight="1"/>
+    <row r="177" ht="18" customHeight="1"/>
+    <row r="178" ht="18" customHeight="1"/>
+    <row r="179" ht="18" customHeight="1"/>
+    <row r="180" ht="18" customHeight="1"/>
+    <row r="181" ht="18" customHeight="1"/>
+    <row r="182" ht="18" customHeight="1"/>
+    <row r="183" ht="18" customHeight="1"/>
+    <row r="184" ht="18" customHeight="1"/>
+    <row r="185" ht="18" customHeight="1"/>
+    <row r="186" ht="18" customHeight="1"/>
+    <row r="187" ht="18" customHeight="1"/>
+    <row r="188" ht="18" customHeight="1"/>
+    <row r="189" ht="18" customHeight="1"/>
+    <row r="190" ht="18" customHeight="1"/>
+    <row r="191" ht="18" customHeight="1"/>
+    <row r="192" ht="18" customHeight="1"/>
+    <row r="193" spans="1:2" ht="18" customHeight="1"/>
+    <row r="194" spans="1:2" ht="18" customHeight="1"/>
+    <row r="195" spans="1:2" ht="18" customHeight="1"/>
+    <row r="196" spans="1:2" ht="18" customHeight="1"/>
+    <row r="197" spans="1:2">
       <c r="A197" s="14"/>
       <c r="B197" s="15"/>
     </row>
-    <row r="198" spans="1:2">
+    <row r="198" spans="1:2" ht="29" customHeight="1">
       <c r="A198" s="14"/>
       <c r="B198" s="15"/>
     </row>
@@ -11002,11 +10989,11 @@
       <c r="A200" s="14"/>
       <c r="B200" s="15"/>
     </row>
-    <row r="201" spans="1:2" ht="29" customHeight="1">
+    <row r="201" spans="1:2">
       <c r="A201" s="14"/>
       <c r="B201" s="15"/>
     </row>
-    <row r="202" spans="1:2">
+    <row r="202" spans="1:2" ht="43.5" customHeight="1">
       <c r="A202" s="14"/>
       <c r="B202" s="15"/>
     </row>
@@ -11018,15 +11005,15 @@
       <c r="A204" s="14"/>
       <c r="B204" s="15"/>
     </row>
-    <row r="205" spans="1:2" ht="29" customHeight="1">
+    <row r="205" spans="1:2">
       <c r="A205" s="14"/>
       <c r="B205" s="15"/>
     </row>
-    <row r="206" spans="1:2">
+    <row r="206" spans="1:2" ht="29" customHeight="1">
       <c r="A206" s="14"/>
       <c r="B206" s="15"/>
     </row>
-    <row r="207" spans="1:2" ht="43.5" customHeight="1">
+    <row r="207" spans="1:2">
       <c r="A207" s="14"/>
       <c r="B207" s="15"/>
     </row>
@@ -11038,19 +11025,19 @@
       <c r="A209" s="14"/>
       <c r="B209" s="15"/>
     </row>
-    <row r="210" spans="1:2">
+    <row r="210" spans="1:2" ht="29" customHeight="1">
       <c r="A210" s="14"/>
       <c r="B210" s="15"/>
     </row>
-    <row r="211" spans="1:2" ht="29" customHeight="1">
+    <row r="211" spans="1:2">
       <c r="A211" s="14"/>
       <c r="B211" s="15"/>
     </row>
-    <row r="212" spans="1:2">
+    <row r="212" spans="1:2" ht="43.5" customHeight="1">
       <c r="A212" s="14"/>
       <c r="B212" s="15"/>
     </row>
-    <row r="213" spans="1:2" ht="43.5" customHeight="1">
+    <row r="213" spans="1:2">
       <c r="A213" s="14"/>
       <c r="B213" s="15"/>
     </row>
@@ -11062,15 +11049,15 @@
       <c r="A215" s="14"/>
       <c r="B215" s="15"/>
     </row>
-    <row r="216" spans="1:2">
+    <row r="216" spans="1:2" ht="29" customHeight="1">
       <c r="A216" s="14"/>
       <c r="B216" s="15"/>
     </row>
-    <row r="217" spans="1:2" ht="29" customHeight="1">
+    <row r="217" spans="1:2">
       <c r="A217" s="14"/>
       <c r="B217" s="15"/>
     </row>
-    <row r="218" spans="1:2">
+    <row r="218" spans="1:2" ht="43.5" customHeight="1">
       <c r="A218" s="14"/>
       <c r="B218" s="15"/>
     </row>
@@ -11082,7 +11069,7 @@
       <c r="A220" s="14"/>
       <c r="B220" s="15"/>
     </row>
-    <row r="221" spans="1:2" ht="43.5" customHeight="1">
+    <row r="221" spans="1:2">
       <c r="A221" s="14"/>
       <c r="B221" s="15"/>
     </row>
@@ -11098,15 +11085,15 @@
       <c r="A224" s="14"/>
       <c r="B224" s="15"/>
     </row>
-    <row r="225" spans="1:2" ht="29" customHeight="1">
+    <row r="225" spans="1:2">
       <c r="A225" s="14"/>
       <c r="B225" s="15"/>
     </row>
-    <row r="226" spans="1:2">
+    <row r="226" spans="1:2" ht="43.5" customHeight="1">
       <c r="A226" s="14"/>
       <c r="B226" s="15"/>
     </row>
-    <row r="227" spans="1:2">
+    <row r="227" spans="1:2" ht="29" customHeight="1">
       <c r="A227" s="14"/>
       <c r="B227" s="15"/>
     </row>
@@ -11114,11 +11101,11 @@
       <c r="A228" s="14"/>
       <c r="B228" s="15"/>
     </row>
-    <row r="229" spans="1:2" ht="29" customHeight="1">
+    <row r="229" spans="1:2">
       <c r="A229" s="14"/>
       <c r="B229" s="15"/>
     </row>
-    <row r="230" spans="1:2">
+    <row r="230" spans="1:2" ht="29" customHeight="1">
       <c r="A230" s="14"/>
       <c r="B230" s="15"/>
     </row>
@@ -11130,11 +11117,11 @@
       <c r="A232" s="14"/>
       <c r="B232" s="15"/>
     </row>
-    <row r="233" spans="1:2" ht="29" customHeight="1">
+    <row r="233" spans="1:2">
       <c r="A233" s="14"/>
       <c r="B233" s="15"/>
     </row>
-    <row r="234" spans="1:2">
+    <row r="234" spans="1:2" ht="29" customHeight="1">
       <c r="A234" s="14"/>
       <c r="B234" s="15"/>
     </row>
@@ -11146,11 +11133,11 @@
       <c r="A236" s="14"/>
       <c r="B236" s="15"/>
     </row>
-    <row r="237" spans="1:2" ht="29" customHeight="1">
+    <row r="237" spans="1:2">
       <c r="A237" s="14"/>
       <c r="B237" s="15"/>
     </row>
-    <row r="238" spans="1:2">
+    <row r="238" spans="1:2" ht="29" customHeight="1">
       <c r="A238" s="14"/>
       <c r="B238" s="15"/>
     </row>
@@ -11162,11 +11149,11 @@
       <c r="A240" s="14"/>
       <c r="B240" s="15"/>
     </row>
-    <row r="241" spans="1:2" ht="29" customHeight="1">
+    <row r="241" spans="1:2">
       <c r="A241" s="14"/>
       <c r="B241" s="15"/>
     </row>
-    <row r="242" spans="1:2">
+    <row r="242" spans="1:2" ht="29" customHeight="1">
       <c r="A242" s="14"/>
       <c r="B242" s="15"/>
     </row>
@@ -11178,15 +11165,15 @@
       <c r="A244" s="14"/>
       <c r="B244" s="15"/>
     </row>
-    <row r="245" spans="1:2" ht="29" customHeight="1">
+    <row r="245" spans="1:2">
       <c r="A245" s="14"/>
       <c r="B245" s="15"/>
     </row>
-    <row r="246" spans="1:2">
+    <row r="246" spans="1:2" ht="29" customHeight="1">
       <c r="A246" s="14"/>
       <c r="B246" s="15"/>
     </row>
-    <row r="247" spans="1:2" ht="29" customHeight="1">
+    <row r="247" spans="1:2">
       <c r="A247" s="14"/>
       <c r="B247" s="15"/>
     </row>
@@ -11198,15 +11185,15 @@
       <c r="A249" s="14"/>
       <c r="B249" s="15"/>
     </row>
-    <row r="250" spans="1:2">
+    <row r="250" spans="1:2" ht="29" customHeight="1">
       <c r="A250" s="14"/>
       <c r="B250" s="15"/>
     </row>
-    <row r="251" spans="1:2" ht="29" customHeight="1">
+    <row r="251" spans="1:2">
       <c r="A251" s="14"/>
       <c r="B251" s="15"/>
     </row>
-    <row r="252" spans="1:2">
+    <row r="252" spans="1:2" ht="29" customHeight="1">
       <c r="A252" s="14"/>
       <c r="B252" s="15"/>
     </row>
@@ -11218,11 +11205,11 @@
       <c r="A254" s="14"/>
       <c r="B254" s="15"/>
     </row>
-    <row r="255" spans="1:2" ht="29" customHeight="1">
+    <row r="255" spans="1:2">
       <c r="A255" s="14"/>
       <c r="B255" s="15"/>
     </row>
-    <row r="256" spans="1:2">
+    <row r="256" spans="1:2" ht="29" customHeight="1">
       <c r="A256" s="14"/>
       <c r="B256" s="15"/>
     </row>
@@ -11234,11 +11221,11 @@
       <c r="A258" s="14"/>
       <c r="B258" s="15"/>
     </row>
-    <row r="259" spans="1:2" ht="29" customHeight="1">
+    <row r="259" spans="1:2">
       <c r="A259" s="14"/>
       <c r="B259" s="15"/>
     </row>
-    <row r="260" spans="1:2">
+    <row r="260" spans="1:2" ht="29" customHeight="1">
       <c r="A260" s="14"/>
       <c r="B260" s="15"/>
     </row>
@@ -11250,11 +11237,11 @@
       <c r="A262" s="14"/>
       <c r="B262" s="15"/>
     </row>
-    <row r="263" spans="1:2" ht="29" customHeight="1">
+    <row r="263" spans="1:2">
       <c r="A263" s="14"/>
       <c r="B263" s="15"/>
     </row>
-    <row r="264" spans="1:2">
+    <row r="264" spans="1:2" ht="29" customHeight="1">
       <c r="A264" s="14"/>
       <c r="B264" s="15"/>
     </row>
@@ -11266,11 +11253,11 @@
       <c r="A266" s="14"/>
       <c r="B266" s="15"/>
     </row>
-    <row r="267" spans="1:2" ht="29" customHeight="1">
+    <row r="267" spans="1:2">
       <c r="A267" s="14"/>
       <c r="B267" s="15"/>
     </row>
-    <row r="268" spans="1:2">
+    <row r="268" spans="1:2" ht="29" customHeight="1">
       <c r="A268" s="14"/>
       <c r="B268" s="15"/>
     </row>
@@ -11282,11 +11269,11 @@
       <c r="A270" s="14"/>
       <c r="B270" s="15"/>
     </row>
-    <row r="271" spans="1:2" ht="29" customHeight="1">
+    <row r="271" spans="1:2">
       <c r="A271" s="14"/>
       <c r="B271" s="15"/>
     </row>
-    <row r="272" spans="1:2">
+    <row r="272" spans="1:2" ht="29" customHeight="1">
       <c r="A272" s="14"/>
       <c r="B272" s="15"/>
     </row>
@@ -11298,11 +11285,11 @@
       <c r="A274" s="14"/>
       <c r="B274" s="15"/>
     </row>
-    <row r="275" spans="1:2" ht="29" customHeight="1">
+    <row r="275" spans="1:2">
       <c r="A275" s="14"/>
       <c r="B275" s="15"/>
     </row>
-    <row r="276" spans="1:2">
+    <row r="276" spans="1:2" ht="29" customHeight="1">
       <c r="A276" s="14"/>
       <c r="B276" s="15"/>
     </row>
@@ -11314,11 +11301,11 @@
       <c r="A278" s="14"/>
       <c r="B278" s="15"/>
     </row>
-    <row r="279" spans="1:2" ht="29" customHeight="1">
+    <row r="279" spans="1:2">
       <c r="A279" s="14"/>
       <c r="B279" s="15"/>
     </row>
-    <row r="280" spans="1:2">
+    <row r="280" spans="1:2" ht="29" customHeight="1">
       <c r="A280" s="14"/>
       <c r="B280" s="15"/>
     </row>
@@ -11334,11 +11321,11 @@
       <c r="A283" s="14"/>
       <c r="B283" s="15"/>
     </row>
-    <row r="284" spans="1:2">
+    <row r="284" spans="1:2" ht="29" customHeight="1">
       <c r="A284" s="14"/>
       <c r="B284" s="15"/>
     </row>
-    <row r="285" spans="1:2" ht="29" customHeight="1">
+    <row r="285" spans="1:2">
       <c r="A285" s="14"/>
       <c r="B285" s="15"/>
     </row>
@@ -11354,11 +11341,11 @@
       <c r="A288" s="14"/>
       <c r="B288" s="15"/>
     </row>
-    <row r="289" spans="1:2" ht="29" customHeight="1">
+    <row r="289" spans="1:2">
       <c r="A289" s="14"/>
       <c r="B289" s="15"/>
     </row>
-    <row r="290" spans="1:2">
+    <row r="290" spans="1:2" ht="29" customHeight="1">
       <c r="A290" s="14"/>
       <c r="B290" s="15"/>
     </row>
@@ -11370,11 +11357,11 @@
       <c r="A292" s="14"/>
       <c r="B292" s="15"/>
     </row>
-    <row r="293" spans="1:2" ht="43.5" customHeight="1">
+    <row r="293" spans="1:2">
       <c r="A293" s="14"/>
       <c r="B293" s="15"/>
     </row>
-    <row r="294" spans="1:2">
+    <row r="294" spans="1:2" ht="29" customHeight="1">
       <c r="A294" s="14"/>
       <c r="B294" s="15"/>
     </row>
@@ -11386,15 +11373,15 @@
       <c r="A296" s="14"/>
       <c r="B296" s="15"/>
     </row>
-    <row r="297" spans="1:2" ht="29" customHeight="1">
+    <row r="297" spans="1:2">
       <c r="A297" s="14"/>
       <c r="B297" s="15"/>
     </row>
-    <row r="298" spans="1:2">
+    <row r="298" spans="1:2" ht="43.5" customHeight="1">
       <c r="A298" s="14"/>
       <c r="B298" s="15"/>
     </row>
-    <row r="299" spans="1:2" ht="43.5" customHeight="1">
+    <row r="299" spans="1:2">
       <c r="A299" s="14"/>
       <c r="B299" s="15"/>
     </row>
@@ -11406,19 +11393,19 @@
       <c r="A301" s="14"/>
       <c r="B301" s="15"/>
     </row>
-    <row r="302" spans="1:2">
+    <row r="302" spans="1:2" ht="29" customHeight="1">
       <c r="A302" s="14"/>
       <c r="B302" s="15"/>
     </row>
-    <row r="303" spans="1:2" ht="29" customHeight="1">
+    <row r="303" spans="1:2">
       <c r="A303" s="14"/>
       <c r="B303" s="15"/>
     </row>
-    <row r="304" spans="1:2">
+    <row r="304" spans="1:2" ht="43.5" customHeight="1">
       <c r="A304" s="14"/>
       <c r="B304" s="15"/>
     </row>
-    <row r="305" spans="1:2" ht="43.5" customHeight="1">
+    <row r="305" spans="1:2">
       <c r="A305" s="14"/>
       <c r="B305" s="15"/>
     </row>
@@ -11430,19 +11417,19 @@
       <c r="A307" s="14"/>
       <c r="B307" s="15"/>
     </row>
-    <row r="308" spans="1:2">
+    <row r="308" spans="1:2" ht="29" customHeight="1">
       <c r="A308" s="14"/>
       <c r="B308" s="15"/>
     </row>
-    <row r="309" spans="1:2" ht="29" customHeight="1">
+    <row r="309" spans="1:2">
       <c r="A309" s="14"/>
       <c r="B309" s="15"/>
     </row>
-    <row r="310" spans="1:2">
+    <row r="310" spans="1:2" ht="43.5" customHeight="1">
       <c r="A310" s="14"/>
       <c r="B310" s="15"/>
     </row>
-    <row r="311" spans="1:2" ht="29" customHeight="1">
+    <row r="311" spans="1:2">
       <c r="A311" s="14"/>
       <c r="B311" s="15"/>
     </row>
@@ -11454,15 +11441,15 @@
       <c r="A313" s="14"/>
       <c r="B313" s="15"/>
     </row>
-    <row r="314" spans="1:2">
+    <row r="314" spans="1:2" ht="29" customHeight="1">
       <c r="A314" s="14"/>
       <c r="B314" s="15"/>
     </row>
-    <row r="315" spans="1:2" ht="43.5" customHeight="1">
+    <row r="315" spans="1:2">
       <c r="A315" s="14"/>
       <c r="B315" s="15"/>
     </row>
-    <row r="316" spans="1:2">
+    <row r="316" spans="1:2" ht="29" customHeight="1">
       <c r="A316" s="14"/>
       <c r="B316" s="15"/>
     </row>
@@ -11474,11 +11461,11 @@
       <c r="A318" s="14"/>
       <c r="B318" s="15"/>
     </row>
-    <row r="319" spans="1:2" ht="29" customHeight="1">
+    <row r="319" spans="1:2">
       <c r="A319" s="14"/>
       <c r="B319" s="15"/>
     </row>
-    <row r="320" spans="1:2">
+    <row r="320" spans="1:2" ht="43.5" customHeight="1">
       <c r="A320" s="14"/>
       <c r="B320" s="15"/>
     </row>
@@ -11490,11 +11477,11 @@
       <c r="A322" s="14"/>
       <c r="B322" s="15"/>
     </row>
-    <row r="323" spans="1:2" ht="29" customHeight="1">
+    <row r="323" spans="1:2">
       <c r="A323" s="14"/>
       <c r="B323" s="15"/>
     </row>
-    <row r="324" spans="1:2">
+    <row r="324" spans="1:2" ht="29" customHeight="1">
       <c r="A324" s="14"/>
       <c r="B324" s="15"/>
     </row>
@@ -11506,15 +11493,15 @@
       <c r="A326" s="14"/>
       <c r="B326" s="15"/>
     </row>
-    <row r="327" spans="1:2" ht="43.5" customHeight="1">
+    <row r="327" spans="1:2">
       <c r="A327" s="14"/>
       <c r="B327" s="15"/>
     </row>
-    <row r="328" spans="1:2">
+    <row r="328" spans="1:2" ht="29" customHeight="1">
       <c r="A328" s="14"/>
       <c r="B328" s="15"/>
     </row>
-    <row r="329" spans="1:2" ht="43.5" customHeight="1">
+    <row r="329" spans="1:2">
       <c r="A329" s="14"/>
       <c r="B329" s="15"/>
     </row>
@@ -11526,15 +11513,15 @@
       <c r="A331" s="14"/>
       <c r="B331" s="15"/>
     </row>
-    <row r="332" spans="1:2">
+    <row r="332" spans="1:2" ht="43.5" customHeight="1">
       <c r="A332" s="14"/>
       <c r="B332" s="15"/>
     </row>
-    <row r="333" spans="1:2" ht="58" customHeight="1">
+    <row r="333" spans="1:2">
       <c r="A333" s="14"/>
       <c r="B333" s="15"/>
     </row>
-    <row r="334" spans="1:2">
+    <row r="334" spans="1:2" ht="43.5" customHeight="1">
       <c r="A334" s="14"/>
       <c r="B334" s="15"/>
     </row>
@@ -11546,11 +11533,11 @@
       <c r="A336" s="14"/>
       <c r="B336" s="15"/>
     </row>
-    <row r="337" spans="1:2" ht="29" customHeight="1">
+    <row r="337" spans="1:2">
       <c r="A337" s="14"/>
       <c r="B337" s="15"/>
     </row>
-    <row r="338" spans="1:2">
+    <row r="338" spans="1:2" ht="58" customHeight="1">
       <c r="A338" s="14"/>
       <c r="B338" s="15"/>
     </row>
@@ -11562,11 +11549,11 @@
       <c r="A340" s="14"/>
       <c r="B340" s="15"/>
     </row>
-    <row r="341" spans="1:2" ht="29" customHeight="1">
+    <row r="341" spans="1:2">
       <c r="A341" s="14"/>
       <c r="B341" s="15"/>
     </row>
-    <row r="342" spans="1:2">
+    <row r="342" spans="1:2" ht="29" customHeight="1">
       <c r="A342" s="14"/>
       <c r="B342" s="15"/>
     </row>
@@ -11578,7 +11565,7 @@
       <c r="A344" s="14"/>
       <c r="B344" s="15"/>
     </row>
-    <row r="345" spans="1:2" ht="29" customHeight="1">
+    <row r="345" spans="1:2">
       <c r="A345" s="14"/>
       <c r="B345" s="15"/>
     </row>
@@ -11594,15 +11581,15 @@
       <c r="A348" s="14"/>
       <c r="B348" s="15"/>
     </row>
-    <row r="349" spans="1:2" ht="29" customHeight="1">
+    <row r="349" spans="1:2">
       <c r="A349" s="14"/>
       <c r="B349" s="15"/>
     </row>
-    <row r="350" spans="1:2">
+    <row r="350" spans="1:2" ht="29" customHeight="1">
       <c r="A350" s="14"/>
       <c r="B350" s="15"/>
     </row>
-    <row r="351" spans="1:2" ht="43.5" customHeight="1">
+    <row r="351" spans="1:2" ht="29" customHeight="1">
       <c r="A351" s="14"/>
       <c r="B351" s="15"/>
     </row>
@@ -11614,19 +11601,19 @@
       <c r="A353" s="14"/>
       <c r="B353" s="15"/>
     </row>
-    <row r="354" spans="1:2">
+    <row r="354" spans="1:2" ht="29" customHeight="1">
       <c r="A354" s="14"/>
       <c r="B354" s="15"/>
     </row>
-    <row r="355" spans="1:2" ht="29" customHeight="1">
+    <row r="355" spans="1:2">
       <c r="A355" s="14"/>
       <c r="B355" s="15"/>
     </row>
-    <row r="356" spans="1:2">
+    <row r="356" spans="1:2" ht="43.5" customHeight="1">
       <c r="A356" s="14"/>
       <c r="B356" s="15"/>
     </row>
-    <row r="357" spans="1:2" ht="29" customHeight="1">
+    <row r="357" spans="1:2">
       <c r="A357" s="14"/>
       <c r="B357" s="15"/>
     </row>
@@ -11638,43 +11625,43 @@
       <c r="A359" s="14"/>
       <c r="B359" s="15"/>
     </row>
-    <row r="360" spans="1:2">
+    <row r="360" spans="1:2" ht="29" customHeight="1">
       <c r="A360" s="14"/>
-      <c r="B360" s="14"/>
+      <c r="B360" s="15"/>
     </row>
     <row r="361" spans="1:2">
       <c r="A361" s="14"/>
-      <c r="B361" s="14"/>
-    </row>
-    <row r="362" spans="1:2">
+      <c r="B361" s="15"/>
+    </row>
+    <row r="362" spans="1:2" ht="29" customHeight="1">
       <c r="A362" s="14"/>
-      <c r="B362" s="14"/>
+      <c r="B362" s="15"/>
     </row>
     <row r="363" spans="1:2">
       <c r="A363" s="14"/>
       <c r="B363" s="15"/>
     </row>
-    <row r="364" spans="1:2" ht="29" customHeight="1">
+    <row r="364" spans="1:2">
       <c r="A364" s="14"/>
       <c r="B364" s="15"/>
     </row>
     <row r="365" spans="1:2">
       <c r="A365" s="14"/>
-      <c r="B365" s="15"/>
+      <c r="B365" s="14"/>
     </row>
     <row r="366" spans="1:2">
       <c r="A366" s="14"/>
-      <c r="B366" s="15"/>
+      <c r="B366" s="14"/>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" s="14"/>
-      <c r="B367" s="15"/>
-    </row>
-    <row r="368" spans="1:2" ht="29" customHeight="1">
+      <c r="B367" s="14"/>
+    </row>
+    <row r="368" spans="1:2">
       <c r="A368" s="14"/>
       <c r="B368" s="15"/>
     </row>
-    <row r="369" spans="1:2">
+    <row r="369" spans="1:2" ht="29" customHeight="1">
       <c r="A369" s="14"/>
       <c r="B369" s="15"/>
     </row>
@@ -11690,11 +11677,11 @@
       <c r="A372" s="14"/>
       <c r="B372" s="15"/>
     </row>
-    <row r="373" spans="1:2">
+    <row r="373" spans="1:2" ht="29" customHeight="1">
       <c r="A373" s="14"/>
       <c r="B373" s="15"/>
     </row>
-    <row r="374" spans="1:2" ht="43.5" customHeight="1">
+    <row r="374" spans="1:2">
       <c r="A374" s="14"/>
       <c r="B374" s="15"/>
     </row>
@@ -11710,15 +11697,15 @@
       <c r="A377" s="14"/>
       <c r="B377" s="15"/>
     </row>
-    <row r="378" spans="1:2" ht="43.5" customHeight="1">
+    <row r="378" spans="1:2">
       <c r="A378" s="14"/>
       <c r="B378" s="15"/>
     </row>
-    <row r="379" spans="1:2">
+    <row r="379" spans="1:2" ht="43.5" customHeight="1">
       <c r="A379" s="14"/>
       <c r="B379" s="15"/>
     </row>
-    <row r="380" spans="1:2" ht="29" customHeight="1">
+    <row r="380" spans="1:2">
       <c r="A380" s="14"/>
       <c r="B380" s="15"/>
     </row>
@@ -11730,15 +11717,15 @@
       <c r="A382" s="14"/>
       <c r="B382" s="15"/>
     </row>
-    <row r="383" spans="1:2">
+    <row r="383" spans="1:2" ht="43.5" customHeight="1">
       <c r="A383" s="14"/>
       <c r="B383" s="15"/>
     </row>
-    <row r="384" spans="1:2" ht="29" customHeight="1">
+    <row r="384" spans="1:2">
       <c r="A384" s="14"/>
       <c r="B384" s="15"/>
     </row>
-    <row r="385" spans="1:2">
+    <row r="385" spans="1:2" ht="29" customHeight="1">
       <c r="A385" s="14"/>
       <c r="B385" s="15"/>
     </row>
@@ -11750,11 +11737,11 @@
       <c r="A387" s="14"/>
       <c r="B387" s="15"/>
     </row>
-    <row r="388" spans="1:2" ht="29" customHeight="1">
+    <row r="388" spans="1:2">
       <c r="A388" s="14"/>
       <c r="B388" s="15"/>
     </row>
-    <row r="389" spans="1:2">
+    <row r="389" spans="1:2" ht="29" customHeight="1">
       <c r="A389" s="14"/>
       <c r="B389" s="15"/>
     </row>
@@ -11766,15 +11753,15 @@
       <c r="A391" s="14"/>
       <c r="B391" s="15"/>
     </row>
-    <row r="392" spans="1:2" ht="29" customHeight="1">
+    <row r="392" spans="1:2">
       <c r="A392" s="14"/>
       <c r="B392" s="15"/>
     </row>
-    <row r="393" spans="1:2">
+    <row r="393" spans="1:2" ht="29" customHeight="1">
       <c r="A393" s="14"/>
       <c r="B393" s="15"/>
     </row>
-    <row r="394" spans="1:2" ht="43.5" customHeight="1">
+    <row r="394" spans="1:2">
       <c r="A394" s="14"/>
       <c r="B394" s="15"/>
     </row>
@@ -11786,15 +11773,15 @@
       <c r="A396" s="14"/>
       <c r="B396" s="15"/>
     </row>
-    <row r="397" spans="1:2">
+    <row r="397" spans="1:2" ht="29" customHeight="1">
       <c r="A397" s="14"/>
       <c r="B397" s="15"/>
     </row>
-    <row r="398" spans="1:2" ht="29" customHeight="1">
+    <row r="398" spans="1:2">
       <c r="A398" s="14"/>
       <c r="B398" s="15"/>
     </row>
-    <row r="399" spans="1:2">
+    <row r="399" spans="1:2" ht="43.5" customHeight="1">
       <c r="A399" s="14"/>
       <c r="B399" s="15"/>
     </row>
@@ -11806,11 +11793,11 @@
       <c r="A401" s="14"/>
       <c r="B401" s="15"/>
     </row>
-    <row r="402" spans="1:2" ht="29" customHeight="1">
+    <row r="402" spans="1:2">
       <c r="A402" s="14"/>
       <c r="B402" s="15"/>
     </row>
-    <row r="403" spans="1:2">
+    <row r="403" spans="1:2" ht="29" customHeight="1">
       <c r="A403" s="14"/>
       <c r="B403" s="15"/>
     </row>
@@ -11826,11 +11813,11 @@
       <c r="A406" s="14"/>
       <c r="B406" s="15"/>
     </row>
-    <row r="407" spans="1:2">
+    <row r="407" spans="1:2" ht="29" customHeight="1">
       <c r="A407" s="14"/>
       <c r="B407" s="15"/>
     </row>
-    <row r="408" spans="1:2" ht="29" customHeight="1">
+    <row r="408" spans="1:2">
       <c r="A408" s="14"/>
       <c r="B408" s="15"/>
     </row>
@@ -11844,41 +11831,41 @@
     </row>
     <row r="411" spans="1:2">
       <c r="A411" s="14"/>
-      <c r="B411" s="14"/>
+      <c r="B411" s="15"/>
     </row>
     <row r="412" spans="1:2">
       <c r="A412" s="14"/>
-      <c r="B412" s="14"/>
-    </row>
-    <row r="413" spans="1:2">
+      <c r="B412" s="15"/>
+    </row>
+    <row r="413" spans="1:2" ht="29" customHeight="1">
       <c r="A413" s="14"/>
-      <c r="B413" s="14"/>
+      <c r="B413" s="15"/>
     </row>
     <row r="414" spans="1:2">
       <c r="A414" s="14"/>
       <c r="B414" s="15"/>
     </row>
-    <row r="415" spans="1:2" ht="43.5" customHeight="1">
+    <row r="415" spans="1:2">
       <c r="A415" s="14"/>
       <c r="B415" s="15"/>
     </row>
     <row r="416" spans="1:2">
       <c r="A416" s="14"/>
-      <c r="B416" s="15"/>
+      <c r="B416" s="14"/>
     </row>
     <row r="417" spans="1:2">
       <c r="A417" s="14"/>
-      <c r="B417" s="15"/>
+      <c r="B417" s="14"/>
     </row>
     <row r="418" spans="1:2">
       <c r="A418" s="14"/>
-      <c r="B418" s="15"/>
-    </row>
-    <row r="419" spans="1:2" ht="29" customHeight="1">
+      <c r="B418" s="14"/>
+    </row>
+    <row r="419" spans="1:2">
       <c r="A419" s="14"/>
       <c r="B419" s="15"/>
     </row>
-    <row r="420" spans="1:2">
+    <row r="420" spans="1:2" ht="43.5" customHeight="1">
       <c r="A420" s="14"/>
       <c r="B420" s="15"/>
     </row>
@@ -11890,11 +11877,11 @@
       <c r="A422" s="14"/>
       <c r="B422" s="15"/>
     </row>
-    <row r="423" spans="1:2" ht="43.5" customHeight="1">
+    <row r="423" spans="1:2">
       <c r="A423" s="14"/>
       <c r="B423" s="15"/>
     </row>
-    <row r="424" spans="1:2">
+    <row r="424" spans="1:2" ht="29" customHeight="1">
       <c r="A424" s="14"/>
       <c r="B424" s="15"/>
     </row>
@@ -11906,11 +11893,11 @@
       <c r="A426" s="14"/>
       <c r="B426" s="15"/>
     </row>
-    <row r="427" spans="1:2" ht="29" customHeight="1">
+    <row r="427" spans="1:2">
       <c r="A427" s="14"/>
       <c r="B427" s="15"/>
     </row>
-    <row r="428" spans="1:2">
+    <row r="428" spans="1:2" ht="43.5" customHeight="1">
       <c r="A428" s="14"/>
       <c r="B428" s="15"/>
     </row>
@@ -11922,7 +11909,7 @@
       <c r="A430" s="14"/>
       <c r="B430" s="15"/>
     </row>
-    <row r="431" spans="1:2" ht="29" customHeight="1">
+    <row r="431" spans="1:2">
       <c r="A431" s="14"/>
       <c r="B431" s="15"/>
     </row>
@@ -11938,15 +11925,15 @@
       <c r="A434" s="14"/>
       <c r="B434" s="15"/>
     </row>
-    <row r="435" spans="1:2" ht="29" customHeight="1">
+    <row r="435" spans="1:2">
       <c r="A435" s="14"/>
       <c r="B435" s="15"/>
     </row>
-    <row r="436" spans="1:2">
+    <row r="436" spans="1:2" ht="29" customHeight="1">
       <c r="A436" s="14"/>
       <c r="B436" s="15"/>
     </row>
-    <row r="437" spans="1:2">
+    <row r="437" spans="1:2" ht="29" customHeight="1">
       <c r="A437" s="14"/>
       <c r="B437" s="15"/>
     </row>
@@ -11954,11 +11941,11 @@
       <c r="A438" s="14"/>
       <c r="B438" s="15"/>
     </row>
-    <row r="439" spans="1:2" ht="29" customHeight="1">
+    <row r="439" spans="1:2">
       <c r="A439" s="14"/>
       <c r="B439" s="15"/>
     </row>
-    <row r="440" spans="1:2">
+    <row r="440" spans="1:2" ht="29" customHeight="1">
       <c r="A440" s="14"/>
       <c r="B440" s="15"/>
     </row>
@@ -11974,11 +11961,11 @@
       <c r="A443" s="14"/>
       <c r="B443" s="15"/>
     </row>
-    <row r="444" spans="1:2">
+    <row r="444" spans="1:2" ht="29" customHeight="1">
       <c r="A444" s="14"/>
       <c r="B444" s="15"/>
     </row>
-    <row r="445" spans="1:2" ht="29" customHeight="1">
+    <row r="445" spans="1:2">
       <c r="A445" s="14"/>
       <c r="B445" s="15"/>
     </row>
@@ -11994,11 +11981,11 @@
       <c r="A448" s="14"/>
       <c r="B448" s="15"/>
     </row>
-    <row r="449" spans="1:2" ht="29" customHeight="1">
+    <row r="449" spans="1:2">
       <c r="A449" s="14"/>
       <c r="B449" s="15"/>
     </row>
-    <row r="450" spans="1:2">
+    <row r="450" spans="1:2" ht="29" customHeight="1">
       <c r="A450" s="14"/>
       <c r="B450" s="15"/>
     </row>
@@ -12010,11 +11997,11 @@
       <c r="A452" s="14"/>
       <c r="B452" s="15"/>
     </row>
-    <row r="453" spans="1:2" ht="29" customHeight="1">
+    <row r="453" spans="1:2">
       <c r="A453" s="14"/>
       <c r="B453" s="15"/>
     </row>
-    <row r="454" spans="1:2">
+    <row r="454" spans="1:2" ht="29" customHeight="1">
       <c r="A454" s="14"/>
       <c r="B454" s="15"/>
     </row>
@@ -12026,7 +12013,7 @@
       <c r="A456" s="14"/>
       <c r="B456" s="15"/>
     </row>
-    <row r="457" spans="1:2" ht="29" customHeight="1">
+    <row r="457" spans="1:2">
       <c r="A457" s="14"/>
       <c r="B457" s="15"/>
     </row>
@@ -12042,15 +12029,15 @@
       <c r="A460" s="14"/>
       <c r="B460" s="15"/>
     </row>
-    <row r="461" spans="1:2" ht="29" customHeight="1">
+    <row r="461" spans="1:2">
       <c r="A461" s="14"/>
       <c r="B461" s="15"/>
     </row>
-    <row r="462" spans="1:2">
+    <row r="462" spans="1:2" ht="29" customHeight="1">
       <c r="A462" s="14"/>
       <c r="B462" s="15"/>
     </row>
-    <row r="463" spans="1:2">
+    <row r="463" spans="1:2" ht="29" customHeight="1">
       <c r="A463" s="14"/>
       <c r="B463" s="15"/>
     </row>
@@ -12058,11 +12045,11 @@
       <c r="A464" s="14"/>
       <c r="B464" s="15"/>
     </row>
-    <row r="465" spans="1:2" ht="29" customHeight="1">
+    <row r="465" spans="1:2">
       <c r="A465" s="14"/>
       <c r="B465" s="15"/>
     </row>
-    <row r="466" spans="1:2">
+    <row r="466" spans="1:2" ht="29" customHeight="1">
       <c r="A466" s="14"/>
       <c r="B466" s="15"/>
     </row>
@@ -12074,11 +12061,11 @@
       <c r="A468" s="14"/>
       <c r="B468" s="15"/>
     </row>
-    <row r="469" spans="1:2" ht="43.5" customHeight="1">
+    <row r="469" spans="1:2">
       <c r="A469" s="14"/>
       <c r="B469" s="15"/>
     </row>
-    <row r="470" spans="1:2">
+    <row r="470" spans="1:2" ht="29" customHeight="1">
       <c r="A470" s="14"/>
       <c r="B470" s="15"/>
     </row>
@@ -12094,7 +12081,7 @@
       <c r="A473" s="14"/>
       <c r="B473" s="15"/>
     </row>
-    <row r="474" spans="1:2">
+    <row r="474" spans="1:2" ht="43.5" customHeight="1">
       <c r="A474" s="14"/>
       <c r="B474" s="15"/>
     </row>
@@ -12114,7 +12101,7 @@
       <c r="A478" s="14"/>
       <c r="B478" s="15"/>
     </row>
-    <row r="479" spans="1:2" ht="29" customHeight="1">
+    <row r="479" spans="1:2">
       <c r="A479" s="14"/>
       <c r="B479" s="15"/>
     </row>
@@ -12130,11 +12117,11 @@
       <c r="A482" s="14"/>
       <c r="B482" s="15"/>
     </row>
-    <row r="483" spans="1:2" ht="29" customHeight="1">
+    <row r="483" spans="1:2">
       <c r="A483" s="14"/>
       <c r="B483" s="15"/>
     </row>
-    <row r="484" spans="1:2">
+    <row r="484" spans="1:2" ht="29" customHeight="1">
       <c r="A484" s="14"/>
       <c r="B484" s="15"/>
     </row>
@@ -12150,11 +12137,11 @@
       <c r="A487" s="14"/>
       <c r="B487" s="15"/>
     </row>
-    <row r="488" spans="1:2">
+    <row r="488" spans="1:2" ht="29" customHeight="1">
       <c r="A488" s="14"/>
       <c r="B488" s="15"/>
     </row>
-    <row r="489" spans="1:2" ht="29" customHeight="1">
+    <row r="489" spans="1:2">
       <c r="A489" s="14"/>
       <c r="B489" s="15"/>
     </row>
@@ -12170,11 +12157,11 @@
       <c r="A492" s="14"/>
       <c r="B492" s="15"/>
     </row>
-    <row r="493" spans="1:2" ht="29" customHeight="1">
+    <row r="493" spans="1:2">
       <c r="A493" s="14"/>
       <c r="B493" s="15"/>
     </row>
-    <row r="494" spans="1:2">
+    <row r="494" spans="1:2" ht="29" customHeight="1">
       <c r="A494" s="14"/>
       <c r="B494" s="15"/>
     </row>
@@ -12186,15 +12173,15 @@
       <c r="A496" s="14"/>
       <c r="B496" s="15"/>
     </row>
-    <row r="497" spans="1:2" ht="29" customHeight="1">
+    <row r="497" spans="1:2">
       <c r="A497" s="14"/>
       <c r="B497" s="15"/>
     </row>
-    <row r="498" spans="1:2">
+    <row r="498" spans="1:2" ht="29" customHeight="1">
       <c r="A498" s="14"/>
       <c r="B498" s="15"/>
     </row>
-    <row r="499" spans="1:2" ht="43.5" customHeight="1">
+    <row r="499" spans="1:2">
       <c r="A499" s="14"/>
       <c r="B499" s="15"/>
     </row>
@@ -12206,19 +12193,19 @@
       <c r="A501" s="14"/>
       <c r="B501" s="15"/>
     </row>
-    <row r="502" spans="1:2">
+    <row r="502" spans="1:2" ht="29" customHeight="1">
       <c r="A502" s="14"/>
       <c r="B502" s="15"/>
     </row>
-    <row r="503" spans="1:2" ht="29" customHeight="1">
+    <row r="503" spans="1:2">
       <c r="A503" s="14"/>
       <c r="B503" s="15"/>
     </row>
-    <row r="504" spans="1:2">
+    <row r="504" spans="1:2" ht="43.5" customHeight="1">
       <c r="A504" s="14"/>
       <c r="B504" s="15"/>
     </row>
-    <row r="505" spans="1:2" ht="43.5" customHeight="1">
+    <row r="505" spans="1:2">
       <c r="A505" s="14"/>
       <c r="B505" s="15"/>
     </row>
@@ -12230,19 +12217,19 @@
       <c r="A507" s="14"/>
       <c r="B507" s="15"/>
     </row>
-    <row r="508" spans="1:2">
+    <row r="508" spans="1:2" ht="29" customHeight="1">
       <c r="A508" s="14"/>
       <c r="B508" s="15"/>
     </row>
-    <row r="509" spans="1:2" ht="29" customHeight="1">
+    <row r="509" spans="1:2">
       <c r="A509" s="14"/>
       <c r="B509" s="15"/>
     </row>
-    <row r="510" spans="1:2">
+    <row r="510" spans="1:2" ht="43.5" customHeight="1">
       <c r="A510" s="14"/>
       <c r="B510" s="15"/>
     </row>
-    <row r="511" spans="1:2" ht="43.5" customHeight="1">
+    <row r="511" spans="1:2">
       <c r="A511" s="14"/>
       <c r="B511" s="15"/>
     </row>
@@ -12254,15 +12241,15 @@
       <c r="A513" s="14"/>
       <c r="B513" s="15"/>
     </row>
-    <row r="514" spans="1:2">
+    <row r="514" spans="1:2" ht="29" customHeight="1">
       <c r="A514" s="14"/>
       <c r="B514" s="15"/>
     </row>
-    <row r="515" spans="1:2" ht="29" customHeight="1">
+    <row r="515" spans="1:2">
       <c r="A515" s="14"/>
       <c r="B515" s="15"/>
     </row>
-    <row r="516" spans="1:2">
+    <row r="516" spans="1:2" ht="43.5" customHeight="1">
       <c r="A516" s="14"/>
       <c r="B516" s="15"/>
     </row>
@@ -12274,11 +12261,11 @@
       <c r="A518" s="14"/>
       <c r="B518" s="15"/>
     </row>
-    <row r="519" spans="1:2" ht="43.5" customHeight="1">
+    <row r="519" spans="1:2">
       <c r="A519" s="14"/>
       <c r="B519" s="15"/>
     </row>
-    <row r="520" spans="1:2">
+    <row r="520" spans="1:2" ht="29" customHeight="1">
       <c r="A520" s="14"/>
       <c r="B520" s="15"/>
     </row>
@@ -12290,11 +12277,11 @@
       <c r="A522" s="14"/>
       <c r="B522" s="15"/>
     </row>
-    <row r="523" spans="1:2" ht="58" customHeight="1">
+    <row r="523" spans="1:2">
       <c r="A523" s="14"/>
       <c r="B523" s="15"/>
     </row>
-    <row r="524" spans="1:2">
+    <row r="524" spans="1:2" ht="43.5" customHeight="1">
       <c r="A524" s="14"/>
       <c r="B524" s="15"/>
     </row>
@@ -12306,11 +12293,11 @@
       <c r="A526" s="14"/>
       <c r="B526" s="15"/>
     </row>
-    <row r="527" spans="1:2" ht="29" customHeight="1">
+    <row r="527" spans="1:2">
       <c r="A527" s="14"/>
       <c r="B527" s="15"/>
     </row>
-    <row r="528" spans="1:2">
+    <row r="528" spans="1:2" ht="58" customHeight="1">
       <c r="A528" s="14"/>
       <c r="B528" s="15"/>
     </row>
@@ -12322,15 +12309,15 @@
       <c r="A530" s="14"/>
       <c r="B530" s="15"/>
     </row>
-    <row r="531" spans="1:2" ht="29" customHeight="1">
+    <row r="531" spans="1:2">
       <c r="A531" s="14"/>
       <c r="B531" s="15"/>
     </row>
-    <row r="532" spans="1:2">
+    <row r="532" spans="1:2" ht="29" customHeight="1">
       <c r="A532" s="14"/>
       <c r="B532" s="15"/>
     </row>
-    <row r="533" spans="1:2" ht="29" customHeight="1">
+    <row r="533" spans="1:2">
       <c r="A533" s="14"/>
       <c r="B533" s="15"/>
     </row>
@@ -12342,15 +12329,15 @@
       <c r="A535" s="14"/>
       <c r="B535" s="15"/>
     </row>
-    <row r="536" spans="1:2">
+    <row r="536" spans="1:2" ht="29" customHeight="1">
       <c r="A536" s="14"/>
       <c r="B536" s="15"/>
     </row>
-    <row r="537" spans="1:2" ht="29" customHeight="1">
+    <row r="537" spans="1:2">
       <c r="A537" s="14"/>
       <c r="B537" s="15"/>
     </row>
-    <row r="538" spans="1:2">
+    <row r="538" spans="1:2" ht="29" customHeight="1">
       <c r="A538" s="14"/>
       <c r="B538" s="15"/>
     </row>
@@ -12366,7 +12353,7 @@
       <c r="A541" s="14"/>
       <c r="B541" s="15"/>
     </row>
-    <row r="542" spans="1:2">
+    <row r="542" spans="1:2" ht="29" customHeight="1">
       <c r="A542" s="14"/>
       <c r="B542" s="15"/>
     </row>
@@ -12378,7 +12365,7 @@
       <c r="A544" s="14"/>
       <c r="B544" s="15"/>
     </row>
-    <row r="545" spans="1:2" ht="29" customHeight="1">
+    <row r="545" spans="1:2">
       <c r="A545" s="14"/>
       <c r="B545" s="15"/>
     </row>
@@ -12394,11 +12381,11 @@
       <c r="A548" s="14"/>
       <c r="B548" s="15"/>
     </row>
-    <row r="549" spans="1:2" ht="29" customHeight="1">
+    <row r="549" spans="1:2">
       <c r="A549" s="14"/>
       <c r="B549" s="15"/>
     </row>
-    <row r="550" spans="1:2">
+    <row r="550" spans="1:2" ht="29" customHeight="1">
       <c r="A550" s="14"/>
       <c r="B550" s="15"/>
     </row>
@@ -12410,11 +12397,11 @@
       <c r="A552" s="14"/>
       <c r="B552" s="15"/>
     </row>
-    <row r="553" spans="1:2" ht="29" customHeight="1">
+    <row r="553" spans="1:2">
       <c r="A553" s="14"/>
       <c r="B553" s="15"/>
     </row>
-    <row r="554" spans="1:2">
+    <row r="554" spans="1:2" ht="29" customHeight="1">
       <c r="A554" s="14"/>
       <c r="B554" s="15"/>
     </row>
@@ -12426,11 +12413,11 @@
       <c r="A556" s="14"/>
       <c r="B556" s="15"/>
     </row>
-    <row r="557" spans="1:2" ht="29" customHeight="1">
+    <row r="557" spans="1:2">
       <c r="A557" s="14"/>
       <c r="B557" s="15"/>
     </row>
-    <row r="558" spans="1:2">
+    <row r="558" spans="1:2" ht="29" customHeight="1">
       <c r="A558" s="14"/>
       <c r="B558" s="15"/>
     </row>
@@ -12442,11 +12429,11 @@
       <c r="A560" s="14"/>
       <c r="B560" s="15"/>
     </row>
-    <row r="561" spans="1:2" ht="29" customHeight="1">
+    <row r="561" spans="1:2">
       <c r="A561" s="14"/>
       <c r="B561" s="15"/>
     </row>
-    <row r="562" spans="1:2">
+    <row r="562" spans="1:2" ht="29" customHeight="1">
       <c r="A562" s="14"/>
       <c r="B562" s="15"/>
     </row>
@@ -12458,11 +12445,11 @@
       <c r="A564" s="14"/>
       <c r="B564" s="15"/>
     </row>
-    <row r="565" spans="1:2" ht="29" customHeight="1">
+    <row r="565" spans="1:2">
       <c r="A565" s="14"/>
       <c r="B565" s="15"/>
     </row>
-    <row r="566" spans="1:2">
+    <row r="566" spans="1:2" ht="29" customHeight="1">
       <c r="A566" s="14"/>
       <c r="B566" s="15"/>
     </row>
@@ -12474,11 +12461,11 @@
       <c r="A568" s="14"/>
       <c r="B568" s="15"/>
     </row>
-    <row r="569" spans="1:2" ht="29" customHeight="1">
+    <row r="569" spans="1:2">
       <c r="A569" s="14"/>
       <c r="B569" s="15"/>
     </row>
-    <row r="570" spans="1:2">
+    <row r="570" spans="1:2" ht="29" customHeight="1">
       <c r="A570" s="14"/>
       <c r="B570" s="15"/>
     </row>
@@ -12490,11 +12477,11 @@
       <c r="A572" s="14"/>
       <c r="B572" s="15"/>
     </row>
-    <row r="573" spans="1:2" ht="29" customHeight="1">
+    <row r="573" spans="1:2">
       <c r="A573" s="14"/>
       <c r="B573" s="15"/>
     </row>
-    <row r="574" spans="1:2">
+    <row r="574" spans="1:2" ht="29" customHeight="1">
       <c r="A574" s="14"/>
       <c r="B574" s="15"/>
     </row>
@@ -12506,11 +12493,11 @@
       <c r="A576" s="14"/>
       <c r="B576" s="15"/>
     </row>
-    <row r="577" spans="1:2" ht="29" customHeight="1">
+    <row r="577" spans="1:2">
       <c r="A577" s="14"/>
       <c r="B577" s="15"/>
     </row>
-    <row r="578" spans="1:2">
+    <row r="578" spans="1:2" ht="29" customHeight="1">
       <c r="A578" s="14"/>
       <c r="B578" s="15"/>
     </row>
@@ -12522,11 +12509,11 @@
       <c r="A580" s="14"/>
       <c r="B580" s="15"/>
     </row>
-    <row r="581" spans="1:2" ht="29" customHeight="1">
+    <row r="581" spans="1:2">
       <c r="A581" s="14"/>
       <c r="B581" s="15"/>
     </row>
-    <row r="582" spans="1:2">
+    <row r="582" spans="1:2" ht="29" customHeight="1">
       <c r="A582" s="14"/>
       <c r="B582" s="15"/>
     </row>
@@ -12538,11 +12525,11 @@
       <c r="A584" s="14"/>
       <c r="B584" s="15"/>
     </row>
-    <row r="585" spans="1:2" ht="29" customHeight="1">
+    <row r="585" spans="1:2">
       <c r="A585" s="14"/>
       <c r="B585" s="15"/>
     </row>
-    <row r="586" spans="1:2">
+    <row r="586" spans="1:2" ht="29" customHeight="1">
       <c r="A586" s="14"/>
       <c r="B586" s="15"/>
     </row>
@@ -12554,11 +12541,11 @@
       <c r="A588" s="14"/>
       <c r="B588" s="15"/>
     </row>
-    <row r="589" spans="1:2" ht="29" customHeight="1">
+    <row r="589" spans="1:2">
       <c r="A589" s="14"/>
       <c r="B589" s="15"/>
     </row>
-    <row r="590" spans="1:2">
+    <row r="590" spans="1:2" ht="29" customHeight="1">
       <c r="A590" s="14"/>
       <c r="B590" s="15"/>
     </row>
@@ -12570,11 +12557,11 @@
       <c r="A592" s="14"/>
       <c r="B592" s="15"/>
     </row>
-    <row r="593" spans="1:2" ht="29" customHeight="1">
+    <row r="593" spans="1:2">
       <c r="A593" s="14"/>
       <c r="B593" s="15"/>
     </row>
-    <row r="594" spans="1:2">
+    <row r="594" spans="1:2" ht="29" customHeight="1">
       <c r="A594" s="14"/>
       <c r="B594" s="15"/>
     </row>
@@ -12602,7 +12589,7 @@
       <c r="A600" s="14"/>
       <c r="B600" s="15"/>
     </row>
-    <row r="601" spans="1:2" ht="29" customHeight="1">
+    <row r="601" spans="1:2">
       <c r="A601" s="14"/>
       <c r="B601" s="15"/>
     </row>
@@ -12610,11 +12597,11 @@
       <c r="A602" s="14"/>
       <c r="B602" s="15"/>
     </row>
-    <row r="603" spans="1:2" ht="43.5" customHeight="1">
+    <row r="603" spans="1:2" ht="29" customHeight="1">
       <c r="A603" s="14"/>
       <c r="B603" s="15"/>
     </row>
-    <row r="604" spans="1:2" ht="29" customHeight="1">
+    <row r="604" spans="1:2">
       <c r="A604" s="14"/>
       <c r="B604" s="15"/>
     </row>
@@ -12622,19 +12609,19 @@
       <c r="A605" s="14"/>
       <c r="B605" s="15"/>
     </row>
-    <row r="606" spans="1:2">
+    <row r="606" spans="1:2" ht="29" customHeight="1">
       <c r="A606" s="14"/>
       <c r="B606" s="15"/>
     </row>
-    <row r="607" spans="1:2" ht="29" customHeight="1">
+    <row r="607" spans="1:2">
       <c r="A607" s="14"/>
       <c r="B607" s="15"/>
     </row>
-    <row r="608" spans="1:2">
+    <row r="608" spans="1:2" ht="43.5" customHeight="1">
       <c r="A608" s="14"/>
       <c r="B608" s="15"/>
     </row>
-    <row r="609" spans="1:2">
+    <row r="609" spans="1:2" ht="29" customHeight="1">
       <c r="A609" s="14"/>
       <c r="B609" s="15"/>
     </row>
@@ -12642,11 +12629,11 @@
       <c r="A610" s="14"/>
       <c r="B610" s="15"/>
     </row>
-    <row r="611" spans="1:2" ht="29" customHeight="1">
+    <row r="611" spans="1:2">
       <c r="A611" s="14"/>
       <c r="B611" s="15"/>
     </row>
-    <row r="612" spans="1:2">
+    <row r="612" spans="1:2" ht="29" customHeight="1">
       <c r="A612" s="14"/>
       <c r="B612" s="15"/>
     </row>
@@ -12662,7 +12649,7 @@
       <c r="A615" s="14"/>
       <c r="B615" s="15"/>
     </row>
-    <row r="616" spans="1:2">
+    <row r="616" spans="1:2" ht="29" customHeight="1">
       <c r="A616" s="14"/>
       <c r="B616" s="15"/>
     </row>
@@ -12682,7 +12669,7 @@
       <c r="A620" s="14"/>
       <c r="B620" s="15"/>
     </row>
-    <row r="621" spans="1:2" ht="29" customHeight="1">
+    <row r="621" spans="1:2">
       <c r="A621" s="14"/>
       <c r="B621" s="15"/>
     </row>
@@ -12698,11 +12685,11 @@
       <c r="A624" s="14"/>
       <c r="B624" s="15"/>
     </row>
-    <row r="625" spans="1:2" ht="29" customHeight="1">
+    <row r="625" spans="1:2">
       <c r="A625" s="14"/>
       <c r="B625" s="15"/>
     </row>
-    <row r="626" spans="1:2" ht="43.5" customHeight="1">
+    <row r="626" spans="1:2" ht="29" customHeight="1">
       <c r="A626" s="14"/>
       <c r="B626" s="15"/>
     </row>
@@ -12714,7 +12701,7 @@
       <c r="A628" s="14"/>
       <c r="B628" s="15"/>
     </row>
-    <row r="629" spans="1:2" ht="43.5" customHeight="1">
+    <row r="629" spans="1:2">
       <c r="A629" s="14"/>
       <c r="B629" s="15"/>
     </row>
@@ -12722,7 +12709,7 @@
       <c r="A630" s="14"/>
       <c r="B630" s="15"/>
     </row>
-    <row r="631" spans="1:2">
+    <row r="631" spans="1:2" ht="43.5" customHeight="1">
       <c r="A631" s="14"/>
       <c r="B631" s="15"/>
     </row>
@@ -12730,15 +12717,15 @@
       <c r="A632" s="14"/>
       <c r="B632" s="15"/>
     </row>
-    <row r="633" spans="1:2" ht="29" customHeight="1">
+    <row r="633" spans="1:2">
       <c r="A633" s="14"/>
       <c r="B633" s="15"/>
     </row>
-    <row r="634" spans="1:2">
+    <row r="634" spans="1:2" ht="43.5" customHeight="1">
       <c r="A634" s="14"/>
       <c r="B634" s="15"/>
     </row>
-    <row r="635" spans="1:2">
+    <row r="635" spans="1:2" ht="29" customHeight="1">
       <c r="A635" s="14"/>
       <c r="B635" s="15"/>
     </row>
@@ -12750,11 +12737,11 @@
       <c r="A637" s="14"/>
       <c r="B637" s="15"/>
     </row>
-    <row r="638" spans="1:2">
+    <row r="638" spans="1:2" ht="29" customHeight="1">
       <c r="A638" s="14"/>
       <c r="B638" s="15"/>
     </row>
-    <row r="639" spans="1:2" ht="29" customHeight="1">
+    <row r="639" spans="1:2">
       <c r="A639" s="14"/>
       <c r="B639" s="15"/>
     </row>
@@ -12770,11 +12757,11 @@
       <c r="A642" s="14"/>
       <c r="B642" s="15"/>
     </row>
-    <row r="643" spans="1:2" ht="29" customHeight="1">
+    <row r="643" spans="1:2">
       <c r="A643" s="14"/>
       <c r="B643" s="15"/>
     </row>
-    <row r="644" spans="1:2">
+    <row r="644" spans="1:2" ht="29" customHeight="1">
       <c r="A644" s="14"/>
       <c r="B644" s="15"/>
     </row>
@@ -12786,11 +12773,11 @@
       <c r="A646" s="14"/>
       <c r="B646" s="15"/>
     </row>
-    <row r="647" spans="1:2" ht="29" customHeight="1">
+    <row r="647" spans="1:2">
       <c r="A647" s="14"/>
       <c r="B647" s="15"/>
     </row>
-    <row r="648" spans="1:2">
+    <row r="648" spans="1:2" ht="29" customHeight="1">
       <c r="A648" s="14"/>
       <c r="B648" s="15"/>
     </row>
@@ -12802,11 +12789,11 @@
       <c r="A650" s="14"/>
       <c r="B650" s="15"/>
     </row>
-    <row r="651" spans="1:2" ht="29" customHeight="1">
+    <row r="651" spans="1:2">
       <c r="A651" s="14"/>
       <c r="B651" s="15"/>
     </row>
-    <row r="652" spans="1:2">
+    <row r="652" spans="1:2" ht="29" customHeight="1">
       <c r="A652" s="14"/>
       <c r="B652" s="15"/>
     </row>
@@ -12818,11 +12805,11 @@
       <c r="A654" s="14"/>
       <c r="B654" s="15"/>
     </row>
-    <row r="655" spans="1:2" ht="43.5" customHeight="1">
+    <row r="655" spans="1:2">
       <c r="A655" s="14"/>
       <c r="B655" s="15"/>
     </row>
-    <row r="656" spans="1:2">
+    <row r="656" spans="1:2" ht="29" customHeight="1">
       <c r="A656" s="14"/>
       <c r="B656" s="15"/>
     </row>
@@ -12838,7 +12825,7 @@
       <c r="A659" s="14"/>
       <c r="B659" s="15"/>
     </row>
-    <row r="660" spans="1:2">
+    <row r="660" spans="1:2" ht="43.5" customHeight="1">
       <c r="A660" s="14"/>
       <c r="B660" s="15"/>
     </row>
@@ -12850,7 +12837,7 @@
       <c r="A662" s="14"/>
       <c r="B662" s="15"/>
     </row>
-    <row r="663" spans="1:2" ht="29" customHeight="1">
+    <row r="663" spans="1:2">
       <c r="A663" s="14"/>
       <c r="B663" s="15"/>
     </row>
@@ -12866,15 +12853,15 @@
       <c r="A666" s="14"/>
       <c r="B666" s="15"/>
     </row>
-    <row r="667" spans="1:2" ht="29" customHeight="1">
+    <row r="667" spans="1:2">
       <c r="A667" s="14"/>
       <c r="B667" s="15"/>
     </row>
-    <row r="668" spans="1:2">
+    <row r="668" spans="1:2" ht="29" customHeight="1">
       <c r="A668" s="14"/>
       <c r="B668" s="15"/>
     </row>
-    <row r="669" spans="1:2" ht="29" customHeight="1">
+    <row r="669" spans="1:2">
       <c r="A669" s="14"/>
       <c r="B669" s="15"/>
     </row>
@@ -12886,7 +12873,7 @@
       <c r="A671" s="14"/>
       <c r="B671" s="15"/>
     </row>
-    <row r="672" spans="1:2">
+    <row r="672" spans="1:2" ht="29" customHeight="1">
       <c r="A672" s="14"/>
       <c r="B672" s="15"/>
     </row>
@@ -12894,7 +12881,7 @@
       <c r="A673" s="14"/>
       <c r="B673" s="15"/>
     </row>
-    <row r="674" spans="1:2">
+    <row r="674" spans="1:2" ht="29" customHeight="1">
       <c r="A674" s="14"/>
       <c r="B674" s="15"/>
     </row>
@@ -12914,7 +12901,7 @@
       <c r="A678" s="14"/>
       <c r="B678" s="15"/>
     </row>
-    <row r="679" spans="1:2" ht="29" customHeight="1">
+    <row r="679" spans="1:2">
       <c r="A679" s="14"/>
       <c r="B679" s="15"/>
     </row>
@@ -12930,11 +12917,11 @@
       <c r="A682" s="14"/>
       <c r="B682" s="15"/>
     </row>
-    <row r="683" spans="1:2" ht="29" customHeight="1">
+    <row r="683" spans="1:2">
       <c r="A683" s="14"/>
       <c r="B683" s="15"/>
     </row>
-    <row r="684" spans="1:2">
+    <row r="684" spans="1:2" ht="29" customHeight="1">
       <c r="A684" s="14"/>
       <c r="B684" s="15"/>
     </row>
@@ -12946,11 +12933,11 @@
       <c r="A686" s="14"/>
       <c r="B686" s="15"/>
     </row>
-    <row r="687" spans="1:2" ht="29" customHeight="1">
+    <row r="687" spans="1:2">
       <c r="A687" s="14"/>
       <c r="B687" s="15"/>
     </row>
-    <row r="688" spans="1:2">
+    <row r="688" spans="1:2" ht="29" customHeight="1">
       <c r="A688" s="14"/>
       <c r="B688" s="15"/>
     </row>
@@ -12962,11 +12949,11 @@
       <c r="A690" s="14"/>
       <c r="B690" s="15"/>
     </row>
-    <row r="691" spans="1:2" ht="29" customHeight="1">
+    <row r="691" spans="1:2">
       <c r="A691" s="14"/>
       <c r="B691" s="15"/>
     </row>
-    <row r="692" spans="1:2">
+    <row r="692" spans="1:2" ht="29" customHeight="1">
       <c r="A692" s="14"/>
       <c r="B692" s="15"/>
     </row>
@@ -12978,11 +12965,11 @@
       <c r="A694" s="14"/>
       <c r="B694" s="15"/>
     </row>
-    <row r="695" spans="1:2" ht="29" customHeight="1">
+    <row r="695" spans="1:2">
       <c r="A695" s="14"/>
       <c r="B695" s="15"/>
     </row>
-    <row r="696" spans="1:2">
+    <row r="696" spans="1:2" ht="29" customHeight="1">
       <c r="A696" s="14"/>
       <c r="B696" s="15"/>
     </row>
@@ -12998,11 +12985,11 @@
       <c r="A699" s="14"/>
       <c r="B699" s="15"/>
     </row>
-    <row r="700" spans="1:2">
+    <row r="700" spans="1:2" ht="29" customHeight="1">
       <c r="A700" s="14"/>
       <c r="B700" s="15"/>
     </row>
-    <row r="701" spans="1:2" ht="43.5" customHeight="1">
+    <row r="701" spans="1:2">
       <c r="A701" s="14"/>
       <c r="B701" s="15"/>
     </row>
@@ -13010,7 +12997,7 @@
       <c r="A702" s="14"/>
       <c r="B702" s="15"/>
     </row>
-    <row r="703" spans="1:2" ht="29" customHeight="1">
+    <row r="703" spans="1:2">
       <c r="A703" s="14"/>
       <c r="B703" s="15"/>
     </row>
@@ -13022,19 +13009,19 @@
       <c r="A705" s="14"/>
       <c r="B705" s="15"/>
     </row>
-    <row r="706" spans="1:2">
+    <row r="706" spans="1:2" ht="43.5" customHeight="1">
       <c r="A706" s="14"/>
       <c r="B706" s="15"/>
     </row>
-    <row r="707" spans="1:2" ht="29" customHeight="1">
+    <row r="707" spans="1:2">
       <c r="A707" s="14"/>
       <c r="B707" s="15"/>
     </row>
-    <row r="708" spans="1:2">
+    <row r="708" spans="1:2" ht="29" customHeight="1">
       <c r="A708" s="14"/>
       <c r="B708" s="15"/>
     </row>
-    <row r="709" spans="1:2" ht="29" customHeight="1">
+    <row r="709" spans="1:2">
       <c r="A709" s="14"/>
       <c r="B709" s="15"/>
     </row>
@@ -13046,7 +13033,7 @@
       <c r="A711" s="14"/>
       <c r="B711" s="15"/>
     </row>
-    <row r="712" spans="1:2">
+    <row r="712" spans="1:2" ht="29" customHeight="1">
       <c r="A712" s="14"/>
       <c r="B712" s="15"/>
     </row>
@@ -13054,7 +13041,7 @@
       <c r="A713" s="14"/>
       <c r="B713" s="15"/>
     </row>
-    <row r="714" spans="1:2">
+    <row r="714" spans="1:2" ht="29" customHeight="1">
       <c r="A714" s="14"/>
       <c r="B714" s="15"/>
     </row>
@@ -13066,7 +13053,7 @@
       <c r="A716" s="14"/>
       <c r="B716" s="15"/>
     </row>
-    <row r="717" spans="1:2" ht="29" customHeight="1">
+    <row r="717" spans="1:2">
       <c r="A717" s="14"/>
       <c r="B717" s="15"/>
     </row>
@@ -13082,11 +13069,11 @@
       <c r="A720" s="14"/>
       <c r="B720" s="15"/>
     </row>
-    <row r="721" spans="1:2" ht="29" customHeight="1">
+    <row r="721" spans="1:2">
       <c r="A721" s="14"/>
       <c r="B721" s="15"/>
     </row>
-    <row r="722" spans="1:2">
+    <row r="722" spans="1:2" ht="29" customHeight="1">
       <c r="A722" s="14"/>
       <c r="B722" s="15"/>
     </row>
@@ -13096,41 +13083,41 @@
     </row>
     <row r="724" spans="1:2">
       <c r="A724" s="14"/>
-      <c r="B724" s="14"/>
+      <c r="B724" s="15"/>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" s="14"/>
-      <c r="B725" s="14"/>
-    </row>
-    <row r="726" spans="1:2">
+      <c r="B725" s="15"/>
+    </row>
+    <row r="726" spans="1:2" ht="29" customHeight="1">
       <c r="A726" s="14"/>
-      <c r="B726" s="14"/>
+      <c r="B726" s="15"/>
     </row>
     <row r="727" spans="1:2">
       <c r="A727" s="14"/>
       <c r="B727" s="15"/>
     </row>
-    <row r="728" spans="1:2" ht="43.5" customHeight="1">
+    <row r="728" spans="1:2">
       <c r="A728" s="14"/>
       <c r="B728" s="15"/>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" s="14"/>
-      <c r="B729" s="15"/>
+      <c r="B729" s="14"/>
     </row>
     <row r="730" spans="1:2">
       <c r="A730" s="14"/>
-      <c r="B730" s="15"/>
+      <c r="B730" s="14"/>
     </row>
     <row r="731" spans="1:2">
       <c r="A731" s="14"/>
-      <c r="B731" s="15"/>
-    </row>
-    <row r="732" spans="1:2" ht="29" customHeight="1">
+      <c r="B731" s="14"/>
+    </row>
+    <row r="732" spans="1:2">
       <c r="A732" s="14"/>
       <c r="B732" s="15"/>
     </row>
-    <row r="733" spans="1:2">
+    <row r="733" spans="1:2" ht="43.5" customHeight="1">
       <c r="A733" s="14"/>
       <c r="B733" s="15"/>
     </row>
@@ -13142,11 +13129,11 @@
       <c r="A735" s="14"/>
       <c r="B735" s="15"/>
     </row>
-    <row r="736" spans="1:2" ht="29" customHeight="1">
+    <row r="736" spans="1:2">
       <c r="A736" s="14"/>
       <c r="B736" s="15"/>
     </row>
-    <row r="737" spans="1:2">
+    <row r="737" spans="1:2" ht="29" customHeight="1">
       <c r="A737" s="14"/>
       <c r="B737" s="15"/>
     </row>
@@ -13158,11 +13145,11 @@
       <c r="A739" s="14"/>
       <c r="B739" s="15"/>
     </row>
-    <row r="740" spans="1:2" ht="29" customHeight="1">
+    <row r="740" spans="1:2">
       <c r="A740" s="14"/>
       <c r="B740" s="15"/>
     </row>
-    <row r="741" spans="1:2">
+    <row r="741" spans="1:2" ht="29" customHeight="1">
       <c r="A741" s="14"/>
       <c r="B741" s="15"/>
     </row>
@@ -13174,11 +13161,11 @@
       <c r="A743" s="14"/>
       <c r="B743" s="15"/>
     </row>
-    <row r="744" spans="1:2" ht="29" customHeight="1">
+    <row r="744" spans="1:2">
       <c r="A744" s="14"/>
       <c r="B744" s="15"/>
     </row>
-    <row r="745" spans="1:2">
+    <row r="745" spans="1:2" ht="29" customHeight="1">
       <c r="A745" s="14"/>
       <c r="B745" s="15"/>
     </row>
@@ -13190,11 +13177,11 @@
       <c r="A747" s="14"/>
       <c r="B747" s="15"/>
     </row>
-    <row r="748" spans="1:2" ht="29" customHeight="1">
+    <row r="748" spans="1:2">
       <c r="A748" s="14"/>
       <c r="B748" s="15"/>
     </row>
-    <row r="749" spans="1:2">
+    <row r="749" spans="1:2" ht="29" customHeight="1">
       <c r="A749" s="14"/>
       <c r="B749" s="15"/>
     </row>
@@ -13206,15 +13193,15 @@
       <c r="A751" s="14"/>
       <c r="B751" s="15"/>
     </row>
-    <row r="752" spans="1:2" ht="29" customHeight="1">
+    <row r="752" spans="1:2">
       <c r="A752" s="14"/>
       <c r="B752" s="15"/>
     </row>
-    <row r="753" spans="1:2">
+    <row r="753" spans="1:2" ht="29" customHeight="1">
       <c r="A753" s="14"/>
       <c r="B753" s="15"/>
     </row>
-    <row r="754" spans="1:2" ht="29" customHeight="1">
+    <row r="754" spans="1:2">
       <c r="A754" s="14"/>
       <c r="B754" s="15"/>
     </row>
@@ -13226,15 +13213,15 @@
       <c r="A756" s="14"/>
       <c r="B756" s="15"/>
     </row>
-    <row r="757" spans="1:2">
+    <row r="757" spans="1:2" ht="29" customHeight="1">
       <c r="A757" s="14"/>
       <c r="B757" s="15"/>
     </row>
-    <row r="758" spans="1:2" ht="43.5" customHeight="1">
+    <row r="758" spans="1:2">
       <c r="A758" s="14"/>
       <c r="B758" s="15"/>
     </row>
-    <row r="759" spans="1:2">
+    <row r="759" spans="1:2" ht="29" customHeight="1">
       <c r="A759" s="14"/>
       <c r="B759" s="15"/>
     </row>
@@ -13246,11 +13233,11 @@
       <c r="A761" s="14"/>
       <c r="B761" s="15"/>
     </row>
-    <row r="762" spans="1:2" ht="29" customHeight="1">
+    <row r="762" spans="1:2">
       <c r="A762" s="14"/>
       <c r="B762" s="15"/>
     </row>
-    <row r="763" spans="1:2">
+    <row r="763" spans="1:2" ht="43.5" customHeight="1">
       <c r="A763" s="14"/>
       <c r="B763" s="15"/>
     </row>
@@ -13262,11 +13249,11 @@
       <c r="A765" s="14"/>
       <c r="B765" s="15"/>
     </row>
-    <row r="766" spans="1:2" ht="29" customHeight="1">
+    <row r="766" spans="1:2">
       <c r="A766" s="14"/>
       <c r="B766" s="15"/>
     </row>
-    <row r="767" spans="1:2">
+    <row r="767" spans="1:2" ht="29" customHeight="1">
       <c r="A767" s="14"/>
       <c r="B767" s="15"/>
     </row>
@@ -13278,11 +13265,11 @@
       <c r="A769" s="14"/>
       <c r="B769" s="15"/>
     </row>
-    <row r="770" spans="1:2" ht="43.5" customHeight="1">
+    <row r="770" spans="1:2">
       <c r="A770" s="14"/>
       <c r="B770" s="15"/>
     </row>
-    <row r="771" spans="1:2">
+    <row r="771" spans="1:2" ht="29" customHeight="1">
       <c r="A771" s="14"/>
       <c r="B771" s="15"/>
     </row>
@@ -13294,11 +13281,11 @@
       <c r="A773" s="14"/>
       <c r="B773" s="15"/>
     </row>
-    <row r="774" spans="1:2" ht="29" customHeight="1">
+    <row r="774" spans="1:2">
       <c r="A774" s="14"/>
       <c r="B774" s="15"/>
     </row>
-    <row r="775" spans="1:2">
+    <row r="775" spans="1:2" ht="43.5" customHeight="1">
       <c r="A775" s="14"/>
       <c r="B775" s="15"/>
     </row>
@@ -13310,11 +13297,11 @@
       <c r="A777" s="14"/>
       <c r="B777" s="15"/>
     </row>
-    <row r="778" spans="1:2" ht="29" customHeight="1">
+    <row r="778" spans="1:2">
       <c r="A778" s="14"/>
       <c r="B778" s="15"/>
     </row>
-    <row r="779" spans="1:2">
+    <row r="779" spans="1:2" ht="29" customHeight="1">
       <c r="A779" s="14"/>
       <c r="B779" s="15"/>
     </row>
@@ -13326,11 +13313,11 @@
       <c r="A781" s="14"/>
       <c r="B781" s="15"/>
     </row>
-    <row r="782" spans="1:2" ht="29" customHeight="1">
+    <row r="782" spans="1:2">
       <c r="A782" s="14"/>
       <c r="B782" s="15"/>
     </row>
-    <row r="783" spans="1:2">
+    <row r="783" spans="1:2" ht="29" customHeight="1">
       <c r="A783" s="14"/>
       <c r="B783" s="15"/>
     </row>
@@ -13342,11 +13329,11 @@
       <c r="A785" s="14"/>
       <c r="B785" s="15"/>
     </row>
-    <row r="786" spans="1:2" ht="29" customHeight="1">
+    <row r="786" spans="1:2">
       <c r="A786" s="14"/>
       <c r="B786" s="15"/>
     </row>
-    <row r="787" spans="1:2">
+    <row r="787" spans="1:2" ht="29" customHeight="1">
       <c r="A787" s="14"/>
       <c r="B787" s="15"/>
     </row>
@@ -13358,11 +13345,11 @@
       <c r="A789" s="14"/>
       <c r="B789" s="15"/>
     </row>
-    <row r="790" spans="1:2" ht="29" customHeight="1">
+    <row r="790" spans="1:2">
       <c r="A790" s="14"/>
       <c r="B790" s="15"/>
     </row>
-    <row r="791" spans="1:2">
+    <row r="791" spans="1:2" ht="29" customHeight="1">
       <c r="A791" s="14"/>
       <c r="B791" s="15"/>
     </row>
@@ -13374,11 +13361,11 @@
       <c r="A793" s="14"/>
       <c r="B793" s="15"/>
     </row>
-    <row r="794" spans="1:2" ht="29" customHeight="1">
+    <row r="794" spans="1:2">
       <c r="A794" s="14"/>
       <c r="B794" s="15"/>
     </row>
-    <row r="795" spans="1:2">
+    <row r="795" spans="1:2" ht="29" customHeight="1">
       <c r="A795" s="14"/>
       <c r="B795" s="15"/>
     </row>
@@ -13394,7 +13381,7 @@
       <c r="A798" s="14"/>
       <c r="B798" s="15"/>
     </row>
-    <row r="799" spans="1:2">
+    <row r="799" spans="1:2" ht="29" customHeight="1">
       <c r="A799" s="14"/>
       <c r="B799" s="15"/>
     </row>
@@ -13414,7 +13401,7 @@
       <c r="A803" s="14"/>
       <c r="B803" s="15"/>
     </row>
-    <row r="804" spans="1:2" ht="29" customHeight="1">
+    <row r="804" spans="1:2">
       <c r="A804" s="14"/>
       <c r="B804" s="15"/>
     </row>
@@ -13422,7 +13409,7 @@
       <c r="A805" s="14"/>
       <c r="B805" s="15"/>
     </row>
-    <row r="806" spans="1:2" ht="29" customHeight="1">
+    <row r="806" spans="1:2">
       <c r="A806" s="14"/>
       <c r="B806" s="15"/>
     </row>
@@ -13434,15 +13421,15 @@
       <c r="A808" s="14"/>
       <c r="B808" s="15"/>
     </row>
-    <row r="809" spans="1:2">
+    <row r="809" spans="1:2" ht="29" customHeight="1">
       <c r="A809" s="14"/>
       <c r="B809" s="15"/>
     </row>
-    <row r="810" spans="1:2" ht="29" customHeight="1">
+    <row r="810" spans="1:2">
       <c r="A810" s="14"/>
       <c r="B810" s="15"/>
     </row>
-    <row r="811" spans="1:2">
+    <row r="811" spans="1:2" ht="29" customHeight="1">
       <c r="A811" s="14"/>
       <c r="B811" s="15"/>
     </row>
@@ -13454,11 +13441,11 @@
       <c r="A813" s="14"/>
       <c r="B813" s="15"/>
     </row>
-    <row r="814" spans="1:2" ht="29" customHeight="1">
+    <row r="814" spans="1:2">
       <c r="A814" s="14"/>
       <c r="B814" s="15"/>
     </row>
-    <row r="815" spans="1:2">
+    <row r="815" spans="1:2" ht="29" customHeight="1">
       <c r="A815" s="14"/>
       <c r="B815" s="15"/>
     </row>
@@ -13470,7 +13457,7 @@
       <c r="A817" s="14"/>
       <c r="B817" s="15"/>
     </row>
-    <row r="818" spans="1:2" ht="29" customHeight="1">
+    <row r="818" spans="1:2">
       <c r="A818" s="14"/>
       <c r="B818" s="15"/>
     </row>
@@ -13486,15 +13473,15 @@
       <c r="A821" s="14"/>
       <c r="B821" s="15"/>
     </row>
-    <row r="822" spans="1:2" ht="29" customHeight="1">
+    <row r="822" spans="1:2">
       <c r="A822" s="14"/>
       <c r="B822" s="15"/>
     </row>
-    <row r="823" spans="1:2">
+    <row r="823" spans="1:2" ht="29" customHeight="1">
       <c r="A823" s="14"/>
       <c r="B823" s="15"/>
     </row>
-    <row r="824" spans="1:2" ht="43.5" customHeight="1">
+    <row r="824" spans="1:2" ht="29" customHeight="1">
       <c r="A824" s="14"/>
       <c r="B824" s="15"/>
     </row>
@@ -13506,15 +13493,15 @@
       <c r="A826" s="14"/>
       <c r="B826" s="15"/>
     </row>
-    <row r="827" spans="1:2">
+    <row r="827" spans="1:2" ht="29" customHeight="1">
       <c r="A827" s="14"/>
       <c r="B827" s="15"/>
     </row>
-    <row r="828" spans="1:2" ht="29" customHeight="1">
+    <row r="828" spans="1:2">
       <c r="A828" s="14"/>
       <c r="B828" s="15"/>
     </row>
-    <row r="829" spans="1:2">
+    <row r="829" spans="1:2" ht="43.5" customHeight="1">
       <c r="A829" s="14"/>
       <c r="B829" s="15"/>
     </row>
@@ -13530,11 +13517,11 @@
       <c r="A832" s="14"/>
       <c r="B832" s="15"/>
     </row>
-    <row r="833" spans="1:2">
+    <row r="833" spans="1:2" ht="29" customHeight="1">
       <c r="A833" s="14"/>
       <c r="B833" s="15"/>
     </row>
-    <row r="834" spans="1:2" ht="43.5" customHeight="1">
+    <row r="834" spans="1:2">
       <c r="A834" s="14"/>
       <c r="B834" s="15"/>
     </row>
@@ -13550,11 +13537,11 @@
       <c r="A837" s="14"/>
       <c r="B837" s="15"/>
     </row>
-    <row r="838" spans="1:2" ht="29" customHeight="1">
+    <row r="838" spans="1:2">
       <c r="A838" s="14"/>
       <c r="B838" s="15"/>
     </row>
-    <row r="839" spans="1:2">
+    <row r="839" spans="1:2" ht="43.5" customHeight="1">
       <c r="A839" s="14"/>
       <c r="B839" s="15"/>
     </row>
@@ -13566,11 +13553,11 @@
       <c r="A841" s="14"/>
       <c r="B841" s="15"/>
     </row>
-    <row r="842" spans="1:2" ht="29" customHeight="1">
+    <row r="842" spans="1:2">
       <c r="A842" s="14"/>
       <c r="B842" s="15"/>
     </row>
-    <row r="843" spans="1:2">
+    <row r="843" spans="1:2" ht="29" customHeight="1">
       <c r="A843" s="14"/>
       <c r="B843" s="15"/>
     </row>
@@ -13582,11 +13569,11 @@
       <c r="A845" s="14"/>
       <c r="B845" s="15"/>
     </row>
-    <row r="846" spans="1:2" ht="29" customHeight="1">
+    <row r="846" spans="1:2">
       <c r="A846" s="14"/>
       <c r="B846" s="15"/>
     </row>
-    <row r="847" spans="1:2">
+    <row r="847" spans="1:2" ht="29" customHeight="1">
       <c r="A847" s="14"/>
       <c r="B847" s="15"/>
     </row>
@@ -13598,11 +13585,11 @@
       <c r="A849" s="14"/>
       <c r="B849" s="15"/>
     </row>
-    <row r="850" spans="1:2" ht="29" customHeight="1">
+    <row r="850" spans="1:2">
       <c r="A850" s="14"/>
       <c r="B850" s="15"/>
     </row>
-    <row r="851" spans="1:2">
+    <row r="851" spans="1:2" ht="29" customHeight="1">
       <c r="A851" s="14"/>
       <c r="B851" s="15"/>
     </row>
@@ -13614,15 +13601,15 @@
       <c r="A853" s="14"/>
       <c r="B853" s="15"/>
     </row>
-    <row r="854" spans="1:2" ht="29" customHeight="1">
+    <row r="854" spans="1:2">
       <c r="A854" s="14"/>
       <c r="B854" s="15"/>
     </row>
-    <row r="855" spans="1:2">
+    <row r="855" spans="1:2" ht="29" customHeight="1">
       <c r="A855" s="14"/>
       <c r="B855" s="15"/>
     </row>
-    <row r="856" spans="1:2" ht="29" customHeight="1">
+    <row r="856" spans="1:2">
       <c r="A856" s="14"/>
       <c r="B856" s="15"/>
     </row>
@@ -13633,6 +13620,26 @@
     <row r="858" spans="1:2">
       <c r="A858" s="14"/>
       <c r="B858" s="15"/>
+    </row>
+    <row r="859" spans="1:2" ht="29" customHeight="1">
+      <c r="A859" s="14"/>
+      <c r="B859" s="15"/>
+    </row>
+    <row r="860" spans="1:2">
+      <c r="A860" s="14"/>
+      <c r="B860" s="15"/>
+    </row>
+    <row r="861" spans="1:2" ht="29" customHeight="1">
+      <c r="A861" s="14"/>
+      <c r="B861" s="15"/>
+    </row>
+    <row r="862" spans="1:2">
+      <c r="A862" s="14"/>
+      <c r="B862" s="15"/>
+    </row>
+    <row r="863" spans="1:2">
+      <c r="A863" s="14"/>
+      <c r="B863" s="15"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -13790,36 +13797,6 @@
     <hyperlink ref="B159" r:id="rId152" display="https://www.premierleague.com/en/players/17500/emmanuel-adebayor/overview" xr:uid="{00000000-0004-0000-0100-000097000000}"/>
     <hyperlink ref="B160" r:id="rId153" display="https://www.premierleague.com/en/players/4857/ruud-van-nistelrooy/overview" xr:uid="{00000000-0004-0000-0100-000098000000}"/>
     <hyperlink ref="B161" r:id="rId154" display="https://www.premierleague.com/en/players/4857/ruud-van-nistelrooy/overview" xr:uid="{00000000-0004-0000-0100-000099000000}"/>
-    <hyperlink ref="B162" r:id="rId155" display="https://www.premierleague.com/en/players/4857/ruud-van-nistelrooy/overview" xr:uid="{00000000-0004-0000-0100-00009A000000}"/>
-    <hyperlink ref="B163" r:id="rId156" display="https://www.premierleague.com/en/players/4857/ruud-van-nistelrooy/overview" xr:uid="{00000000-0004-0000-0100-00009B000000}"/>
-    <hyperlink ref="B164" r:id="rId157" display="https://www.premierleague.com/en/players/13239/yakubu/overview" xr:uid="{00000000-0004-0000-0100-00009C000000}"/>
-    <hyperlink ref="B165" r:id="rId158" display="https://www.premierleague.com/en/players/13239/yakubu/overview" xr:uid="{00000000-0004-0000-0100-00009D000000}"/>
-    <hyperlink ref="B166" r:id="rId159" display="https://www.premierleague.com/en/players/13239/yakubu/overview" xr:uid="{00000000-0004-0000-0100-00009E000000}"/>
-    <hyperlink ref="B167" r:id="rId160" display="https://www.premierleague.com/en/players/13239/yakubu/overview" xr:uid="{00000000-0004-0000-0100-00009F000000}"/>
-    <hyperlink ref="B168" r:id="rId161" display="https://www.premierleague.com/en/players/8595/dimitar-berbatov/overview" xr:uid="{00000000-0004-0000-0100-0000A0000000}"/>
-    <hyperlink ref="B169" r:id="rId162" display="https://www.premierleague.com/en/players/8595/dimitar-berbatov/overview" xr:uid="{00000000-0004-0000-0100-0000A1000000}"/>
-    <hyperlink ref="B170" r:id="rId163" display="https://www.premierleague.com/en/players/8595/dimitar-berbatov/overview" xr:uid="{00000000-0004-0000-0100-0000A2000000}"/>
-    <hyperlink ref="B171" r:id="rId164" display="https://www.premierleague.com/en/players/8595/dimitar-berbatov/overview" xr:uid="{00000000-0004-0000-0100-0000A3000000}"/>
-    <hyperlink ref="B172" r:id="rId165" display="https://www.premierleague.com/en/players/75115/callum-wilson/overview" xr:uid="{00000000-0004-0000-0100-0000A4000000}"/>
-    <hyperlink ref="B173" r:id="rId166" display="https://www.premierleague.com/en/players/75115/callum-wilson/overview" xr:uid="{00000000-0004-0000-0100-0000A5000000}"/>
-    <hyperlink ref="B174" r:id="rId167" display="https://www.premierleague.com/en/players/75115/callum-wilson/overview" xr:uid="{00000000-0004-0000-0100-0000A6000000}"/>
-    <hyperlink ref="B175" r:id="rId168" display="https://www.premierleague.com/en/players/75115/callum-wilson/overview" xr:uid="{00000000-0004-0000-0100-0000A7000000}"/>
-    <hyperlink ref="B176" r:id="rId169" display="https://www.premierleague.com/en/players/75115/callum-wilson/overview" xr:uid="{00000000-0004-0000-0100-0000A8000000}"/>
-    <hyperlink ref="B177" r:id="rId170" display="https://www.premierleague.com/en/players/75115/callum-wilson/overview" xr:uid="{00000000-0004-0000-0100-0000A9000000}"/>
-    <hyperlink ref="B178" r:id="rId171" display="https://www.premierleague.com/en/players/2183/mark-viduka/overview" xr:uid="{00000000-0004-0000-0100-0000AA000000}"/>
-    <hyperlink ref="B179" r:id="rId172" display="https://www.premierleague.com/en/players/2183/mark-viduka/overview" xr:uid="{00000000-0004-0000-0100-0000AB000000}"/>
-    <hyperlink ref="B180" r:id="rId173" display="https://www.premierleague.com/en/players/2183/mark-viduka/overview" xr:uid="{00000000-0004-0000-0100-0000AC000000}"/>
-    <hyperlink ref="B181" r:id="rId174" display="https://www.premierleague.com/en/players/2183/mark-viduka/overview" xr:uid="{00000000-0004-0000-0100-0000AD000000}"/>
-    <hyperlink ref="B182" r:id="rId175" display="https://www.premierleague.com/en/players/1972/kevin-phillips/overview" xr:uid="{00000000-0004-0000-0100-0000AE000000}"/>
-    <hyperlink ref="B183" r:id="rId176" display="https://www.premierleague.com/en/players/1972/kevin-phillips/overview" xr:uid="{00000000-0004-0000-0100-0000AF000000}"/>
-    <hyperlink ref="B184" r:id="rId177" display="https://www.premierleague.com/en/players/1972/kevin-phillips/overview" xr:uid="{00000000-0004-0000-0100-0000B0000000}"/>
-    <hyperlink ref="B185" r:id="rId178" display="https://www.premierleague.com/en/players/1972/kevin-phillips/overview" xr:uid="{00000000-0004-0000-0100-0000B1000000}"/>
-    <hyperlink ref="B186" r:id="rId179" display="https://www.premierleague.com/en/players/60689/chris-wood/overview" xr:uid="{00000000-0004-0000-0100-0000B2000000}"/>
-    <hyperlink ref="B187" r:id="rId180" display="https://www.premierleague.com/en/players/60689/chris-wood/overview" xr:uid="{00000000-0004-0000-0100-0000B3000000}"/>
-    <hyperlink ref="B188" r:id="rId181" display="https://www.premierleague.com/en/players/60689/chris-wood/overview" xr:uid="{00000000-0004-0000-0100-0000B4000000}"/>
-    <hyperlink ref="B189" r:id="rId182" display="https://www.premierleague.com/en/players/60689/chris-wood/overview" xr:uid="{00000000-0004-0000-0100-0000B5000000}"/>
-    <hyperlink ref="B190" r:id="rId183" display="https://www.premierleague.com/en/players/60689/chris-wood/overview" xr:uid="{00000000-0004-0000-0100-0000B6000000}"/>
-    <hyperlink ref="B191" r:id="rId184" display="https://www.premierleague.com/en/players/60689/chris-wood/overview" xr:uid="{00000000-0004-0000-0100-0000B7000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Stats For Rush.xlsx
+++ b/Stats For Rush.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurtl\Desktop\statstreaks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26321694-BA01-4D50-BEBE-92204E36464B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D55A820-FD6C-4D15-A96C-F678CCD2D96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" tabRatio="866" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="866" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PL assists" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,12 @@
     <sheet name="PL Appearances" sheetId="3" r:id="rId3"/>
     <sheet name="Intl Appearances" sheetId="4" r:id="rId4"/>
     <sheet name="Intl Goals" sheetId="5" r:id="rId5"/>
-    <sheet name="Man U goals" sheetId="6" r:id="rId6"/>
-    <sheet name="Liverpool goals" sheetId="7" r:id="rId7"/>
-    <sheet name="Champs league goals" sheetId="9" r:id="rId8"/>
-    <sheet name="La Liga goals" sheetId="8" r:id="rId9"/>
-    <sheet name="Transfers" sheetId="10" r:id="rId10"/>
+    <sheet name="Sheet1" sheetId="11" r:id="rId6"/>
+    <sheet name="Man U goals" sheetId="6" r:id="rId7"/>
+    <sheet name="Liverpool goals" sheetId="7" r:id="rId8"/>
+    <sheet name="Champs league goals" sheetId="9" r:id="rId9"/>
+    <sheet name="La Liga goals" sheetId="8" r:id="rId10"/>
+    <sheet name="Transfers" sheetId="10" r:id="rId11"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2686" uniqueCount="1208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2994" uniqueCount="1223">
   <si>
     <t>Rank</t>
   </si>
@@ -3658,13 +3659,58 @@
   </si>
   <si>
     <t>Cesar Azpilicueta</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Goals (All Competitions)</t>
+  </si>
+  <si>
+    <t>Roger Hunt</t>
+  </si>
+  <si>
+    <t>Man Utd</t>
+  </si>
+  <si>
+    <t>Sadio Mane</t>
+  </si>
+  <si>
+    <t>John Barnes</t>
+  </si>
+  <si>
+    <t>Kevin Keegan</t>
+  </si>
+  <si>
+    <t>John Toshack</t>
+  </si>
+  <si>
+    <t>Luis Suarez</t>
+  </si>
+  <si>
+    <t>Terry McDermott</t>
+  </si>
+  <si>
+    <t>Jan Molby</t>
+  </si>
+  <si>
+    <t>Gordon Strachan</t>
+  </si>
+  <si>
+    <t>Djibril Cisse</t>
+  </si>
+  <si>
+    <t>Gary Pallister</t>
+  </si>
+  <si>
+    <t>Alisson</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3706,8 +3752,43 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1A1A2E"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1A1A2E"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF003087"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF003087"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFCC0000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFCC0000"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3773,6 +3854,21 @@
         <bgColor rgb="FF1B5E20"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A1A2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCE0FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -3831,7 +3927,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3907,6 +4003,29 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -8379,6 +8498,1358 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A1:E84"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="111.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D1" t="s">
+        <v>904</v>
+      </c>
+      <c r="E1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>906</v>
+      </c>
+      <c r="C2">
+        <v>474</v>
+      </c>
+      <c r="D2">
+        <v>520</v>
+      </c>
+      <c r="E2" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>908</v>
+      </c>
+      <c r="C3">
+        <v>311</v>
+      </c>
+      <c r="D3">
+        <v>292</v>
+      </c>
+      <c r="E3" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>910</v>
+      </c>
+      <c r="C4">
+        <v>251</v>
+      </c>
+      <c r="D4">
+        <v>277</v>
+      </c>
+      <c r="E4" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>912</v>
+      </c>
+      <c r="C5">
+        <v>238</v>
+      </c>
+      <c r="D5">
+        <v>439</v>
+      </c>
+      <c r="E5" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>913</v>
+      </c>
+      <c r="C6">
+        <v>234</v>
+      </c>
+      <c r="D6">
+        <v>347</v>
+      </c>
+      <c r="E6" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>915</v>
+      </c>
+      <c r="C7">
+        <v>228</v>
+      </c>
+      <c r="D7">
+        <v>550</v>
+      </c>
+      <c r="E7" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>916</v>
+      </c>
+      <c r="C8">
+        <v>227</v>
+      </c>
+      <c r="D8">
+        <v>329</v>
+      </c>
+      <c r="E8" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>918</v>
+      </c>
+      <c r="C9">
+        <v>221</v>
+      </c>
+      <c r="D9">
+        <v>353</v>
+      </c>
+      <c r="E9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>920</v>
+      </c>
+      <c r="C10">
+        <v>219</v>
+      </c>
+      <c r="D10">
+        <v>448</v>
+      </c>
+      <c r="E10" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>922</v>
+      </c>
+      <c r="C11">
+        <v>212</v>
+      </c>
+      <c r="D11">
+        <v>278</v>
+      </c>
+      <c r="E11" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>924</v>
+      </c>
+      <c r="C12">
+        <v>204</v>
+      </c>
+      <c r="D12">
+        <v>557</v>
+      </c>
+      <c r="E12" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>926</v>
+      </c>
+      <c r="C13">
+        <v>195</v>
+      </c>
+      <c r="D13">
+        <v>231</v>
+      </c>
+      <c r="E13" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>928</v>
+      </c>
+      <c r="C14">
+        <v>186</v>
+      </c>
+      <c r="D14">
+        <v>352</v>
+      </c>
+      <c r="E14" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" t="s">
+        <v>930</v>
+      </c>
+      <c r="C15">
+        <v>186</v>
+      </c>
+      <c r="D15">
+        <v>461</v>
+      </c>
+      <c r="E15" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>931</v>
+      </c>
+      <c r="C16">
+        <v>183</v>
+      </c>
+      <c r="D16">
+        <v>255</v>
+      </c>
+      <c r="E16" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>933</v>
+      </c>
+      <c r="C17">
+        <v>182</v>
+      </c>
+      <c r="D17">
+        <v>349</v>
+      </c>
+      <c r="E17" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>935</v>
+      </c>
+      <c r="C18">
+        <v>179</v>
+      </c>
+      <c r="D18">
+        <v>258</v>
+      </c>
+      <c r="E18" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>937</v>
+      </c>
+      <c r="C19">
+        <v>169</v>
+      </c>
+      <c r="D19">
+        <v>411</v>
+      </c>
+      <c r="E19" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>939</v>
+      </c>
+      <c r="C20">
+        <v>162</v>
+      </c>
+      <c r="D20">
+        <v>280</v>
+      </c>
+      <c r="E20" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>941</v>
+      </c>
+      <c r="C21">
+        <v>160</v>
+      </c>
+      <c r="D21">
+        <v>360</v>
+      </c>
+      <c r="E21" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>943</v>
+      </c>
+      <c r="C22">
+        <v>158</v>
+      </c>
+      <c r="D22">
+        <v>443</v>
+      </c>
+      <c r="E22" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>945</v>
+      </c>
+      <c r="C23">
+        <v>156</v>
+      </c>
+      <c r="D23">
+        <v>180</v>
+      </c>
+      <c r="E23" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>946</v>
+      </c>
+      <c r="C24">
+        <v>152</v>
+      </c>
+      <c r="D24">
+        <v>417</v>
+      </c>
+      <c r="E24" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>948</v>
+      </c>
+      <c r="C25">
+        <v>150</v>
+      </c>
+      <c r="D25">
+        <v>287</v>
+      </c>
+      <c r="E25" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>950</v>
+      </c>
+      <c r="C26">
+        <v>147</v>
+      </c>
+      <c r="D26">
+        <v>303</v>
+      </c>
+      <c r="E26" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>951</v>
+      </c>
+      <c r="C27">
+        <v>146</v>
+      </c>
+      <c r="D27">
+        <v>407</v>
+      </c>
+      <c r="E27" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>953</v>
+      </c>
+      <c r="C28">
+        <v>140</v>
+      </c>
+      <c r="D28">
+        <v>283</v>
+      </c>
+      <c r="E28" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>955</v>
+      </c>
+      <c r="C29">
+        <v>139</v>
+      </c>
+      <c r="D29">
+        <v>199</v>
+      </c>
+      <c r="E29" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="B30" t="s">
+        <v>957</v>
+      </c>
+      <c r="C30">
+        <v>139</v>
+      </c>
+      <c r="D30">
+        <v>207</v>
+      </c>
+      <c r="E30" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="B31" t="s">
+        <v>958</v>
+      </c>
+      <c r="C31">
+        <v>139</v>
+      </c>
+      <c r="D31">
+        <v>484</v>
+      </c>
+      <c r="E31" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>960</v>
+      </c>
+      <c r="C32">
+        <v>138</v>
+      </c>
+      <c r="D32">
+        <v>215</v>
+      </c>
+      <c r="E32" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>962</v>
+      </c>
+      <c r="C33">
+        <v>136</v>
+      </c>
+      <c r="D33">
+        <v>326</v>
+      </c>
+      <c r="E33" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>963</v>
+      </c>
+      <c r="C34">
+        <v>133</v>
+      </c>
+      <c r="D34">
+        <v>297</v>
+      </c>
+      <c r="E34" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="B35" t="s">
+        <v>965</v>
+      </c>
+      <c r="C35">
+        <v>133</v>
+      </c>
+      <c r="D35">
+        <v>438</v>
+      </c>
+      <c r="E35" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>967</v>
+      </c>
+      <c r="C36">
+        <v>131</v>
+      </c>
+      <c r="D36">
+        <v>226</v>
+      </c>
+      <c r="E36" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>969</v>
+      </c>
+      <c r="C37">
+        <v>130</v>
+      </c>
+      <c r="D37">
+        <v>323</v>
+      </c>
+      <c r="E37" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>971</v>
+      </c>
+      <c r="C38">
+        <v>129</v>
+      </c>
+      <c r="D38">
+        <v>305</v>
+      </c>
+      <c r="E38" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="B39" t="s">
+        <v>973</v>
+      </c>
+      <c r="C39">
+        <v>129</v>
+      </c>
+      <c r="D39">
+        <v>323</v>
+      </c>
+      <c r="E39" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="B40" t="s">
+        <v>975</v>
+      </c>
+      <c r="C40">
+        <v>129</v>
+      </c>
+      <c r="D40">
+        <v>337</v>
+      </c>
+      <c r="E40" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="B41" t="s">
+        <v>977</v>
+      </c>
+      <c r="C41">
+        <v>129</v>
+      </c>
+      <c r="D41">
+        <v>437</v>
+      </c>
+      <c r="E41" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>979</v>
+      </c>
+      <c r="C42">
+        <v>128</v>
+      </c>
+      <c r="D42">
+        <v>240</v>
+      </c>
+      <c r="E42" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="B43" t="s">
+        <v>981</v>
+      </c>
+      <c r="C43">
+        <v>128</v>
+      </c>
+      <c r="D43">
+        <v>244</v>
+      </c>
+      <c r="E43" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="B44" t="s">
+        <v>982</v>
+      </c>
+      <c r="C44">
+        <v>128</v>
+      </c>
+      <c r="D44">
+        <v>361</v>
+      </c>
+      <c r="E44" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>984</v>
+      </c>
+      <c r="C45">
+        <v>127</v>
+      </c>
+      <c r="D45">
+        <v>204</v>
+      </c>
+      <c r="E45" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>986</v>
+      </c>
+      <c r="C46">
+        <v>126</v>
+      </c>
+      <c r="D46">
+        <v>222</v>
+      </c>
+      <c r="E46" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47">
+        <v>47</v>
+      </c>
+      <c r="B47" t="s">
+        <v>988</v>
+      </c>
+      <c r="C47">
+        <v>125</v>
+      </c>
+      <c r="D47">
+        <v>334</v>
+      </c>
+      <c r="E47" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>990</v>
+      </c>
+      <c r="C48">
+        <v>124</v>
+      </c>
+      <c r="D48">
+        <v>337</v>
+      </c>
+      <c r="E48" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>992</v>
+      </c>
+      <c r="C49">
+        <v>123</v>
+      </c>
+      <c r="D49">
+        <v>341</v>
+      </c>
+      <c r="E49" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="B50" t="s">
+        <v>993</v>
+      </c>
+      <c r="C50">
+        <v>123</v>
+      </c>
+      <c r="D50">
+        <v>417</v>
+      </c>
+      <c r="E50" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>994</v>
+      </c>
+      <c r="C51">
+        <v>119</v>
+      </c>
+      <c r="D51">
+        <v>229</v>
+      </c>
+      <c r="E51" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="B52" t="s">
+        <v>996</v>
+      </c>
+      <c r="C52">
+        <v>119</v>
+      </c>
+      <c r="D52">
+        <v>344</v>
+      </c>
+      <c r="E52" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>997</v>
+      </c>
+      <c r="C53">
+        <v>117</v>
+      </c>
+      <c r="D53">
+        <v>164</v>
+      </c>
+      <c r="E53" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="B54" t="s">
+        <v>999</v>
+      </c>
+      <c r="C54">
+        <v>117</v>
+      </c>
+      <c r="D54">
+        <v>380</v>
+      </c>
+      <c r="E54" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C55">
+        <v>115</v>
+      </c>
+      <c r="D55">
+        <v>216</v>
+      </c>
+      <c r="E55" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="B56" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C56">
+        <v>115</v>
+      </c>
+      <c r="D56">
+        <v>308</v>
+      </c>
+      <c r="E56" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C57">
+        <v>114</v>
+      </c>
+      <c r="D57">
+        <v>232</v>
+      </c>
+      <c r="E57" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="B58" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C58">
+        <v>114</v>
+      </c>
+      <c r="D58">
+        <v>239</v>
+      </c>
+      <c r="E58" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="B59" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C59">
+        <v>114</v>
+      </c>
+      <c r="D59">
+        <v>338</v>
+      </c>
+      <c r="E59" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C60">
+        <v>112</v>
+      </c>
+      <c r="D60">
+        <v>418</v>
+      </c>
+      <c r="E60" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="B61" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C61">
+        <v>112</v>
+      </c>
+      <c r="D61">
+        <v>609</v>
+      </c>
+      <c r="E61" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C62">
+        <v>111</v>
+      </c>
+      <c r="D62">
+        <v>314</v>
+      </c>
+      <c r="E62" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="B63" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C63">
+        <v>111</v>
+      </c>
+      <c r="D63">
+        <v>338</v>
+      </c>
+      <c r="E63" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="B64" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C64">
+        <v>111</v>
+      </c>
+      <c r="D64">
+        <v>381</v>
+      </c>
+      <c r="E64" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C65">
+        <v>109</v>
+      </c>
+      <c r="D65">
+        <v>241</v>
+      </c>
+      <c r="E65" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C66">
+        <v>108</v>
+      </c>
+      <c r="D66">
+        <v>118</v>
+      </c>
+      <c r="E66" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="B67" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C67">
+        <v>108</v>
+      </c>
+      <c r="D67">
+        <v>420</v>
+      </c>
+      <c r="E67" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C68">
+        <v>107</v>
+      </c>
+      <c r="D68">
+        <v>130</v>
+      </c>
+      <c r="E68" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="B69" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C69">
+        <v>107</v>
+      </c>
+      <c r="D69">
+        <v>190</v>
+      </c>
+      <c r="E69" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="B70" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C70">
+        <v>107</v>
+      </c>
+      <c r="D70">
+        <v>198</v>
+      </c>
+      <c r="E70" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="B71" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C71">
+        <v>107</v>
+      </c>
+      <c r="D71">
+        <v>261</v>
+      </c>
+      <c r="E71" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="B72" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C72">
+        <v>107</v>
+      </c>
+      <c r="D72">
+        <v>276</v>
+      </c>
+      <c r="E72" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C73">
+        <v>105</v>
+      </c>
+      <c r="D73">
+        <v>90</v>
+      </c>
+      <c r="E73" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="B74" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C74">
+        <v>105</v>
+      </c>
+      <c r="D74">
+        <v>263</v>
+      </c>
+      <c r="E74" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="B75" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C75">
+        <v>105</v>
+      </c>
+      <c r="D75">
+        <v>497</v>
+      </c>
+      <c r="E75" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C76">
+        <v>104</v>
+      </c>
+      <c r="D76">
+        <v>160</v>
+      </c>
+      <c r="E76" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C77">
+        <v>103</v>
+      </c>
+      <c r="D77">
+        <v>265</v>
+      </c>
+      <c r="E77" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="B78" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C78">
+        <v>103</v>
+      </c>
+      <c r="D78">
+        <v>400</v>
+      </c>
+      <c r="E78" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C79">
+        <v>102</v>
+      </c>
+      <c r="D79">
+        <v>157</v>
+      </c>
+      <c r="E79" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="B80" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C80">
+        <v>102</v>
+      </c>
+      <c r="D80">
+        <v>281</v>
+      </c>
+      <c r="E80" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="B81" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C81">
+        <v>102</v>
+      </c>
+      <c r="D81">
+        <v>363</v>
+      </c>
+      <c r="E81" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C82">
+        <v>101</v>
+      </c>
+      <c r="D82">
+        <v>141</v>
+      </c>
+      <c r="E82" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="B83" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C83">
+        <v>101</v>
+      </c>
+      <c r="D83">
+        <v>372</v>
+      </c>
+      <c r="E83" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C84">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -22002,6 +23473,2158 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28830BBA-01E9-4290-8134-6C4FA2F187F1}">
+  <dimension ref="A1:D153"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="29" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="30">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="33">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="30">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="33">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="34">
+        <v>3</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D4" s="37">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="34">
+        <v>4</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>740</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D5" s="37">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="34">
+        <v>5</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>653</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D6" s="37">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="30">
+        <v>6</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="33">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="30">
+        <v>7</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="33">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="34">
+        <v>8</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>655</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D9" s="37">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="30">
+        <v>9</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>599</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="33">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="34">
+        <v>10</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D11" s="37">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="34">
+        <v>11</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D12" s="37">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="30">
+        <v>12</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="33">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="34">
+        <v>13</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D14" s="37">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="34">
+        <v>14</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>176</v>
+      </c>
+      <c r="C15" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D15" s="37">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="34">
+        <v>15</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D16" s="37">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="34">
+        <v>16</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>747</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D17" s="37">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="34">
+        <v>17</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D18" s="37">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="34">
+        <v>18</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D19" s="37">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="30">
+        <v>19</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="33">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="30">
+        <v>20</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="33">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="30">
+        <v>21</v>
+      </c>
+      <c r="B22" s="31" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="33">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="30">
+        <v>22</v>
+      </c>
+      <c r="B23" s="31" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="34">
+        <v>23</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>628</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D24" s="37">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="34">
+        <v>24</v>
+      </c>
+      <c r="B25" s="35" t="s">
+        <v>750</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D25" s="37">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="30">
+        <v>25</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="33">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="34">
+        <v>26</v>
+      </c>
+      <c r="B27" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D27" s="37">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="34">
+        <v>27</v>
+      </c>
+      <c r="B28" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D28" s="37">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="30">
+        <v>28</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="33">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="34">
+        <v>29</v>
+      </c>
+      <c r="B30" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D30" s="37">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="30">
+        <v>30</v>
+      </c>
+      <c r="B31" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="33">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="30">
+        <v>31</v>
+      </c>
+      <c r="B32" s="31" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="33">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="34">
+        <v>32</v>
+      </c>
+      <c r="B33" s="35" t="s">
+        <v>737</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D33" s="37">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="30">
+        <v>33</v>
+      </c>
+      <c r="B34" s="31" t="s">
+        <v>835</v>
+      </c>
+      <c r="C34" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="33">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="30">
+        <v>34</v>
+      </c>
+      <c r="B35" s="31" t="s">
+        <v>836</v>
+      </c>
+      <c r="C35" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" s="33">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="30">
+        <v>35</v>
+      </c>
+      <c r="B36" s="31" t="s">
+        <v>837</v>
+      </c>
+      <c r="C36" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="33">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="34">
+        <v>36</v>
+      </c>
+      <c r="B37" s="35" t="s">
+        <v>751</v>
+      </c>
+      <c r="C37" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D37" s="37">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="34">
+        <v>37</v>
+      </c>
+      <c r="B38" s="35" t="s">
+        <v>752</v>
+      </c>
+      <c r="C38" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D38" s="37">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="30">
+        <v>38</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="C39" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="33">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="30">
+        <v>39</v>
+      </c>
+      <c r="B40" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="33">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="34">
+        <v>40</v>
+      </c>
+      <c r="B41" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="C41" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D41" s="37">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="30">
+        <v>41</v>
+      </c>
+      <c r="B42" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="C42" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="33">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="34">
+        <v>42</v>
+      </c>
+      <c r="B43" s="35" t="s">
+        <v>753</v>
+      </c>
+      <c r="C43" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D43" s="37">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="30">
+        <v>43</v>
+      </c>
+      <c r="B44" s="31" t="s">
+        <v>839</v>
+      </c>
+      <c r="C44" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" s="33">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="30">
+        <v>44</v>
+      </c>
+      <c r="B45" s="31" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C45" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" s="33">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="30">
+        <v>45</v>
+      </c>
+      <c r="B46" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="C46" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D46" s="33">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="30">
+        <v>46</v>
+      </c>
+      <c r="B47" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="C47" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" s="33">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="34">
+        <v>47</v>
+      </c>
+      <c r="B48" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="C48" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D48" s="37">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="34">
+        <v>48</v>
+      </c>
+      <c r="B49" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="C49" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D49" s="37">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="34">
+        <v>49</v>
+      </c>
+      <c r="B50" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="C50" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D50" s="37">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="30">
+        <v>50</v>
+      </c>
+      <c r="B51" s="31" t="s">
+        <v>844</v>
+      </c>
+      <c r="C51" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" s="33">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="30">
+        <v>51</v>
+      </c>
+      <c r="B52" s="31" t="s">
+        <v>845</v>
+      </c>
+      <c r="C52" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D52" s="33">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="30">
+        <v>52</v>
+      </c>
+      <c r="B53" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C53" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" s="33">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="34">
+        <v>53</v>
+      </c>
+      <c r="B54" s="35" t="s">
+        <v>285</v>
+      </c>
+      <c r="C54" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D54" s="37">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="34">
+        <v>54</v>
+      </c>
+      <c r="B55" s="35" t="s">
+        <v>755</v>
+      </c>
+      <c r="C55" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D55" s="37">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="34">
+        <v>55</v>
+      </c>
+      <c r="B56" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D56" s="37">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="30">
+        <v>56</v>
+      </c>
+      <c r="B57" s="31" t="s">
+        <v>847</v>
+      </c>
+      <c r="C57" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" s="33">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="30">
+        <v>57</v>
+      </c>
+      <c r="B58" s="31" t="s">
+        <v>849</v>
+      </c>
+      <c r="C58" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D58" s="33">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="30">
+        <v>58</v>
+      </c>
+      <c r="B59" s="31" t="s">
+        <v>851</v>
+      </c>
+      <c r="C59" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59" s="33">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="30">
+        <v>59</v>
+      </c>
+      <c r="B60" s="31" t="s">
+        <v>852</v>
+      </c>
+      <c r="C60" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D60" s="33">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="34">
+        <v>60</v>
+      </c>
+      <c r="B61" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D61" s="37">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="30">
+        <v>61</v>
+      </c>
+      <c r="B62" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C62" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D62" s="33">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="30">
+        <v>62</v>
+      </c>
+      <c r="B63" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="C63" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D63" s="33">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="34">
+        <v>63</v>
+      </c>
+      <c r="B64" s="35" t="s">
+        <v>169</v>
+      </c>
+      <c r="C64" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D64" s="37">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="34">
+        <v>64</v>
+      </c>
+      <c r="B65" s="35" t="s">
+        <v>187</v>
+      </c>
+      <c r="C65" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D65" s="37">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="30">
+        <v>65</v>
+      </c>
+      <c r="B66" s="31" t="s">
+        <v>855</v>
+      </c>
+      <c r="C66" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D66" s="33">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="30">
+        <v>66</v>
+      </c>
+      <c r="B67" s="31" t="s">
+        <v>857</v>
+      </c>
+      <c r="C67" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D67" s="33">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="34">
+        <v>67</v>
+      </c>
+      <c r="B68" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="C68" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D68" s="37">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="30">
+        <v>68</v>
+      </c>
+      <c r="B69" s="31" t="s">
+        <v>859</v>
+      </c>
+      <c r="C69" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D69" s="33">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="34">
+        <v>69</v>
+      </c>
+      <c r="B70" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="C70" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D70" s="37">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="30">
+        <v>70</v>
+      </c>
+      <c r="B71" s="31" t="s">
+        <v>861</v>
+      </c>
+      <c r="C71" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" s="33">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="30">
+        <v>71</v>
+      </c>
+      <c r="B72" s="31" t="s">
+        <v>862</v>
+      </c>
+      <c r="C72" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D72" s="33">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="34">
+        <v>72</v>
+      </c>
+      <c r="B73" s="35" t="s">
+        <v>758</v>
+      </c>
+      <c r="C73" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D73" s="37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="34">
+        <v>73</v>
+      </c>
+      <c r="B74" s="35" t="s">
+        <v>756</v>
+      </c>
+      <c r="C74" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D74" s="37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="34">
+        <v>74</v>
+      </c>
+      <c r="B75" s="35" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C75" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D75" s="37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="34">
+        <v>75</v>
+      </c>
+      <c r="B76" s="35" t="s">
+        <v>759</v>
+      </c>
+      <c r="C76" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D76" s="37">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="34">
+        <v>76</v>
+      </c>
+      <c r="B77" s="35" t="s">
+        <v>760</v>
+      </c>
+      <c r="C77" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D77" s="37">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="30">
+        <v>77</v>
+      </c>
+      <c r="B78" s="31" t="s">
+        <v>217</v>
+      </c>
+      <c r="C78" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D78" s="33">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="30">
+        <v>78</v>
+      </c>
+      <c r="B79" s="31" t="s">
+        <v>863</v>
+      </c>
+      <c r="C79" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D79" s="33">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="30">
+        <v>79</v>
+      </c>
+      <c r="B80" s="31" t="s">
+        <v>864</v>
+      </c>
+      <c r="C80" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D80" s="33">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="34">
+        <v>80</v>
+      </c>
+      <c r="B81" s="35" t="s">
+        <v>761</v>
+      </c>
+      <c r="C81" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D81" s="37">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="34">
+        <v>81</v>
+      </c>
+      <c r="B82" s="35" t="s">
+        <v>423</v>
+      </c>
+      <c r="C82" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D82" s="37">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="30">
+        <v>82</v>
+      </c>
+      <c r="B83" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="C83" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D83" s="33">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="30">
+        <v>83</v>
+      </c>
+      <c r="B84" s="31" t="s">
+        <v>441</v>
+      </c>
+      <c r="C84" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D84" s="33">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="30">
+        <v>84</v>
+      </c>
+      <c r="B85" s="31" t="s">
+        <v>867</v>
+      </c>
+      <c r="C85" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D85" s="33">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="34">
+        <v>85</v>
+      </c>
+      <c r="B86" s="35" t="s">
+        <v>762</v>
+      </c>
+      <c r="C86" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D86" s="37">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="34">
+        <v>86</v>
+      </c>
+      <c r="B87" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="C87" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D87" s="37">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="34">
+        <v>87</v>
+      </c>
+      <c r="B88" s="35" t="s">
+        <v>467</v>
+      </c>
+      <c r="C88" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D88" s="37">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="30">
+        <v>88</v>
+      </c>
+      <c r="B89" s="31" t="s">
+        <v>868</v>
+      </c>
+      <c r="C89" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D89" s="33">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="34">
+        <v>89</v>
+      </c>
+      <c r="B90" s="35" t="s">
+        <v>764</v>
+      </c>
+      <c r="C90" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D90" s="37">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="30">
+        <v>90</v>
+      </c>
+      <c r="B91" s="31" t="s">
+        <v>869</v>
+      </c>
+      <c r="C91" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D91" s="33">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="34">
+        <v>91</v>
+      </c>
+      <c r="B92" s="35" t="s">
+        <v>351</v>
+      </c>
+      <c r="C92" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D92" s="37">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="30">
+        <v>92</v>
+      </c>
+      <c r="B93" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C93" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D93" s="33">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="30">
+        <v>93</v>
+      </c>
+      <c r="B94" s="31" t="s">
+        <v>872</v>
+      </c>
+      <c r="C94" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D94" s="33">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="34">
+        <v>94</v>
+      </c>
+      <c r="B95" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="C95" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D95" s="37">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="34">
+        <v>95</v>
+      </c>
+      <c r="B96" s="35" t="s">
+        <v>414</v>
+      </c>
+      <c r="C96" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D96" s="37">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="34">
+        <v>96</v>
+      </c>
+      <c r="B97" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C97" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D97" s="37">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="30">
+        <v>97</v>
+      </c>
+      <c r="B98" s="31" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C98" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D98" s="33">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="34">
+        <v>98</v>
+      </c>
+      <c r="B99" s="35" t="s">
+        <v>769</v>
+      </c>
+      <c r="C99" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D99" s="37">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="30">
+        <v>99</v>
+      </c>
+      <c r="B100" s="31" t="s">
+        <v>876</v>
+      </c>
+      <c r="C100" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D100" s="33">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="30">
+        <v>100</v>
+      </c>
+      <c r="B101" s="31" t="s">
+        <v>875</v>
+      </c>
+      <c r="C101" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D101" s="33">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="30">
+        <v>101</v>
+      </c>
+      <c r="B102" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="C102" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D102" s="33">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="30">
+        <v>102</v>
+      </c>
+      <c r="B103" s="31" t="s">
+        <v>874</v>
+      </c>
+      <c r="C103" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D103" s="33">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="34">
+        <v>103</v>
+      </c>
+      <c r="B104" s="35" t="s">
+        <v>770</v>
+      </c>
+      <c r="C104" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D104" s="37">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="34">
+        <v>104</v>
+      </c>
+      <c r="B105" s="35" t="s">
+        <v>771</v>
+      </c>
+      <c r="C105" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D105" s="37">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="30">
+        <v>105</v>
+      </c>
+      <c r="B106" s="31" t="s">
+        <v>878</v>
+      </c>
+      <c r="C106" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D106" s="33">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="34">
+        <v>106</v>
+      </c>
+      <c r="B107" s="35" t="s">
+        <v>772</v>
+      </c>
+      <c r="C107" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D107" s="37">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="34">
+        <v>107</v>
+      </c>
+      <c r="B108" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C108" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D108" s="37">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="30">
+        <v>108</v>
+      </c>
+      <c r="B109" s="31" t="s">
+        <v>549</v>
+      </c>
+      <c r="C109" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D109" s="33">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="30">
+        <v>109</v>
+      </c>
+      <c r="B110" s="31" t="s">
+        <v>881</v>
+      </c>
+      <c r="C110" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D110" s="33">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="30">
+        <v>110</v>
+      </c>
+      <c r="B111" s="31" t="s">
+        <v>883</v>
+      </c>
+      <c r="C111" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D111" s="33">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="34">
+        <v>111</v>
+      </c>
+      <c r="B112" s="35" t="s">
+        <v>773</v>
+      </c>
+      <c r="C112" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D112" s="37">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="30">
+        <v>112</v>
+      </c>
+      <c r="B113" s="31" t="s">
+        <v>884</v>
+      </c>
+      <c r="C113" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D113" s="33">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="30">
+        <v>113</v>
+      </c>
+      <c r="B114" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="C114" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D114" s="33">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="30">
+        <v>114</v>
+      </c>
+      <c r="B115" s="31" t="s">
+        <v>886</v>
+      </c>
+      <c r="C115" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D115" s="33">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="30">
+        <v>115</v>
+      </c>
+      <c r="B116" s="31" t="s">
+        <v>887</v>
+      </c>
+      <c r="C116" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D116" s="33">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" s="34">
+        <v>116</v>
+      </c>
+      <c r="B117" s="35" t="s">
+        <v>774</v>
+      </c>
+      <c r="C117" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D117" s="37">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="34">
+        <v>117</v>
+      </c>
+      <c r="B118" s="35" t="s">
+        <v>775</v>
+      </c>
+      <c r="C118" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D118" s="37">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="30">
+        <v>118</v>
+      </c>
+      <c r="B119" s="31" t="s">
+        <v>889</v>
+      </c>
+      <c r="C119" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D119" s="33">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="30">
+        <v>119</v>
+      </c>
+      <c r="B120" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="C120" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D120" s="33">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="30">
+        <v>120</v>
+      </c>
+      <c r="B121" s="31" t="s">
+        <v>891</v>
+      </c>
+      <c r="C121" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D121" s="33">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="34">
+        <v>121</v>
+      </c>
+      <c r="B122" s="35" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C122" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D122" s="37">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="34">
+        <v>122</v>
+      </c>
+      <c r="B123" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="C123" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D123" s="37">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="30">
+        <v>123</v>
+      </c>
+      <c r="B124" s="31" t="s">
+        <v>893</v>
+      </c>
+      <c r="C124" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D124" s="33">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" s="34">
+        <v>124</v>
+      </c>
+      <c r="B125" s="35" t="s">
+        <v>779</v>
+      </c>
+      <c r="C125" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D125" s="37">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" s="30">
+        <v>125</v>
+      </c>
+      <c r="B126" s="31" t="s">
+        <v>895</v>
+      </c>
+      <c r="C126" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D126" s="33">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" s="30">
+        <v>126</v>
+      </c>
+      <c r="B127" s="31" t="s">
+        <v>896</v>
+      </c>
+      <c r="C127" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D127" s="33">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" s="30">
+        <v>127</v>
+      </c>
+      <c r="B128" s="31" t="s">
+        <v>898</v>
+      </c>
+      <c r="C128" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D128" s="33">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" s="30">
+        <v>128</v>
+      </c>
+      <c r="B129" s="31" t="s">
+        <v>897</v>
+      </c>
+      <c r="C129" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D129" s="33">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" s="34">
+        <v>129</v>
+      </c>
+      <c r="B130" s="35" t="s">
+        <v>780</v>
+      </c>
+      <c r="C130" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D130" s="37">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" s="30">
+        <v>130</v>
+      </c>
+      <c r="B131" s="31" t="s">
+        <v>899</v>
+      </c>
+      <c r="C131" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D131" s="33">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="30">
+        <v>131</v>
+      </c>
+      <c r="B132" s="31" t="s">
+        <v>901</v>
+      </c>
+      <c r="C132" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D132" s="33">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="34">
+        <v>132</v>
+      </c>
+      <c r="B133" s="35" t="s">
+        <v>781</v>
+      </c>
+      <c r="C133" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D133" s="37">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="30">
+        <v>133</v>
+      </c>
+      <c r="B134" s="31" t="s">
+        <v>715</v>
+      </c>
+      <c r="C134" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D134" s="33">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="30">
+        <v>134</v>
+      </c>
+      <c r="B135" s="31" t="s">
+        <v>903</v>
+      </c>
+      <c r="C135" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D135" s="33">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" s="34">
+        <v>135</v>
+      </c>
+      <c r="B136" s="35" t="s">
+        <v>265</v>
+      </c>
+      <c r="C136" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D136" s="37">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="34">
+        <v>136</v>
+      </c>
+      <c r="B137" s="35" t="s">
+        <v>784</v>
+      </c>
+      <c r="C137" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D137" s="37">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" s="34">
+        <v>137</v>
+      </c>
+      <c r="B138" s="35" t="s">
+        <v>791</v>
+      </c>
+      <c r="C138" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D138" s="37">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="34">
+        <v>138</v>
+      </c>
+      <c r="B139" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C139" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D139" s="37">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="34">
+        <v>139</v>
+      </c>
+      <c r="B140" s="35" t="s">
+        <v>308</v>
+      </c>
+      <c r="C140" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D140" s="37">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="34">
+        <v>140</v>
+      </c>
+      <c r="B141" s="35" t="s">
+        <v>270</v>
+      </c>
+      <c r="C141" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D141" s="37">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="34">
+        <v>141</v>
+      </c>
+      <c r="B142" s="35" t="s">
+        <v>572</v>
+      </c>
+      <c r="C142" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D142" s="37">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="34">
+        <v>142</v>
+      </c>
+      <c r="B143" s="35" t="s">
+        <v>799</v>
+      </c>
+      <c r="C143" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D143" s="37">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="34">
+        <v>143</v>
+      </c>
+      <c r="B144" s="35" t="s">
+        <v>800</v>
+      </c>
+      <c r="C144" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D144" s="37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" s="30">
+        <v>144</v>
+      </c>
+      <c r="B145" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="C145" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D145" s="33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" s="34">
+        <v>145</v>
+      </c>
+      <c r="B146" s="35" t="s">
+        <v>804</v>
+      </c>
+      <c r="C146" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D146" s="37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" s="34">
+        <v>146</v>
+      </c>
+      <c r="B147" s="35" t="s">
+        <v>803</v>
+      </c>
+      <c r="C147" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D147" s="37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" s="34">
+        <v>147</v>
+      </c>
+      <c r="B148" s="35" t="s">
+        <v>614</v>
+      </c>
+      <c r="C148" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D148" s="37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" s="34">
+        <v>148</v>
+      </c>
+      <c r="B149" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="C149" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D149" s="37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" s="34">
+        <v>149</v>
+      </c>
+      <c r="B150" s="35" t="s">
+        <v>537</v>
+      </c>
+      <c r="C150" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D150" s="37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" s="34">
+        <v>150</v>
+      </c>
+      <c r="B151" s="35" t="s">
+        <v>460</v>
+      </c>
+      <c r="C151" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D151" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="34">
+        <v>151</v>
+      </c>
+      <c r="B152" s="35" t="s">
+        <v>812</v>
+      </c>
+      <c r="C152" s="36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D152" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" s="30">
+        <v>152</v>
+      </c>
+      <c r="B153" s="31" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C153" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D153" s="33">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -22993,7 +26616,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -24198,7 +27821,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -25537,1356 +29160,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FFFF0000"/>
-  </sheetPr>
-  <dimension ref="A1:E84"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="111.08984375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D1" t="s">
-        <v>904</v>
-      </c>
-      <c r="E1" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>906</v>
-      </c>
-      <c r="C2">
-        <v>474</v>
-      </c>
-      <c r="D2">
-        <v>520</v>
-      </c>
-      <c r="E2" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>908</v>
-      </c>
-      <c r="C3">
-        <v>311</v>
-      </c>
-      <c r="D3">
-        <v>292</v>
-      </c>
-      <c r="E3" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>910</v>
-      </c>
-      <c r="C4">
-        <v>251</v>
-      </c>
-      <c r="D4">
-        <v>277</v>
-      </c>
-      <c r="E4" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>912</v>
-      </c>
-      <c r="C5">
-        <v>238</v>
-      </c>
-      <c r="D5">
-        <v>439</v>
-      </c>
-      <c r="E5" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>913</v>
-      </c>
-      <c r="C6">
-        <v>234</v>
-      </c>
-      <c r="D6">
-        <v>347</v>
-      </c>
-      <c r="E6" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>915</v>
-      </c>
-      <c r="C7">
-        <v>228</v>
-      </c>
-      <c r="D7">
-        <v>550</v>
-      </c>
-      <c r="E7" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>916</v>
-      </c>
-      <c r="C8">
-        <v>227</v>
-      </c>
-      <c r="D8">
-        <v>329</v>
-      </c>
-      <c r="E8" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>918</v>
-      </c>
-      <c r="C9">
-        <v>221</v>
-      </c>
-      <c r="D9">
-        <v>353</v>
-      </c>
-      <c r="E9" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>920</v>
-      </c>
-      <c r="C10">
-        <v>219</v>
-      </c>
-      <c r="D10">
-        <v>448</v>
-      </c>
-      <c r="E10" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>922</v>
-      </c>
-      <c r="C11">
-        <v>212</v>
-      </c>
-      <c r="D11">
-        <v>278</v>
-      </c>
-      <c r="E11" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>924</v>
-      </c>
-      <c r="C12">
-        <v>204</v>
-      </c>
-      <c r="D12">
-        <v>557</v>
-      </c>
-      <c r="E12" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>926</v>
-      </c>
-      <c r="C13">
-        <v>195</v>
-      </c>
-      <c r="D13">
-        <v>231</v>
-      </c>
-      <c r="E13" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>928</v>
-      </c>
-      <c r="C14">
-        <v>186</v>
-      </c>
-      <c r="D14">
-        <v>352</v>
-      </c>
-      <c r="E14" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="B15" t="s">
-        <v>930</v>
-      </c>
-      <c r="C15">
-        <v>186</v>
-      </c>
-      <c r="D15">
-        <v>461</v>
-      </c>
-      <c r="E15" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>931</v>
-      </c>
-      <c r="C16">
-        <v>183</v>
-      </c>
-      <c r="D16">
-        <v>255</v>
-      </c>
-      <c r="E16" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>933</v>
-      </c>
-      <c r="C17">
-        <v>182</v>
-      </c>
-      <c r="D17">
-        <v>349</v>
-      </c>
-      <c r="E17" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>935</v>
-      </c>
-      <c r="C18">
-        <v>179</v>
-      </c>
-      <c r="D18">
-        <v>258</v>
-      </c>
-      <c r="E18" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>937</v>
-      </c>
-      <c r="C19">
-        <v>169</v>
-      </c>
-      <c r="D19">
-        <v>411</v>
-      </c>
-      <c r="E19" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>939</v>
-      </c>
-      <c r="C20">
-        <v>162</v>
-      </c>
-      <c r="D20">
-        <v>280</v>
-      </c>
-      <c r="E20" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>941</v>
-      </c>
-      <c r="C21">
-        <v>160</v>
-      </c>
-      <c r="D21">
-        <v>360</v>
-      </c>
-      <c r="E21" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>943</v>
-      </c>
-      <c r="C22">
-        <v>158</v>
-      </c>
-      <c r="D22">
-        <v>443</v>
-      </c>
-      <c r="E22" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>945</v>
-      </c>
-      <c r="C23">
-        <v>156</v>
-      </c>
-      <c r="D23">
-        <v>180</v>
-      </c>
-      <c r="E23" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>946</v>
-      </c>
-      <c r="C24">
-        <v>152</v>
-      </c>
-      <c r="D24">
-        <v>417</v>
-      </c>
-      <c r="E24" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>948</v>
-      </c>
-      <c r="C25">
-        <v>150</v>
-      </c>
-      <c r="D25">
-        <v>287</v>
-      </c>
-      <c r="E25" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>950</v>
-      </c>
-      <c r="C26">
-        <v>147</v>
-      </c>
-      <c r="D26">
-        <v>303</v>
-      </c>
-      <c r="E26" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
-        <v>951</v>
-      </c>
-      <c r="C27">
-        <v>146</v>
-      </c>
-      <c r="D27">
-        <v>407</v>
-      </c>
-      <c r="E27" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>953</v>
-      </c>
-      <c r="C28">
-        <v>140</v>
-      </c>
-      <c r="D28">
-        <v>283</v>
-      </c>
-      <c r="E28" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>955</v>
-      </c>
-      <c r="C29">
-        <v>139</v>
-      </c>
-      <c r="D29">
-        <v>199</v>
-      </c>
-      <c r="E29" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="B30" t="s">
-        <v>957</v>
-      </c>
-      <c r="C30">
-        <v>139</v>
-      </c>
-      <c r="D30">
-        <v>207</v>
-      </c>
-      <c r="E30" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="B31" t="s">
-        <v>958</v>
-      </c>
-      <c r="C31">
-        <v>139</v>
-      </c>
-      <c r="D31">
-        <v>484</v>
-      </c>
-      <c r="E31" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>960</v>
-      </c>
-      <c r="C32">
-        <v>138</v>
-      </c>
-      <c r="D32">
-        <v>215</v>
-      </c>
-      <c r="E32" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>962</v>
-      </c>
-      <c r="C33">
-        <v>136</v>
-      </c>
-      <c r="D33">
-        <v>326</v>
-      </c>
-      <c r="E33" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>963</v>
-      </c>
-      <c r="C34">
-        <v>133</v>
-      </c>
-      <c r="D34">
-        <v>297</v>
-      </c>
-      <c r="E34" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="B35" t="s">
-        <v>965</v>
-      </c>
-      <c r="C35">
-        <v>133</v>
-      </c>
-      <c r="D35">
-        <v>438</v>
-      </c>
-      <c r="E35" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>967</v>
-      </c>
-      <c r="C36">
-        <v>131</v>
-      </c>
-      <c r="D36">
-        <v>226</v>
-      </c>
-      <c r="E36" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s">
-        <v>969</v>
-      </c>
-      <c r="C37">
-        <v>130</v>
-      </c>
-      <c r="D37">
-        <v>323</v>
-      </c>
-      <c r="E37" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>971</v>
-      </c>
-      <c r="C38">
-        <v>129</v>
-      </c>
-      <c r="D38">
-        <v>305</v>
-      </c>
-      <c r="E38" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="B39" t="s">
-        <v>973</v>
-      </c>
-      <c r="C39">
-        <v>129</v>
-      </c>
-      <c r="D39">
-        <v>323</v>
-      </c>
-      <c r="E39" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="B40" t="s">
-        <v>975</v>
-      </c>
-      <c r="C40">
-        <v>129</v>
-      </c>
-      <c r="D40">
-        <v>337</v>
-      </c>
-      <c r="E40" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="B41" t="s">
-        <v>977</v>
-      </c>
-      <c r="C41">
-        <v>129</v>
-      </c>
-      <c r="D41">
-        <v>437</v>
-      </c>
-      <c r="E41" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="s">
-        <v>979</v>
-      </c>
-      <c r="C42">
-        <v>128</v>
-      </c>
-      <c r="D42">
-        <v>240</v>
-      </c>
-      <c r="E42" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="B43" t="s">
-        <v>981</v>
-      </c>
-      <c r="C43">
-        <v>128</v>
-      </c>
-      <c r="D43">
-        <v>244</v>
-      </c>
-      <c r="E43" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="B44" t="s">
-        <v>982</v>
-      </c>
-      <c r="C44">
-        <v>128</v>
-      </c>
-      <c r="D44">
-        <v>361</v>
-      </c>
-      <c r="E44" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
-        <v>984</v>
-      </c>
-      <c r="C45">
-        <v>127</v>
-      </c>
-      <c r="D45">
-        <v>204</v>
-      </c>
-      <c r="E45" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="s">
-        <v>986</v>
-      </c>
-      <c r="C46">
-        <v>126</v>
-      </c>
-      <c r="D46">
-        <v>222</v>
-      </c>
-      <c r="E46" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47">
-        <v>47</v>
-      </c>
-      <c r="B47" t="s">
-        <v>988</v>
-      </c>
-      <c r="C47">
-        <v>125</v>
-      </c>
-      <c r="D47">
-        <v>334</v>
-      </c>
-      <c r="E47" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="s">
-        <v>990</v>
-      </c>
-      <c r="C48">
-        <v>124</v>
-      </c>
-      <c r="D48">
-        <v>337</v>
-      </c>
-      <c r="E48" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="s">
-        <v>992</v>
-      </c>
-      <c r="C49">
-        <v>123</v>
-      </c>
-      <c r="D49">
-        <v>341</v>
-      </c>
-      <c r="E49" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="B50" t="s">
-        <v>993</v>
-      </c>
-      <c r="C50">
-        <v>123</v>
-      </c>
-      <c r="D50">
-        <v>417</v>
-      </c>
-      <c r="E50" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="s">
-        <v>994</v>
-      </c>
-      <c r="C51">
-        <v>119</v>
-      </c>
-      <c r="D51">
-        <v>229</v>
-      </c>
-      <c r="E51" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="B52" t="s">
-        <v>996</v>
-      </c>
-      <c r="C52">
-        <v>119</v>
-      </c>
-      <c r="D52">
-        <v>344</v>
-      </c>
-      <c r="E52" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="s">
-        <v>997</v>
-      </c>
-      <c r="C53">
-        <v>117</v>
-      </c>
-      <c r="D53">
-        <v>164</v>
-      </c>
-      <c r="E53" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="B54" t="s">
-        <v>999</v>
-      </c>
-      <c r="C54">
-        <v>117</v>
-      </c>
-      <c r="D54">
-        <v>380</v>
-      </c>
-      <c r="E54" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C55">
-        <v>115</v>
-      </c>
-      <c r="D55">
-        <v>216</v>
-      </c>
-      <c r="E55" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="B56" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C56">
-        <v>115</v>
-      </c>
-      <c r="D56">
-        <v>308</v>
-      </c>
-      <c r="E56" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C57">
-        <v>114</v>
-      </c>
-      <c r="D57">
-        <v>232</v>
-      </c>
-      <c r="E57" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="B58" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C58">
-        <v>114</v>
-      </c>
-      <c r="D58">
-        <v>239</v>
-      </c>
-      <c r="E58" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="B59" t="s">
-        <v>1008</v>
-      </c>
-      <c r="C59">
-        <v>114</v>
-      </c>
-      <c r="D59">
-        <v>338</v>
-      </c>
-      <c r="E59" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C60">
-        <v>112</v>
-      </c>
-      <c r="D60">
-        <v>418</v>
-      </c>
-      <c r="E60" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="B61" t="s">
-        <v>1012</v>
-      </c>
-      <c r="C61">
-        <v>112</v>
-      </c>
-      <c r="D61">
-        <v>609</v>
-      </c>
-      <c r="E61" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C62">
-        <v>111</v>
-      </c>
-      <c r="D62">
-        <v>314</v>
-      </c>
-      <c r="E62" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="B63" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C63">
-        <v>111</v>
-      </c>
-      <c r="D63">
-        <v>338</v>
-      </c>
-      <c r="E63" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="B64" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C64">
-        <v>111</v>
-      </c>
-      <c r="D64">
-        <v>381</v>
-      </c>
-      <c r="E64" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C65">
-        <v>109</v>
-      </c>
-      <c r="D65">
-        <v>241</v>
-      </c>
-      <c r="E65" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C66">
-        <v>108</v>
-      </c>
-      <c r="D66">
-        <v>118</v>
-      </c>
-      <c r="E66" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="B67" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C67">
-        <v>108</v>
-      </c>
-      <c r="D67">
-        <v>420</v>
-      </c>
-      <c r="E67" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C68">
-        <v>107</v>
-      </c>
-      <c r="D68">
-        <v>130</v>
-      </c>
-      <c r="E68" t="s">
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="B69" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C69">
-        <v>107</v>
-      </c>
-      <c r="D69">
-        <v>190</v>
-      </c>
-      <c r="E69" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="B70" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C70">
-        <v>107</v>
-      </c>
-      <c r="D70">
-        <v>198</v>
-      </c>
-      <c r="E70" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="B71" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C71">
-        <v>107</v>
-      </c>
-      <c r="D71">
-        <v>261</v>
-      </c>
-      <c r="E71" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="B72" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C72">
-        <v>107</v>
-      </c>
-      <c r="D72">
-        <v>276</v>
-      </c>
-      <c r="E72" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C73">
-        <v>105</v>
-      </c>
-      <c r="D73">
-        <v>90</v>
-      </c>
-      <c r="E73" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="B74" t="s">
-        <v>1034</v>
-      </c>
-      <c r="C74">
-        <v>105</v>
-      </c>
-      <c r="D74">
-        <v>263</v>
-      </c>
-      <c r="E74" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="B75" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C75">
-        <v>105</v>
-      </c>
-      <c r="D75">
-        <v>497</v>
-      </c>
-      <c r="E75" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C76">
-        <v>104</v>
-      </c>
-      <c r="D76">
-        <v>160</v>
-      </c>
-      <c r="E76" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77">
-        <v>76</v>
-      </c>
-      <c r="B77" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C77">
-        <v>103</v>
-      </c>
-      <c r="D77">
-        <v>265</v>
-      </c>
-      <c r="E77" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="B78" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C78">
-        <v>103</v>
-      </c>
-      <c r="D78">
-        <v>400</v>
-      </c>
-      <c r="E78" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79">
-        <v>78</v>
-      </c>
-      <c r="B79" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C79">
-        <v>102</v>
-      </c>
-      <c r="D79">
-        <v>157</v>
-      </c>
-      <c r="E79" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="B80" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C80">
-        <v>102</v>
-      </c>
-      <c r="D80">
-        <v>281</v>
-      </c>
-      <c r="E80" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="B81" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C81">
-        <v>102</v>
-      </c>
-      <c r="D81">
-        <v>363</v>
-      </c>
-      <c r="E81" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82">
-        <v>81</v>
-      </c>
-      <c r="B82" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C82">
-        <v>101</v>
-      </c>
-      <c r="D82">
-        <v>141</v>
-      </c>
-      <c r="E82" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="B83" t="s">
-        <v>1050</v>
-      </c>
-      <c r="C83">
-        <v>101</v>
-      </c>
-      <c r="D83">
-        <v>372</v>
-      </c>
-      <c r="E83" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84">
-        <v>83</v>
-      </c>
-      <c r="B84" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C84">
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Stats For Rush.xlsx
+++ b/Stats For Rush.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurtl\Desktop\statstreaks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D55A820-FD6C-4D15-A96C-F678CCD2D96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A1C62E-A7FF-4EEF-8EC9-2294976D08E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="866" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="PL Appearances" sheetId="3" r:id="rId3"/>
     <sheet name="Intl Appearances" sheetId="4" r:id="rId4"/>
     <sheet name="Intl Goals" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="11" r:id="rId6"/>
+    <sheet name="Man and liv g" sheetId="11" r:id="rId6"/>
     <sheet name="Man U goals" sheetId="6" r:id="rId7"/>
     <sheet name="Liverpool goals" sheetId="7" r:id="rId8"/>
     <sheet name="Champs league goals" sheetId="9" r:id="rId9"/>
@@ -23474,6 +23474,9 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28830BBA-01E9-4290-8134-6C4FA2F187F1}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:D153"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>

--- a/Stats For Rush.xlsx
+++ b/Stats For Rush.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurtl\Desktop\statstreaks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A1C62E-A7FF-4EEF-8EC9-2294976D08E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61A61AE-4099-48C4-ACAF-97DB6461C71F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="866" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" tabRatio="866" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PL assists" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,26 @@
     <sheet name="Intl Appearances" sheetId="4" r:id="rId4"/>
     <sheet name="Intl Goals" sheetId="5" r:id="rId5"/>
     <sheet name="Man and liv g" sheetId="11" r:id="rId6"/>
-    <sheet name="Man U goals" sheetId="6" r:id="rId7"/>
-    <sheet name="Liverpool goals" sheetId="7" r:id="rId8"/>
-    <sheet name="Champs league goals" sheetId="9" r:id="rId9"/>
-    <sheet name="La Liga goals" sheetId="8" r:id="rId10"/>
-    <sheet name="Transfers" sheetId="10" r:id="rId11"/>
+    <sheet name="Arsenalspurs goals" sheetId="12" r:id="rId7"/>
+    <sheet name="Man U goals" sheetId="6" r:id="rId8"/>
+    <sheet name="Liverpool goals" sheetId="7" r:id="rId9"/>
+    <sheet name="Champs league goals" sheetId="9" r:id="rId10"/>
+    <sheet name="La Liga goals" sheetId="8" r:id="rId11"/>
+    <sheet name="Transfers" sheetId="10" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -35,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2994" uniqueCount="1223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3223" uniqueCount="1276">
   <si>
     <t>Rank</t>
   </si>
@@ -3704,6 +3716,165 @@
   </si>
   <si>
     <t>Alisson</t>
+  </si>
+  <si>
+    <t>Robert Pirés</t>
+  </si>
+  <si>
+    <t>Tony Adams</t>
+  </si>
+  <si>
+    <t>Nicklas Bendtner</t>
+  </si>
+  <si>
+    <t>Nwankwo Kanu</t>
+  </si>
+  <si>
+    <t>Marc Overmars</t>
+  </si>
+  <si>
+    <t>Eddie Nketiah</t>
+  </si>
+  <si>
+    <t>Andrey Arshavin</t>
+  </si>
+  <si>
+    <t>Santi Cazorla</t>
+  </si>
+  <si>
+    <t>Nicolas Pépé</t>
+  </si>
+  <si>
+    <t>Laurent Koscielny</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Jimmy Greaves</t>
+  </si>
+  <si>
+    <t>Heung-min Son</t>
+  </si>
+  <si>
+    <t>Glenn Hoddle</t>
+  </si>
+  <si>
+    <t>Garth Crooks</t>
+  </si>
+  <si>
+    <t>Martin Peters</t>
+  </si>
+  <si>
+    <t>Steffen Iversen</t>
+  </si>
+  <si>
+    <t>Chris Waddle</t>
+  </si>
+  <si>
+    <t>Lucas Moura</t>
+  </si>
+  <si>
+    <t>Érik Lamela</t>
+  </si>
+  <si>
+    <t>Paul Gascoigne</t>
+  </si>
+  <si>
+    <t>Jermaine Jenas</t>
+  </si>
+  <si>
+    <t>Nacer Chadli</t>
+  </si>
+  <si>
+    <t>Dejan Kulusevski</t>
+  </si>
+  <si>
+    <t>Frédéric Kanouté</t>
+  </si>
+  <si>
+    <t>Alf Ramsey</t>
+  </si>
+  <si>
+    <t>Osvaldo Ardiles</t>
+  </si>
+  <si>
+    <t>Gilberto Silva</t>
+  </si>
+  <si>
+    <t>Jose Antonio Reyes</t>
+  </si>
+  <si>
+    <t>Abou Diaby</t>
+  </si>
+  <si>
+    <t>Emile Smith Rowe</t>
+  </si>
+  <si>
+    <t>Jack Wilshere</t>
+  </si>
+  <si>
+    <t>Kolo Toure</t>
+  </si>
+  <si>
+    <t>Mathieu Flamini</t>
+  </si>
+  <si>
+    <t>Gervinho</t>
+  </si>
+  <si>
+    <t>Emmanuel Petit</t>
+  </si>
+  <si>
+    <t>Julio Baptista</t>
+  </si>
+  <si>
+    <t>Emmanuel Eboue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashley Cole </t>
+  </si>
+  <si>
+    <t>Bacary Sagna</t>
+  </si>
+  <si>
+    <t>Luka Modric</t>
+  </si>
+  <si>
+    <t>Roberto Soldado</t>
+  </si>
+  <si>
+    <t>Ledley King</t>
+  </si>
+  <si>
+    <t>Fernando Llorente</t>
+  </si>
+  <si>
+    <t>Eric Dier</t>
+  </si>
+  <si>
+    <t>Niko Kranjcar</t>
+  </si>
+  <si>
+    <t>Giovani Lo Celso</t>
+  </si>
+  <si>
+    <t>Pierre-Emile Hojbjerg</t>
+  </si>
+  <si>
+    <t>Michael Dawson</t>
+  </si>
+  <si>
+    <t>Jamie O'Hara</t>
+  </si>
+  <si>
+    <t>Moussa Sissoko</t>
+  </si>
+  <si>
+    <t>Ryan Mason</t>
+  </si>
+  <si>
+    <t>Jonathan Woodgate</t>
   </si>
 </sst>
 </file>
@@ -4090,6 +4261,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{BAB16F13-4D5B-4E4F-A69F-0A941D92DCFA}" name="Table4" displayName="Table4" ref="B2:D115" totalsRowShown="0">
+  <autoFilter ref="B2:D115" xr:uid="{BAB16F13-4D5B-4E4F-A69F-0A941D92DCFA}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{F1356686-7060-40BA-994C-5FF59CF1C54C}" name="Player"/>
+    <tableColumn id="2" xr3:uid="{B9E60B2B-4F34-4D3B-98A4-11740A30000B}" name="Goals"/>
+    <tableColumn id="3" xr3:uid="{855F4929-63A2-4087-AB7C-91DA651C0DCD}" name="Team"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:B121" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A1:B121" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B101">
@@ -4103,7 +4286,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:B200" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
   <autoFilter ref="A1:B200" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="2">
@@ -4114,7 +4297,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table3" displayName="Table3" ref="A1:C120" totalsRowShown="0">
   <autoFilter ref="A1:C120" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C120">
@@ -8498,6 +8681,1347 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="A1:C120"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="29.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.54296875" customWidth="1"/>
+    <col min="3" max="3" width="110.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2">
+        <v>140</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>486</v>
+      </c>
+      <c r="B3">
+        <v>129</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>492</v>
+      </c>
+      <c r="B4">
+        <v>109</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>616</v>
+      </c>
+      <c r="B5">
+        <v>90</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>598</v>
+      </c>
+      <c r="B6">
+        <v>71</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B7">
+        <v>69</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8">
+        <v>57</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B9">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B14">
+        <v>49</v>
+      </c>
+      <c r="C14" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B15">
+        <v>48</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>535</v>
+      </c>
+      <c r="B16">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B17">
+        <v>46</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>720</v>
+      </c>
+      <c r="B18">
+        <v>46</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>511</v>
+      </c>
+      <c r="B20">
+        <v>44</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B21">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>627</v>
+      </c>
+      <c r="B22">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B24">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>513</v>
+      </c>
+      <c r="B25">
+        <v>35</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B26">
+        <v>34</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B27">
+        <v>34</v>
+      </c>
+      <c r="C27" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>715</v>
+      </c>
+      <c r="B28">
+        <v>33</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>681</v>
+      </c>
+      <c r="B29">
+        <v>31</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B30">
+        <v>30</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31">
+        <v>30</v>
+      </c>
+      <c r="C31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B32">
+        <v>30</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B33">
+        <v>30</v>
+      </c>
+      <c r="C33" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>688</v>
+      </c>
+      <c r="B34">
+        <v>29</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B35">
+        <v>29</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>677</v>
+      </c>
+      <c r="B36">
+        <v>29</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B37">
+        <v>29</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>680</v>
+      </c>
+      <c r="B38">
+        <v>29</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>697</v>
+      </c>
+      <c r="B39">
+        <v>28</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40">
+        <v>28</v>
+      </c>
+      <c r="C40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B41">
+        <v>27</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>200</v>
+      </c>
+      <c r="B42">
+        <v>27</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>686</v>
+      </c>
+      <c r="B43">
+        <v>27</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44">
+        <v>27</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>695</v>
+      </c>
+      <c r="B45">
+        <v>26</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>132</v>
+      </c>
+      <c r="B46">
+        <v>26</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B47">
+        <v>26</v>
+      </c>
+      <c r="C47" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B48">
+        <v>25</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>74</v>
+      </c>
+      <c r="B49">
+        <v>25</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>685</v>
+      </c>
+      <c r="B50">
+        <v>25</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>682</v>
+      </c>
+      <c r="B51">
+        <v>25</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>74</v>
+      </c>
+      <c r="B52">
+        <v>25</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B53">
+        <v>25</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>804</v>
+      </c>
+      <c r="B54">
+        <v>24</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B55">
+        <v>24</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B56">
+        <v>24</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B57">
+        <v>24</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58">
+        <v>24</v>
+      </c>
+      <c r="C58" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>184</v>
+      </c>
+      <c r="B59">
+        <v>24</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>14</v>
+      </c>
+      <c r="B60">
+        <v>23</v>
+      </c>
+      <c r="C60" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B61">
+        <v>23</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>75</v>
+      </c>
+      <c r="B62">
+        <v>22</v>
+      </c>
+      <c r="C62" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B63">
+        <v>21</v>
+      </c>
+      <c r="C63" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B64">
+        <v>21</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B65">
+        <v>21</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B66">
+        <v>21</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B67">
+        <v>20</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>237</v>
+      </c>
+      <c r="B68">
+        <v>20</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>48</v>
+      </c>
+      <c r="B69">
+        <v>20</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B70">
+        <v>20</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B71">
+        <v>20</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>152</v>
+      </c>
+      <c r="B72">
+        <v>19</v>
+      </c>
+      <c r="C72" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B73">
+        <v>19</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B74">
+        <v>19</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B75">
+        <v>19</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B76">
+        <v>18</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B77">
+        <v>18</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>611</v>
+      </c>
+      <c r="B78">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B79">
+        <v>18</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>800</v>
+      </c>
+      <c r="B80">
+        <v>17</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B81">
+        <v>17</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B82">
+        <v>17</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
+        <v>487</v>
+      </c>
+      <c r="B83">
+        <v>17</v>
+      </c>
+      <c r="C83" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
+        <v>24</v>
+      </c>
+      <c r="B84">
+        <v>16</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B85">
+        <v>16</v>
+      </c>
+      <c r="C85" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>673</v>
+      </c>
+      <c r="B86">
+        <v>16</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>532</v>
+      </c>
+      <c r="B87">
+        <v>16</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B88">
+        <v>15</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B89">
+        <v>15</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B90">
+        <v>15</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>573</v>
+      </c>
+      <c r="B91">
+        <v>14</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
+        <v>658</v>
+      </c>
+      <c r="B92">
+        <v>14</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>510</v>
+      </c>
+      <c r="B93">
+        <v>14</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>609</v>
+      </c>
+      <c r="B94">
+        <v>14</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>57</v>
+      </c>
+      <c r="B95">
+        <v>13</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B96">
+        <v>13</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B97">
+        <v>13</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B98">
+        <v>13</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
+        <v>527</v>
+      </c>
+      <c r="B99">
+        <v>12</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" t="s">
+        <v>515</v>
+      </c>
+      <c r="B100">
+        <v>12</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
+        <v>517</v>
+      </c>
+      <c r="B101">
+        <v>12</v>
+      </c>
+      <c r="C101" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" t="s">
+        <v>141</v>
+      </c>
+      <c r="B102">
+        <v>12</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B103">
+        <v>11</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B104">
+        <v>11</v>
+      </c>
+      <c r="C104" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" t="s">
+        <v>650</v>
+      </c>
+      <c r="B105">
+        <v>11</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" t="s">
+        <v>172</v>
+      </c>
+      <c r="B106">
+        <v>11</v>
+      </c>
+      <c r="C106" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" t="s">
+        <v>316</v>
+      </c>
+      <c r="B107">
+        <v>10</v>
+      </c>
+      <c r="C107" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" t="s">
+        <v>69</v>
+      </c>
+      <c r="B108">
+        <v>10</v>
+      </c>
+      <c r="C108" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B109">
+        <v>10</v>
+      </c>
+      <c r="C109" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B110">
+        <v>10</v>
+      </c>
+      <c r="C110" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
+        <v>566</v>
+      </c>
+      <c r="B111">
+        <v>9</v>
+      </c>
+      <c r="C111" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B112">
+        <v>9</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B113">
+        <v>9</v>
+      </c>
+      <c r="C113" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
+        <v>655</v>
+      </c>
+      <c r="B114">
+        <v>9</v>
+      </c>
+      <c r="C114" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
+        <v>59</v>
+      </c>
+      <c r="B115">
+        <v>8</v>
+      </c>
+      <c r="C115" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B116">
+        <v>8</v>
+      </c>
+      <c r="C116" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B117">
+        <v>8</v>
+      </c>
+      <c r="C117" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B118">
+        <v>8</v>
+      </c>
+      <c r="C118" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119">
+        <v>7</v>
+      </c>
+      <c r="C119" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" t="s">
+        <v>229</v>
+      </c>
+      <c r="B120">
+        <v>7</v>
+      </c>
+      <c r="C120" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -9849,7 +11373,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -25628,6 +27152,1277 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98F72596-567D-4A46-9580-D5E8D1461B30}">
+  <dimension ref="B2:D115"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3">
+        <v>229</v>
+      </c>
+      <c r="D3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="B4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4">
+        <v>185</v>
+      </c>
+      <c r="D4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5">
+        <v>132</v>
+      </c>
+      <c r="D5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>120</v>
+      </c>
+      <c r="D6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="B7" t="s">
+        <v>265</v>
+      </c>
+      <c r="C7">
+        <v>115</v>
+      </c>
+      <c r="D7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8">
+        <v>108</v>
+      </c>
+      <c r="D8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="B9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9">
+        <v>105</v>
+      </c>
+      <c r="D9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10">
+        <v>98</v>
+      </c>
+      <c r="D10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="B11" t="s">
+        <v>197</v>
+      </c>
+      <c r="C11">
+        <v>92</v>
+      </c>
+      <c r="D11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="B12" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C12">
+        <v>84</v>
+      </c>
+      <c r="D12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="B13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C13">
+        <v>80</v>
+      </c>
+      <c r="D13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="B14" t="s">
+        <v>255</v>
+      </c>
+      <c r="C14">
+        <v>72</v>
+      </c>
+      <c r="D14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="B15" t="s">
+        <v>230</v>
+      </c>
+      <c r="C15">
+        <v>71</v>
+      </c>
+      <c r="D15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="B16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16">
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" t="s">
+        <v>165</v>
+      </c>
+      <c r="C17">
+        <v>62</v>
+      </c>
+      <c r="D17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C18">
+        <v>59</v>
+      </c>
+      <c r="D18" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19">
+        <v>57</v>
+      </c>
+      <c r="D19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" t="s">
+        <v>718</v>
+      </c>
+      <c r="C20">
+        <v>49</v>
+      </c>
+      <c r="D20" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C21">
+        <v>48</v>
+      </c>
+      <c r="D21" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C22">
+        <v>46</v>
+      </c>
+      <c r="D22" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C23">
+        <v>44</v>
+      </c>
+      <c r="D23" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24">
+        <v>44</v>
+      </c>
+      <c r="D24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C25">
+        <v>40</v>
+      </c>
+      <c r="D25" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C26">
+        <v>38</v>
+      </c>
+      <c r="D26" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27" t="s">
+        <v>275</v>
+      </c>
+      <c r="C27">
+        <v>32</v>
+      </c>
+      <c r="D27" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="B28" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="B29" t="s">
+        <v>371</v>
+      </c>
+      <c r="C29">
+        <v>32</v>
+      </c>
+      <c r="D29" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="B30" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C30">
+        <v>31</v>
+      </c>
+      <c r="D30" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="B31" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C31">
+        <v>31</v>
+      </c>
+      <c r="D31" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="B32" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C32">
+        <v>29</v>
+      </c>
+      <c r="D32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="B33" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33">
+        <v>28</v>
+      </c>
+      <c r="D33" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34" t="s">
+        <v>587</v>
+      </c>
+      <c r="C34">
+        <v>28</v>
+      </c>
+      <c r="D34" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35" t="s">
+        <v>473</v>
+      </c>
+      <c r="C35">
+        <v>27</v>
+      </c>
+      <c r="D35" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C36">
+        <v>27</v>
+      </c>
+      <c r="D36" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37" t="s">
+        <v>130</v>
+      </c>
+      <c r="C37">
+        <v>27</v>
+      </c>
+      <c r="D37" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="B38" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C38">
+        <v>27</v>
+      </c>
+      <c r="D38" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" s="28" customFormat="1">
+      <c r="B39" s="28" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C39" s="28">
+        <v>26</v>
+      </c>
+      <c r="D39" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" s="28" customFormat="1">
+      <c r="B40" s="28" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C40" s="28">
+        <v>23</v>
+      </c>
+      <c r="D40" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" s="28" customFormat="1">
+      <c r="B41" s="28" t="s">
+        <v>508</v>
+      </c>
+      <c r="C41" s="28">
+        <v>23</v>
+      </c>
+      <c r="D41" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" s="28" customFormat="1">
+      <c r="B42" s="28" t="s">
+        <v>884</v>
+      </c>
+      <c r="C42" s="28">
+        <v>20</v>
+      </c>
+      <c r="D42" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" s="28" customFormat="1">
+      <c r="B43" s="28" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C43" s="28">
+        <v>19</v>
+      </c>
+      <c r="D43" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" s="28" customFormat="1">
+      <c r="B44" s="28" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C44" s="28">
+        <v>18</v>
+      </c>
+      <c r="D44" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" s="28" customFormat="1">
+      <c r="B45" s="28" t="s">
+        <v>439</v>
+      </c>
+      <c r="C45" s="28">
+        <v>17</v>
+      </c>
+      <c r="D45" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" s="28" customFormat="1">
+      <c r="B46" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="C46" s="28">
+        <v>16</v>
+      </c>
+      <c r="D46" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" s="28" customFormat="1">
+      <c r="B47" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C47" s="28">
+        <v>15</v>
+      </c>
+      <c r="D47" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" s="28" customFormat="1">
+      <c r="B48" s="28" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C48" s="28">
+        <v>14</v>
+      </c>
+      <c r="D48" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" s="28" customFormat="1">
+      <c r="B49" s="28" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C49" s="28">
+        <v>14</v>
+      </c>
+      <c r="D49" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" s="28" customFormat="1">
+      <c r="B50" s="28" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C50" s="28">
+        <v>13</v>
+      </c>
+      <c r="D50" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" s="28" customFormat="1">
+      <c r="B51" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="C51" s="28">
+        <v>12</v>
+      </c>
+      <c r="D51" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" s="28" customFormat="1">
+      <c r="B52" s="28" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C52" s="28">
+        <v>11</v>
+      </c>
+      <c r="D52" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" s="28" customFormat="1">
+      <c r="B53" s="28" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C53" s="28">
+        <v>11</v>
+      </c>
+      <c r="D53" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" s="28" customFormat="1">
+      <c r="B54" s="28" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C54" s="28">
+        <v>10</v>
+      </c>
+      <c r="D54" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" s="28" customFormat="1">
+      <c r="B55" s="28" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C55" s="28">
+        <v>10</v>
+      </c>
+      <c r="D55" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" s="28" customFormat="1">
+      <c r="B56" s="28" t="s">
+        <v>593</v>
+      </c>
+      <c r="C56" s="28">
+        <v>10</v>
+      </c>
+      <c r="D56" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" s="28" customFormat="1">
+      <c r="B57" s="28" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C57" s="28">
+        <v>9</v>
+      </c>
+      <c r="D57" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" s="28" customFormat="1">
+      <c r="B58" s="28" t="s">
+        <v>434</v>
+      </c>
+      <c r="C58" s="28">
+        <v>8</v>
+      </c>
+      <c r="D58" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" s="28" customFormat="1">
+      <c r="B59" s="28" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C59" s="28">
+        <v>5</v>
+      </c>
+      <c r="D59" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" s="28" customFormat="1">
+      <c r="B60" s="28" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C60" s="28">
+        <v>4</v>
+      </c>
+      <c r="D60" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="B61" t="s">
+        <v>99</v>
+      </c>
+      <c r="C61">
+        <v>280</v>
+      </c>
+      <c r="D61" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4">
+      <c r="B62" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C62">
+        <v>266</v>
+      </c>
+      <c r="D62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4">
+      <c r="B63" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C63">
+        <v>173</v>
+      </c>
+      <c r="D63" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="B64" t="s">
+        <v>171</v>
+      </c>
+      <c r="C64">
+        <v>143</v>
+      </c>
+      <c r="D64" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4">
+      <c r="B65" t="s">
+        <v>28</v>
+      </c>
+      <c r="C65">
+        <v>125</v>
+      </c>
+      <c r="D65" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4">
+      <c r="B66" t="s">
+        <v>138</v>
+      </c>
+      <c r="C66">
+        <v>122</v>
+      </c>
+      <c r="D66" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4">
+      <c r="B67" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C67">
+        <v>85</v>
+      </c>
+      <c r="D67" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4">
+      <c r="B68" t="s">
+        <v>665</v>
+      </c>
+      <c r="C68">
+        <v>80</v>
+      </c>
+      <c r="D68" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4">
+      <c r="B69" t="s">
+        <v>237</v>
+      </c>
+      <c r="C69">
+        <v>72</v>
+      </c>
+      <c r="D69" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="B70" t="s">
+        <v>25</v>
+      </c>
+      <c r="C70">
+        <v>69</v>
+      </c>
+      <c r="D70" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4">
+      <c r="B71" t="s">
+        <v>247</v>
+      </c>
+      <c r="C71">
+        <v>67</v>
+      </c>
+      <c r="D71" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="B72" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C72">
+        <v>61</v>
+      </c>
+      <c r="D72" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="B73" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C73">
+        <v>59</v>
+      </c>
+      <c r="D73" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4">
+      <c r="B74" t="s">
+        <v>37</v>
+      </c>
+      <c r="C74">
+        <v>49</v>
+      </c>
+      <c r="D74" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4">
+      <c r="B75" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C75">
+        <v>47</v>
+      </c>
+      <c r="D75" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4">
+      <c r="B76" t="s">
+        <v>127</v>
+      </c>
+      <c r="C76">
+        <v>46</v>
+      </c>
+      <c r="D76" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4">
+      <c r="B77" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C77">
+        <v>43</v>
+      </c>
+      <c r="D77" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4">
+      <c r="B78" t="s">
+        <v>165</v>
+      </c>
+      <c r="C78">
+        <v>42</v>
+      </c>
+      <c r="D78" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4">
+      <c r="B79" t="s">
+        <v>733</v>
+      </c>
+      <c r="C79">
+        <v>42</v>
+      </c>
+      <c r="D79" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4">
+      <c r="B80" t="s">
+        <v>86</v>
+      </c>
+      <c r="C80">
+        <v>39</v>
+      </c>
+      <c r="D80" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4">
+      <c r="B81" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C81">
+        <v>39</v>
+      </c>
+      <c r="D81" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4">
+      <c r="B82" t="s">
+        <v>577</v>
+      </c>
+      <c r="C82">
+        <v>38</v>
+      </c>
+      <c r="D82" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4">
+      <c r="B83" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C83">
+        <v>37</v>
+      </c>
+      <c r="D83" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4">
+      <c r="B84" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C84">
+        <v>33</v>
+      </c>
+      <c r="D84" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4">
+      <c r="B85" t="s">
+        <v>80</v>
+      </c>
+      <c r="C85">
+        <v>30</v>
+      </c>
+      <c r="D85" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4">
+      <c r="B86" t="s">
+        <v>566</v>
+      </c>
+      <c r="C86">
+        <v>28</v>
+      </c>
+      <c r="D86" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4">
+      <c r="B87" t="s">
+        <v>79</v>
+      </c>
+      <c r="C87">
+        <v>27</v>
+      </c>
+      <c r="D87" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4">
+      <c r="B88" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C88">
+        <v>26</v>
+      </c>
+      <c r="D88" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4">
+      <c r="B89" t="s">
+        <v>175</v>
+      </c>
+      <c r="C89">
+        <v>25</v>
+      </c>
+      <c r="D89" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4">
+      <c r="B90" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C90">
+        <v>25</v>
+      </c>
+      <c r="D90" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4">
+      <c r="B91" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C91">
+        <v>25</v>
+      </c>
+      <c r="D91" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4">
+      <c r="B92" t="s">
+        <v>57</v>
+      </c>
+      <c r="C92">
+        <v>24</v>
+      </c>
+      <c r="D92" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4">
+      <c r="B93" t="s">
+        <v>233</v>
+      </c>
+      <c r="C93">
+        <v>23</v>
+      </c>
+      <c r="D93" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4">
+      <c r="B94" t="s">
+        <v>123</v>
+      </c>
+      <c r="C94">
+        <v>21</v>
+      </c>
+      <c r="D94" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4">
+      <c r="B95" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C95">
+        <v>21</v>
+      </c>
+      <c r="D95" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4">
+      <c r="B96" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C96">
+        <v>20</v>
+      </c>
+      <c r="D96" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4">
+      <c r="B97" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C97">
+        <v>19</v>
+      </c>
+      <c r="D97" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4">
+      <c r="B98" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C98">
+        <v>17</v>
+      </c>
+      <c r="D98" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4">
+      <c r="B99" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C99">
+        <v>16</v>
+      </c>
+      <c r="D99" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4">
+      <c r="B100" t="s">
+        <v>312</v>
+      </c>
+      <c r="C100">
+        <v>15</v>
+      </c>
+      <c r="D100" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4">
+      <c r="B101" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C101">
+        <v>14</v>
+      </c>
+      <c r="D101" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4">
+      <c r="B102" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C102">
+        <v>13</v>
+      </c>
+      <c r="D102" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4">
+      <c r="B103" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C103">
+        <v>13</v>
+      </c>
+      <c r="D103" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4">
+      <c r="B104" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C104">
+        <v>11</v>
+      </c>
+      <c r="D104" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4">
+      <c r="B105" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C105">
+        <v>10</v>
+      </c>
+      <c r="D105" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4">
+      <c r="B106" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C106">
+        <v>10</v>
+      </c>
+      <c r="D106" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4">
+      <c r="B107" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C107">
+        <v>10</v>
+      </c>
+      <c r="D107" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4">
+      <c r="B108" t="s">
+        <v>526</v>
+      </c>
+      <c r="C108">
+        <v>9</v>
+      </c>
+      <c r="D108" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4">
+      <c r="B109" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C109">
+        <v>7</v>
+      </c>
+      <c r="D109" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4">
+      <c r="B110" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C110">
+        <v>5</v>
+      </c>
+      <c r="D110" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4">
+      <c r="B111" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C111">
+        <v>4</v>
+      </c>
+      <c r="D111" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4">
+      <c r="B112" t="s">
+        <v>144</v>
+      </c>
+      <c r="C112">
+        <v>4</v>
+      </c>
+      <c r="D112" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4">
+      <c r="B113" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C113">
+        <v>3</v>
+      </c>
+      <c r="D113" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4">
+      <c r="B114" t="s">
+        <v>131</v>
+      </c>
+      <c r="C114">
+        <v>2</v>
+      </c>
+      <c r="D114" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4">
+      <c r="B115" t="s">
+        <v>135</v>
+      </c>
+      <c r="C115">
+        <v>2</v>
+      </c>
+      <c r="D115" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -26619,7 +29414,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -27822,1345 +30617,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FFFFC000"/>
-  </sheetPr>
-  <dimension ref="A1:C120"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" width="29.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.54296875" customWidth="1"/>
-    <col min="3" max="3" width="110.90625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B2">
-        <v>140</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>486</v>
-      </c>
-      <c r="B3">
-        <v>129</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>492</v>
-      </c>
-      <c r="B4">
-        <v>109</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>616</v>
-      </c>
-      <c r="B5">
-        <v>90</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>598</v>
-      </c>
-      <c r="B6">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>1186</v>
-      </c>
-      <c r="B7">
-        <v>69</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>174</v>
-      </c>
-      <c r="B8">
-        <v>57</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>1187</v>
-      </c>
-      <c r="B9">
-        <v>57</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B10">
-        <v>56</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B11">
-        <v>51</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12">
-        <v>50</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13">
-        <v>50</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>1188</v>
-      </c>
-      <c r="B14">
-        <v>49</v>
-      </c>
-      <c r="C14" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>1189</v>
-      </c>
-      <c r="B15">
-        <v>48</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>535</v>
-      </c>
-      <c r="B16">
-        <v>48</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B17">
-        <v>46</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>720</v>
-      </c>
-      <c r="B18">
-        <v>46</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>66</v>
-      </c>
-      <c r="B19">
-        <v>44</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>511</v>
-      </c>
-      <c r="B20">
-        <v>44</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>1191</v>
-      </c>
-      <c r="B21">
-        <v>43</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>627</v>
-      </c>
-      <c r="B22">
-        <v>42</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>96</v>
-      </c>
-      <c r="B23">
-        <v>41</v>
-      </c>
-      <c r="C23" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>1192</v>
-      </c>
-      <c r="B24">
-        <v>36</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>513</v>
-      </c>
-      <c r="B25">
-        <v>35</v>
-      </c>
-      <c r="C25" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>1193</v>
-      </c>
-      <c r="B26">
-        <v>34</v>
-      </c>
-      <c r="C26" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B27">
-        <v>34</v>
-      </c>
-      <c r="C27" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>715</v>
-      </c>
-      <c r="B28">
-        <v>33</v>
-      </c>
-      <c r="C28" t="s">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>681</v>
-      </c>
-      <c r="B29">
-        <v>31</v>
-      </c>
-      <c r="C29" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>1195</v>
-      </c>
-      <c r="B30">
-        <v>30</v>
-      </c>
-      <c r="C30" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31">
-        <v>30</v>
-      </c>
-      <c r="C31" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>1196</v>
-      </c>
-      <c r="B32">
-        <v>30</v>
-      </c>
-      <c r="C32" t="s">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>1197</v>
-      </c>
-      <c r="B33">
-        <v>30</v>
-      </c>
-      <c r="C33" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
-        <v>688</v>
-      </c>
-      <c r="B34">
-        <v>29</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1079</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>1198</v>
-      </c>
-      <c r="B35">
-        <v>29</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
-        <v>677</v>
-      </c>
-      <c r="B36">
-        <v>29</v>
-      </c>
-      <c r="C36" t="s">
-        <v>1081</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
-        <v>1199</v>
-      </c>
-      <c r="B37">
-        <v>29</v>
-      </c>
-      <c r="C37" t="s">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
-        <v>680</v>
-      </c>
-      <c r="B38">
-        <v>29</v>
-      </c>
-      <c r="C38" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" t="s">
-        <v>697</v>
-      </c>
-      <c r="B39">
-        <v>28</v>
-      </c>
-      <c r="C39" t="s">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" t="s">
-        <v>5</v>
-      </c>
-      <c r="B40">
-        <v>28</v>
-      </c>
-      <c r="C40" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" t="s">
-        <v>1200</v>
-      </c>
-      <c r="B41">
-        <v>27</v>
-      </c>
-      <c r="C41" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
-        <v>200</v>
-      </c>
-      <c r="B42">
-        <v>27</v>
-      </c>
-      <c r="C42" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" t="s">
-        <v>686</v>
-      </c>
-      <c r="B43">
-        <v>27</v>
-      </c>
-      <c r="C43" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44">
-        <v>27</v>
-      </c>
-      <c r="C44" t="s">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
-        <v>695</v>
-      </c>
-      <c r="B45">
-        <v>26</v>
-      </c>
-      <c r="C45" t="s">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" t="s">
-        <v>132</v>
-      </c>
-      <c r="B46">
-        <v>26</v>
-      </c>
-      <c r="C46" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
-        <v>1201</v>
-      </c>
-      <c r="B47">
-        <v>26</v>
-      </c>
-      <c r="C47" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" t="s">
-        <v>1202</v>
-      </c>
-      <c r="B48">
-        <v>25</v>
-      </c>
-      <c r="C48" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" t="s">
-        <v>74</v>
-      </c>
-      <c r="B49">
-        <v>25</v>
-      </c>
-      <c r="C49" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" t="s">
-        <v>685</v>
-      </c>
-      <c r="B50">
-        <v>25</v>
-      </c>
-      <c r="C50" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" t="s">
-        <v>682</v>
-      </c>
-      <c r="B51">
-        <v>25</v>
-      </c>
-      <c r="C51" t="s">
-        <v>1094</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" t="s">
-        <v>74</v>
-      </c>
-      <c r="B52">
-        <v>25</v>
-      </c>
-      <c r="C52" t="s">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B53">
-        <v>25</v>
-      </c>
-      <c r="C53" t="s">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" t="s">
-        <v>804</v>
-      </c>
-      <c r="B54">
-        <v>24</v>
-      </c>
-      <c r="C54" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" t="s">
-        <v>1099</v>
-      </c>
-      <c r="B55">
-        <v>24</v>
-      </c>
-      <c r="C55" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" t="s">
-        <v>1101</v>
-      </c>
-      <c r="B56">
-        <v>24</v>
-      </c>
-      <c r="C56" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" t="s">
-        <v>1103</v>
-      </c>
-      <c r="B57">
-        <v>24</v>
-      </c>
-      <c r="C57" t="s">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" t="s">
-        <v>62</v>
-      </c>
-      <c r="B58">
-        <v>24</v>
-      </c>
-      <c r="C58" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" t="s">
-        <v>184</v>
-      </c>
-      <c r="B59">
-        <v>24</v>
-      </c>
-      <c r="C59" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" t="s">
-        <v>14</v>
-      </c>
-      <c r="B60">
-        <v>23</v>
-      </c>
-      <c r="C60" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" t="s">
-        <v>1106</v>
-      </c>
-      <c r="B61">
-        <v>23</v>
-      </c>
-      <c r="C61" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" t="s">
-        <v>75</v>
-      </c>
-      <c r="B62">
-        <v>22</v>
-      </c>
-      <c r="C62" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" t="s">
-        <v>1108</v>
-      </c>
-      <c r="B63">
-        <v>21</v>
-      </c>
-      <c r="C63" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" t="s">
-        <v>1109</v>
-      </c>
-      <c r="B64">
-        <v>21</v>
-      </c>
-      <c r="C64" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" t="s">
-        <v>1111</v>
-      </c>
-      <c r="B65">
-        <v>21</v>
-      </c>
-      <c r="C65" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B66">
-        <v>21</v>
-      </c>
-      <c r="C66" t="s">
-        <v>1114</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" t="s">
-        <v>1115</v>
-      </c>
-      <c r="B67">
-        <v>20</v>
-      </c>
-      <c r="C67" t="s">
-        <v>1116</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" t="s">
-        <v>237</v>
-      </c>
-      <c r="B68">
-        <v>20</v>
-      </c>
-      <c r="C68" t="s">
-        <v>1117</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" t="s">
-        <v>48</v>
-      </c>
-      <c r="B69">
-        <v>20</v>
-      </c>
-      <c r="C69" t="s">
-        <v>1118</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" t="s">
-        <v>1119</v>
-      </c>
-      <c r="B70">
-        <v>20</v>
-      </c>
-      <c r="C70" t="s">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" t="s">
-        <v>1121</v>
-      </c>
-      <c r="B71">
-        <v>20</v>
-      </c>
-      <c r="C71" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" t="s">
-        <v>152</v>
-      </c>
-      <c r="B72">
-        <v>19</v>
-      </c>
-      <c r="C72" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" t="s">
-        <v>1123</v>
-      </c>
-      <c r="B73">
-        <v>19</v>
-      </c>
-      <c r="C73" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" t="s">
-        <v>1125</v>
-      </c>
-      <c r="B74">
-        <v>19</v>
-      </c>
-      <c r="C74" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75" t="s">
-        <v>1127</v>
-      </c>
-      <c r="B75">
-        <v>19</v>
-      </c>
-      <c r="C75" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" t="s">
-        <v>1129</v>
-      </c>
-      <c r="B76">
-        <v>18</v>
-      </c>
-      <c r="C76" t="s">
-        <v>1130</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" t="s">
-        <v>1131</v>
-      </c>
-      <c r="B77">
-        <v>18</v>
-      </c>
-      <c r="C77" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" t="s">
-        <v>611</v>
-      </c>
-      <c r="B78">
-        <v>18</v>
-      </c>
-      <c r="C78" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" t="s">
-        <v>1129</v>
-      </c>
-      <c r="B79">
-        <v>18</v>
-      </c>
-      <c r="C79" t="s">
-        <v>1130</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" t="s">
-        <v>800</v>
-      </c>
-      <c r="B80">
-        <v>17</v>
-      </c>
-      <c r="C80" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" t="s">
-        <v>1135</v>
-      </c>
-      <c r="B81">
-        <v>17</v>
-      </c>
-      <c r="C81" t="s">
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82" t="s">
-        <v>1137</v>
-      </c>
-      <c r="B82">
-        <v>17</v>
-      </c>
-      <c r="C82" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="A83" t="s">
-        <v>487</v>
-      </c>
-      <c r="B83">
-        <v>17</v>
-      </c>
-      <c r="C83" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3">
-      <c r="A84" t="s">
-        <v>24</v>
-      </c>
-      <c r="B84">
-        <v>16</v>
-      </c>
-      <c r="C84" t="s">
-        <v>1139</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3">
-      <c r="A85" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B85">
-        <v>16</v>
-      </c>
-      <c r="C85" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
-      <c r="A86" t="s">
-        <v>673</v>
-      </c>
-      <c r="B86">
-        <v>16</v>
-      </c>
-      <c r="C86" t="s">
-        <v>1141</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3">
-      <c r="A87" t="s">
-        <v>532</v>
-      </c>
-      <c r="B87">
-        <v>16</v>
-      </c>
-      <c r="C87" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3">
-      <c r="A88" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B88">
-        <v>15</v>
-      </c>
-      <c r="C88" t="s">
-        <v>1144</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
-      <c r="A89" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B89">
-        <v>15</v>
-      </c>
-      <c r="C89" t="s">
-        <v>1146</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3">
-      <c r="A90" t="s">
-        <v>1147</v>
-      </c>
-      <c r="B90">
-        <v>15</v>
-      </c>
-      <c r="C90" t="s">
-        <v>1148</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
-      <c r="A91" t="s">
-        <v>573</v>
-      </c>
-      <c r="B91">
-        <v>14</v>
-      </c>
-      <c r="C91" t="s">
-        <v>1149</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
-      <c r="A92" t="s">
-        <v>658</v>
-      </c>
-      <c r="B92">
-        <v>14</v>
-      </c>
-      <c r="C92" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3">
-      <c r="A93" t="s">
-        <v>510</v>
-      </c>
-      <c r="B93">
-        <v>14</v>
-      </c>
-      <c r="C93" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3">
-      <c r="A94" t="s">
-        <v>609</v>
-      </c>
-      <c r="B94">
-        <v>14</v>
-      </c>
-      <c r="C94" t="s">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3">
-      <c r="A95" t="s">
-        <v>57</v>
-      </c>
-      <c r="B95">
-        <v>13</v>
-      </c>
-      <c r="C95" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="A96" t="s">
-        <v>1154</v>
-      </c>
-      <c r="B96">
-        <v>13</v>
-      </c>
-      <c r="C96" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3">
-      <c r="A97" t="s">
-        <v>1156</v>
-      </c>
-      <c r="B97">
-        <v>13</v>
-      </c>
-      <c r="C97" t="s">
-        <v>1157</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="A98" t="s">
-        <v>1158</v>
-      </c>
-      <c r="B98">
-        <v>13</v>
-      </c>
-      <c r="C98" t="s">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="A99" t="s">
-        <v>527</v>
-      </c>
-      <c r="B99">
-        <v>12</v>
-      </c>
-      <c r="C99" t="s">
-        <v>1160</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3">
-      <c r="A100" t="s">
-        <v>515</v>
-      </c>
-      <c r="B100">
-        <v>12</v>
-      </c>
-      <c r="C100" t="s">
-        <v>1161</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101" t="s">
-        <v>517</v>
-      </c>
-      <c r="B101">
-        <v>12</v>
-      </c>
-      <c r="C101" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" t="s">
-        <v>141</v>
-      </c>
-      <c r="B102">
-        <v>12</v>
-      </c>
-      <c r="C102" t="s">
-        <v>1162</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3">
-      <c r="A103" t="s">
-        <v>1163</v>
-      </c>
-      <c r="B103">
-        <v>11</v>
-      </c>
-      <c r="C103" t="s">
-        <v>1164</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3">
-      <c r="A104" t="s">
-        <v>1165</v>
-      </c>
-      <c r="B104">
-        <v>11</v>
-      </c>
-      <c r="C104" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3">
-      <c r="A105" t="s">
-        <v>650</v>
-      </c>
-      <c r="B105">
-        <v>11</v>
-      </c>
-      <c r="C105" t="s">
-        <v>1166</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3">
-      <c r="A106" t="s">
-        <v>172</v>
-      </c>
-      <c r="B106">
-        <v>11</v>
-      </c>
-      <c r="C106" t="s">
-        <v>1167</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3">
-      <c r="A107" t="s">
-        <v>316</v>
-      </c>
-      <c r="B107">
-        <v>10</v>
-      </c>
-      <c r="C107" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3">
-      <c r="A108" t="s">
-        <v>69</v>
-      </c>
-      <c r="B108">
-        <v>10</v>
-      </c>
-      <c r="C108" t="s">
-        <v>1168</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3">
-      <c r="A109" t="s">
-        <v>1169</v>
-      </c>
-      <c r="B109">
-        <v>10</v>
-      </c>
-      <c r="C109" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3">
-      <c r="A110" t="s">
-        <v>1170</v>
-      </c>
-      <c r="B110">
-        <v>10</v>
-      </c>
-      <c r="C110" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" t="s">
-        <v>566</v>
-      </c>
-      <c r="B111">
-        <v>9</v>
-      </c>
-      <c r="C111" t="s">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3">
-      <c r="A112" t="s">
-        <v>1173</v>
-      </c>
-      <c r="B112">
-        <v>9</v>
-      </c>
-      <c r="C112" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" t="s">
-        <v>1175</v>
-      </c>
-      <c r="B113">
-        <v>9</v>
-      </c>
-      <c r="C113" t="s">
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3">
-      <c r="A114" t="s">
-        <v>655</v>
-      </c>
-      <c r="B114">
-        <v>9</v>
-      </c>
-      <c r="C114" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3">
-      <c r="A115" t="s">
-        <v>59</v>
-      </c>
-      <c r="B115">
-        <v>8</v>
-      </c>
-      <c r="C115" t="s">
-        <v>1177</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3">
-      <c r="A116" t="s">
-        <v>1178</v>
-      </c>
-      <c r="B116">
-        <v>8</v>
-      </c>
-      <c r="C116" t="s">
-        <v>1179</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3">
-      <c r="A117" t="s">
-        <v>1180</v>
-      </c>
-      <c r="B117">
-        <v>8</v>
-      </c>
-      <c r="C117" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3">
-      <c r="A118" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B118">
-        <v>8</v>
-      </c>
-      <c r="C118" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119">
-        <v>7</v>
-      </c>
-      <c r="C119" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3">
-      <c r="A120" t="s">
-        <v>229</v>
-      </c>
-      <c r="B120">
-        <v>7</v>
-      </c>
-      <c r="C120" t="s">
-        <v>1185</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/Stats For Rush.xlsx
+++ b/Stats For Rush.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurtl\Desktop\statstreaks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E9B5F6E-1EF8-4546-AB20-7202689A7C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16771134-18BD-49CB-9BD0-7F53F462318A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="866" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" tabRatio="866" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PL assists" sheetId="1" r:id="rId1"/>
     <sheet name="PL Goals" sheetId="2" r:id="rId2"/>
     <sheet name="PL Appearances" sheetId="3" r:id="rId3"/>
     <sheet name="Intl Appearances" sheetId="4" r:id="rId4"/>
-    <sheet name="Intl Goals" sheetId="5" r:id="rId5"/>
-    <sheet name="Man and liv g" sheetId="11" r:id="rId6"/>
-    <sheet name="Arsenalspurs goals" sheetId="12" r:id="rId7"/>
-    <sheet name="Man U goals" sheetId="6" r:id="rId8"/>
-    <sheet name="Liverpool goals" sheetId="7" r:id="rId9"/>
-    <sheet name="Champs league goals" sheetId="9" r:id="rId10"/>
-    <sheet name="La Liga goals" sheetId="8" r:id="rId11"/>
-    <sheet name="Transfers" sheetId="10" r:id="rId12"/>
+    <sheet name="Womens int" sheetId="13" r:id="rId5"/>
+    <sheet name="Intl Goals" sheetId="5" r:id="rId6"/>
+    <sheet name="Man and liv g" sheetId="11" r:id="rId7"/>
+    <sheet name="Arsenalspurs goals" sheetId="12" r:id="rId8"/>
+    <sheet name="Man U goals" sheetId="6" r:id="rId9"/>
+    <sheet name="Liverpool goals" sheetId="7" r:id="rId10"/>
+    <sheet name="Champs league goals" sheetId="9" r:id="rId11"/>
+    <sheet name="La Liga goals" sheetId="8" r:id="rId12"/>
+    <sheet name="Transfers" sheetId="10" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3223" uniqueCount="1276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3458" uniqueCount="1396">
   <si>
     <t>Rank</t>
   </si>
@@ -3875,13 +3876,373 @@
   </si>
   <si>
     <t>Jonathan Woodgate</t>
+  </si>
+  <si>
+    <t>Kristine Lilly</t>
+  </si>
+  <si>
+    <t>Christine Sinclair</t>
+  </si>
+  <si>
+    <t>Carli Lloyd</t>
+  </si>
+  <si>
+    <t>Mia Hamm</t>
+  </si>
+  <si>
+    <t>Julie Foudy</t>
+  </si>
+  <si>
+    <t>Abby Wambach</t>
+  </si>
+  <si>
+    <t>Caroline Seger</t>
+  </si>
+  <si>
+    <t>Heather O'Reilly</t>
+  </si>
+  <si>
+    <t>Sophie Schmidt</t>
+  </si>
+  <si>
+    <t>Alex Morgan</t>
+  </si>
+  <si>
+    <t>Formiga</t>
+  </si>
+  <si>
+    <t>Birgit Prinz</t>
+  </si>
+  <si>
+    <t>Therese Sjögran</t>
+  </si>
+  <si>
+    <t>Katrine Pedersen</t>
+  </si>
+  <si>
+    <t>Diana Matheson</t>
+  </si>
+  <si>
+    <t>Homare Sawa</t>
+  </si>
+  <si>
+    <t>Patrizia Panico</t>
+  </si>
+  <si>
+    <t>Gemma Fay</t>
+  </si>
+  <si>
+    <t>Megan Rapinoe</t>
+  </si>
+  <si>
+    <t>Hope Solo</t>
+  </si>
+  <si>
+    <t>Eugénie Le Sommer</t>
+  </si>
+  <si>
+    <t>Marta</t>
+  </si>
+  <si>
+    <t>Shannon Boxx</t>
+  </si>
+  <si>
+    <t>Brandi Chastain</t>
+  </si>
+  <si>
+    <t>Élise Bussaglia</t>
+  </si>
+  <si>
+    <t>Joanne Love</t>
+  </si>
+  <si>
+    <t>Hedvig Lindahl</t>
+  </si>
+  <si>
+    <t>Hege Riise</t>
+  </si>
+  <si>
+    <t>Laura Georges</t>
+  </si>
+  <si>
+    <t>Nilla Fischer</t>
+  </si>
+  <si>
+    <t>Lotta Schelin</t>
+  </si>
+  <si>
+    <t>Janine van Wyk</t>
+  </si>
+  <si>
+    <t>Solveig Gulbrandsen</t>
+  </si>
+  <si>
+    <t>Camille Abily</t>
+  </si>
+  <si>
+    <t>Rhian Wilkinson</t>
+  </si>
+  <si>
+    <t>Tobin Heath</t>
+  </si>
+  <si>
+    <t>Shannon MacMillan</t>
+  </si>
+  <si>
+    <t>Fara Williams</t>
+  </si>
+  <si>
+    <t>Briana Scurry</t>
+  </si>
+  <si>
+    <t>Bente Nordby</t>
+  </si>
+  <si>
+    <t>Pu Wei</t>
+  </si>
+  <si>
+    <t>Jill Scott</t>
+  </si>
+  <si>
+    <t>Wendie Renard</t>
+  </si>
+  <si>
+    <t>Han Duan</t>
+  </si>
+  <si>
+    <t>Victoria Svensson</t>
+  </si>
+  <si>
+    <t>Gaëtane Thiney</t>
+  </si>
+  <si>
+    <t>Trine Rønning</t>
+  </si>
+  <si>
+    <t>Aya Miyama</t>
+  </si>
+  <si>
+    <t>Kelley O'Hara</t>
+  </si>
+  <si>
+    <t>Cindy Parlow Cone</t>
+  </si>
+  <si>
+    <t>Anja Mittag</t>
+  </si>
+  <si>
+    <t>Cristiane</t>
+  </si>
+  <si>
+    <t>Michelle Akers</t>
+  </si>
+  <si>
+    <t>Tatiana Zorri</t>
+  </si>
+  <si>
+    <t>Christen Press</t>
+  </si>
+  <si>
+    <t>Rachel Corsie</t>
+  </si>
+  <si>
+    <t>Carolina Morace</t>
+  </si>
+  <si>
+    <t>Linda Medalen</t>
+  </si>
+  <si>
+    <t>Cheryl Salisbury</t>
+  </si>
+  <si>
+    <t>Lisa De Vanna</t>
+  </si>
+  <si>
+    <t>Karen Carney</t>
+  </si>
+  <si>
+    <t>Kim Little</t>
+  </si>
+  <si>
+    <t>Pia Sundhage</t>
+  </si>
+  <si>
+    <t>Nadine Angerer</t>
+  </si>
+  <si>
+    <t>Alex Scott</t>
+  </si>
+  <si>
+    <t>Marleen Wissink</t>
+  </si>
+  <si>
+    <t>Daphne Koster</t>
+  </si>
+  <si>
+    <t>Shinobu Ohno</t>
+  </si>
+  <si>
+    <t>Merete Pedersen</t>
+  </si>
+  <si>
+    <t>Casey Stoney</t>
+  </si>
+  <si>
+    <t>Rachel Yankey</t>
+  </si>
+  <si>
+    <t>Lauren Holiday</t>
+  </si>
+  <si>
+    <t>Isabell Herlovsen</t>
+  </si>
+  <si>
+    <t>Yūki Nagasato</t>
+  </si>
+  <si>
+    <t>Line Røddik Hansen</t>
+  </si>
+  <si>
+    <t>Amy Rodriguez</t>
+  </si>
+  <si>
+    <t>Hanna Ljungberg</t>
+  </si>
+  <si>
+    <t>Heather Garriock</t>
+  </si>
+  <si>
+    <t>Charmaine Hooper</t>
+  </si>
+  <si>
+    <t>Steph Houghton</t>
+  </si>
+  <si>
+    <t>Sun Wen</t>
+  </si>
+  <si>
+    <t>Silke Rottenberg</t>
+  </si>
+  <si>
+    <t>Kozue Ando</t>
+  </si>
+  <si>
+    <t>Gillian Coultard</t>
+  </si>
+  <si>
+    <t>Loes Geurts</t>
+  </si>
+  <si>
+    <t>Melanie Behringer</t>
+  </si>
+  <si>
+    <t>Marie-Laure Delie</t>
+  </si>
+  <si>
+    <t>Julie Ertz</t>
+  </si>
+  <si>
+    <t>Azusa Iwashimizu</t>
+  </si>
+  <si>
+    <t>Kelly Smith</t>
+  </si>
+  <si>
+    <t>Melania Gabbiadini</t>
+  </si>
+  <si>
+    <t>Ellen White</t>
+  </si>
+  <si>
+    <t>Erin McLeod</t>
+  </si>
+  <si>
+    <t>Áine O'Gorman</t>
+  </si>
+  <si>
+    <t>Julie Fleeting</t>
+  </si>
+  <si>
+    <t>Rosana</t>
+  </si>
+  <si>
+    <t>Elise Kellond-Knight</t>
+  </si>
+  <si>
+    <t>Rumi Utsugi</t>
+  </si>
+  <si>
+    <t>Dzsenifer Marozsán</t>
+  </si>
+  <si>
+    <t>Steffi Jones</t>
+  </si>
+  <si>
+    <t>Célia Šašić</t>
+  </si>
+  <si>
+    <t>Kyah Simon</t>
+  </si>
+  <si>
+    <t>Eniola Aluko</t>
+  </si>
+  <si>
+    <t>Amandine Henry</t>
+  </si>
+  <si>
+    <t>Ali Krieger</t>
+  </si>
+  <si>
+    <t>Nadia Nadim</t>
+  </si>
+  <si>
+    <t>Lena Goeßling</t>
+  </si>
+  <si>
+    <t>Andressa Alves</t>
+  </si>
+  <si>
+    <t>Helen Ward</t>
+  </si>
+  <si>
+    <t>Sarina Wiegman</t>
+  </si>
+  <si>
+    <t>Simone Laudehr</t>
+  </si>
+  <si>
+    <t>Natasha Harding</t>
+  </si>
+  <si>
+    <t>Rachel Unitt</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Republic of Ireland</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>Katie Chapman</t>
+  </si>
+  <si>
+    <t>Faye White</t>
+  </si>
+  <si>
+    <t>Anita Asante</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3968,8 +4329,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4050,6 +4417,11 @@
         <fgColor rgb="FFFFCCCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -4108,7 +4480,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4205,6 +4577,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -8691,6 +9067,1211 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="A1:F113"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.1796875" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.81640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" style="25" customWidth="1"/>
+    <col min="4" max="16384" width="8.7265625" style="25"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="25" t="s">
+        <v>813</v>
+      </c>
+      <c r="B2" s="25">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="25" t="s">
+        <v>814</v>
+      </c>
+      <c r="B3" s="25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="25" t="s">
+        <v>815</v>
+      </c>
+      <c r="B4" s="25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="25" t="s">
+        <v>816</v>
+      </c>
+      <c r="B5" s="25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="25" t="s">
+        <v>817</v>
+      </c>
+      <c r="B6" s="25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="25" t="s">
+        <v>818</v>
+      </c>
+      <c r="B7" s="25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="25" t="s">
+        <v>819</v>
+      </c>
+      <c r="B8" s="25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="25" t="s">
+        <v>820</v>
+      </c>
+      <c r="B9" s="25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="25" t="s">
+        <v>821</v>
+      </c>
+      <c r="B10" s="25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="25" t="s">
+        <v>822</v>
+      </c>
+      <c r="B11" s="25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="25" t="s">
+        <v>823</v>
+      </c>
+      <c r="B12" s="25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="25" t="s">
+        <v>824</v>
+      </c>
+      <c r="B13" s="25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="25" t="s">
+        <v>825</v>
+      </c>
+      <c r="B14" s="25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="25" t="s">
+        <v>826</v>
+      </c>
+      <c r="B15" s="25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="25" t="s">
+        <v>827</v>
+      </c>
+      <c r="B16" s="25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="25" t="s">
+        <v>828</v>
+      </c>
+      <c r="B17" s="25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="25" t="s">
+        <v>829</v>
+      </c>
+      <c r="B18" s="25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="25" t="s">
+        <v>830</v>
+      </c>
+      <c r="B19" s="25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="25" t="s">
+        <v>831</v>
+      </c>
+      <c r="B20" s="25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="25" t="s">
+        <v>832</v>
+      </c>
+      <c r="B21" s="26">
+        <v>79</v>
+      </c>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="25" t="s">
+        <v>833</v>
+      </c>
+      <c r="B22" s="26">
+        <v>78</v>
+      </c>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="25" t="s">
+        <v>834</v>
+      </c>
+      <c r="B23" s="26">
+        <v>76</v>
+      </c>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="25" t="s">
+        <v>835</v>
+      </c>
+      <c r="B24" s="26">
+        <v>73</v>
+      </c>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="25" t="s">
+        <v>836</v>
+      </c>
+      <c r="B25" s="26">
+        <v>72</v>
+      </c>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="25" t="s">
+        <v>837</v>
+      </c>
+      <c r="B26" s="26">
+        <v>71</v>
+      </c>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="25" t="s">
+        <v>838</v>
+      </c>
+      <c r="B27" s="26">
+        <v>68</v>
+      </c>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="B28" s="26">
+        <v>67</v>
+      </c>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="26">
+        <v>66</v>
+      </c>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="B30" s="26">
+        <v>65</v>
+      </c>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="25" t="s">
+        <v>839</v>
+      </c>
+      <c r="B31" s="26">
+        <v>63</v>
+      </c>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="25" t="s">
+        <v>840</v>
+      </c>
+      <c r="B32" s="26">
+        <v>63</v>
+      </c>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="25" t="s">
+        <v>841</v>
+      </c>
+      <c r="B33" s="26">
+        <v>61</v>
+      </c>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="25" t="s">
+        <v>842</v>
+      </c>
+      <c r="B34" s="26">
+        <v>61</v>
+      </c>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B35" s="26">
+        <v>60</v>
+      </c>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="B36" s="26">
+        <v>59</v>
+      </c>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="25" t="s">
+        <v>843</v>
+      </c>
+      <c r="B37" s="26">
+        <v>59</v>
+      </c>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="25" t="s">
+        <v>844</v>
+      </c>
+      <c r="B38" s="26">
+        <v>55</v>
+      </c>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="25" t="s">
+        <v>845</v>
+      </c>
+      <c r="B39" s="26">
+        <v>55</v>
+      </c>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="B40" s="26">
+        <v>54</v>
+      </c>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="25" t="s">
+        <v>846</v>
+      </c>
+      <c r="B41" s="26">
+        <v>54</v>
+      </c>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="25" t="s">
+        <v>847</v>
+      </c>
+      <c r="B42" s="26">
+        <v>50</v>
+      </c>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="25" t="s">
+        <v>848</v>
+      </c>
+      <c r="B43" s="26">
+        <v>49</v>
+      </c>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="25" t="s">
+        <v>849</v>
+      </c>
+      <c r="B44" s="26">
+        <v>49</v>
+      </c>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="25" t="s">
+        <v>850</v>
+      </c>
+      <c r="B45" s="26">
+        <v>48</v>
+      </c>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="25" t="s">
+        <v>851</v>
+      </c>
+      <c r="B46" s="26">
+        <v>46</v>
+      </c>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="25" t="s">
+        <v>852</v>
+      </c>
+      <c r="B47" s="26">
+        <v>46</v>
+      </c>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="B48" s="26">
+        <v>44</v>
+      </c>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="26">
+        <v>42</v>
+      </c>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="25" t="s">
+        <v>853</v>
+      </c>
+      <c r="B50" s="26">
+        <v>42</v>
+      </c>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="26"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="25" t="s">
+        <v>854</v>
+      </c>
+      <c r="B51" s="26">
+        <v>42</v>
+      </c>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="26"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="25" t="s">
+        <v>855</v>
+      </c>
+      <c r="B52" s="26">
+        <v>41</v>
+      </c>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="25" t="s">
+        <v>856</v>
+      </c>
+      <c r="B53" s="26">
+        <v>41</v>
+      </c>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="25" t="s">
+        <v>857</v>
+      </c>
+      <c r="B54" s="26">
+        <v>41</v>
+      </c>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="25" t="s">
+        <v>858</v>
+      </c>
+      <c r="B55" s="26">
+        <v>40</v>
+      </c>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" s="25" t="s">
+        <v>859</v>
+      </c>
+      <c r="B56" s="26">
+        <v>40</v>
+      </c>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" s="25" t="s">
+        <v>860</v>
+      </c>
+      <c r="B57" s="26">
+        <v>38</v>
+      </c>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" s="25" t="s">
+        <v>861</v>
+      </c>
+      <c r="B58" s="26">
+        <v>38</v>
+      </c>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" s="25" t="s">
+        <v>862</v>
+      </c>
+      <c r="B59" s="26">
+        <v>37</v>
+      </c>
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="B60" s="26">
+        <v>35</v>
+      </c>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" s="25" t="s">
+        <v>863</v>
+      </c>
+      <c r="B61" s="26">
+        <v>35</v>
+      </c>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" s="25" t="s">
+        <v>864</v>
+      </c>
+      <c r="B62" s="26">
+        <v>35</v>
+      </c>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="26"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" s="25" t="s">
+        <v>865</v>
+      </c>
+      <c r="B63" s="26">
+        <v>33</v>
+      </c>
+      <c r="D63" s="26"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="26"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" s="25" t="s">
+        <v>866</v>
+      </c>
+      <c r="B64" s="26">
+        <v>33</v>
+      </c>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="26"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B65" s="26">
+        <v>33</v>
+      </c>
+      <c r="D65" s="26"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" s="25" t="s">
+        <v>441</v>
+      </c>
+      <c r="B66" s="26">
+        <v>31</v>
+      </c>
+      <c r="D66" s="26"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="26"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" s="25" t="s">
+        <v>867</v>
+      </c>
+      <c r="B67" s="26">
+        <v>30</v>
+      </c>
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" s="25" t="s">
+        <v>868</v>
+      </c>
+      <c r="B68" s="26">
+        <v>29</v>
+      </c>
+      <c r="D68" s="26"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="26"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" s="25" t="s">
+        <v>869</v>
+      </c>
+      <c r="B69" s="26">
+        <v>27</v>
+      </c>
+      <c r="D69" s="26"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="26"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70" s="25" t="s">
+        <v>870</v>
+      </c>
+      <c r="B70" s="26">
+        <v>27</v>
+      </c>
+      <c r="D70" s="26"/>
+      <c r="E70" s="26"/>
+      <c r="F70" s="26"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71" s="25" t="s">
+        <v>871</v>
+      </c>
+      <c r="B71" s="26">
+        <v>26</v>
+      </c>
+      <c r="D71" s="26"/>
+      <c r="E71" s="26"/>
+      <c r="F71" s="26"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B72" s="26">
+        <v>26</v>
+      </c>
+      <c r="D72" s="26"/>
+      <c r="E72" s="26"/>
+      <c r="F72" s="26"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" s="25" t="s">
+        <v>872</v>
+      </c>
+      <c r="B73" s="26">
+        <v>25</v>
+      </c>
+      <c r="D73" s="26"/>
+      <c r="E73" s="26"/>
+      <c r="F73" s="26"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74" s="25" t="s">
+        <v>873</v>
+      </c>
+      <c r="B74" s="26">
+        <v>24</v>
+      </c>
+      <c r="D74" s="26"/>
+      <c r="E74" s="26"/>
+      <c r="F74" s="26"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B75" s="26">
+        <v>23</v>
+      </c>
+      <c r="D75" s="26"/>
+      <c r="E75" s="26"/>
+      <c r="F75" s="26"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A76" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B76" s="26">
+        <v>23</v>
+      </c>
+      <c r="D76" s="26"/>
+      <c r="E76" s="26"/>
+      <c r="F76" s="26"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" s="25" t="s">
+        <v>874</v>
+      </c>
+      <c r="B77" s="26">
+        <v>22</v>
+      </c>
+      <c r="D77" s="26"/>
+      <c r="E77" s="26"/>
+      <c r="F77" s="26"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" s="25" t="s">
+        <v>875</v>
+      </c>
+      <c r="B78" s="26">
+        <v>22</v>
+      </c>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79" s="25" t="s">
+        <v>272</v>
+      </c>
+      <c r="B79" s="26">
+        <v>22</v>
+      </c>
+      <c r="D79" s="26"/>
+      <c r="E79" s="26"/>
+      <c r="F79" s="26"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="25" t="s">
+        <v>876</v>
+      </c>
+      <c r="B80" s="26">
+        <v>22</v>
+      </c>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" s="25" t="s">
+        <v>877</v>
+      </c>
+      <c r="B81" s="26">
+        <v>21</v>
+      </c>
+      <c r="D81" s="26"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="26"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" s="25" t="s">
+        <v>878</v>
+      </c>
+      <c r="B82" s="26">
+        <v>20</v>
+      </c>
+      <c r="D82" s="26"/>
+      <c r="E82" s="26"/>
+      <c r="F82" s="26"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" s="25" t="s">
+        <v>879</v>
+      </c>
+      <c r="B83" s="26">
+        <v>19</v>
+      </c>
+      <c r="D83" s="26"/>
+      <c r="E83" s="26"/>
+      <c r="F83" s="26"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" s="25" t="s">
+        <v>880</v>
+      </c>
+      <c r="B84" s="26">
+        <v>19</v>
+      </c>
+      <c r="D84" s="26"/>
+      <c r="E84" s="26"/>
+      <c r="F84" s="26"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" s="25" t="s">
+        <v>881</v>
+      </c>
+      <c r="B85" s="26">
+        <v>19</v>
+      </c>
+      <c r="D85" s="26"/>
+      <c r="E85" s="26"/>
+      <c r="F85" s="26"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" s="25" t="s">
+        <v>882</v>
+      </c>
+      <c r="B86" s="26">
+        <v>19</v>
+      </c>
+      <c r="D86" s="26"/>
+      <c r="E86" s="26"/>
+      <c r="F86" s="26"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" s="25" t="s">
+        <v>549</v>
+      </c>
+      <c r="B87" s="26">
+        <v>19</v>
+      </c>
+      <c r="D87" s="26"/>
+      <c r="E87" s="26"/>
+      <c r="F87" s="26"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" s="25" t="s">
+        <v>883</v>
+      </c>
+      <c r="B88" s="26">
+        <v>19</v>
+      </c>
+      <c r="D88" s="26"/>
+      <c r="E88" s="26"/>
+      <c r="F88" s="26"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="B89" s="26">
+        <v>18</v>
+      </c>
+      <c r="D89" s="26"/>
+      <c r="E89" s="26"/>
+      <c r="F89" s="26"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="25" t="s">
+        <v>884</v>
+      </c>
+      <c r="B90" s="26">
+        <v>18</v>
+      </c>
+      <c r="D90" s="26"/>
+      <c r="E90" s="26"/>
+      <c r="F90" s="26"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" s="25" t="s">
+        <v>885</v>
+      </c>
+      <c r="B91" s="26">
+        <v>18</v>
+      </c>
+      <c r="D91" s="26"/>
+      <c r="E91" s="26"/>
+      <c r="F91" s="26"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" s="25" t="s">
+        <v>886</v>
+      </c>
+      <c r="B92" s="26">
+        <v>18</v>
+      </c>
+      <c r="D92" s="26"/>
+      <c r="E92" s="26"/>
+      <c r="F92" s="26"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="25" t="s">
+        <v>887</v>
+      </c>
+      <c r="B93" s="26">
+        <v>18</v>
+      </c>
+      <c r="D93" s="26"/>
+      <c r="E93" s="26"/>
+      <c r="F93" s="26"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="25" t="s">
+        <v>888</v>
+      </c>
+      <c r="B94" s="26">
+        <v>17</v>
+      </c>
+      <c r="D94" s="26"/>
+      <c r="E94" s="26"/>
+      <c r="F94" s="26"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="25" t="s">
+        <v>889</v>
+      </c>
+      <c r="B95" s="26">
+        <v>17</v>
+      </c>
+      <c r="D95" s="26"/>
+      <c r="E95" s="26"/>
+      <c r="F95" s="26"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="25" t="s">
+        <v>467</v>
+      </c>
+      <c r="B96" s="26">
+        <v>17</v>
+      </c>
+      <c r="D96" s="26"/>
+      <c r="E96" s="26"/>
+      <c r="F96" s="26"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="25" t="s">
+        <v>890</v>
+      </c>
+      <c r="B97" s="26">
+        <v>17</v>
+      </c>
+      <c r="D97" s="26"/>
+      <c r="E97" s="26"/>
+      <c r="F97" s="26"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="B98" s="26">
+        <v>16</v>
+      </c>
+      <c r="D98" s="26"/>
+      <c r="E98" s="26"/>
+      <c r="F98" s="26"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="25" t="s">
+        <v>891</v>
+      </c>
+      <c r="B99" s="26">
+        <v>16</v>
+      </c>
+      <c r="D99" s="26"/>
+      <c r="E99" s="26"/>
+      <c r="F99" s="26"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="25" t="s">
+        <v>892</v>
+      </c>
+      <c r="B100" s="26">
+        <v>16</v>
+      </c>
+      <c r="D100" s="26"/>
+      <c r="E100" s="26"/>
+      <c r="F100" s="26"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="25" t="s">
+        <v>893</v>
+      </c>
+      <c r="B101" s="26">
+        <v>15</v>
+      </c>
+      <c r="D101" s="26"/>
+      <c r="E101" s="26"/>
+      <c r="F101" s="26"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="25" t="s">
+        <v>894</v>
+      </c>
+      <c r="B102" s="26">
+        <v>15</v>
+      </c>
+      <c r="D102" s="26"/>
+      <c r="E102" s="26"/>
+      <c r="F102" s="26"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="25" t="s">
+        <v>895</v>
+      </c>
+      <c r="B103" s="26">
+        <v>14</v>
+      </c>
+      <c r="D103" s="26"/>
+      <c r="E103" s="26"/>
+      <c r="F103" s="26"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="25" t="s">
+        <v>896</v>
+      </c>
+      <c r="B104" s="26">
+        <v>14</v>
+      </c>
+      <c r="D104" s="26"/>
+      <c r="E104" s="26"/>
+      <c r="F104" s="26"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="25" t="s">
+        <v>897</v>
+      </c>
+      <c r="B105" s="26">
+        <v>14</v>
+      </c>
+      <c r="D105" s="26"/>
+      <c r="E105" s="26"/>
+      <c r="F105" s="26"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="25" t="s">
+        <v>898</v>
+      </c>
+      <c r="B106" s="26">
+        <v>14</v>
+      </c>
+      <c r="D106" s="26"/>
+      <c r="E106" s="26"/>
+      <c r="F106" s="26"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="25" t="s">
+        <v>899</v>
+      </c>
+      <c r="B107" s="26">
+        <v>13</v>
+      </c>
+      <c r="D107" s="26"/>
+      <c r="E107" s="26"/>
+      <c r="F107" s="26"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="25" t="s">
+        <v>900</v>
+      </c>
+      <c r="B108" s="26">
+        <v>13</v>
+      </c>
+      <c r="D108" s="26"/>
+      <c r="E108" s="26"/>
+      <c r="F108" s="26"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B109" s="26">
+        <v>13</v>
+      </c>
+      <c r="D109" s="26"/>
+      <c r="E109" s="26"/>
+      <c r="F109" s="26"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="25" t="s">
+        <v>901</v>
+      </c>
+      <c r="B110" s="26">
+        <v>13</v>
+      </c>
+      <c r="D110" s="26"/>
+      <c r="E110" s="26"/>
+      <c r="F110" s="26"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="25" t="s">
+        <v>715</v>
+      </c>
+      <c r="B111" s="26">
+        <v>12</v>
+      </c>
+      <c r="D111" s="26"/>
+      <c r="E111" s="26"/>
+      <c r="F111" s="26"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="25" t="s">
+        <v>902</v>
+      </c>
+      <c r="B112" s="26">
+        <v>12</v>
+      </c>
+      <c r="D112" s="26"/>
+      <c r="E112" s="26"/>
+      <c r="F112" s="26"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="25" t="s">
+        <v>903</v>
+      </c>
+      <c r="B113" s="26">
+        <v>12</v>
+      </c>
+      <c r="D113" s="26"/>
+      <c r="E113" s="26"/>
+      <c r="F113" s="26"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -10031,7 +11612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -11383,7 +12964,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -22594,6 +24175,3254 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58D3735E-A9BB-4E27-811E-A3D7D4DF0F51}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:G565"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.08984375" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="25" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C2" s="25">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="25" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C3" s="25">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="25" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C4" s="25">
+        <v>316</v>
+      </c>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="25" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C5" s="25">
+        <v>276</v>
+      </c>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="25" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C6" s="25">
+        <v>274</v>
+      </c>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="25" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C7" s="25">
+        <v>255</v>
+      </c>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="25" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="C8" s="25">
+        <v>240</v>
+      </c>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="25" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C9" s="25">
+        <v>231</v>
+      </c>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="25" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C10" s="25">
+        <v>226</v>
+      </c>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="25" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" s="25">
+        <v>224</v>
+      </c>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="25" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="25">
+        <v>217</v>
+      </c>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="25" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="25">
+        <v>214</v>
+      </c>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="25" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="C14" s="25">
+        <v>214</v>
+      </c>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="25" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="25">
+        <v>210</v>
+      </c>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="25" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C16" s="25">
+        <v>206</v>
+      </c>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="25" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C17" s="25">
+        <v>205</v>
+      </c>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="25" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="25">
+        <v>204</v>
+      </c>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="25" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C19" s="25">
+        <v>203</v>
+      </c>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="25" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="25">
+        <v>203</v>
+      </c>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="25" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C21" s="25">
+        <v>202</v>
+      </c>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="25" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="25">
+        <v>200</v>
+      </c>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="25" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="25">
+        <v>200</v>
+      </c>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="25" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C24" s="25">
+        <v>195</v>
+      </c>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="25" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C25" s="25">
+        <v>192</v>
+      </c>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="25" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="25">
+        <v>192</v>
+      </c>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="25" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="25">
+        <v>189</v>
+      </c>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="25" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="C28" s="25">
+        <v>189</v>
+      </c>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="25" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="C29" s="25">
+        <v>188</v>
+      </c>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" s="25" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C30" s="25">
+        <v>188</v>
+      </c>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" s="25" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B31" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="25">
+        <v>188</v>
+      </c>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" s="25" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B32" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="C32" s="25">
+        <v>185</v>
+      </c>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="25" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="C33" s="25">
+        <v>185</v>
+      </c>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="25" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C34" s="25">
+        <v>183</v>
+      </c>
+      <c r="F34" s="38"/>
+      <c r="G34" s="38"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="25" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="25">
+        <v>183</v>
+      </c>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="25" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C36" s="25">
+        <v>181</v>
+      </c>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="25" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C37" s="25">
+        <v>181</v>
+      </c>
+      <c r="F37" s="38"/>
+      <c r="G37" s="38"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" s="25" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C38" s="25">
+        <v>177</v>
+      </c>
+      <c r="F38" s="38"/>
+      <c r="G38" s="38"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="25" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="25">
+        <v>177</v>
+      </c>
+      <c r="F39" s="38"/>
+      <c r="G39" s="38"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" s="25" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C40" s="25">
+        <v>175</v>
+      </c>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" s="25" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C41" s="25">
+        <v>172</v>
+      </c>
+      <c r="F41" s="38"/>
+      <c r="G41" s="38"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" s="25" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="25">
+        <v>170</v>
+      </c>
+      <c r="F42" s="38"/>
+      <c r="G42" s="38"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" s="25" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B43" s="25" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C43" s="25">
+        <v>170</v>
+      </c>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" s="25" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44" s="25">
+        <v>168</v>
+      </c>
+      <c r="F44" s="38"/>
+      <c r="G44" s="38"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" s="25" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B45" s="25" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C45" s="25">
+        <v>167</v>
+      </c>
+      <c r="F45" s="38"/>
+      <c r="G45" s="38"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" s="25" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B46" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="C46" s="25">
+        <v>166</v>
+      </c>
+      <c r="F46" s="38"/>
+      <c r="G46" s="38"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" s="25" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B47" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" s="25">
+        <v>163</v>
+      </c>
+      <c r="F47" s="38"/>
+      <c r="G47" s="38"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" s="25" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C48" s="25">
+        <v>162</v>
+      </c>
+      <c r="F48" s="38"/>
+      <c r="G48" s="38"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49" s="25" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B49" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C49" s="25">
+        <v>162</v>
+      </c>
+      <c r="F49" s="38"/>
+      <c r="G49" s="38"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50" s="25" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B50" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C50" s="25">
+        <v>160</v>
+      </c>
+      <c r="F50" s="38"/>
+      <c r="G50" s="38"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51" s="25" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B51" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C51" s="25">
+        <v>158</v>
+      </c>
+      <c r="F51" s="38"/>
+      <c r="G51" s="38"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52" s="25" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" s="25">
+        <v>158</v>
+      </c>
+      <c r="F52" s="38"/>
+      <c r="G52" s="38"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53" s="25" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B53" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C53" s="25">
+        <v>158</v>
+      </c>
+      <c r="F53" s="38"/>
+      <c r="G53" s="38"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54" s="25" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B54" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C54" s="25">
+        <v>155</v>
+      </c>
+      <c r="F54" s="38"/>
+      <c r="G54" s="38"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55" s="25" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B55" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C55" s="25">
+        <v>155</v>
+      </c>
+      <c r="F55" s="38"/>
+      <c r="G55" s="38"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56" s="25" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B56" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C56" s="25">
+        <v>155</v>
+      </c>
+      <c r="F56" s="38"/>
+      <c r="G56" s="38"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57" s="25" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B57" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C57" s="25">
+        <v>153</v>
+      </c>
+      <c r="F57" s="38"/>
+      <c r="G57" s="38"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58" s="25" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B58" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C58" s="25">
+        <v>152</v>
+      </c>
+      <c r="F58" s="38"/>
+      <c r="G58" s="38"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59" s="25" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B59" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C59" s="25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60" s="25" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B60" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C60" s="25">
+        <v>150</v>
+      </c>
+      <c r="F60" s="38"/>
+      <c r="G60" s="38"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61" s="25" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B61" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="25">
+        <v>149</v>
+      </c>
+      <c r="F61" s="38"/>
+      <c r="G61" s="38"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62" s="25" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B62" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C62" s="25">
+        <v>149</v>
+      </c>
+      <c r="F62" s="38"/>
+      <c r="G62" s="38"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63" s="25" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B63" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C63" s="25">
+        <v>146</v>
+      </c>
+      <c r="F63" s="38"/>
+      <c r="G63" s="38"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64" s="25" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B64" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="C64" s="25">
+        <v>146</v>
+      </c>
+      <c r="F64" s="38"/>
+      <c r="G64" s="38"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65" s="25" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B65" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="25">
+        <v>145</v>
+      </c>
+      <c r="F65" s="38"/>
+      <c r="G65" s="38"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66" s="25" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B66" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" s="25">
+        <v>141</v>
+      </c>
+      <c r="F66" s="38"/>
+      <c r="G66" s="38"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" s="25" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B67" s="25" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C67" s="25">
+        <v>139</v>
+      </c>
+      <c r="F67" s="38"/>
+      <c r="G67" s="38"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" s="25" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B68" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" s="25">
+        <v>139</v>
+      </c>
+      <c r="F68" s="38"/>
+      <c r="G68" s="38"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69" s="25" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B69" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" s="25">
+        <v>136</v>
+      </c>
+      <c r="F69" s="38"/>
+      <c r="G69" s="38"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70" s="25" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B70" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" s="25">
+        <v>135</v>
+      </c>
+      <c r="F70" s="38"/>
+      <c r="G70" s="38"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71" s="25" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B71" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C71" s="25">
+        <v>134</v>
+      </c>
+      <c r="F71" s="38"/>
+      <c r="G71" s="38"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72" s="25" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B72" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C72" s="25">
+        <v>133</v>
+      </c>
+      <c r="F72" s="38"/>
+      <c r="G72" s="38"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73" s="25" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B73" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C73" s="25">
+        <v>133</v>
+      </c>
+      <c r="F73" s="38"/>
+      <c r="G73" s="38"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74" s="25" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B74" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C74" s="25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75" s="25" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B75" s="25" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C75" s="25">
+        <v>132</v>
+      </c>
+      <c r="F75" s="38"/>
+      <c r="G75" s="38"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A76" s="25" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B76" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C76" s="25">
+        <v>132</v>
+      </c>
+      <c r="F76" s="38"/>
+      <c r="G76" s="38"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A77" s="25" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B77" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C77" s="25">
+        <v>132</v>
+      </c>
+      <c r="F77" s="38"/>
+      <c r="G77" s="38"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A78" s="25" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B78" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="C78" s="25">
+        <v>130</v>
+      </c>
+      <c r="F78" s="38"/>
+      <c r="G78" s="38"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A79" s="25" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B79" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C79" s="25">
+        <v>130</v>
+      </c>
+      <c r="F79" s="38"/>
+      <c r="G79" s="38"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A80" s="25" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B80" s="25" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C80" s="25">
+        <v>129</v>
+      </c>
+      <c r="F80" s="38"/>
+      <c r="G80" s="38"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A81" s="25" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B81" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C81" s="25">
+        <v>129</v>
+      </c>
+      <c r="F81" s="38"/>
+      <c r="G81" s="38"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A82" s="25" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B82" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C82" s="25">
+        <v>126</v>
+      </c>
+      <c r="F82" s="38"/>
+      <c r="G82" s="38"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A83" s="25" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B83" s="25" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C83" s="25">
+        <v>126</v>
+      </c>
+      <c r="F83" s="38"/>
+      <c r="G83" s="38"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A84" s="25" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B84" s="25" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C84" s="25">
+        <v>126</v>
+      </c>
+      <c r="F84" s="38"/>
+      <c r="G84" s="38"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A85" s="25" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B85" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C85" s="25">
+        <v>125</v>
+      </c>
+      <c r="F85" s="38"/>
+      <c r="G85" s="38"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A86" s="25" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B86" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" s="25">
+        <v>125</v>
+      </c>
+      <c r="F86" s="38"/>
+      <c r="G86" s="38"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A87" s="25" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B87" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C87" s="25">
+        <v>123</v>
+      </c>
+      <c r="F87" s="38"/>
+      <c r="G87" s="38"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A88" s="25" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B88" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C88" s="25">
+        <v>123</v>
+      </c>
+      <c r="F88" s="38"/>
+      <c r="G88" s="38"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A89" s="25" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B89" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C89" s="25">
+        <v>123</v>
+      </c>
+      <c r="F89" s="38"/>
+      <c r="G89" s="38"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A90" s="25" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B90" s="25" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C90" s="25">
+        <v>122</v>
+      </c>
+      <c r="F90" s="38"/>
+      <c r="G90" s="38"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A91" s="25" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B91" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C91" s="25">
+        <v>121</v>
+      </c>
+      <c r="G91" s="38"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A92" s="25" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B92" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" s="25">
+        <v>121</v>
+      </c>
+      <c r="F92" s="38"/>
+      <c r="G92" s="38"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A93" s="25" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B93" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C93" s="25">
+        <v>121</v>
+      </c>
+      <c r="F93" s="38"/>
+      <c r="G93" s="38"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A94" s="25" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B94" s="25" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C94" s="25">
+        <v>119</v>
+      </c>
+      <c r="F94" s="38"/>
+      <c r="G94" s="38"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A95" s="25" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B95" s="25" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C95" s="25">
+        <v>119</v>
+      </c>
+      <c r="F95" s="38"/>
+      <c r="G95" s="38"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A96" s="25" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B96" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C96" s="25">
+        <v>118</v>
+      </c>
+      <c r="F96" s="38"/>
+      <c r="G96" s="38"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A97" s="25" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B97" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C97" s="25">
+        <v>118</v>
+      </c>
+      <c r="F97" s="38"/>
+      <c r="G97" s="38"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A98" s="25" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B98" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C98" s="25">
+        <v>115</v>
+      </c>
+      <c r="F98" s="38"/>
+      <c r="G98" s="38"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A99" s="25" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B99" s="25" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C99" s="25">
+        <v>113</v>
+      </c>
+      <c r="F99" s="38"/>
+      <c r="G99" s="38"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A100" s="25" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B100" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C100" s="25">
+        <v>112</v>
+      </c>
+      <c r="F100" s="38"/>
+      <c r="G100" s="38"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A101" s="25" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B101" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C101" s="25">
+        <v>111</v>
+      </c>
+      <c r="F101" s="38"/>
+      <c r="G101" s="38"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A102" s="25" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B102" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C102" s="25">
+        <v>111</v>
+      </c>
+      <c r="F102" s="38"/>
+      <c r="G102" s="38"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A103" s="25" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B103" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C103" s="25">
+        <v>111</v>
+      </c>
+      <c r="F103" s="38"/>
+      <c r="G103" s="38"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A104" s="25" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B104" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C104" s="25">
+        <v>110</v>
+      </c>
+      <c r="F104" s="38"/>
+      <c r="G104" s="38"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A105" s="25" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B105" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C105" s="25">
+        <v>109</v>
+      </c>
+      <c r="F105" s="38"/>
+      <c r="G105" s="38"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A106" s="25" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B106" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C106" s="25">
+        <v>108</v>
+      </c>
+      <c r="F106" s="38"/>
+      <c r="G106" s="38"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A107" s="25" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B107" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C107" s="25">
+        <v>106</v>
+      </c>
+      <c r="F107" s="38"/>
+      <c r="G107" s="38"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A108" s="25" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B108" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C108" s="25">
+        <v>106</v>
+      </c>
+      <c r="F108" s="38"/>
+      <c r="G108" s="38"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A109" s="25" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B109" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="25">
+        <v>105</v>
+      </c>
+      <c r="F109" s="38"/>
+      <c r="G109" s="38"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A110" s="25" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B110" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" s="25">
+        <v>104</v>
+      </c>
+      <c r="F110" s="38"/>
+      <c r="G110" s="38"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A111" s="25" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B111" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111" s="25">
+        <v>103</v>
+      </c>
+      <c r="F111" s="38"/>
+      <c r="G111" s="38"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A112" s="25" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B112" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C112" s="25">
+        <v>103</v>
+      </c>
+      <c r="F112" s="38"/>
+      <c r="G112" s="38"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A113" s="25" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B113" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C113" s="25">
+        <v>103</v>
+      </c>
+      <c r="G113" s="38"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A114" s="25" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B114" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C114" s="25">
+        <v>102</v>
+      </c>
+      <c r="F114" s="38"/>
+      <c r="G114" s="38"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A115" s="25" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B115" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C115" s="25">
+        <v>94</v>
+      </c>
+      <c r="F115" s="38"/>
+      <c r="G115" s="38"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A116" s="25" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B116" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C116" s="25">
+        <v>90</v>
+      </c>
+      <c r="F116" s="38"/>
+      <c r="G116" s="38"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A117" s="25" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B117" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C117" s="25">
+        <v>71</v>
+      </c>
+      <c r="F117" s="38"/>
+      <c r="G117" s="38"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F118" s="38"/>
+      <c r="G118" s="38"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F119" s="38"/>
+      <c r="G119" s="38"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F120" s="38"/>
+      <c r="G120" s="38"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F121" s="38"/>
+      <c r="G121" s="38"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F122" s="38"/>
+      <c r="G122" s="38"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F124" s="38"/>
+      <c r="G124" s="38"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F125" s="38"/>
+      <c r="G125" s="38"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F126" s="38"/>
+      <c r="G126" s="38"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F127" s="38"/>
+      <c r="G127" s="38"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F128" s="38"/>
+      <c r="G128" s="38"/>
+    </row>
+    <row r="129" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F129" s="38"/>
+      <c r="G129" s="38"/>
+    </row>
+    <row r="130" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F130" s="38"/>
+      <c r="G130" s="38"/>
+    </row>
+    <row r="131" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F131" s="38"/>
+      <c r="G131" s="38"/>
+    </row>
+    <row r="132" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F132" s="38"/>
+      <c r="G132" s="38"/>
+    </row>
+    <row r="133" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F133" s="38"/>
+      <c r="G133" s="38"/>
+    </row>
+    <row r="135" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F135" s="38"/>
+      <c r="G135" s="38"/>
+    </row>
+    <row r="136" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F136" s="38"/>
+      <c r="G136" s="38"/>
+    </row>
+    <row r="137" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F137" s="38"/>
+      <c r="G137" s="38"/>
+    </row>
+    <row r="139" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F139" s="38"/>
+      <c r="G139" s="38"/>
+    </row>
+    <row r="140" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F140" s="38"/>
+      <c r="G140" s="38"/>
+    </row>
+    <row r="142" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F142" s="38"/>
+      <c r="G142" s="38"/>
+    </row>
+    <row r="143" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F143" s="38"/>
+      <c r="G143" s="38"/>
+    </row>
+    <row r="144" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F144" s="38"/>
+      <c r="G144" s="38"/>
+    </row>
+    <row r="145" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F145" s="38"/>
+      <c r="G145" s="38"/>
+    </row>
+    <row r="146" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F146" s="38"/>
+      <c r="G146" s="38"/>
+    </row>
+    <row r="147" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F147" s="38"/>
+      <c r="G147" s="38"/>
+    </row>
+    <row r="148" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F148" s="38"/>
+      <c r="G148" s="38"/>
+    </row>
+    <row r="149" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F149" s="38"/>
+      <c r="G149" s="38"/>
+    </row>
+    <row r="150" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F150" s="38"/>
+      <c r="G150" s="38"/>
+    </row>
+    <row r="151" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F151" s="38"/>
+      <c r="G151" s="38"/>
+    </row>
+    <row r="152" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F152" s="38"/>
+      <c r="G152" s="38"/>
+    </row>
+    <row r="153" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F153" s="38"/>
+      <c r="G153" s="38"/>
+    </row>
+    <row r="154" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F154" s="38"/>
+      <c r="G154" s="38"/>
+    </row>
+    <row r="155" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F155" s="38"/>
+      <c r="G155" s="38"/>
+    </row>
+    <row r="156" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F156" s="38"/>
+      <c r="G156" s="38"/>
+    </row>
+    <row r="157" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F157" s="38"/>
+      <c r="G157" s="38"/>
+    </row>
+    <row r="159" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F159" s="38"/>
+      <c r="G159" s="38"/>
+    </row>
+    <row r="160" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F160" s="38"/>
+      <c r="G160" s="38"/>
+    </row>
+    <row r="161" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F161" s="38"/>
+      <c r="G161" s="38"/>
+    </row>
+    <row r="162" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F162" s="38"/>
+      <c r="G162" s="38"/>
+    </row>
+    <row r="163" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F163" s="38"/>
+      <c r="G163" s="38"/>
+    </row>
+    <row r="164" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F164" s="38"/>
+      <c r="G164" s="38"/>
+    </row>
+    <row r="165" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F165" s="38"/>
+      <c r="G165" s="38"/>
+    </row>
+    <row r="167" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F167" s="38"/>
+      <c r="G167" s="38"/>
+    </row>
+    <row r="168" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F168" s="38"/>
+      <c r="G168" s="38"/>
+    </row>
+    <row r="169" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F169" s="38"/>
+      <c r="G169" s="38"/>
+    </row>
+    <row r="170" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F170" s="38"/>
+      <c r="G170" s="38"/>
+    </row>
+    <row r="171" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F171" s="38"/>
+      <c r="G171" s="38"/>
+    </row>
+    <row r="172" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F172" s="38"/>
+      <c r="G172" s="38"/>
+    </row>
+    <row r="173" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F173" s="38"/>
+      <c r="G173" s="38"/>
+    </row>
+    <row r="174" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F174" s="38"/>
+      <c r="G174" s="38"/>
+    </row>
+    <row r="175" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F175" s="38"/>
+      <c r="G175" s="38"/>
+    </row>
+    <row r="176" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F176" s="38"/>
+      <c r="G176" s="38"/>
+    </row>
+    <row r="177" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F177" s="38"/>
+      <c r="G177" s="38"/>
+    </row>
+    <row r="178" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F178" s="38"/>
+      <c r="G178" s="38"/>
+    </row>
+    <row r="179" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F179" s="38"/>
+      <c r="G179" s="38"/>
+    </row>
+    <row r="180" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F180" s="38"/>
+      <c r="G180" s="38"/>
+    </row>
+    <row r="181" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F181" s="38"/>
+      <c r="G181" s="38"/>
+    </row>
+    <row r="182" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F182" s="38"/>
+      <c r="G182" s="38"/>
+    </row>
+    <row r="183" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F183" s="38"/>
+      <c r="G183" s="38"/>
+    </row>
+    <row r="184" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F184" s="38"/>
+      <c r="G184" s="38"/>
+    </row>
+    <row r="185" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F185" s="38"/>
+      <c r="G185" s="38"/>
+    </row>
+    <row r="186" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F186" s="38"/>
+      <c r="G186" s="38"/>
+    </row>
+    <row r="187" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F187" s="38"/>
+      <c r="G187" s="38"/>
+    </row>
+    <row r="188" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F188" s="38"/>
+      <c r="G188" s="38"/>
+    </row>
+    <row r="189" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F189" s="38"/>
+      <c r="G189" s="38"/>
+    </row>
+    <row r="190" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F190" s="38"/>
+      <c r="G190" s="38"/>
+    </row>
+    <row r="191" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F191" s="38"/>
+      <c r="G191" s="38"/>
+    </row>
+    <row r="192" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F192" s="38"/>
+      <c r="G192" s="38"/>
+    </row>
+    <row r="193" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F193" s="38"/>
+      <c r="G193" s="38"/>
+    </row>
+    <row r="195" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F195" s="38"/>
+      <c r="G195" s="38"/>
+    </row>
+    <row r="196" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F196" s="38"/>
+      <c r="G196" s="38"/>
+    </row>
+    <row r="197" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F197" s="38"/>
+      <c r="G197" s="38"/>
+    </row>
+    <row r="198" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F198" s="38"/>
+      <c r="G198" s="38"/>
+    </row>
+    <row r="199" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F199" s="38"/>
+      <c r="G199" s="38"/>
+    </row>
+    <row r="200" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F200" s="38"/>
+      <c r="G200" s="38"/>
+    </row>
+    <row r="202" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F202" s="38"/>
+      <c r="G202" s="38"/>
+    </row>
+    <row r="203" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F203" s="38"/>
+      <c r="G203" s="38"/>
+    </row>
+    <row r="204" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F204" s="38"/>
+      <c r="G204" s="38"/>
+    </row>
+    <row r="205" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F205" s="38"/>
+      <c r="G205" s="38"/>
+    </row>
+    <row r="206" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F206" s="38"/>
+      <c r="G206" s="38"/>
+    </row>
+    <row r="207" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F207" s="38"/>
+      <c r="G207" s="38"/>
+    </row>
+    <row r="208" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F208" s="38"/>
+      <c r="G208" s="38"/>
+    </row>
+    <row r="209" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F209" s="38"/>
+      <c r="G209" s="38"/>
+    </row>
+    <row r="210" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F210" s="38"/>
+      <c r="G210" s="38"/>
+    </row>
+    <row r="211" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F211" s="38"/>
+      <c r="G211" s="38"/>
+    </row>
+    <row r="212" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F212" s="38"/>
+      <c r="G212" s="38"/>
+    </row>
+    <row r="213" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F213" s="38"/>
+      <c r="G213" s="38"/>
+    </row>
+    <row r="214" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F214" s="38"/>
+      <c r="G214" s="38"/>
+    </row>
+    <row r="215" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F215" s="38"/>
+      <c r="G215" s="38"/>
+    </row>
+    <row r="216" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F216" s="38"/>
+      <c r="G216" s="38"/>
+    </row>
+    <row r="217" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F217" s="38"/>
+      <c r="G217" s="38"/>
+    </row>
+    <row r="218" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F218" s="38"/>
+      <c r="G218" s="38"/>
+    </row>
+    <row r="219" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F219" s="38"/>
+      <c r="G219" s="38"/>
+    </row>
+    <row r="220" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F220" s="38"/>
+      <c r="G220" s="38"/>
+    </row>
+    <row r="221" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F221" s="38"/>
+      <c r="G221" s="38"/>
+    </row>
+    <row r="222" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F222" s="38"/>
+      <c r="G222" s="38"/>
+    </row>
+    <row r="223" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F223" s="38"/>
+      <c r="G223" s="38"/>
+    </row>
+    <row r="224" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F224" s="38"/>
+      <c r="G224" s="38"/>
+    </row>
+    <row r="225" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F225" s="38"/>
+      <c r="G225" s="38"/>
+    </row>
+    <row r="226" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F226" s="38"/>
+      <c r="G226" s="38"/>
+    </row>
+    <row r="227" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F227" s="38"/>
+      <c r="G227" s="38"/>
+    </row>
+    <row r="228" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F228" s="38"/>
+      <c r="G228" s="38"/>
+    </row>
+    <row r="229" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F229" s="38"/>
+      <c r="G229" s="38"/>
+    </row>
+    <row r="230" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F230" s="38"/>
+      <c r="G230" s="38"/>
+    </row>
+    <row r="231" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F231" s="38"/>
+      <c r="G231" s="38"/>
+    </row>
+    <row r="232" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F232" s="38"/>
+      <c r="G232" s="38"/>
+    </row>
+    <row r="233" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F233" s="38"/>
+      <c r="G233" s="38"/>
+    </row>
+    <row r="234" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F234" s="38"/>
+      <c r="G234" s="38"/>
+    </row>
+    <row r="235" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F235" s="38"/>
+      <c r="G235" s="38"/>
+    </row>
+    <row r="236" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F236" s="38"/>
+      <c r="G236" s="38"/>
+    </row>
+    <row r="237" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F237" s="38"/>
+      <c r="G237" s="38"/>
+    </row>
+    <row r="238" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F238" s="38"/>
+      <c r="G238" s="38"/>
+    </row>
+    <row r="239" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F239" s="38"/>
+      <c r="G239" s="38"/>
+    </row>
+    <row r="240" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F240" s="38"/>
+      <c r="G240" s="38"/>
+    </row>
+    <row r="241" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F241" s="38"/>
+      <c r="G241" s="38"/>
+    </row>
+    <row r="242" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F242" s="38"/>
+      <c r="G242" s="38"/>
+    </row>
+    <row r="243" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F243" s="38"/>
+      <c r="G243" s="38"/>
+    </row>
+    <row r="244" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F244" s="38"/>
+      <c r="G244" s="38"/>
+    </row>
+    <row r="245" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F245" s="38"/>
+      <c r="G245" s="38"/>
+    </row>
+    <row r="246" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F246" s="38"/>
+      <c r="G246" s="38"/>
+    </row>
+    <row r="248" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F248" s="38"/>
+      <c r="G248" s="38"/>
+    </row>
+    <row r="249" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F249" s="38"/>
+      <c r="G249" s="38"/>
+    </row>
+    <row r="250" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F250" s="38"/>
+      <c r="G250" s="38"/>
+    </row>
+    <row r="251" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F251" s="38"/>
+      <c r="G251" s="38"/>
+    </row>
+    <row r="252" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F252" s="38"/>
+      <c r="G252" s="38"/>
+    </row>
+    <row r="253" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F253" s="38"/>
+      <c r="G253" s="38"/>
+    </row>
+    <row r="254" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F254" s="38"/>
+      <c r="G254" s="38"/>
+    </row>
+    <row r="255" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F255" s="38"/>
+      <c r="G255" s="38"/>
+    </row>
+    <row r="256" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F256" s="38"/>
+      <c r="G256" s="38"/>
+    </row>
+    <row r="257" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F257" s="38"/>
+      <c r="G257" s="38"/>
+    </row>
+    <row r="258" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F258" s="38"/>
+      <c r="G258" s="38"/>
+    </row>
+    <row r="259" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F259" s="38"/>
+      <c r="G259" s="38"/>
+    </row>
+    <row r="260" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F260" s="38"/>
+      <c r="G260" s="38"/>
+    </row>
+    <row r="261" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F261" s="38"/>
+      <c r="G261" s="38"/>
+    </row>
+    <row r="262" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F262" s="38"/>
+      <c r="G262" s="38"/>
+    </row>
+    <row r="263" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F263" s="38"/>
+      <c r="G263" s="38"/>
+    </row>
+    <row r="264" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F264" s="38"/>
+      <c r="G264" s="38"/>
+    </row>
+    <row r="265" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F265" s="38"/>
+      <c r="G265" s="38"/>
+    </row>
+    <row r="266" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F266" s="38"/>
+      <c r="G266" s="38"/>
+    </row>
+    <row r="268" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F268" s="38"/>
+      <c r="G268" s="38"/>
+    </row>
+    <row r="269" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F269" s="38"/>
+      <c r="G269" s="38"/>
+    </row>
+    <row r="270" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F270" s="38"/>
+      <c r="G270" s="38"/>
+    </row>
+    <row r="271" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F271" s="38"/>
+      <c r="G271" s="38"/>
+    </row>
+    <row r="272" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F272" s="38"/>
+      <c r="G272" s="38"/>
+    </row>
+    <row r="273" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F273" s="38"/>
+      <c r="G273" s="38"/>
+    </row>
+    <row r="274" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F274" s="38"/>
+      <c r="G274" s="38"/>
+    </row>
+    <row r="275" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F275" s="38"/>
+      <c r="G275" s="38"/>
+    </row>
+    <row r="276" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F276" s="38"/>
+      <c r="G276" s="38"/>
+    </row>
+    <row r="277" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F277" s="38"/>
+      <c r="G277" s="38"/>
+    </row>
+    <row r="278" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="G278" s="38"/>
+    </row>
+    <row r="279" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F279" s="38"/>
+      <c r="G279" s="38"/>
+    </row>
+    <row r="280" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F280" s="38"/>
+      <c r="G280" s="38"/>
+    </row>
+    <row r="281" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F281" s="38"/>
+      <c r="G281" s="38"/>
+    </row>
+    <row r="282" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F282" s="38"/>
+      <c r="G282" s="38"/>
+    </row>
+    <row r="283" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F283" s="38"/>
+      <c r="G283" s="38"/>
+    </row>
+    <row r="284" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F284" s="38"/>
+      <c r="G284" s="38"/>
+    </row>
+    <row r="285" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F285" s="38"/>
+      <c r="G285" s="38"/>
+    </row>
+    <row r="286" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F286" s="38"/>
+      <c r="G286" s="38"/>
+    </row>
+    <row r="287" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F287" s="38"/>
+      <c r="G287" s="38"/>
+    </row>
+    <row r="288" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F288" s="38"/>
+      <c r="G288" s="38"/>
+    </row>
+    <row r="289" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F289" s="38"/>
+      <c r="G289" s="38"/>
+    </row>
+    <row r="290" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F290" s="38"/>
+      <c r="G290" s="38"/>
+    </row>
+    <row r="291" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F291" s="38"/>
+      <c r="G291" s="38"/>
+    </row>
+    <row r="292" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F292" s="38"/>
+      <c r="G292" s="38"/>
+    </row>
+    <row r="293" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F293" s="38"/>
+      <c r="G293" s="38"/>
+    </row>
+    <row r="294" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F294" s="38"/>
+      <c r="G294" s="38"/>
+    </row>
+    <row r="295" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F295" s="38"/>
+      <c r="G295" s="38"/>
+    </row>
+    <row r="296" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F296" s="38"/>
+      <c r="G296" s="38"/>
+    </row>
+    <row r="297" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F297" s="38"/>
+      <c r="G297" s="38"/>
+    </row>
+    <row r="298" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F298" s="38"/>
+      <c r="G298" s="38"/>
+    </row>
+    <row r="299" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F299" s="38"/>
+      <c r="G299" s="38"/>
+    </row>
+    <row r="300" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F300" s="38"/>
+      <c r="G300" s="38"/>
+    </row>
+    <row r="301" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F301" s="38"/>
+      <c r="G301" s="38"/>
+    </row>
+    <row r="302" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F302" s="38"/>
+      <c r="G302" s="38"/>
+    </row>
+    <row r="303" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F303" s="38"/>
+      <c r="G303" s="38"/>
+    </row>
+    <row r="304" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F304" s="38"/>
+      <c r="G304" s="38"/>
+    </row>
+    <row r="305" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F305" s="38"/>
+      <c r="G305" s="38"/>
+    </row>
+    <row r="306" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F306" s="38"/>
+      <c r="G306" s="38"/>
+    </row>
+    <row r="307" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F307" s="38"/>
+      <c r="G307" s="38"/>
+    </row>
+    <row r="308" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F308" s="38"/>
+      <c r="G308" s="38"/>
+    </row>
+    <row r="309" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F309" s="38"/>
+      <c r="G309" s="38"/>
+    </row>
+    <row r="310" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F310" s="38"/>
+      <c r="G310" s="38"/>
+    </row>
+    <row r="311" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F311" s="38"/>
+      <c r="G311" s="38"/>
+    </row>
+    <row r="313" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F313" s="38"/>
+      <c r="G313" s="38"/>
+    </row>
+    <row r="314" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F314" s="38"/>
+      <c r="G314" s="38"/>
+    </row>
+    <row r="315" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F315" s="38"/>
+      <c r="G315" s="38"/>
+    </row>
+    <row r="316" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F316" s="38"/>
+      <c r="G316" s="38"/>
+    </row>
+    <row r="318" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F318" s="38"/>
+      <c r="G318" s="38"/>
+    </row>
+    <row r="319" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F319" s="38"/>
+      <c r="G319" s="38"/>
+    </row>
+    <row r="320" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F320" s="38"/>
+      <c r="G320" s="38"/>
+    </row>
+    <row r="321" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F321" s="38"/>
+      <c r="G321" s="38"/>
+    </row>
+    <row r="323" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F323" s="38"/>
+      <c r="G323" s="38"/>
+    </row>
+    <row r="324" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F324" s="38"/>
+      <c r="G324" s="38"/>
+    </row>
+    <row r="325" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F325" s="38"/>
+      <c r="G325" s="38"/>
+    </row>
+    <row r="327" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F327" s="38"/>
+      <c r="G327" s="38"/>
+    </row>
+    <row r="328" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F328" s="38"/>
+      <c r="G328" s="38"/>
+    </row>
+    <row r="329" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F329" s="38"/>
+      <c r="G329" s="38"/>
+    </row>
+    <row r="330" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F330" s="38"/>
+      <c r="G330" s="38"/>
+    </row>
+    <row r="331" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F331" s="38"/>
+      <c r="G331" s="38"/>
+    </row>
+    <row r="332" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F332" s="38"/>
+      <c r="G332" s="38"/>
+    </row>
+    <row r="333" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F333" s="38"/>
+      <c r="G333" s="38"/>
+    </row>
+    <row r="334" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F334" s="38"/>
+      <c r="G334" s="38"/>
+    </row>
+    <row r="335" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="G335" s="38"/>
+    </row>
+    <row r="336" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F336" s="38"/>
+      <c r="G336" s="38"/>
+    </row>
+    <row r="337" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F337" s="38"/>
+      <c r="G337" s="38"/>
+    </row>
+    <row r="338" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F338" s="38"/>
+      <c r="G338" s="38"/>
+    </row>
+    <row r="339" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F339" s="38"/>
+      <c r="G339" s="38"/>
+    </row>
+    <row r="340" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="G340" s="38"/>
+    </row>
+    <row r="341" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F341" s="38"/>
+      <c r="G341" s="38"/>
+    </row>
+    <row r="342" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F342" s="38"/>
+      <c r="G342" s="38"/>
+    </row>
+    <row r="343" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F343" s="38"/>
+      <c r="G343" s="38"/>
+    </row>
+    <row r="344" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F344" s="38"/>
+      <c r="G344" s="38"/>
+    </row>
+    <row r="345" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F345" s="38"/>
+      <c r="G345" s="38"/>
+    </row>
+    <row r="346" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F346" s="38"/>
+      <c r="G346" s="38"/>
+    </row>
+    <row r="347" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F347" s="38"/>
+      <c r="G347" s="38"/>
+    </row>
+    <row r="348" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F348" s="38"/>
+      <c r="G348" s="38"/>
+    </row>
+    <row r="349" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F349" s="38"/>
+      <c r="G349" s="38"/>
+    </row>
+    <row r="350" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F350" s="38"/>
+      <c r="G350" s="38"/>
+    </row>
+    <row r="351" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F351" s="38"/>
+      <c r="G351" s="38"/>
+    </row>
+    <row r="352" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="G352" s="38"/>
+    </row>
+    <row r="354" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="G354" s="38"/>
+    </row>
+    <row r="355" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F355" s="38"/>
+      <c r="G355" s="38"/>
+    </row>
+    <row r="356" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F356" s="38"/>
+      <c r="G356" s="38"/>
+    </row>
+    <row r="357" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F357" s="38"/>
+      <c r="G357" s="38"/>
+    </row>
+    <row r="358" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F358" s="38"/>
+      <c r="G358" s="38"/>
+    </row>
+    <row r="359" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F359" s="38"/>
+      <c r="G359" s="38"/>
+    </row>
+    <row r="360" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F360" s="38"/>
+      <c r="G360" s="38"/>
+    </row>
+    <row r="361" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F361" s="38"/>
+      <c r="G361" s="38"/>
+    </row>
+    <row r="362" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F362" s="38"/>
+      <c r="G362" s="38"/>
+    </row>
+    <row r="363" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F363" s="38"/>
+      <c r="G363" s="38"/>
+    </row>
+    <row r="364" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F364" s="38"/>
+      <c r="G364" s="38"/>
+    </row>
+    <row r="365" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F365" s="38"/>
+      <c r="G365" s="38"/>
+    </row>
+    <row r="366" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F366" s="38"/>
+      <c r="G366" s="38"/>
+    </row>
+    <row r="367" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F367" s="38"/>
+      <c r="G367" s="38"/>
+    </row>
+    <row r="368" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F368" s="38"/>
+      <c r="G368" s="38"/>
+    </row>
+    <row r="369" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F369" s="38"/>
+      <c r="G369" s="38"/>
+    </row>
+    <row r="370" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F370" s="38"/>
+      <c r="G370" s="38"/>
+    </row>
+    <row r="371" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F371" s="38"/>
+      <c r="G371" s="38"/>
+    </row>
+    <row r="372" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F372" s="38"/>
+      <c r="G372" s="38"/>
+    </row>
+    <row r="373" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F373" s="38"/>
+      <c r="G373" s="38"/>
+    </row>
+    <row r="374" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F374" s="38"/>
+      <c r="G374" s="38"/>
+    </row>
+    <row r="375" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F375" s="38"/>
+      <c r="G375" s="38"/>
+    </row>
+    <row r="376" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F376" s="38"/>
+      <c r="G376" s="38"/>
+    </row>
+    <row r="377" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F377" s="38"/>
+      <c r="G377" s="38"/>
+    </row>
+    <row r="378" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F378" s="38"/>
+      <c r="G378" s="38"/>
+    </row>
+    <row r="379" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F379" s="38"/>
+      <c r="G379" s="38"/>
+    </row>
+    <row r="380" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F380" s="38"/>
+      <c r="G380" s="38"/>
+    </row>
+    <row r="381" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F381" s="38"/>
+      <c r="G381" s="38"/>
+    </row>
+    <row r="382" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F382" s="38"/>
+      <c r="G382" s="38"/>
+    </row>
+    <row r="383" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F383" s="38"/>
+      <c r="G383" s="38"/>
+    </row>
+    <row r="384" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F384" s="38"/>
+      <c r="G384" s="38"/>
+    </row>
+    <row r="385" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F385" s="38"/>
+      <c r="G385" s="38"/>
+    </row>
+    <row r="386" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F386" s="38"/>
+      <c r="G386" s="38"/>
+    </row>
+    <row r="387" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F387" s="38"/>
+      <c r="G387" s="38"/>
+    </row>
+    <row r="388" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F388" s="38"/>
+      <c r="G388" s="38"/>
+    </row>
+    <row r="389" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F389" s="38"/>
+      <c r="G389" s="38"/>
+    </row>
+    <row r="390" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F390" s="38"/>
+      <c r="G390" s="38"/>
+    </row>
+    <row r="391" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F391" s="38"/>
+      <c r="G391" s="38"/>
+    </row>
+    <row r="392" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F392" s="38"/>
+      <c r="G392" s="38"/>
+    </row>
+    <row r="393" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F393" s="38"/>
+      <c r="G393" s="38"/>
+    </row>
+    <row r="394" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F394" s="38"/>
+      <c r="G394" s="38"/>
+    </row>
+    <row r="395" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F395" s="38"/>
+      <c r="G395" s="38"/>
+    </row>
+    <row r="396" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F396" s="38"/>
+      <c r="G396" s="38"/>
+    </row>
+    <row r="397" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F397" s="38"/>
+      <c r="G397" s="38"/>
+    </row>
+    <row r="398" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F398" s="38"/>
+      <c r="G398" s="38"/>
+    </row>
+    <row r="399" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F399" s="38"/>
+      <c r="G399" s="38"/>
+    </row>
+    <row r="400" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F400" s="38"/>
+      <c r="G400" s="38"/>
+    </row>
+    <row r="401" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F401" s="38"/>
+      <c r="G401" s="38"/>
+    </row>
+    <row r="402" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F402" s="38"/>
+      <c r="G402" s="38"/>
+    </row>
+    <row r="403" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F403" s="38"/>
+      <c r="G403" s="38"/>
+    </row>
+    <row r="404" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F404" s="38"/>
+      <c r="G404" s="38"/>
+    </row>
+    <row r="405" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F405" s="38"/>
+      <c r="G405" s="38"/>
+    </row>
+    <row r="406" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F406" s="38"/>
+      <c r="G406" s="38"/>
+    </row>
+    <row r="407" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F407" s="38"/>
+      <c r="G407" s="38"/>
+    </row>
+    <row r="408" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F408" s="38"/>
+      <c r="G408" s="38"/>
+    </row>
+    <row r="409" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F409" s="38"/>
+      <c r="G409" s="38"/>
+    </row>
+    <row r="410" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F410" s="38"/>
+      <c r="G410" s="38"/>
+    </row>
+    <row r="411" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F411" s="38"/>
+      <c r="G411" s="38"/>
+    </row>
+    <row r="412" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F412" s="38"/>
+      <c r="G412" s="38"/>
+    </row>
+    <row r="413" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F413" s="38"/>
+      <c r="G413" s="38"/>
+    </row>
+    <row r="414" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F414" s="38"/>
+      <c r="G414" s="38"/>
+    </row>
+    <row r="415" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F415" s="38"/>
+      <c r="G415" s="38"/>
+    </row>
+    <row r="416" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F416" s="38"/>
+      <c r="G416" s="38"/>
+    </row>
+    <row r="417" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F417" s="38"/>
+      <c r="G417" s="38"/>
+    </row>
+    <row r="418" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F418" s="38"/>
+      <c r="G418" s="38"/>
+    </row>
+    <row r="419" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F419" s="38"/>
+      <c r="G419" s="38"/>
+    </row>
+    <row r="420" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F420" s="38"/>
+      <c r="G420" s="38"/>
+    </row>
+    <row r="421" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F421" s="38"/>
+      <c r="G421" s="38"/>
+    </row>
+    <row r="422" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F422" s="38"/>
+      <c r="G422" s="38"/>
+    </row>
+    <row r="423" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F423" s="38"/>
+      <c r="G423" s="38"/>
+    </row>
+    <row r="425" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F425" s="38"/>
+      <c r="G425" s="38"/>
+    </row>
+    <row r="426" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F426" s="38"/>
+      <c r="G426" s="38"/>
+    </row>
+    <row r="427" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F427" s="38"/>
+      <c r="G427" s="38"/>
+    </row>
+    <row r="428" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F428" s="38"/>
+      <c r="G428" s="38"/>
+    </row>
+    <row r="429" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F429" s="38"/>
+      <c r="G429" s="38"/>
+    </row>
+    <row r="430" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F430" s="38"/>
+      <c r="G430" s="38"/>
+    </row>
+    <row r="431" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F431" s="38"/>
+      <c r="G431" s="38"/>
+    </row>
+    <row r="432" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F432" s="38"/>
+      <c r="G432" s="38"/>
+    </row>
+    <row r="433" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F433" s="38"/>
+      <c r="G433" s="38"/>
+    </row>
+    <row r="434" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F434" s="38"/>
+      <c r="G434" s="38"/>
+    </row>
+    <row r="435" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F435" s="38"/>
+      <c r="G435" s="38"/>
+    </row>
+    <row r="436" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F436" s="38"/>
+      <c r="G436" s="38"/>
+    </row>
+    <row r="437" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F437" s="38"/>
+      <c r="G437" s="38"/>
+    </row>
+    <row r="438" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F438" s="38"/>
+      <c r="G438" s="38"/>
+    </row>
+    <row r="439" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F439" s="38"/>
+      <c r="G439" s="38"/>
+    </row>
+    <row r="440" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F440" s="38"/>
+      <c r="G440" s="38"/>
+    </row>
+    <row r="441" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F441" s="38"/>
+      <c r="G441" s="38"/>
+    </row>
+    <row r="442" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F442" s="38"/>
+      <c r="G442" s="38"/>
+    </row>
+    <row r="443" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F443" s="38"/>
+      <c r="G443" s="38"/>
+    </row>
+    <row r="444" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F444" s="38"/>
+      <c r="G444" s="38"/>
+    </row>
+    <row r="445" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F445" s="38"/>
+      <c r="G445" s="38"/>
+    </row>
+    <row r="446" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F446" s="38"/>
+      <c r="G446" s="38"/>
+    </row>
+    <row r="447" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F447" s="38"/>
+      <c r="G447" s="38"/>
+    </row>
+    <row r="448" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F448" s="38"/>
+      <c r="G448" s="38"/>
+    </row>
+    <row r="449" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F449" s="38"/>
+      <c r="G449" s="38"/>
+    </row>
+    <row r="450" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F450" s="38"/>
+      <c r="G450" s="38"/>
+    </row>
+    <row r="451" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F451" s="38"/>
+      <c r="G451" s="38"/>
+    </row>
+    <row r="452" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F452" s="38"/>
+      <c r="G452" s="38"/>
+    </row>
+    <row r="453" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F453" s="38"/>
+      <c r="G453" s="38"/>
+    </row>
+    <row r="454" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F454" s="38"/>
+      <c r="G454" s="38"/>
+    </row>
+    <row r="455" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F455" s="38"/>
+      <c r="G455" s="38"/>
+    </row>
+    <row r="456" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F456" s="38"/>
+      <c r="G456" s="38"/>
+    </row>
+    <row r="457" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F457" s="38"/>
+      <c r="G457" s="38"/>
+    </row>
+    <row r="458" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F458" s="38"/>
+      <c r="G458" s="38"/>
+    </row>
+    <row r="459" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F459" s="38"/>
+      <c r="G459" s="38"/>
+    </row>
+    <row r="460" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F460" s="38"/>
+      <c r="G460" s="38"/>
+    </row>
+    <row r="461" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F461" s="38"/>
+      <c r="G461" s="38"/>
+    </row>
+    <row r="462" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F462" s="38"/>
+      <c r="G462" s="38"/>
+    </row>
+    <row r="463" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F463" s="38"/>
+      <c r="G463" s="38"/>
+    </row>
+    <row r="464" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F464" s="38"/>
+      <c r="G464" s="38"/>
+    </row>
+    <row r="465" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F465" s="38"/>
+      <c r="G465" s="38"/>
+    </row>
+    <row r="466" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F466" s="38"/>
+      <c r="G466" s="38"/>
+    </row>
+    <row r="467" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F467" s="38"/>
+      <c r="G467" s="38"/>
+    </row>
+    <row r="468" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F468" s="38"/>
+      <c r="G468" s="38"/>
+    </row>
+    <row r="469" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F469" s="38"/>
+      <c r="G469" s="38"/>
+    </row>
+    <row r="470" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F470" s="38"/>
+      <c r="G470" s="38"/>
+    </row>
+    <row r="471" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F471" s="38"/>
+      <c r="G471" s="38"/>
+    </row>
+    <row r="472" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F472" s="38"/>
+      <c r="G472" s="38"/>
+    </row>
+    <row r="473" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F473" s="38"/>
+      <c r="G473" s="38"/>
+    </row>
+    <row r="474" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F474" s="38"/>
+      <c r="G474" s="38"/>
+    </row>
+    <row r="475" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F475" s="38"/>
+      <c r="G475" s="38"/>
+    </row>
+    <row r="476" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F476" s="38"/>
+      <c r="G476" s="38"/>
+    </row>
+    <row r="477" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F477" s="38"/>
+      <c r="G477" s="38"/>
+    </row>
+    <row r="478" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F478" s="38"/>
+      <c r="G478" s="38"/>
+    </row>
+    <row r="479" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F479" s="38"/>
+      <c r="G479" s="38"/>
+    </row>
+    <row r="480" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F480" s="38"/>
+      <c r="G480" s="38"/>
+    </row>
+    <row r="481" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F481" s="38"/>
+      <c r="G481" s="38"/>
+    </row>
+    <row r="482" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F482" s="38"/>
+      <c r="G482" s="38"/>
+    </row>
+    <row r="483" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F483" s="38"/>
+      <c r="G483" s="38"/>
+    </row>
+    <row r="484" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F484" s="38"/>
+      <c r="G484" s="38"/>
+    </row>
+    <row r="485" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F485" s="38"/>
+      <c r="G485" s="38"/>
+    </row>
+    <row r="486" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F486" s="38"/>
+      <c r="G486" s="38"/>
+    </row>
+    <row r="487" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F487" s="38"/>
+      <c r="G487" s="38"/>
+    </row>
+    <row r="488" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F488" s="38"/>
+      <c r="G488" s="38"/>
+    </row>
+    <row r="489" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="G489" s="38"/>
+    </row>
+    <row r="490" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F490" s="38"/>
+      <c r="G490" s="38"/>
+    </row>
+    <row r="491" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F491" s="38"/>
+      <c r="G491" s="38"/>
+    </row>
+    <row r="492" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F492" s="38"/>
+      <c r="G492" s="38"/>
+    </row>
+    <row r="493" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F493" s="38"/>
+      <c r="G493" s="38"/>
+    </row>
+    <row r="494" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F494" s="38"/>
+      <c r="G494" s="38"/>
+    </row>
+    <row r="495" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F495" s="38"/>
+      <c r="G495" s="38"/>
+    </row>
+    <row r="496" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F496" s="38"/>
+      <c r="G496" s="38"/>
+    </row>
+    <row r="497" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F497" s="38"/>
+      <c r="G497" s="38"/>
+    </row>
+    <row r="498" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F498" s="38"/>
+      <c r="G498" s="38"/>
+    </row>
+    <row r="499" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F499" s="38"/>
+      <c r="G499" s="38"/>
+    </row>
+    <row r="500" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F500" s="38"/>
+      <c r="G500" s="38"/>
+    </row>
+    <row r="501" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F501" s="38"/>
+      <c r="G501" s="38"/>
+    </row>
+    <row r="502" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F502" s="38"/>
+      <c r="G502" s="38"/>
+    </row>
+    <row r="503" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F503" s="38"/>
+      <c r="G503" s="38"/>
+    </row>
+    <row r="504" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F504" s="38"/>
+      <c r="G504" s="38"/>
+    </row>
+    <row r="505" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F505" s="38"/>
+      <c r="G505" s="38"/>
+    </row>
+    <row r="506" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F506" s="38"/>
+      <c r="G506" s="38"/>
+    </row>
+    <row r="507" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F507" s="38"/>
+      <c r="G507" s="38"/>
+    </row>
+    <row r="508" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F508" s="38"/>
+      <c r="G508" s="38"/>
+    </row>
+    <row r="509" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F509" s="38"/>
+      <c r="G509" s="38"/>
+    </row>
+    <row r="510" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F510" s="38"/>
+      <c r="G510" s="38"/>
+    </row>
+    <row r="511" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F511" s="38"/>
+      <c r="G511" s="38"/>
+    </row>
+    <row r="512" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F512" s="38"/>
+      <c r="G512" s="38"/>
+    </row>
+    <row r="513" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F513" s="38"/>
+      <c r="G513" s="38"/>
+    </row>
+    <row r="514" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F514" s="38"/>
+      <c r="G514" s="38"/>
+    </row>
+    <row r="515" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F515" s="38"/>
+      <c r="G515" s="38"/>
+    </row>
+    <row r="516" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F516" s="38"/>
+      <c r="G516" s="38"/>
+    </row>
+    <row r="517" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F517" s="38"/>
+      <c r="G517" s="38"/>
+    </row>
+    <row r="518" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F518" s="38"/>
+      <c r="G518" s="38"/>
+    </row>
+    <row r="519" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F519" s="38"/>
+      <c r="G519" s="38"/>
+    </row>
+    <row r="520" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F520" s="38"/>
+      <c r="G520" s="38"/>
+    </row>
+    <row r="521" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F521" s="38"/>
+      <c r="G521" s="38"/>
+    </row>
+    <row r="522" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F522" s="38"/>
+      <c r="G522" s="38"/>
+    </row>
+    <row r="523" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F523" s="38"/>
+      <c r="G523" s="38"/>
+    </row>
+    <row r="525" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F525" s="38"/>
+      <c r="G525" s="38"/>
+    </row>
+    <row r="526" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F526" s="38"/>
+      <c r="G526" s="38"/>
+    </row>
+    <row r="527" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F527" s="38"/>
+      <c r="G527" s="38"/>
+    </row>
+    <row r="528" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F528" s="38"/>
+      <c r="G528" s="38"/>
+    </row>
+    <row r="529" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F529" s="38"/>
+      <c r="G529" s="38"/>
+    </row>
+    <row r="530" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F530" s="38"/>
+      <c r="G530" s="38"/>
+    </row>
+    <row r="531" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F531" s="38"/>
+      <c r="G531" s="38"/>
+    </row>
+    <row r="532" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F532" s="38"/>
+      <c r="G532" s="38"/>
+    </row>
+    <row r="533" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="G533" s="38"/>
+    </row>
+    <row r="534" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F534" s="38"/>
+      <c r="G534" s="38"/>
+    </row>
+    <row r="535" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F535" s="38"/>
+      <c r="G535" s="38"/>
+    </row>
+    <row r="536" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F536" s="38"/>
+      <c r="G536" s="38"/>
+    </row>
+    <row r="537" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F537" s="38"/>
+      <c r="G537" s="38"/>
+    </row>
+    <row r="538" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F538" s="38"/>
+      <c r="G538" s="38"/>
+    </row>
+    <row r="539" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F539" s="38"/>
+      <c r="G539" s="38"/>
+    </row>
+    <row r="540" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F540" s="38"/>
+      <c r="G540" s="38"/>
+    </row>
+    <row r="541" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F541" s="38"/>
+      <c r="G541" s="38"/>
+    </row>
+    <row r="542" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F542" s="38"/>
+      <c r="G542" s="38"/>
+    </row>
+    <row r="543" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F543" s="38"/>
+      <c r="G543" s="38"/>
+    </row>
+    <row r="544" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F544" s="38"/>
+      <c r="G544" s="38"/>
+    </row>
+    <row r="545" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F545" s="38"/>
+      <c r="G545" s="38"/>
+    </row>
+    <row r="546" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F546" s="38"/>
+      <c r="G546" s="38"/>
+    </row>
+    <row r="547" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F547" s="38"/>
+      <c r="G547" s="38"/>
+    </row>
+    <row r="548" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F548" s="38"/>
+      <c r="G548" s="38"/>
+    </row>
+    <row r="549" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F549" s="38"/>
+      <c r="G549" s="38"/>
+    </row>
+    <row r="550" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F550" s="38"/>
+      <c r="G550" s="38"/>
+    </row>
+    <row r="551" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F551" s="38"/>
+      <c r="G551" s="38"/>
+    </row>
+    <row r="552" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F552" s="38"/>
+      <c r="G552" s="38"/>
+    </row>
+    <row r="553" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F553" s="38"/>
+      <c r="G553" s="38"/>
+    </row>
+    <row r="554" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F554" s="38"/>
+      <c r="G554" s="38"/>
+    </row>
+    <row r="555" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F555" s="38"/>
+      <c r="G555" s="38"/>
+    </row>
+    <row r="556" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F556" s="38"/>
+      <c r="G556" s="38"/>
+    </row>
+    <row r="557" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F557" s="38"/>
+      <c r="G557" s="38"/>
+    </row>
+    <row r="558" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F558" s="38"/>
+      <c r="G558" s="38"/>
+    </row>
+    <row r="559" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F559" s="38"/>
+      <c r="G559" s="38"/>
+    </row>
+    <row r="560" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F560" s="38"/>
+      <c r="G560" s="38"/>
+    </row>
+    <row r="561" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F561" s="38"/>
+      <c r="G561" s="38"/>
+    </row>
+    <row r="562" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F562" s="38"/>
+      <c r="G562" s="38"/>
+    </row>
+    <row r="563" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F563" s="38"/>
+      <c r="G563" s="38"/>
+    </row>
+    <row r="564" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F564" s="38"/>
+      <c r="G564" s="38"/>
+    </row>
+    <row r="565" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F565" s="38"/>
+      <c r="G565" s="38"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -25006,7 +29835,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28830BBA-01E9-4290-8134-6C4FA2F187F1}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -27161,7 +31990,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98F72596-567D-4A46-9580-D5E8D1461B30}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -28435,7 +33264,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -29425,1209 +34254,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FFFFC000"/>
-  </sheetPr>
-  <dimension ref="A1:F113"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="15.1796875" style="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.81640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7265625" style="25" customWidth="1"/>
-    <col min="4" max="16384" width="8.7265625" style="25"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="25" t="s">
-        <v>813</v>
-      </c>
-      <c r="B2" s="25">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="25" t="s">
-        <v>814</v>
-      </c>
-      <c r="B3" s="25">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="25" t="s">
-        <v>815</v>
-      </c>
-      <c r="B4" s="25">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="25" t="s">
-        <v>816</v>
-      </c>
-      <c r="B5" s="25">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="25" t="s">
-        <v>817</v>
-      </c>
-      <c r="B6" s="25">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="25" t="s">
-        <v>818</v>
-      </c>
-      <c r="B7" s="25">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="25" t="s">
-        <v>819</v>
-      </c>
-      <c r="B8" s="25">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="25" t="s">
-        <v>820</v>
-      </c>
-      <c r="B9" s="25">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="25" t="s">
-        <v>821</v>
-      </c>
-      <c r="B10" s="25">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="25" t="s">
-        <v>822</v>
-      </c>
-      <c r="B11" s="25">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="25" t="s">
-        <v>823</v>
-      </c>
-      <c r="B12" s="25">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="25" t="s">
-        <v>824</v>
-      </c>
-      <c r="B13" s="25">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="25" t="s">
-        <v>825</v>
-      </c>
-      <c r="B14" s="25">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="25" t="s">
-        <v>826</v>
-      </c>
-      <c r="B15" s="25">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="25" t="s">
-        <v>827</v>
-      </c>
-      <c r="B16" s="25">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="25" t="s">
-        <v>828</v>
-      </c>
-      <c r="B17" s="25">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="25" t="s">
-        <v>829</v>
-      </c>
-      <c r="B18" s="25">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="25" t="s">
-        <v>830</v>
-      </c>
-      <c r="B19" s="25">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="25" t="s">
-        <v>831</v>
-      </c>
-      <c r="B20" s="25">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="25" t="s">
-        <v>832</v>
-      </c>
-      <c r="B21" s="26">
-        <v>79</v>
-      </c>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="25" t="s">
-        <v>833</v>
-      </c>
-      <c r="B22" s="26">
-        <v>78</v>
-      </c>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="25" t="s">
-        <v>834</v>
-      </c>
-      <c r="B23" s="26">
-        <v>76</v>
-      </c>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="25" t="s">
-        <v>835</v>
-      </c>
-      <c r="B24" s="26">
-        <v>73</v>
-      </c>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="25" t="s">
-        <v>836</v>
-      </c>
-      <c r="B25" s="26">
-        <v>72</v>
-      </c>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="25" t="s">
-        <v>837</v>
-      </c>
-      <c r="B26" s="26">
-        <v>71</v>
-      </c>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="25" t="s">
-        <v>838</v>
-      </c>
-      <c r="B27" s="26">
-        <v>68</v>
-      </c>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="25" t="s">
-        <v>192</v>
-      </c>
-      <c r="B28" s="26">
-        <v>67</v>
-      </c>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="26">
-        <v>66</v>
-      </c>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="25" t="s">
-        <v>214</v>
-      </c>
-      <c r="B30" s="26">
-        <v>65</v>
-      </c>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="25" t="s">
-        <v>839</v>
-      </c>
-      <c r="B31" s="26">
-        <v>63</v>
-      </c>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="25" t="s">
-        <v>840</v>
-      </c>
-      <c r="B32" s="26">
-        <v>63</v>
-      </c>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="25" t="s">
-        <v>841</v>
-      </c>
-      <c r="B33" s="26">
-        <v>61</v>
-      </c>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="25" t="s">
-        <v>842</v>
-      </c>
-      <c r="B34" s="26">
-        <v>61</v>
-      </c>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="B35" s="26">
-        <v>60</v>
-      </c>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="B36" s="26">
-        <v>59</v>
-      </c>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="25" t="s">
-        <v>843</v>
-      </c>
-      <c r="B37" s="26">
-        <v>59</v>
-      </c>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="25" t="s">
-        <v>844</v>
-      </c>
-      <c r="B38" s="26">
-        <v>55</v>
-      </c>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="25" t="s">
-        <v>845</v>
-      </c>
-      <c r="B39" s="26">
-        <v>55</v>
-      </c>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="B40" s="26">
-        <v>54</v>
-      </c>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="25" t="s">
-        <v>846</v>
-      </c>
-      <c r="B41" s="26">
-        <v>54</v>
-      </c>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="25" t="s">
-        <v>847</v>
-      </c>
-      <c r="B42" s="26">
-        <v>50</v>
-      </c>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="25" t="s">
-        <v>848</v>
-      </c>
-      <c r="B43" s="26">
-        <v>49</v>
-      </c>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="26"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="25" t="s">
-        <v>849</v>
-      </c>
-      <c r="B44" s="26">
-        <v>49</v>
-      </c>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="26"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="25" t="s">
-        <v>850</v>
-      </c>
-      <c r="B45" s="26">
-        <v>48</v>
-      </c>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="26"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="25" t="s">
-        <v>851</v>
-      </c>
-      <c r="B46" s="26">
-        <v>46</v>
-      </c>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="25" t="s">
-        <v>852</v>
-      </c>
-      <c r="B47" s="26">
-        <v>46</v>
-      </c>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B48" s="26">
-        <v>44</v>
-      </c>
-      <c r="D48" s="26"/>
-      <c r="E48" s="26"/>
-      <c r="F48" s="26"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="B49" s="26">
-        <v>42</v>
-      </c>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" s="25" t="s">
-        <v>853</v>
-      </c>
-      <c r="B50" s="26">
-        <v>42</v>
-      </c>
-      <c r="D50" s="26"/>
-      <c r="E50" s="26"/>
-      <c r="F50" s="26"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" s="25" t="s">
-        <v>854</v>
-      </c>
-      <c r="B51" s="26">
-        <v>42</v>
-      </c>
-      <c r="D51" s="26"/>
-      <c r="E51" s="26"/>
-      <c r="F51" s="26"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A52" s="25" t="s">
-        <v>855</v>
-      </c>
-      <c r="B52" s="26">
-        <v>41</v>
-      </c>
-      <c r="D52" s="26"/>
-      <c r="E52" s="26"/>
-      <c r="F52" s="26"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A53" s="25" t="s">
-        <v>856</v>
-      </c>
-      <c r="B53" s="26">
-        <v>41</v>
-      </c>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A54" s="25" t="s">
-        <v>857</v>
-      </c>
-      <c r="B54" s="26">
-        <v>41</v>
-      </c>
-      <c r="D54" s="26"/>
-      <c r="E54" s="26"/>
-      <c r="F54" s="26"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A55" s="25" t="s">
-        <v>858</v>
-      </c>
-      <c r="B55" s="26">
-        <v>40</v>
-      </c>
-      <c r="D55" s="26"/>
-      <c r="E55" s="26"/>
-      <c r="F55" s="26"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A56" s="25" t="s">
-        <v>859</v>
-      </c>
-      <c r="B56" s="26">
-        <v>40</v>
-      </c>
-      <c r="D56" s="26"/>
-      <c r="E56" s="26"/>
-      <c r="F56" s="26"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A57" s="25" t="s">
-        <v>860</v>
-      </c>
-      <c r="B57" s="26">
-        <v>38</v>
-      </c>
-      <c r="D57" s="26"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="26"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A58" s="25" t="s">
-        <v>861</v>
-      </c>
-      <c r="B58" s="26">
-        <v>38</v>
-      </c>
-      <c r="D58" s="26"/>
-      <c r="E58" s="26"/>
-      <c r="F58" s="26"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A59" s="25" t="s">
-        <v>862</v>
-      </c>
-      <c r="B59" s="26">
-        <v>37</v>
-      </c>
-      <c r="D59" s="26"/>
-      <c r="E59" s="26"/>
-      <c r="F59" s="26"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A60" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="B60" s="26">
-        <v>35</v>
-      </c>
-      <c r="D60" s="26"/>
-      <c r="E60" s="26"/>
-      <c r="F60" s="26"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A61" s="25" t="s">
-        <v>863</v>
-      </c>
-      <c r="B61" s="26">
-        <v>35</v>
-      </c>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A62" s="25" t="s">
-        <v>864</v>
-      </c>
-      <c r="B62" s="26">
-        <v>35</v>
-      </c>
-      <c r="D62" s="26"/>
-      <c r="E62" s="26"/>
-      <c r="F62" s="26"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A63" s="25" t="s">
-        <v>865</v>
-      </c>
-      <c r="B63" s="26">
-        <v>33</v>
-      </c>
-      <c r="D63" s="26"/>
-      <c r="E63" s="26"/>
-      <c r="F63" s="26"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A64" s="25" t="s">
-        <v>866</v>
-      </c>
-      <c r="B64" s="26">
-        <v>33</v>
-      </c>
-      <c r="D64" s="26"/>
-      <c r="E64" s="26"/>
-      <c r="F64" s="26"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A65" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="B65" s="26">
-        <v>33</v>
-      </c>
-      <c r="D65" s="26"/>
-      <c r="E65" s="26"/>
-      <c r="F65" s="26"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A66" s="25" t="s">
-        <v>441</v>
-      </c>
-      <c r="B66" s="26">
-        <v>31</v>
-      </c>
-      <c r="D66" s="26"/>
-      <c r="E66" s="26"/>
-      <c r="F66" s="26"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A67" s="25" t="s">
-        <v>867</v>
-      </c>
-      <c r="B67" s="26">
-        <v>30</v>
-      </c>
-      <c r="D67" s="26"/>
-      <c r="E67" s="26"/>
-      <c r="F67" s="26"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A68" s="25" t="s">
-        <v>868</v>
-      </c>
-      <c r="B68" s="26">
-        <v>29</v>
-      </c>
-      <c r="D68" s="26"/>
-      <c r="E68" s="26"/>
-      <c r="F68" s="26"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A69" s="25" t="s">
-        <v>869</v>
-      </c>
-      <c r="B69" s="26">
-        <v>27</v>
-      </c>
-      <c r="D69" s="26"/>
-      <c r="E69" s="26"/>
-      <c r="F69" s="26"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A70" s="25" t="s">
-        <v>870</v>
-      </c>
-      <c r="B70" s="26">
-        <v>27</v>
-      </c>
-      <c r="D70" s="26"/>
-      <c r="E70" s="26"/>
-      <c r="F70" s="26"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A71" s="25" t="s">
-        <v>871</v>
-      </c>
-      <c r="B71" s="26">
-        <v>26</v>
-      </c>
-      <c r="D71" s="26"/>
-      <c r="E71" s="26"/>
-      <c r="F71" s="26"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A72" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B72" s="26">
-        <v>26</v>
-      </c>
-      <c r="D72" s="26"/>
-      <c r="E72" s="26"/>
-      <c r="F72" s="26"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A73" s="25" t="s">
-        <v>872</v>
-      </c>
-      <c r="B73" s="26">
-        <v>25</v>
-      </c>
-      <c r="D73" s="26"/>
-      <c r="E73" s="26"/>
-      <c r="F73" s="26"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A74" s="25" t="s">
-        <v>873</v>
-      </c>
-      <c r="B74" s="26">
-        <v>24</v>
-      </c>
-      <c r="D74" s="26"/>
-      <c r="E74" s="26"/>
-      <c r="F74" s="26"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A75" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="26">
-        <v>23</v>
-      </c>
-      <c r="D75" s="26"/>
-      <c r="E75" s="26"/>
-      <c r="F75" s="26"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A76" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="B76" s="26">
-        <v>23</v>
-      </c>
-      <c r="D76" s="26"/>
-      <c r="E76" s="26"/>
-      <c r="F76" s="26"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A77" s="25" t="s">
-        <v>874</v>
-      </c>
-      <c r="B77" s="26">
-        <v>22</v>
-      </c>
-      <c r="D77" s="26"/>
-      <c r="E77" s="26"/>
-      <c r="F77" s="26"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A78" s="25" t="s">
-        <v>875</v>
-      </c>
-      <c r="B78" s="26">
-        <v>22</v>
-      </c>
-      <c r="D78" s="26"/>
-      <c r="E78" s="26"/>
-      <c r="F78" s="26"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" s="25" t="s">
-        <v>272</v>
-      </c>
-      <c r="B79" s="26">
-        <v>22</v>
-      </c>
-      <c r="D79" s="26"/>
-      <c r="E79" s="26"/>
-      <c r="F79" s="26"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A80" s="25" t="s">
-        <v>876</v>
-      </c>
-      <c r="B80" s="26">
-        <v>22</v>
-      </c>
-      <c r="D80" s="26"/>
-      <c r="E80" s="26"/>
-      <c r="F80" s="26"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A81" s="25" t="s">
-        <v>877</v>
-      </c>
-      <c r="B81" s="26">
-        <v>21</v>
-      </c>
-      <c r="D81" s="26"/>
-      <c r="E81" s="26"/>
-      <c r="F81" s="26"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A82" s="25" t="s">
-        <v>878</v>
-      </c>
-      <c r="B82" s="26">
-        <v>20</v>
-      </c>
-      <c r="D82" s="26"/>
-      <c r="E82" s="26"/>
-      <c r="F82" s="26"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A83" s="25" t="s">
-        <v>879</v>
-      </c>
-      <c r="B83" s="26">
-        <v>19</v>
-      </c>
-      <c r="D83" s="26"/>
-      <c r="E83" s="26"/>
-      <c r="F83" s="26"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A84" s="25" t="s">
-        <v>880</v>
-      </c>
-      <c r="B84" s="26">
-        <v>19</v>
-      </c>
-      <c r="D84" s="26"/>
-      <c r="E84" s="26"/>
-      <c r="F84" s="26"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A85" s="25" t="s">
-        <v>881</v>
-      </c>
-      <c r="B85" s="26">
-        <v>19</v>
-      </c>
-      <c r="D85" s="26"/>
-      <c r="E85" s="26"/>
-      <c r="F85" s="26"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A86" s="25" t="s">
-        <v>882</v>
-      </c>
-      <c r="B86" s="26">
-        <v>19</v>
-      </c>
-      <c r="D86" s="26"/>
-      <c r="E86" s="26"/>
-      <c r="F86" s="26"/>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A87" s="25" t="s">
-        <v>549</v>
-      </c>
-      <c r="B87" s="26">
-        <v>19</v>
-      </c>
-      <c r="D87" s="26"/>
-      <c r="E87" s="26"/>
-      <c r="F87" s="26"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A88" s="25" t="s">
-        <v>883</v>
-      </c>
-      <c r="B88" s="26">
-        <v>19</v>
-      </c>
-      <c r="D88" s="26"/>
-      <c r="E88" s="26"/>
-      <c r="F88" s="26"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A89" s="25" t="s">
-        <v>190</v>
-      </c>
-      <c r="B89" s="26">
-        <v>18</v>
-      </c>
-      <c r="D89" s="26"/>
-      <c r="E89" s="26"/>
-      <c r="F89" s="26"/>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A90" s="25" t="s">
-        <v>884</v>
-      </c>
-      <c r="B90" s="26">
-        <v>18</v>
-      </c>
-      <c r="D90" s="26"/>
-      <c r="E90" s="26"/>
-      <c r="F90" s="26"/>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A91" s="25" t="s">
-        <v>885</v>
-      </c>
-      <c r="B91" s="26">
-        <v>18</v>
-      </c>
-      <c r="D91" s="26"/>
-      <c r="E91" s="26"/>
-      <c r="F91" s="26"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A92" s="25" t="s">
-        <v>886</v>
-      </c>
-      <c r="B92" s="26">
-        <v>18</v>
-      </c>
-      <c r="D92" s="26"/>
-      <c r="E92" s="26"/>
-      <c r="F92" s="26"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A93" s="25" t="s">
-        <v>887</v>
-      </c>
-      <c r="B93" s="26">
-        <v>18</v>
-      </c>
-      <c r="D93" s="26"/>
-      <c r="E93" s="26"/>
-      <c r="F93" s="26"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A94" s="25" t="s">
-        <v>888</v>
-      </c>
-      <c r="B94" s="26">
-        <v>17</v>
-      </c>
-      <c r="D94" s="26"/>
-      <c r="E94" s="26"/>
-      <c r="F94" s="26"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A95" s="25" t="s">
-        <v>889</v>
-      </c>
-      <c r="B95" s="26">
-        <v>17</v>
-      </c>
-      <c r="D95" s="26"/>
-      <c r="E95" s="26"/>
-      <c r="F95" s="26"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" s="25" t="s">
-        <v>467</v>
-      </c>
-      <c r="B96" s="26">
-        <v>17</v>
-      </c>
-      <c r="D96" s="26"/>
-      <c r="E96" s="26"/>
-      <c r="F96" s="26"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A97" s="25" t="s">
-        <v>890</v>
-      </c>
-      <c r="B97" s="26">
-        <v>17</v>
-      </c>
-      <c r="D97" s="26"/>
-      <c r="E97" s="26"/>
-      <c r="F97" s="26"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A98" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="B98" s="26">
-        <v>16</v>
-      </c>
-      <c r="D98" s="26"/>
-      <c r="E98" s="26"/>
-      <c r="F98" s="26"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" s="25" t="s">
-        <v>891</v>
-      </c>
-      <c r="B99" s="26">
-        <v>16</v>
-      </c>
-      <c r="D99" s="26"/>
-      <c r="E99" s="26"/>
-      <c r="F99" s="26"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="25" t="s">
-        <v>892</v>
-      </c>
-      <c r="B100" s="26">
-        <v>16</v>
-      </c>
-      <c r="D100" s="26"/>
-      <c r="E100" s="26"/>
-      <c r="F100" s="26"/>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="25" t="s">
-        <v>893</v>
-      </c>
-      <c r="B101" s="26">
-        <v>15</v>
-      </c>
-      <c r="D101" s="26"/>
-      <c r="E101" s="26"/>
-      <c r="F101" s="26"/>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="25" t="s">
-        <v>894</v>
-      </c>
-      <c r="B102" s="26">
-        <v>15</v>
-      </c>
-      <c r="D102" s="26"/>
-      <c r="E102" s="26"/>
-      <c r="F102" s="26"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" s="25" t="s">
-        <v>895</v>
-      </c>
-      <c r="B103" s="26">
-        <v>14</v>
-      </c>
-      <c r="D103" s="26"/>
-      <c r="E103" s="26"/>
-      <c r="F103" s="26"/>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" s="25" t="s">
-        <v>896</v>
-      </c>
-      <c r="B104" s="26">
-        <v>14</v>
-      </c>
-      <c r="D104" s="26"/>
-      <c r="E104" s="26"/>
-      <c r="F104" s="26"/>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" s="25" t="s">
-        <v>897</v>
-      </c>
-      <c r="B105" s="26">
-        <v>14</v>
-      </c>
-      <c r="D105" s="26"/>
-      <c r="E105" s="26"/>
-      <c r="F105" s="26"/>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" s="25" t="s">
-        <v>898</v>
-      </c>
-      <c r="B106" s="26">
-        <v>14</v>
-      </c>
-      <c r="D106" s="26"/>
-      <c r="E106" s="26"/>
-      <c r="F106" s="26"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="25" t="s">
-        <v>899</v>
-      </c>
-      <c r="B107" s="26">
-        <v>13</v>
-      </c>
-      <c r="D107" s="26"/>
-      <c r="E107" s="26"/>
-      <c r="F107" s="26"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="25" t="s">
-        <v>900</v>
-      </c>
-      <c r="B108" s="26">
-        <v>13</v>
-      </c>
-      <c r="D108" s="26"/>
-      <c r="E108" s="26"/>
-      <c r="F108" s="26"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="B109" s="26">
-        <v>13</v>
-      </c>
-      <c r="D109" s="26"/>
-      <c r="E109" s="26"/>
-      <c r="F109" s="26"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="25" t="s">
-        <v>901</v>
-      </c>
-      <c r="B110" s="26">
-        <v>13</v>
-      </c>
-      <c r="D110" s="26"/>
-      <c r="E110" s="26"/>
-      <c r="F110" s="26"/>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" s="25" t="s">
-        <v>715</v>
-      </c>
-      <c r="B111" s="26">
-        <v>12</v>
-      </c>
-      <c r="D111" s="26"/>
-      <c r="E111" s="26"/>
-      <c r="F111" s="26"/>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" s="25" t="s">
-        <v>902</v>
-      </c>
-      <c r="B112" s="26">
-        <v>12</v>
-      </c>
-      <c r="D112" s="26"/>
-      <c r="E112" s="26"/>
-      <c r="F112" s="26"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" s="25" t="s">
-        <v>903</v>
-      </c>
-      <c r="B113" s="26">
-        <v>12</v>
-      </c>
-      <c r="D113" s="26"/>
-      <c r="E113" s="26"/>
-      <c r="F113" s="26"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/Stats For Rush.xlsx
+++ b/Stats For Rush.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurtl\Desktop\statstreaks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16771134-18BD-49CB-9BD0-7F53F462318A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67B47A3-FDE6-4623-AB99-628566AA4D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" tabRatio="866" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="866" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PL assists" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,15 @@
     <sheet name="PL Appearances" sheetId="3" r:id="rId3"/>
     <sheet name="Intl Appearances" sheetId="4" r:id="rId4"/>
     <sheet name="Womens int" sheetId="13" r:id="rId5"/>
-    <sheet name="Intl Goals" sheetId="5" r:id="rId6"/>
-    <sheet name="Man and liv g" sheetId="11" r:id="rId7"/>
-    <sheet name="Arsenalspurs goals" sheetId="12" r:id="rId8"/>
-    <sheet name="Man U goals" sheetId="6" r:id="rId9"/>
-    <sheet name="Liverpool goals" sheetId="7" r:id="rId10"/>
-    <sheet name="Champs league goals" sheetId="9" r:id="rId11"/>
-    <sheet name="La Liga goals" sheetId="8" r:id="rId12"/>
-    <sheet name="Transfers" sheetId="10" r:id="rId13"/>
+    <sheet name="Eng cap" sheetId="14" r:id="rId6"/>
+    <sheet name="Intl Goals" sheetId="5" r:id="rId7"/>
+    <sheet name="Man and liv g" sheetId="11" r:id="rId8"/>
+    <sheet name="Arsenalspurs goals" sheetId="12" r:id="rId9"/>
+    <sheet name="Man U goals" sheetId="6" r:id="rId10"/>
+    <sheet name="Liverpool goals" sheetId="7" r:id="rId11"/>
+    <sheet name="Champs league goals" sheetId="9" r:id="rId12"/>
+    <sheet name="La Liga goals" sheetId="8" r:id="rId13"/>
+    <sheet name="Transfers" sheetId="10" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3458" uniqueCount="1396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4124" uniqueCount="1615">
   <si>
     <t>Rank</t>
   </si>
@@ -4236,6 +4237,663 @@
   </si>
   <si>
     <t>Anita Asante</t>
+  </si>
+  <si>
+    <t>Pos.</t>
+  </si>
+  <si>
+    <t>FW / MF</t>
+  </si>
+  <si>
+    <t>HB</t>
+  </si>
+  <si>
+    <t>John Stones</t>
+  </si>
+  <si>
+    <t>Kenny Sansom</t>
+  </si>
+  <si>
+    <t>Ray Wilkins</t>
+  </si>
+  <si>
+    <t>MF / FW</t>
+  </si>
+  <si>
+    <t>Jordan Pickford</t>
+  </si>
+  <si>
+    <t>Stuart Pearce</t>
+  </si>
+  <si>
+    <t>Terry Butcher</t>
+  </si>
+  <si>
+    <t>Gordon Banks †</t>
+  </si>
+  <si>
+    <t>Alan Ball Jr. †</t>
+  </si>
+  <si>
+    <t>Declan Rice</t>
+  </si>
+  <si>
+    <t>Martin Peters †</t>
+  </si>
+  <si>
+    <t>David Watson</t>
+  </si>
+  <si>
+    <t>Ray Wilson †</t>
+  </si>
+  <si>
+    <t>DF / MF</t>
+  </si>
+  <si>
+    <t>Ray Clemence</t>
+  </si>
+  <si>
+    <t>MF / DF</t>
+  </si>
+  <si>
+    <t>Des Walker</t>
+  </si>
+  <si>
+    <t>Johnny Haynes</t>
+  </si>
+  <si>
+    <t>Stanley Matthews</t>
+  </si>
+  <si>
+    <t>Trevor Francis</t>
+  </si>
+  <si>
+    <t>Ron Flowers †</t>
+  </si>
+  <si>
+    <t>Geoff Hurst †</t>
+  </si>
+  <si>
+    <t>Jimmy Dickinson</t>
+  </si>
+  <si>
+    <t>Colin Bell</t>
+  </si>
+  <si>
+    <t>Trevor Brooking</t>
+  </si>
+  <si>
+    <t>Mick Channon</t>
+  </si>
+  <si>
+    <t>Gary Stevens</t>
+  </si>
+  <si>
+    <t>Jude Bellingham</t>
+  </si>
+  <si>
+    <t>Mark Wright</t>
+  </si>
+  <si>
+    <t>Jimmy Armfield †</t>
+  </si>
+  <si>
+    <t>Chris Woods</t>
+  </si>
+  <si>
+    <t>Mick Mills</t>
+  </si>
+  <si>
+    <t>Tony Woodcock</t>
+  </si>
+  <si>
+    <t>David Batty</t>
+  </si>
+  <si>
+    <t>Bob Crompton</t>
+  </si>
+  <si>
+    <t>FB</t>
+  </si>
+  <si>
+    <t>George Cohen †</t>
+  </si>
+  <si>
+    <t>Bryan Douglas</t>
+  </si>
+  <si>
+    <t>Trevor Steven</t>
+  </si>
+  <si>
+    <t>Mason Mount</t>
+  </si>
+  <si>
+    <t>Ronnie Clayton</t>
+  </si>
+  <si>
+    <t>Alan Mullery</t>
+  </si>
+  <si>
+    <t>Jack Charlton †</t>
+  </si>
+  <si>
+    <t>Paul Mariner</t>
+  </si>
+  <si>
+    <t>Roger Hunt †</t>
+  </si>
+  <si>
+    <t>Roger Byrne</t>
+  </si>
+  <si>
+    <t>Ron Springett †</t>
+  </si>
+  <si>
+    <t>Kieron Dyer</t>
+  </si>
+  <si>
+    <t>Alf Ramsey †</t>
+  </si>
+  <si>
+    <t>Mark Hateley</t>
+  </si>
+  <si>
+    <t>Kalvin Phillips</t>
+  </si>
+  <si>
+    <t>Eddie Hapgood</t>
+  </si>
+  <si>
+    <t>Viv Anderson</t>
+  </si>
+  <si>
+    <t>Danny Rose</t>
+  </si>
+  <si>
+    <t>Nobby Stiles †</t>
+  </si>
+  <si>
+    <t>Norman Hunter †</t>
+  </si>
+  <si>
+    <t>Roy McFarland</t>
+  </si>
+  <si>
+    <t>Neil Franklin</t>
+  </si>
+  <si>
+    <t>Keith Newton</t>
+  </si>
+  <si>
+    <t>Francis Lee</t>
+  </si>
+  <si>
+    <t>Colin Todd</t>
+  </si>
+  <si>
+    <t>Trevor Cherry</t>
+  </si>
+  <si>
+    <t>Phil Jones</t>
+  </si>
+  <si>
+    <t>Marc Guéhi</t>
+  </si>
+  <si>
+    <t>Billy Wedlock</t>
+  </si>
+  <si>
+    <t>Ernie Blenkinsop</t>
+  </si>
+  <si>
+    <t>Sammy Crooks</t>
+  </si>
+  <si>
+    <t>Wilf Mannion</t>
+  </si>
+  <si>
+    <t>Brian Labone</t>
+  </si>
+  <si>
+    <t>Neil Webb</t>
+  </si>
+  <si>
+    <t>Joleon Lescott</t>
+  </si>
+  <si>
+    <t>Jesse Pennington</t>
+  </si>
+  <si>
+    <t>Roy Goodall</t>
+  </si>
+  <si>
+    <t>Harry Hibbs</t>
+  </si>
+  <si>
+    <t>Stan Mortensen</t>
+  </si>
+  <si>
+    <t>Bert Williams</t>
+  </si>
+  <si>
+    <t>Martin Chivers</t>
+  </si>
+  <si>
+    <t>Paul Madeley</t>
+  </si>
+  <si>
+    <t>Steve Hodge</t>
+  </si>
+  <si>
+    <t>Tommy Lawton</t>
+  </si>
+  <si>
+    <t>Gil Merrick</t>
+  </si>
+  <si>
+    <t>Don Howe</t>
+  </si>
+  <si>
+    <t>Maurice Norman</t>
+  </si>
+  <si>
+    <t>Ben Warren</t>
+  </si>
+  <si>
+    <t>Peter Barnes</t>
+  </si>
+  <si>
+    <t>Reece James</t>
+  </si>
+  <si>
+    <t>Conor Gallagher</t>
+  </si>
+  <si>
+    <t>Sam Hardy</t>
+  </si>
+  <si>
+    <t>Cliff Bastin</t>
+  </si>
+  <si>
+    <t>Rob Lee</t>
+  </si>
+  <si>
+    <t>Matthew Upson</t>
+  </si>
+  <si>
+    <t>Ben Chilwell</t>
+  </si>
+  <si>
+    <t>G. O. Smith</t>
+  </si>
+  <si>
+    <t>Alfred Strange</t>
+  </si>
+  <si>
+    <t>Wilf Copping</t>
+  </si>
+  <si>
+    <t>Bobby Robson</t>
+  </si>
+  <si>
+    <t>FW / HB</t>
+  </si>
+  <si>
+    <t>John Connelly †</t>
+  </si>
+  <si>
+    <t>Terry Cooper</t>
+  </si>
+  <si>
+    <t>Terry Fenwick</t>
+  </si>
+  <si>
+    <t>Fabian Delph</t>
+  </si>
+  <si>
+    <t>Norman Bailey</t>
+  </si>
+  <si>
+    <t>George Male</t>
+  </si>
+  <si>
+    <t>Vic Woodley</t>
+  </si>
+  <si>
+    <t>Frank Swift</t>
+  </si>
+  <si>
+    <t>Peter Swan</t>
+  </si>
+  <si>
+    <t>George Eastham †</t>
+  </si>
+  <si>
+    <t>Terry Paine †</t>
+  </si>
+  <si>
+    <t>Allan Clarke</t>
+  </si>
+  <si>
+    <t>Peter Storey</t>
+  </si>
+  <si>
+    <t>Paul Parker</t>
+  </si>
+  <si>
+    <t>Danny Mills</t>
+  </si>
+  <si>
+    <t>Ryan Bertrand</t>
+  </si>
+  <si>
+    <t>Charles Bambridge</t>
+  </si>
+  <si>
+    <t>Billy Walker</t>
+  </si>
+  <si>
+    <t>Eric Brook</t>
+  </si>
+  <si>
+    <t>Duncan Edwards</t>
+  </si>
+  <si>
+    <t>HB / FW</t>
+  </si>
+  <si>
+    <t>Brian Greenhoff</t>
+  </si>
+  <si>
+    <t>Carlton Palmer</t>
+  </si>
+  <si>
+    <t>Tyrone Mings</t>
+  </si>
+  <si>
+    <t>Ezri Konsa</t>
+  </si>
+  <si>
+    <t>Laurie Scott</t>
+  </si>
+  <si>
+    <t>John Aston Sr.</t>
+  </si>
+  <si>
+    <t>Bill Eckersley</t>
+  </si>
+  <si>
+    <t>Jeff Hall</t>
+  </si>
+  <si>
+    <t>Tony Currie</t>
+  </si>
+  <si>
+    <t>Graham Rix</t>
+  </si>
+  <si>
+    <t>Alvin Martin</t>
+  </si>
+  <si>
+    <t>Anthony Gordon</t>
+  </si>
+  <si>
+    <t>Billy Bassett</t>
+  </si>
+  <si>
+    <t>Ernest Needham</t>
+  </si>
+  <si>
+    <t>William Oakley</t>
+  </si>
+  <si>
+    <t>Willis Edwards</t>
+  </si>
+  <si>
+    <t>Dixie Dean</t>
+  </si>
+  <si>
+    <t>Gary Mabbutt</t>
+  </si>
+  <si>
+    <t>Eberechi Eze</t>
+  </si>
+  <si>
+    <t>Tom Cooper</t>
+  </si>
+  <si>
+    <t>Bobby Smith</t>
+  </si>
+  <si>
+    <t>Stuart Pearson</t>
+  </si>
+  <si>
+    <t>Tony Dorigo</t>
+  </si>
+  <si>
+    <t>Joe Gomez</t>
+  </si>
+  <si>
+    <t>John Goodall</t>
+  </si>
+  <si>
+    <t>Jimmy Crabtree</t>
+  </si>
+  <si>
+    <t>HB / FB</t>
+  </si>
+  <si>
+    <t>Bob Kelly</t>
+  </si>
+  <si>
+    <t>Len Goulden</t>
+  </si>
+  <si>
+    <t>Ivor Broadis</t>
+  </si>
+  <si>
+    <t>Derek Kevan</t>
+  </si>
+  <si>
+    <t>Eddie Hopkinson</t>
+  </si>
+  <si>
+    <t>Gordon Milne</t>
+  </si>
+  <si>
+    <t>Malcolm Macdonald</t>
+  </si>
+  <si>
+    <t>Luther Blissett</t>
+  </si>
+  <si>
+    <t>David Rocastle</t>
+  </si>
+  <si>
+    <t>Nigel Clough</t>
+  </si>
+  <si>
+    <t>Nathaniel Clyne</t>
+  </si>
+  <si>
+    <t>Tinsley Lindley</t>
+  </si>
+  <si>
+    <t>Percy Melmoth Walters</t>
+  </si>
+  <si>
+    <t>Raich Carter</t>
+  </si>
+  <si>
+    <t>Henry Cockburn</t>
+  </si>
+  <si>
+    <t>George Hardwick</t>
+  </si>
+  <si>
+    <t>Jackie Milburn</t>
+  </si>
+  <si>
+    <t>Jack Froggatt</t>
+  </si>
+  <si>
+    <t>Peter Reid</t>
+  </si>
+  <si>
+    <t>Steve Bull</t>
+  </si>
+  <si>
+    <t>Micah Richards</t>
+  </si>
+  <si>
+    <t>Tom Cleverley</t>
+  </si>
+  <si>
+    <t>Andros Townsend</t>
+  </si>
+  <si>
+    <t>Morgan Rogers</t>
+  </si>
+  <si>
+    <t>Charlie Athersmith</t>
+  </si>
+  <si>
+    <t>George Wilson</t>
+  </si>
+  <si>
+    <t>Joe Bradford</t>
+  </si>
+  <si>
+    <t>Ken Willingham</t>
+  </si>
+  <si>
+    <t>Stan Cullis</t>
+  </si>
+  <si>
+    <t>Jimmy Mullen</t>
+  </si>
+  <si>
+    <t>Roy Bentley</t>
+  </si>
+  <si>
+    <t>Dennis Wilshaw</t>
+  </si>
+  <si>
+    <t>Bill Slater</t>
+  </si>
+  <si>
+    <t>Gerry Francis</t>
+  </si>
+  <si>
+    <t>Bob Latchford</t>
+  </si>
+  <si>
+    <t>Dave Watson</t>
+  </si>
+  <si>
+    <t>Andy Sinton</t>
+  </si>
+  <si>
+    <t>Robert Green</t>
+  </si>
+  <si>
+    <t>Adam Johnson</t>
+  </si>
+  <si>
+    <t>Michael Keane</t>
+  </si>
+  <si>
+    <t>Kobbie Mainoo</t>
+  </si>
+  <si>
+    <t>Jimmy Forrest</t>
+  </si>
+  <si>
+    <t>Jack Robinson</t>
+  </si>
+  <si>
+    <t>Jock Rutherford</t>
+  </si>
+  <si>
+    <t>Arthur Bridgett</t>
+  </si>
+  <si>
+    <t>Harold Fleming</t>
+  </si>
+  <si>
+    <t>Jack Hill</t>
+  </si>
+  <si>
+    <t>Jack Barker</t>
+  </si>
+  <si>
+    <t>Bert Sproston</t>
+  </si>
+  <si>
+    <t>Bobby Langton</t>
+  </si>
+  <si>
+    <t>Johnny Byrne</t>
+  </si>
+  <si>
+    <t>Tommy Wright</t>
+  </si>
+  <si>
+    <t>Russell Osman</t>
+  </si>
+  <si>
+    <t>Peter Withe</t>
+  </si>
+  <si>
+    <t>Tim Flowers</t>
+  </si>
+  <si>
+    <t>Rickie Lambert</t>
+  </si>
+  <si>
+    <t>Tammy Abraham</t>
+  </si>
+  <si>
+    <t>Ruben Loftus-Cheek</t>
+  </si>
+  <si>
+    <t>Johnny Holt</t>
+  </si>
+  <si>
+    <t>Tommy Crawshaw</t>
+  </si>
+  <si>
+    <t>George Holley</t>
+  </si>
+  <si>
+    <t>Willie Hall</t>
+  </si>
+  <si>
+    <t>Harry Johnston</t>
+  </si>
+  <si>
+    <t>Gordon Cowans</t>
+  </si>
+  <si>
+    <t>Mike Duxbury</t>
+  </si>
+  <si>
+    <t>Kieran Gibbs</t>
+  </si>
+  <si>
+    <t>Harry Winks</t>
+  </si>
+  <si>
+    <t>Nick Pope</t>
+  </si>
+  <si>
+    <t>Conor Coady</t>
+  </si>
+  <si>
+    <t>Noni Madueke</t>
+  </si>
+  <si>
+    <t>Bobby Moore</t>
   </si>
 </sst>
 </file>
@@ -4647,6 +5305,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7322E742-DC59-4087-8560-8C5794A10624}" name="Table5" displayName="Table5" ref="B2:E333" totalsRowShown="0">
+  <autoFilter ref="B2:E333" xr:uid="{7322E742-DC59-4087-8560-8C5794A10624}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{0C999B38-3833-43CB-96EF-38447879121C}" name="Player"/>
+    <tableColumn id="2" xr3:uid="{0AA9306F-E92A-49DC-96A0-E09D3E98A142}" name="Pos."/>
+    <tableColumn id="3" xr3:uid="{FC098C55-5A7A-479A-94D8-8B8C43F21CB7}" name="Caps"/>
+    <tableColumn id="4" xr3:uid="{7E5C07F1-9F84-4137-8CC4-0EFDAFF2D3A8}" name="Goals"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{BAB16F13-4D5B-4E4F-A69F-0A941D92DCFA}" name="Table4" displayName="Table4" ref="B2:D115" totalsRowShown="0">
   <autoFilter ref="B2:D115" xr:uid="{BAB16F13-4D5B-4E4F-A69F-0A941D92DCFA}"/>
   <tableColumns count="3">
@@ -4658,7 +5329,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:B121" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A1:B121" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B101">
@@ -4672,7 +5343,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:B200" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
   <autoFilter ref="A1:B200" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="2">
@@ -4683,7 +5354,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table3" displayName="Table3" ref="A1:C120" totalsRowShown="0">
   <autoFilter ref="A1:C120" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C120">
@@ -9067,6 +9738,998 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="A1:B121"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.36328125" style="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.54296875" style="24" customWidth="1"/>
+    <col min="3" max="3" width="3.81640625" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="24" customWidth="1"/>
+    <col min="5" max="16384" width="8.7265625" style="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="24" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="24">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="24" t="s">
+        <v>740</v>
+      </c>
+      <c r="B3" s="24">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="24" t="s">
+        <v>653</v>
+      </c>
+      <c r="B4" s="24">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="24" t="s">
+        <v>741</v>
+      </c>
+      <c r="B5" s="24">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="24" t="s">
+        <v>742</v>
+      </c>
+      <c r="B6" s="24">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="24" t="s">
+        <v>655</v>
+      </c>
+      <c r="B7" s="24">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="24">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="24" t="s">
+        <v>743</v>
+      </c>
+      <c r="B9" s="24">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="B10" s="24">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="24">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="B12" s="24">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="24" t="s">
+        <v>744</v>
+      </c>
+      <c r="B13" s="24">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="B14" s="24">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="24" t="s">
+        <v>745</v>
+      </c>
+      <c r="B15" s="24">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="24">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="24" t="s">
+        <v>746</v>
+      </c>
+      <c r="B17" s="24">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="24" t="s">
+        <v>747</v>
+      </c>
+      <c r="B18" s="24">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="24" t="s">
+        <v>748</v>
+      </c>
+      <c r="B19" s="24">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="24">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="24" t="s">
+        <v>749</v>
+      </c>
+      <c r="B21" s="24">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="24" t="s">
+        <v>628</v>
+      </c>
+      <c r="B22" s="24">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="B23" s="24">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="24">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="24">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="24" t="s">
+        <v>750</v>
+      </c>
+      <c r="B26" s="24">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="24" t="s">
+        <v>737</v>
+      </c>
+      <c r="B27" s="24">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="24" t="s">
+        <v>751</v>
+      </c>
+      <c r="B28" s="24">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="24">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="24" t="s">
+        <v>752</v>
+      </c>
+      <c r="B30" s="24">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="24" t="s">
+        <v>753</v>
+      </c>
+      <c r="B31" s="24">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="24" t="s">
+        <v>754</v>
+      </c>
+      <c r="B32" s="24">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="24">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" s="24">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="24">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="24" t="s">
+        <v>755</v>
+      </c>
+      <c r="B36" s="24">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="24" t="s">
+        <v>285</v>
+      </c>
+      <c r="B37" s="24">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" s="24">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="B39" s="24">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="B40" s="24">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="B41" s="24">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="B42" s="24">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="24" t="s">
+        <v>756</v>
+      </c>
+      <c r="B43" s="24">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="24" t="s">
+        <v>757</v>
+      </c>
+      <c r="B44" s="24">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="24" t="s">
+        <v>758</v>
+      </c>
+      <c r="B45" s="24">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="24" t="s">
+        <v>759</v>
+      </c>
+      <c r="B46" s="24">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="24" t="s">
+        <v>760</v>
+      </c>
+      <c r="B47" s="24">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="24" t="s">
+        <v>761</v>
+      </c>
+      <c r="B48" s="24">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="24" t="s">
+        <v>423</v>
+      </c>
+      <c r="B49" s="24">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" s="24" t="s">
+        <v>762</v>
+      </c>
+      <c r="B50" s="24">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="B51" s="24">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="24" t="s">
+        <v>763</v>
+      </c>
+      <c r="B52" s="24">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" s="24" t="s">
+        <v>467</v>
+      </c>
+      <c r="B53" s="24">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="24" t="s">
+        <v>764</v>
+      </c>
+      <c r="B54" s="24">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" s="24" t="s">
+        <v>765</v>
+      </c>
+      <c r="B55" s="24">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" s="24" t="s">
+        <v>766</v>
+      </c>
+      <c r="B56" s="24">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" s="24" t="s">
+        <v>767</v>
+      </c>
+      <c r="B57" s="24">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="B58" s="24">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" s="24" t="s">
+        <v>768</v>
+      </c>
+      <c r="B59" s="24">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" s="24" t="s">
+        <v>414</v>
+      </c>
+      <c r="B60" s="24">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="B61" s="24">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" s="24" t="s">
+        <v>769</v>
+      </c>
+      <c r="B62" s="24">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" s="24" t="s">
+        <v>770</v>
+      </c>
+      <c r="B63" s="24">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" s="24" t="s">
+        <v>771</v>
+      </c>
+      <c r="B64" s="24">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" s="24" t="s">
+        <v>772</v>
+      </c>
+      <c r="B65" s="24">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B66" s="24">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" s="24" t="s">
+        <v>773</v>
+      </c>
+      <c r="B67" s="24">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" s="24" t="s">
+        <v>774</v>
+      </c>
+      <c r="B68" s="24">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="B69" s="24">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" s="24" t="s">
+        <v>775</v>
+      </c>
+      <c r="B70" s="24">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" s="24" t="s">
+        <v>776</v>
+      </c>
+      <c r="B71" s="24">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" s="24" t="s">
+        <v>777</v>
+      </c>
+      <c r="B72" s="24">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" s="24" t="s">
+        <v>332</v>
+      </c>
+      <c r="B73" s="24">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" s="24" t="s">
+        <v>778</v>
+      </c>
+      <c r="B74" s="24">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" s="24" t="s">
+        <v>779</v>
+      </c>
+      <c r="B75" s="24">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" s="24" t="s">
+        <v>780</v>
+      </c>
+      <c r="B76" s="24">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" s="24" t="s">
+        <v>781</v>
+      </c>
+      <c r="B77" s="24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="B78" s="24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" s="24" t="s">
+        <v>782</v>
+      </c>
+      <c r="B79" s="24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" s="24" t="s">
+        <v>783</v>
+      </c>
+      <c r="B80" s="24">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" s="24" t="s">
+        <v>784</v>
+      </c>
+      <c r="B81" s="24">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" s="24" t="s">
+        <v>785</v>
+      </c>
+      <c r="B82" s="24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" s="24" t="s">
+        <v>786</v>
+      </c>
+      <c r="B83" s="24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" s="24" t="s">
+        <v>787</v>
+      </c>
+      <c r="B84" s="24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85" s="24" t="s">
+        <v>788</v>
+      </c>
+      <c r="B85" s="24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" s="24" t="s">
+        <v>789</v>
+      </c>
+      <c r="B86" s="24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" s="24" t="s">
+        <v>790</v>
+      </c>
+      <c r="B87" s="24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88" s="24" t="s">
+        <v>791</v>
+      </c>
+      <c r="B88" s="24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" s="24" t="s">
+        <v>792</v>
+      </c>
+      <c r="B89" s="24">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90" s="24" t="s">
+        <v>793</v>
+      </c>
+      <c r="B90" s="24">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91" s="24" t="s">
+        <v>794</v>
+      </c>
+      <c r="B91" s="24">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A92" s="24" t="s">
+        <v>795</v>
+      </c>
+      <c r="B92" s="24">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93" s="24" t="s">
+        <v>796</v>
+      </c>
+      <c r="B93" s="24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B94" s="24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A95" s="24" t="s">
+        <v>365</v>
+      </c>
+      <c r="B95" s="24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A96" s="24" t="s">
+        <v>308</v>
+      </c>
+      <c r="B96" s="24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97" s="24" t="s">
+        <v>310</v>
+      </c>
+      <c r="B97" s="24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98" s="24" t="s">
+        <v>797</v>
+      </c>
+      <c r="B98" s="24">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" s="24" t="s">
+        <v>572</v>
+      </c>
+      <c r="B99" s="24">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="B100" s="24">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" s="24" t="s">
+        <v>798</v>
+      </c>
+      <c r="B101" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" s="24" t="s">
+        <v>799</v>
+      </c>
+      <c r="B102" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" s="24" t="s">
+        <v>800</v>
+      </c>
+      <c r="B103" s="24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104" s="24" t="s">
+        <v>801</v>
+      </c>
+      <c r="B104" s="24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105" s="24" t="s">
+        <v>802</v>
+      </c>
+      <c r="B105" s="24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106" s="24" t="s">
+        <v>465</v>
+      </c>
+      <c r="B106" s="24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107" s="24" t="s">
+        <v>803</v>
+      </c>
+      <c r="B107" s="24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" s="24" t="s">
+        <v>804</v>
+      </c>
+      <c r="B108" s="24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A109" s="24" t="s">
+        <v>805</v>
+      </c>
+      <c r="B109" s="24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A110" s="24" t="s">
+        <v>614</v>
+      </c>
+      <c r="B110" s="24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A111" s="24" t="s">
+        <v>806</v>
+      </c>
+      <c r="B111" s="24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A112" s="24" t="s">
+        <v>807</v>
+      </c>
+      <c r="B112" s="24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A113" s="24" t="s">
+        <v>808</v>
+      </c>
+      <c r="B113" s="24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A114" s="24" t="s">
+        <v>581</v>
+      </c>
+      <c r="B114" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A115" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="B115" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A116" s="24" t="s">
+        <v>809</v>
+      </c>
+      <c r="B116" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A117" s="24" t="s">
+        <v>537</v>
+      </c>
+      <c r="B117" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A118" s="24" t="s">
+        <v>810</v>
+      </c>
+      <c r="B118" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A119" s="24" t="s">
+        <v>811</v>
+      </c>
+      <c r="B119" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A120" s="24" t="s">
+        <v>812</v>
+      </c>
+      <c r="B120" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A121" s="24" t="s">
+        <v>460</v>
+      </c>
+      <c r="B121" s="24">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -10271,7 +11934,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -11612,7 +13275,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -12964,7 +14627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -27423,6 +29086,4676 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CFFBFA1-CA33-48C3-9699-1E7D6FB62738}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="B2:E333"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="45.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.08984375" customWidth="1"/>
+    <col min="5" max="5" width="7.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D3">
+        <v>125</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D4">
+        <v>120</v>
+      </c>
+      <c r="E4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>293</v>
+      </c>
+      <c r="D5">
+        <v>115</v>
+      </c>
+      <c r="E5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>293</v>
+      </c>
+      <c r="D6">
+        <v>114</v>
+      </c>
+      <c r="E6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D7">
+        <v>112</v>
+      </c>
+      <c r="E7">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C8" t="s">
+        <v>306</v>
+      </c>
+      <c r="D8">
+        <v>108</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>367</v>
+      </c>
+      <c r="C9" t="s">
+        <v>306</v>
+      </c>
+      <c r="D9">
+        <v>107</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>740</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D10">
+        <v>106</v>
+      </c>
+      <c r="E10">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>293</v>
+      </c>
+      <c r="D11">
+        <v>106</v>
+      </c>
+      <c r="E11">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>588</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D12">
+        <v>105</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" t="s">
+        <v>306</v>
+      </c>
+      <c r="D13">
+        <v>96</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>628</v>
+      </c>
+      <c r="C14" t="s">
+        <v>293</v>
+      </c>
+      <c r="D14">
+        <v>90</v>
+      </c>
+      <c r="E14">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" t="s">
+        <v>301</v>
+      </c>
+      <c r="D15">
+        <v>89</v>
+      </c>
+      <c r="E15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" t="s">
+        <v>293</v>
+      </c>
+      <c r="D16">
+        <v>89</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C17" t="s">
+        <v>306</v>
+      </c>
+      <c r="D17">
+        <v>87</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C18" t="s">
+        <v>306</v>
+      </c>
+      <c r="D18">
+        <v>86</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>270</v>
+      </c>
+      <c r="C19" t="s">
+        <v>306</v>
+      </c>
+      <c r="D19">
+        <v>85</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C20" t="s">
+        <v>293</v>
+      </c>
+      <c r="D20">
+        <v>84</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D21">
+        <v>82</v>
+      </c>
+      <c r="E21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C22" t="s">
+        <v>298</v>
+      </c>
+      <c r="D22">
+        <v>82</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>310</v>
+      </c>
+      <c r="C23" t="s">
+        <v>306</v>
+      </c>
+      <c r="D23">
+        <v>81</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>665</v>
+      </c>
+      <c r="C24" t="s">
+        <v>301</v>
+      </c>
+      <c r="D24">
+        <v>80</v>
+      </c>
+      <c r="E24">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C25" t="s">
+        <v>293</v>
+      </c>
+      <c r="D25">
+        <v>79</v>
+      </c>
+      <c r="E25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C26" t="s">
+        <v>306</v>
+      </c>
+      <c r="D26">
+        <v>78</v>
+      </c>
+      <c r="E26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>316</v>
+      </c>
+      <c r="C27" t="s">
+        <v>306</v>
+      </c>
+      <c r="D27">
+        <v>78</v>
+      </c>
+      <c r="E27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C28" t="s">
+        <v>306</v>
+      </c>
+      <c r="D28">
+        <v>77</v>
+      </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>702</v>
+      </c>
+      <c r="C29" t="s">
+        <v>301</v>
+      </c>
+      <c r="D29">
+        <v>76</v>
+      </c>
+      <c r="E29">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>411</v>
+      </c>
+      <c r="C30" t="s">
+        <v>298</v>
+      </c>
+      <c r="D30">
+        <v>75</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>415</v>
+      </c>
+      <c r="C31" t="s">
+        <v>298</v>
+      </c>
+      <c r="D31">
+        <v>75</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B32" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C32" t="s">
+        <v>298</v>
+      </c>
+      <c r="D32">
+        <v>73</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B33" t="s">
+        <v>312</v>
+      </c>
+      <c r="C33" t="s">
+        <v>306</v>
+      </c>
+      <c r="D33">
+        <v>73</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B34" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C34" t="s">
+        <v>293</v>
+      </c>
+      <c r="D34">
+        <v>72</v>
+      </c>
+      <c r="E34">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B35" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C35" t="s">
+        <v>293</v>
+      </c>
+      <c r="D35">
+        <v>72</v>
+      </c>
+      <c r="E35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B36" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" t="s">
+        <v>301</v>
+      </c>
+      <c r="D36">
+        <v>70</v>
+      </c>
+      <c r="E36">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B37" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C37" t="s">
+        <v>293</v>
+      </c>
+      <c r="D37">
+        <v>67</v>
+      </c>
+      <c r="E37">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B38" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C38" t="s">
+        <v>306</v>
+      </c>
+      <c r="D38">
+        <v>66</v>
+      </c>
+      <c r="E38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B39" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" t="s">
+        <v>293</v>
+      </c>
+      <c r="D39">
+        <v>66</v>
+      </c>
+      <c r="E39">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
+        <v>776</v>
+      </c>
+      <c r="C40" t="s">
+        <v>306</v>
+      </c>
+      <c r="D40">
+        <v>66</v>
+      </c>
+      <c r="E40">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B41" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C41" t="s">
+        <v>306</v>
+      </c>
+      <c r="D41">
+        <v>65</v>
+      </c>
+      <c r="E41">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B42" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C42" t="s">
+        <v>306</v>
+      </c>
+      <c r="D42">
+        <v>63</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B43" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C43" t="s">
+        <v>301</v>
+      </c>
+      <c r="D43">
+        <v>63</v>
+      </c>
+      <c r="E43">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" t="s">
+        <v>301</v>
+      </c>
+      <c r="D44">
+        <v>63</v>
+      </c>
+      <c r="E44">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B45" t="s">
+        <v>849</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D45">
+        <v>62</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B46" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C46" t="s">
+        <v>293</v>
+      </c>
+      <c r="D46">
+        <v>62</v>
+      </c>
+      <c r="E46">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B47" t="s">
+        <v>714</v>
+      </c>
+      <c r="C47" t="s">
+        <v>293</v>
+      </c>
+      <c r="D47">
+        <v>62</v>
+      </c>
+      <c r="E47">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B48" t="s">
+        <v>72</v>
+      </c>
+      <c r="C48" t="s">
+        <v>301</v>
+      </c>
+      <c r="D48">
+        <v>62</v>
+      </c>
+      <c r="E48">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B49" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C49" t="s">
+        <v>298</v>
+      </c>
+      <c r="D49">
+        <v>61</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B50" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D50">
+        <v>61</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B51" t="s">
+        <v>363</v>
+      </c>
+      <c r="C51" t="s">
+        <v>306</v>
+      </c>
+      <c r="D51">
+        <v>61</v>
+      </c>
+      <c r="E51">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B52" t="s">
+        <v>219</v>
+      </c>
+      <c r="C52" t="s">
+        <v>301</v>
+      </c>
+      <c r="D52">
+        <v>59</v>
+      </c>
+      <c r="E52">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B53" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C53" t="s">
+        <v>306</v>
+      </c>
+      <c r="D53">
+        <v>59</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B54" t="s">
+        <v>308</v>
+      </c>
+      <c r="C54" t="s">
+        <v>306</v>
+      </c>
+      <c r="D54">
+        <v>59</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B55" t="s">
+        <v>670</v>
+      </c>
+      <c r="C55" t="s">
+        <v>301</v>
+      </c>
+      <c r="D55">
+        <v>57</v>
+      </c>
+      <c r="E55">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B56" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C56" t="s">
+        <v>293</v>
+      </c>
+      <c r="D56">
+        <v>57</v>
+      </c>
+      <c r="E56">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B57" t="s">
+        <v>343</v>
+      </c>
+      <c r="C57" t="s">
+        <v>306</v>
+      </c>
+      <c r="D57">
+        <v>57</v>
+      </c>
+      <c r="E57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B58" t="s">
+        <v>171</v>
+      </c>
+      <c r="C58" t="s">
+        <v>301</v>
+      </c>
+      <c r="D58">
+        <v>57</v>
+      </c>
+      <c r="E58">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B59" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C59" t="s">
+        <v>301</v>
+      </c>
+      <c r="D59">
+        <v>56</v>
+      </c>
+      <c r="E59">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B60" t="s">
+        <v>160</v>
+      </c>
+      <c r="C60" t="s">
+        <v>293</v>
+      </c>
+      <c r="D60">
+        <v>56</v>
+      </c>
+      <c r="E60">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B61" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C61" t="s">
+        <v>301</v>
+      </c>
+      <c r="D61">
+        <v>54</v>
+      </c>
+      <c r="E61">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B62" t="s">
+        <v>394</v>
+      </c>
+      <c r="C62" t="s">
+        <v>306</v>
+      </c>
+      <c r="D62">
+        <v>54</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B63" t="s">
+        <v>135</v>
+      </c>
+      <c r="C63" t="s">
+        <v>306</v>
+      </c>
+      <c r="D63">
+        <v>54</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B64" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C64" t="s">
+        <v>293</v>
+      </c>
+      <c r="D64">
+        <v>53</v>
+      </c>
+      <c r="E64">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B65" t="s">
+        <v>467</v>
+      </c>
+      <c r="C65" t="s">
+        <v>293</v>
+      </c>
+      <c r="D65">
+        <v>53</v>
+      </c>
+      <c r="E65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B66" t="s">
+        <v>297</v>
+      </c>
+      <c r="C66" t="s">
+        <v>298</v>
+      </c>
+      <c r="D66">
+        <v>53</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B67" t="s">
+        <v>43</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D67">
+        <v>53</v>
+      </c>
+      <c r="E67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B68" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D68">
+        <v>52</v>
+      </c>
+      <c r="E68">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B69" t="s">
+        <v>28</v>
+      </c>
+      <c r="C69" t="s">
+        <v>301</v>
+      </c>
+      <c r="D69">
+        <v>51</v>
+      </c>
+      <c r="E69">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B70" t="s">
+        <v>843</v>
+      </c>
+      <c r="C70" t="s">
+        <v>306</v>
+      </c>
+      <c r="D70">
+        <v>50</v>
+      </c>
+      <c r="E70">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B71" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D71">
+        <v>49</v>
+      </c>
+      <c r="E71">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B72" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C72" t="s">
+        <v>301</v>
+      </c>
+      <c r="D72">
+        <v>49</v>
+      </c>
+      <c r="E72">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B73" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D73">
+        <v>49</v>
+      </c>
+      <c r="E73">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B74" t="s">
+        <v>205</v>
+      </c>
+      <c r="C74" t="s">
+        <v>293</v>
+      </c>
+      <c r="D74">
+        <v>49</v>
+      </c>
+      <c r="E74">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B75" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D75">
+        <v>48</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B76" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C76" t="s">
+        <v>293</v>
+      </c>
+      <c r="D76">
+        <v>48</v>
+      </c>
+      <c r="E76">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B77" t="s">
+        <v>90</v>
+      </c>
+      <c r="C77" t="s">
+        <v>301</v>
+      </c>
+      <c r="D77">
+        <v>48</v>
+      </c>
+      <c r="E77">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B78" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C78" t="s">
+        <v>293</v>
+      </c>
+      <c r="D78">
+        <v>47</v>
+      </c>
+      <c r="E78">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B79" t="s">
+        <v>58</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D79">
+        <v>47</v>
+      </c>
+      <c r="E79">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B80" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C80" t="s">
+        <v>301</v>
+      </c>
+      <c r="D80">
+        <v>46</v>
+      </c>
+      <c r="E80">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B81" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C81" t="s">
+        <v>306</v>
+      </c>
+      <c r="D81">
+        <v>46</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B82" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C82" t="s">
+        <v>293</v>
+      </c>
+      <c r="D82">
+        <v>46</v>
+      </c>
+      <c r="E82">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B83" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C83" t="s">
+        <v>306</v>
+      </c>
+      <c r="D83">
+        <v>45</v>
+      </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B84" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C84" t="s">
+        <v>306</v>
+      </c>
+      <c r="D84">
+        <v>43</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B85" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C85" t="s">
+        <v>298</v>
+      </c>
+      <c r="D85">
+        <v>43</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B86" t="s">
+        <v>434</v>
+      </c>
+      <c r="C86" t="s">
+        <v>306</v>
+      </c>
+      <c r="D86">
+        <v>43</v>
+      </c>
+      <c r="E86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B87" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D87">
+        <v>42</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B88" t="s">
+        <v>901</v>
+      </c>
+      <c r="C88" t="s">
+        <v>306</v>
+      </c>
+      <c r="D88">
+        <v>42</v>
+      </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B89" t="s">
+        <v>753</v>
+      </c>
+      <c r="C89" t="s">
+        <v>293</v>
+      </c>
+      <c r="D89">
+        <v>42</v>
+      </c>
+      <c r="E89">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B90" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C90" t="s">
+        <v>301</v>
+      </c>
+      <c r="D90">
+        <v>42</v>
+      </c>
+      <c r="E90">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B91" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C91" t="s">
+        <v>293</v>
+      </c>
+      <c r="D91">
+        <v>42</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B92" t="s">
+        <v>811</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D92">
+        <v>42</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B93" t="s">
+        <v>57</v>
+      </c>
+      <c r="C93" t="s">
+        <v>301</v>
+      </c>
+      <c r="D93">
+        <v>42</v>
+      </c>
+      <c r="E93">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B94" t="s">
+        <v>185</v>
+      </c>
+      <c r="C94" t="s">
+        <v>301</v>
+      </c>
+      <c r="D94">
+        <v>42</v>
+      </c>
+      <c r="E94">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B95" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D95">
+        <v>41</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B96" t="s">
+        <v>377</v>
+      </c>
+      <c r="C96" t="s">
+        <v>298</v>
+      </c>
+      <c r="D96">
+        <v>41</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B97" t="s">
+        <v>378</v>
+      </c>
+      <c r="C97" t="s">
+        <v>306</v>
+      </c>
+      <c r="D97">
+        <v>40</v>
+      </c>
+      <c r="E97">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B98" t="s">
+        <v>351</v>
+      </c>
+      <c r="C98" t="s">
+        <v>293</v>
+      </c>
+      <c r="D98">
+        <v>39</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B99" t="s">
+        <v>29</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D99">
+        <v>39</v>
+      </c>
+      <c r="E99">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B100" t="s">
+        <v>278</v>
+      </c>
+      <c r="C100" t="s">
+        <v>301</v>
+      </c>
+      <c r="D100">
+        <v>39</v>
+      </c>
+      <c r="E100">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B101" t="s">
+        <v>305</v>
+      </c>
+      <c r="C101" t="s">
+        <v>306</v>
+      </c>
+      <c r="D101">
+        <v>38</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B102" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C102" t="s">
+        <v>306</v>
+      </c>
+      <c r="D102">
+        <v>37</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B103" t="s">
+        <v>52</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D103">
+        <v>37</v>
+      </c>
+      <c r="E103">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B104" t="s">
+        <v>247</v>
+      </c>
+      <c r="C104" t="s">
+        <v>293</v>
+      </c>
+      <c r="D104">
+        <v>37</v>
+      </c>
+      <c r="E104">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B105" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C105" t="s">
+        <v>301</v>
+      </c>
+      <c r="D105">
+        <v>36</v>
+      </c>
+      <c r="E105">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B106" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C106" t="s">
+        <v>293</v>
+      </c>
+      <c r="D106">
+        <v>36</v>
+      </c>
+      <c r="E106">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B107" t="s">
+        <v>115</v>
+      </c>
+      <c r="C107" t="s">
+        <v>306</v>
+      </c>
+      <c r="D107">
+        <v>36</v>
+      </c>
+      <c r="E107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B108" t="s">
+        <v>452</v>
+      </c>
+      <c r="C108" t="s">
+        <v>306</v>
+      </c>
+      <c r="D108">
+        <v>36</v>
+      </c>
+      <c r="E108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B109" t="s">
+        <v>271</v>
+      </c>
+      <c r="C109" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D109">
+        <v>36</v>
+      </c>
+      <c r="E109">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B110" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C110" t="s">
+        <v>293</v>
+      </c>
+      <c r="D110">
+        <v>36</v>
+      </c>
+      <c r="E110">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B111" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C111" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D111">
+        <v>35</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B112" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C112" t="s">
+        <v>293</v>
+      </c>
+      <c r="D112">
+        <v>35</v>
+      </c>
+      <c r="E112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B113" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C113" t="s">
+        <v>306</v>
+      </c>
+      <c r="D113">
+        <v>35</v>
+      </c>
+      <c r="E113">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B114" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C114" t="s">
+        <v>301</v>
+      </c>
+      <c r="D114">
+        <v>35</v>
+      </c>
+      <c r="E114">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="115" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B115" t="s">
+        <v>53</v>
+      </c>
+      <c r="C115" t="s">
+        <v>293</v>
+      </c>
+      <c r="D115">
+        <v>35</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B116" t="s">
+        <v>884</v>
+      </c>
+      <c r="C116" t="s">
+        <v>293</v>
+      </c>
+      <c r="D116">
+        <v>35</v>
+      </c>
+      <c r="E116">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B117" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C117" t="s">
+        <v>301</v>
+      </c>
+      <c r="D117">
+        <v>34</v>
+      </c>
+      <c r="E117">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="118" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B118" t="s">
+        <v>131</v>
+      </c>
+      <c r="C118" t="s">
+        <v>293</v>
+      </c>
+      <c r="D118">
+        <v>34</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B119" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C119" t="s">
+        <v>293</v>
+      </c>
+      <c r="D119">
+        <v>34</v>
+      </c>
+      <c r="E119">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B120" t="s">
+        <v>272</v>
+      </c>
+      <c r="C120" t="s">
+        <v>293</v>
+      </c>
+      <c r="D120">
+        <v>34</v>
+      </c>
+      <c r="E120">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B121" t="s">
+        <v>808</v>
+      </c>
+      <c r="C121" t="s">
+        <v>306</v>
+      </c>
+      <c r="D121">
+        <v>34</v>
+      </c>
+      <c r="E121">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B122" t="s">
+        <v>42</v>
+      </c>
+      <c r="C122" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D122">
+        <v>34</v>
+      </c>
+      <c r="E122">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B123" t="s">
+        <v>703</v>
+      </c>
+      <c r="C123" t="s">
+        <v>301</v>
+      </c>
+      <c r="D123">
+        <v>33</v>
+      </c>
+      <c r="E123">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="124" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B124" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C124" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D124">
+        <v>33</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B125" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C125" t="s">
+        <v>298</v>
+      </c>
+      <c r="D125">
+        <v>33</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B126" t="s">
+        <v>173</v>
+      </c>
+      <c r="C126" t="s">
+        <v>301</v>
+      </c>
+      <c r="D126">
+        <v>33</v>
+      </c>
+      <c r="E126">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B127" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C127" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D127">
+        <v>33</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B128" t="s">
+        <v>279</v>
+      </c>
+      <c r="C128" t="s">
+        <v>293</v>
+      </c>
+      <c r="D128">
+        <v>33</v>
+      </c>
+      <c r="E128">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B129" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D129">
+        <v>32</v>
+      </c>
+      <c r="E129">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B130" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C130" t="s">
+        <v>301</v>
+      </c>
+      <c r="D130">
+        <v>32</v>
+      </c>
+      <c r="E130">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B131" t="s">
+        <v>760</v>
+      </c>
+      <c r="C131" t="s">
+        <v>293</v>
+      </c>
+      <c r="D131">
+        <v>32</v>
+      </c>
+      <c r="E131">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B132" t="s">
+        <v>773</v>
+      </c>
+      <c r="C132" t="s">
+        <v>306</v>
+      </c>
+      <c r="D132">
+        <v>31</v>
+      </c>
+      <c r="E132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B133" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C133" t="s">
+        <v>293</v>
+      </c>
+      <c r="D133">
+        <v>31</v>
+      </c>
+      <c r="E133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B134" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C134" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D134">
+        <v>30</v>
+      </c>
+      <c r="E134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B135" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C135" t="s">
+        <v>306</v>
+      </c>
+      <c r="D135">
+        <v>30</v>
+      </c>
+      <c r="E135">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B136" t="s">
+        <v>37</v>
+      </c>
+      <c r="C136" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D136">
+        <v>30</v>
+      </c>
+      <c r="E136">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B137" t="s">
+        <v>73</v>
+      </c>
+      <c r="C137" t="s">
+        <v>306</v>
+      </c>
+      <c r="D137">
+        <v>30</v>
+      </c>
+      <c r="E137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B138" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C138" t="s">
+        <v>306</v>
+      </c>
+      <c r="D138">
+        <v>29</v>
+      </c>
+      <c r="E138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B139" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C139" t="s">
+        <v>293</v>
+      </c>
+      <c r="D139">
+        <v>28</v>
+      </c>
+      <c r="E139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B140" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C140" t="s">
+        <v>306</v>
+      </c>
+      <c r="D140">
+        <v>28</v>
+      </c>
+      <c r="E140">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B141" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C141" t="s">
+        <v>306</v>
+      </c>
+      <c r="D141">
+        <v>28</v>
+      </c>
+      <c r="E141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B142" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C142" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D142">
+        <v>27</v>
+      </c>
+      <c r="E142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B143" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C143" t="s">
+        <v>306</v>
+      </c>
+      <c r="D143">
+        <v>27</v>
+      </c>
+      <c r="E143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B144" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C144" t="s">
+        <v>301</v>
+      </c>
+      <c r="D144">
+        <v>27</v>
+      </c>
+      <c r="E144">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="145" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B145" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C145" t="s">
+        <v>306</v>
+      </c>
+      <c r="D145">
+        <v>27</v>
+      </c>
+      <c r="E145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B146" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D146">
+        <v>27</v>
+      </c>
+      <c r="E146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B147" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C147" t="s">
+        <v>306</v>
+      </c>
+      <c r="D147">
+        <v>27</v>
+      </c>
+      <c r="E147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B148" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C148" t="s">
+        <v>306</v>
+      </c>
+      <c r="D148">
+        <v>27</v>
+      </c>
+      <c r="E148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B149" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C149" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D149">
+        <v>26</v>
+      </c>
+      <c r="E149">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B150" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C150" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D150">
+        <v>26</v>
+      </c>
+      <c r="E150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B151" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C151" t="s">
+        <v>301</v>
+      </c>
+      <c r="D151">
+        <v>26</v>
+      </c>
+      <c r="E151">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="152" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B152" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C152" t="s">
+        <v>301</v>
+      </c>
+      <c r="D152">
+        <v>26</v>
+      </c>
+      <c r="E152">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B153" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C153" t="s">
+        <v>306</v>
+      </c>
+      <c r="D153">
+        <v>26</v>
+      </c>
+      <c r="E153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B154" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C154" t="s">
+        <v>293</v>
+      </c>
+      <c r="D154">
+        <v>26</v>
+      </c>
+      <c r="E154">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B155" t="s">
+        <v>137</v>
+      </c>
+      <c r="C155" t="s">
+        <v>301</v>
+      </c>
+      <c r="D155">
+        <v>26</v>
+      </c>
+      <c r="E155">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B156" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C156" t="s">
+        <v>306</v>
+      </c>
+      <c r="D156">
+        <v>26</v>
+      </c>
+      <c r="E156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B157" t="s">
+        <v>192</v>
+      </c>
+      <c r="C157" t="s">
+        <v>301</v>
+      </c>
+      <c r="D157">
+        <v>26</v>
+      </c>
+      <c r="E157">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B158" t="s">
+        <v>93</v>
+      </c>
+      <c r="C158" t="s">
+        <v>301</v>
+      </c>
+      <c r="D158">
+        <v>26</v>
+      </c>
+      <c r="E158">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="159" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B159" t="s">
+        <v>1470</v>
+      </c>
+      <c r="C159" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D159">
+        <v>25</v>
+      </c>
+      <c r="E159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B160" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C160" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D160">
+        <v>25</v>
+      </c>
+      <c r="E160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B161" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C161" t="s">
+        <v>298</v>
+      </c>
+      <c r="D161">
+        <v>25</v>
+      </c>
+      <c r="E161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B162" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C162" t="s">
+        <v>301</v>
+      </c>
+      <c r="D162">
+        <v>25</v>
+      </c>
+      <c r="E162">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="163" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B163" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C163" t="s">
+        <v>293</v>
+      </c>
+      <c r="D163">
+        <v>25</v>
+      </c>
+      <c r="E163">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="164" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B164" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C164" t="s">
+        <v>298</v>
+      </c>
+      <c r="D164">
+        <v>24</v>
+      </c>
+      <c r="E164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B165" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C165" t="s">
+        <v>301</v>
+      </c>
+      <c r="D165">
+        <v>24</v>
+      </c>
+      <c r="E165">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="166" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B166" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C166" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D166">
+        <v>24</v>
+      </c>
+      <c r="E166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B167" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C167" t="s">
+        <v>293</v>
+      </c>
+      <c r="D167">
+        <v>24</v>
+      </c>
+      <c r="E167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B168" t="s">
+        <v>711</v>
+      </c>
+      <c r="C168" t="s">
+        <v>301</v>
+      </c>
+      <c r="D168">
+        <v>23</v>
+      </c>
+      <c r="E168">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="169" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B169" t="s">
+        <v>704</v>
+      </c>
+      <c r="C169" t="s">
+        <v>301</v>
+      </c>
+      <c r="D169">
+        <v>23</v>
+      </c>
+      <c r="E169">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="170" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B170" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C170" t="s">
+        <v>301</v>
+      </c>
+      <c r="D170">
+        <v>23</v>
+      </c>
+      <c r="E170">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="171" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B171" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C171" t="s">
+        <v>298</v>
+      </c>
+      <c r="D171">
+        <v>23</v>
+      </c>
+      <c r="E171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B172" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C172" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D172">
+        <v>23</v>
+      </c>
+      <c r="E172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B173" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C173" t="s">
+        <v>306</v>
+      </c>
+      <c r="D173">
+        <v>23</v>
+      </c>
+      <c r="E173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B174" t="s">
+        <v>381</v>
+      </c>
+      <c r="C174" t="s">
+        <v>298</v>
+      </c>
+      <c r="D174">
+        <v>23</v>
+      </c>
+      <c r="E174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B175" t="s">
+        <v>79</v>
+      </c>
+      <c r="C175" t="s">
+        <v>293</v>
+      </c>
+      <c r="D175">
+        <v>23</v>
+      </c>
+      <c r="E175">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B176" t="s">
+        <v>465</v>
+      </c>
+      <c r="C176" t="s">
+        <v>306</v>
+      </c>
+      <c r="D176">
+        <v>23</v>
+      </c>
+      <c r="E176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B177" t="s">
+        <v>781</v>
+      </c>
+      <c r="C177" t="s">
+        <v>301</v>
+      </c>
+      <c r="D177">
+        <v>23</v>
+      </c>
+      <c r="E177">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="178" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B178" t="s">
+        <v>1482</v>
+      </c>
+      <c r="C178" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D178">
+        <v>22</v>
+      </c>
+      <c r="E178">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B179" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C179" t="s">
+        <v>293</v>
+      </c>
+      <c r="D179">
+        <v>22</v>
+      </c>
+      <c r="E179">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B180" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C180" t="s">
+        <v>306</v>
+      </c>
+      <c r="D180">
+        <v>22</v>
+      </c>
+      <c r="E180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B181" t="s">
+        <v>473</v>
+      </c>
+      <c r="C181" t="s">
+        <v>306</v>
+      </c>
+      <c r="D181">
+        <v>22</v>
+      </c>
+      <c r="E181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B182" t="s">
+        <v>241</v>
+      </c>
+      <c r="C182" t="s">
+        <v>301</v>
+      </c>
+      <c r="D182">
+        <v>22</v>
+      </c>
+      <c r="E182">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="183" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B183" t="s">
+        <v>1484</v>
+      </c>
+      <c r="C183" t="s">
+        <v>306</v>
+      </c>
+      <c r="D183">
+        <v>22</v>
+      </c>
+      <c r="E183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B184" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C184" t="s">
+        <v>293</v>
+      </c>
+      <c r="D184">
+        <v>22</v>
+      </c>
+      <c r="E184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B185" t="s">
+        <v>113</v>
+      </c>
+      <c r="C185" t="s">
+        <v>301</v>
+      </c>
+      <c r="D185">
+        <v>22</v>
+      </c>
+      <c r="E185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B186" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C186" t="s">
+        <v>298</v>
+      </c>
+      <c r="D186">
+        <v>21</v>
+      </c>
+      <c r="E186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B187" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C187" t="s">
+        <v>301</v>
+      </c>
+      <c r="D187">
+        <v>21</v>
+      </c>
+      <c r="E187">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="188" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B188" t="s">
+        <v>139</v>
+      </c>
+      <c r="C188" t="s">
+        <v>293</v>
+      </c>
+      <c r="D188">
+        <v>21</v>
+      </c>
+      <c r="E188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B189" t="s">
+        <v>117</v>
+      </c>
+      <c r="C189" t="s">
+        <v>293</v>
+      </c>
+      <c r="D189">
+        <v>21</v>
+      </c>
+      <c r="E189">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="190" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B190" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C190" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D190">
+        <v>21</v>
+      </c>
+      <c r="E190">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B191" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C191" t="s">
+        <v>306</v>
+      </c>
+      <c r="D191">
+        <v>21</v>
+      </c>
+      <c r="E191">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B192" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C192" t="s">
+        <v>293</v>
+      </c>
+      <c r="D192">
+        <v>21</v>
+      </c>
+      <c r="E192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B193" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C193" t="s">
+        <v>306</v>
+      </c>
+      <c r="D193">
+        <v>21</v>
+      </c>
+      <c r="E193">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B194" t="s">
+        <v>80</v>
+      </c>
+      <c r="C194" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D194">
+        <v>21</v>
+      </c>
+      <c r="E194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B195" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C195" t="s">
+        <v>306</v>
+      </c>
+      <c r="D195">
+        <v>21</v>
+      </c>
+      <c r="E195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B196" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C196" t="s">
+        <v>301</v>
+      </c>
+      <c r="D196">
+        <v>20</v>
+      </c>
+      <c r="E196">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="197" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B197" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C197" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D197">
+        <v>20</v>
+      </c>
+      <c r="E197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B198" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C198" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D198">
+        <v>20</v>
+      </c>
+      <c r="E198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B199" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C199" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D199">
+        <v>20</v>
+      </c>
+      <c r="E199">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B200" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C200" t="s">
+        <v>301</v>
+      </c>
+      <c r="D200">
+        <v>20</v>
+      </c>
+      <c r="E200">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="201" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B201" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C201" t="s">
+        <v>306</v>
+      </c>
+      <c r="D201">
+        <v>20</v>
+      </c>
+      <c r="E201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B202" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C202" t="s">
+        <v>306</v>
+      </c>
+      <c r="D202">
+        <v>20</v>
+      </c>
+      <c r="E202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B203" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C203" t="s">
+        <v>293</v>
+      </c>
+      <c r="D203">
+        <v>20</v>
+      </c>
+      <c r="E203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B204" t="s">
+        <v>189</v>
+      </c>
+      <c r="C204" t="s">
+        <v>301</v>
+      </c>
+      <c r="D204">
+        <v>20</v>
+      </c>
+      <c r="E204">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="205" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B205" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C205" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D205">
+        <v>19</v>
+      </c>
+      <c r="E205">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="206" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B206" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C206" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D206">
+        <v>19</v>
+      </c>
+      <c r="E206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B207" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C207" t="s">
+        <v>298</v>
+      </c>
+      <c r="D207">
+        <v>19</v>
+      </c>
+      <c r="E207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B208" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C208" t="s">
+        <v>298</v>
+      </c>
+      <c r="D208">
+        <v>19</v>
+      </c>
+      <c r="E208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B209" t="s">
+        <v>746</v>
+      </c>
+      <c r="C209" t="s">
+        <v>301</v>
+      </c>
+      <c r="D209">
+        <v>19</v>
+      </c>
+      <c r="E209">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="210" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B210" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C210" t="s">
+        <v>306</v>
+      </c>
+      <c r="D210">
+        <v>19</v>
+      </c>
+      <c r="E210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B211" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C211" t="s">
+        <v>301</v>
+      </c>
+      <c r="D211">
+        <v>19</v>
+      </c>
+      <c r="E211">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B212" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C212" t="s">
+        <v>301</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="213" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B213" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C213" t="s">
+        <v>301</v>
+      </c>
+      <c r="D213">
+        <v>19</v>
+      </c>
+      <c r="E213">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="214" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B214" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C214" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D214">
+        <v>19</v>
+      </c>
+      <c r="E214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B215" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C215" t="s">
+        <v>306</v>
+      </c>
+      <c r="D215">
+        <v>19</v>
+      </c>
+      <c r="E215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B216" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C216" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D216">
+        <v>19</v>
+      </c>
+      <c r="E216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B217" t="s">
+        <v>265</v>
+      </c>
+      <c r="C217" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D217">
+        <v>19</v>
+      </c>
+      <c r="E217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B218" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C218" t="s">
+        <v>306</v>
+      </c>
+      <c r="D218">
+        <v>19</v>
+      </c>
+      <c r="E218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B219" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C219" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D219">
+        <v>18</v>
+      </c>
+      <c r="E219">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="220" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B220" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C220" t="s">
+        <v>301</v>
+      </c>
+      <c r="D220">
+        <v>18</v>
+      </c>
+      <c r="E220">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="221" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B221" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C221" t="s">
+        <v>301</v>
+      </c>
+      <c r="D221">
+        <v>18</v>
+      </c>
+      <c r="E221">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="222" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B222" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C222" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D222">
+        <v>18</v>
+      </c>
+      <c r="E222">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="223" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B223" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C223" t="s">
+        <v>306</v>
+      </c>
+      <c r="D223">
+        <v>18</v>
+      </c>
+      <c r="E223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B224" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C224" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D224">
+        <v>18</v>
+      </c>
+      <c r="E224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B225" t="s">
+        <v>382</v>
+      </c>
+      <c r="C225" t="s">
+        <v>293</v>
+      </c>
+      <c r="D225">
+        <v>18</v>
+      </c>
+      <c r="E225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B226" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C226" t="s">
+        <v>306</v>
+      </c>
+      <c r="D226">
+        <v>18</v>
+      </c>
+      <c r="E226">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B227" t="s">
+        <v>1520</v>
+      </c>
+      <c r="C227" t="s">
+        <v>306</v>
+      </c>
+      <c r="D227">
+        <v>18</v>
+      </c>
+      <c r="E227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B228" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C228" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D228">
+        <v>17</v>
+      </c>
+      <c r="E228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B229" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C229" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D229">
+        <v>17</v>
+      </c>
+      <c r="E229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B230" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C230" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D230">
+        <v>17</v>
+      </c>
+      <c r="E230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B231" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C231" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D231">
+        <v>17</v>
+      </c>
+      <c r="E231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B232" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C232" t="s">
+        <v>293</v>
+      </c>
+      <c r="D232">
+        <v>17</v>
+      </c>
+      <c r="E232">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="233" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B233" t="s">
+        <v>836</v>
+      </c>
+      <c r="C233" t="s">
+        <v>293</v>
+      </c>
+      <c r="D233">
+        <v>17</v>
+      </c>
+      <c r="E233">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="234" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B234" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C234" t="s">
+        <v>293</v>
+      </c>
+      <c r="D234">
+        <v>17</v>
+      </c>
+      <c r="E234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B235" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C235" t="s">
+        <v>306</v>
+      </c>
+      <c r="D235">
+        <v>17</v>
+      </c>
+      <c r="E235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B236" t="s">
+        <v>847</v>
+      </c>
+      <c r="C236" t="s">
+        <v>293</v>
+      </c>
+      <c r="D236">
+        <v>17</v>
+      </c>
+      <c r="E236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B237" t="s">
+        <v>86</v>
+      </c>
+      <c r="C237" t="s">
+        <v>301</v>
+      </c>
+      <c r="D237">
+        <v>17</v>
+      </c>
+      <c r="E237">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="238" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B238" t="s">
+        <v>857</v>
+      </c>
+      <c r="C238" t="s">
+        <v>293</v>
+      </c>
+      <c r="D238">
+        <v>17</v>
+      </c>
+      <c r="E238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B239" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C239" t="s">
+        <v>301</v>
+      </c>
+      <c r="D239">
+        <v>17</v>
+      </c>
+      <c r="E239">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B240" t="s">
+        <v>1529</v>
+      </c>
+      <c r="C240" t="s">
+        <v>301</v>
+      </c>
+      <c r="D240">
+        <v>16</v>
+      </c>
+      <c r="E240">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="241" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B241" t="s">
+        <v>1530</v>
+      </c>
+      <c r="C241" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D241">
+        <v>16</v>
+      </c>
+      <c r="E241">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="242" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B242" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C242" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D242">
+        <v>16</v>
+      </c>
+      <c r="E242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B243" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C243" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D243">
+        <v>16</v>
+      </c>
+      <c r="E243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B244" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C244" t="s">
+        <v>301</v>
+      </c>
+      <c r="D244">
+        <v>16</v>
+      </c>
+      <c r="E244">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="245" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B245" t="s">
+        <v>846</v>
+      </c>
+      <c r="C245" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D245">
+        <v>16</v>
+      </c>
+      <c r="E245">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B246" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C246" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D246">
+        <v>16</v>
+      </c>
+      <c r="E246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B247" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C247" t="s">
+        <v>293</v>
+      </c>
+      <c r="D247">
+        <v>16</v>
+      </c>
+      <c r="E247">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="248" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B248" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C248" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D248">
+        <v>15</v>
+      </c>
+      <c r="E248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B249" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C249" t="s">
+        <v>301</v>
+      </c>
+      <c r="D249">
+        <v>15</v>
+      </c>
+      <c r="E249">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="250" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B250" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C250" t="s">
+        <v>301</v>
+      </c>
+      <c r="D250">
+        <v>15</v>
+      </c>
+      <c r="E250">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="251" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B251" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C251" t="s">
+        <v>306</v>
+      </c>
+      <c r="D251">
+        <v>15</v>
+      </c>
+      <c r="E251">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B252" t="s">
+        <v>348</v>
+      </c>
+      <c r="C252" t="s">
+        <v>301</v>
+      </c>
+      <c r="D252">
+        <v>15</v>
+      </c>
+      <c r="E252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B253" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C253" t="s">
+        <v>306</v>
+      </c>
+      <c r="D253">
+        <v>15</v>
+      </c>
+      <c r="E253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B254" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C254" t="s">
+        <v>301</v>
+      </c>
+      <c r="D254">
+        <v>14</v>
+      </c>
+      <c r="E254">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="255" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B255" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C255" t="s">
+        <v>1543</v>
+      </c>
+      <c r="D255">
+        <v>14</v>
+      </c>
+      <c r="E255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B256" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C256" t="s">
+        <v>301</v>
+      </c>
+      <c r="D256">
+        <v>14</v>
+      </c>
+      <c r="E256">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="257" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B257" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C257" t="s">
+        <v>301</v>
+      </c>
+      <c r="D257">
+        <v>14</v>
+      </c>
+      <c r="E257">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="258" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B258" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C258" t="s">
+        <v>301</v>
+      </c>
+      <c r="D258">
+        <v>14</v>
+      </c>
+      <c r="E258">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="259" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B259" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C259" t="s">
+        <v>301</v>
+      </c>
+      <c r="D259">
+        <v>14</v>
+      </c>
+      <c r="E259">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="260" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B260" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C260" t="s">
+        <v>298</v>
+      </c>
+      <c r="D260">
+        <v>14</v>
+      </c>
+      <c r="E260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B261" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C261" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D261">
+        <v>14</v>
+      </c>
+      <c r="E261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B262" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C262" t="s">
+        <v>301</v>
+      </c>
+      <c r="D262">
+        <v>14</v>
+      </c>
+      <c r="E262">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="263" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B263" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C263" t="s">
+        <v>301</v>
+      </c>
+      <c r="D263">
+        <v>14</v>
+      </c>
+      <c r="E263">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="264" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B264" t="s">
+        <v>883</v>
+      </c>
+      <c r="C264" t="s">
+        <v>293</v>
+      </c>
+      <c r="D264">
+        <v>14</v>
+      </c>
+      <c r="E264">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="265" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B265" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C265" t="s">
+        <v>293</v>
+      </c>
+      <c r="D265">
+        <v>14</v>
+      </c>
+      <c r="E265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B266" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C266" t="s">
+        <v>293</v>
+      </c>
+      <c r="D266">
+        <v>14</v>
+      </c>
+      <c r="E266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B267" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C267" t="s">
+        <v>306</v>
+      </c>
+      <c r="D267">
+        <v>14</v>
+      </c>
+      <c r="E267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B268" t="s">
+        <v>260</v>
+      </c>
+      <c r="C268" t="s">
+        <v>293</v>
+      </c>
+      <c r="D268">
+        <v>14</v>
+      </c>
+      <c r="E268">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="269" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B269" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C269" t="s">
+        <v>301</v>
+      </c>
+      <c r="D269">
+        <v>13</v>
+      </c>
+      <c r="E269">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="270" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B270" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C270" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D270">
+        <v>13</v>
+      </c>
+      <c r="E270">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B271" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C271" t="s">
+        <v>301</v>
+      </c>
+      <c r="D271">
+        <v>13</v>
+      </c>
+      <c r="E271">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="272" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B272" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C272" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D272">
+        <v>13</v>
+      </c>
+      <c r="E272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B273" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C273" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D273">
+        <v>13</v>
+      </c>
+      <c r="E273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B274" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C274" t="s">
+        <v>301</v>
+      </c>
+      <c r="D274">
+        <v>13</v>
+      </c>
+      <c r="E274">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="275" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B275" t="s">
+        <v>1561</v>
+      </c>
+      <c r="C275" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D275">
+        <v>13</v>
+      </c>
+      <c r="E275">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="276" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B276" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C276" t="s">
+        <v>293</v>
+      </c>
+      <c r="D276">
+        <v>13</v>
+      </c>
+      <c r="E276">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B277" t="s">
+        <v>265</v>
+      </c>
+      <c r="C277" t="s">
+        <v>301</v>
+      </c>
+      <c r="D277">
+        <v>13</v>
+      </c>
+      <c r="E277">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="278" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B278" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C278" t="s">
+        <v>301</v>
+      </c>
+      <c r="D278">
+        <v>13</v>
+      </c>
+      <c r="E278">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B279" t="s">
+        <v>175</v>
+      </c>
+      <c r="C279" t="s">
+        <v>301</v>
+      </c>
+      <c r="D279">
+        <v>13</v>
+      </c>
+      <c r="E279">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B280" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C280" t="s">
+        <v>306</v>
+      </c>
+      <c r="D280">
+        <v>13</v>
+      </c>
+      <c r="E280">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B281" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C281" t="s">
+        <v>293</v>
+      </c>
+      <c r="D281">
+        <v>13</v>
+      </c>
+      <c r="E281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B282" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C282" t="s">
+        <v>293</v>
+      </c>
+      <c r="D282">
+        <v>13</v>
+      </c>
+      <c r="E282">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="283" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B283" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C283" t="s">
+        <v>301</v>
+      </c>
+      <c r="D283">
+        <v>13</v>
+      </c>
+      <c r="E283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B284" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C284" t="s">
+        <v>301</v>
+      </c>
+      <c r="D284">
+        <v>12</v>
+      </c>
+      <c r="E284">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="285" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B285" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C285" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D285">
+        <v>12</v>
+      </c>
+      <c r="E285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B286" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C286" t="s">
+        <v>301</v>
+      </c>
+      <c r="D286">
+        <v>12</v>
+      </c>
+      <c r="E286">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="287" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B287" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C287" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D287">
+        <v>12</v>
+      </c>
+      <c r="E287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B288" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C288" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D288">
+        <v>12</v>
+      </c>
+      <c r="E288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B289" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C289" t="s">
+        <v>301</v>
+      </c>
+      <c r="D289">
+        <v>12</v>
+      </c>
+      <c r="E289">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="290" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B290" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C290" t="s">
+        <v>301</v>
+      </c>
+      <c r="D290">
+        <v>12</v>
+      </c>
+      <c r="E290">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="291" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B291" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C291" t="s">
+        <v>301</v>
+      </c>
+      <c r="D291">
+        <v>12</v>
+      </c>
+      <c r="E291">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="292" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B292" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C292" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D292">
+        <v>12</v>
+      </c>
+      <c r="E292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B293" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C293" t="s">
+        <v>293</v>
+      </c>
+      <c r="D293">
+        <v>12</v>
+      </c>
+      <c r="E293">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="294" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B294" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C294" t="s">
+        <v>301</v>
+      </c>
+      <c r="D294">
+        <v>12</v>
+      </c>
+      <c r="E294">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="295" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B295" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C295" t="s">
+        <v>306</v>
+      </c>
+      <c r="D295">
+        <v>12</v>
+      </c>
+      <c r="E295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B296" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C296" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D296">
+        <v>12</v>
+      </c>
+      <c r="E296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B297" t="s">
+        <v>106</v>
+      </c>
+      <c r="C297" t="s">
+        <v>293</v>
+      </c>
+      <c r="D297">
+        <v>12</v>
+      </c>
+      <c r="E297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B298" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C298" t="s">
+        <v>298</v>
+      </c>
+      <c r="D298">
+        <v>12</v>
+      </c>
+      <c r="E298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B299" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C299" t="s">
+        <v>293</v>
+      </c>
+      <c r="D299">
+        <v>12</v>
+      </c>
+      <c r="E299">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="300" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B300" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C300" t="s">
+        <v>306</v>
+      </c>
+      <c r="D300">
+        <v>12</v>
+      </c>
+      <c r="E300">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B301" t="s">
+        <v>209</v>
+      </c>
+      <c r="C301" t="s">
+        <v>301</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="302" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B302" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C302" t="s">
+        <v>293</v>
+      </c>
+      <c r="D302">
+        <v>12</v>
+      </c>
+      <c r="E302">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B303" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C303" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D303">
+        <v>11</v>
+      </c>
+      <c r="E303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B304" t="s">
+        <v>1586</v>
+      </c>
+      <c r="C304" t="s">
+        <v>298</v>
+      </c>
+      <c r="D304">
+        <v>11</v>
+      </c>
+      <c r="E304">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B305" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C305" t="s">
+        <v>301</v>
+      </c>
+      <c r="D305">
+        <v>11</v>
+      </c>
+      <c r="E305">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="306" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B306" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C306" t="s">
+        <v>301</v>
+      </c>
+      <c r="D306">
+        <v>11</v>
+      </c>
+      <c r="E306">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="307" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B307" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C307" t="s">
+        <v>301</v>
+      </c>
+      <c r="D307">
+        <v>11</v>
+      </c>
+      <c r="E307">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="308" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B308" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C308" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D308">
+        <v>11</v>
+      </c>
+      <c r="E308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B309" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C309" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D309">
+        <v>11</v>
+      </c>
+      <c r="E309">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B310" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C310" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D310">
+        <v>11</v>
+      </c>
+      <c r="E310">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B311" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C311" t="s">
+        <v>301</v>
+      </c>
+      <c r="D311">
+        <v>11</v>
+      </c>
+      <c r="E311">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B312" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C312" t="s">
+        <v>301</v>
+      </c>
+      <c r="D312">
+        <v>11</v>
+      </c>
+      <c r="E312">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="313" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B313" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C313" t="s">
+        <v>306</v>
+      </c>
+      <c r="D313">
+        <v>11</v>
+      </c>
+      <c r="E313">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B314" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C314" t="s">
+        <v>306</v>
+      </c>
+      <c r="D314">
+        <v>11</v>
+      </c>
+      <c r="E314">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B315" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C315" t="s">
+        <v>301</v>
+      </c>
+      <c r="D315">
+        <v>11</v>
+      </c>
+      <c r="E315">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B316" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C316" t="s">
+        <v>298</v>
+      </c>
+      <c r="D316">
+        <v>11</v>
+      </c>
+      <c r="E316">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B317" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C317" t="s">
+        <v>301</v>
+      </c>
+      <c r="D317">
+        <v>11</v>
+      </c>
+      <c r="E317">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="318" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B318" t="s">
+        <v>94</v>
+      </c>
+      <c r="C318" t="s">
+        <v>293</v>
+      </c>
+      <c r="D318">
+        <v>11</v>
+      </c>
+      <c r="E318">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="319" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B319" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C319" t="s">
+        <v>301</v>
+      </c>
+      <c r="D319">
+        <v>11</v>
+      </c>
+      <c r="E319">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="320" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B320" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C320" t="s">
+        <v>293</v>
+      </c>
+      <c r="D320">
+        <v>11</v>
+      </c>
+      <c r="E320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B321" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C321" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D321">
+        <v>10</v>
+      </c>
+      <c r="E321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B322" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C322" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D322">
+        <v>10</v>
+      </c>
+      <c r="E322">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B323" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C323" t="s">
+        <v>301</v>
+      </c>
+      <c r="D323">
+        <v>10</v>
+      </c>
+      <c r="E323">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="324" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B324" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C324" t="s">
+        <v>301</v>
+      </c>
+      <c r="D324">
+        <v>10</v>
+      </c>
+      <c r="E324">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="325" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B325" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C325" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D325">
+        <v>10</v>
+      </c>
+      <c r="E325">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B326" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C326" t="s">
+        <v>293</v>
+      </c>
+      <c r="D326">
+        <v>10</v>
+      </c>
+      <c r="E326">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="327" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B327" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C327" t="s">
+        <v>306</v>
+      </c>
+      <c r="D327">
+        <v>10</v>
+      </c>
+      <c r="E327">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B328" t="s">
+        <v>371</v>
+      </c>
+      <c r="C328" t="s">
+        <v>293</v>
+      </c>
+      <c r="D328">
+        <v>10</v>
+      </c>
+      <c r="E328">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B329" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C329" t="s">
+        <v>306</v>
+      </c>
+      <c r="D329">
+        <v>10</v>
+      </c>
+      <c r="E329">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B330" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C330" t="s">
+        <v>293</v>
+      </c>
+      <c r="D330">
+        <v>10</v>
+      </c>
+      <c r="E330">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B331" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C331" t="s">
+        <v>298</v>
+      </c>
+      <c r="D331">
+        <v>10</v>
+      </c>
+      <c r="E331">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B332" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C332" t="s">
+        <v>306</v>
+      </c>
+      <c r="D332">
+        <v>10</v>
+      </c>
+      <c r="E332">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B333" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C333" t="s">
+        <v>301</v>
+      </c>
+      <c r="D333">
+        <v>10</v>
+      </c>
+      <c r="E333">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -29835,7 +36168,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28830BBA-01E9-4290-8134-6C4FA2F187F1}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -31990,7 +38323,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98F72596-567D-4A46-9580-D5E8D1461B30}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -33262,996 +39595,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FFFFC000"/>
-  </sheetPr>
-  <dimension ref="A1:B121"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.36328125" style="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.54296875" style="24" customWidth="1"/>
-    <col min="3" max="3" width="3.81640625" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7265625" style="24" customWidth="1"/>
-    <col min="5" max="16384" width="8.7265625" style="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
-        <v>739</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="24">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="24" t="s">
-        <v>740</v>
-      </c>
-      <c r="B3" s="24">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="24" t="s">
-        <v>653</v>
-      </c>
-      <c r="B4" s="24">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="24" t="s">
-        <v>741</v>
-      </c>
-      <c r="B5" s="24">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="24" t="s">
-        <v>742</v>
-      </c>
-      <c r="B6" s="24">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="24" t="s">
-        <v>655</v>
-      </c>
-      <c r="B7" s="24">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="24">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="24" t="s">
-        <v>743</v>
-      </c>
-      <c r="B9" s="24">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="B10" s="24">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="24">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="B12" s="24">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="24" t="s">
-        <v>744</v>
-      </c>
-      <c r="B13" s="24">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="B14" s="24">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="24" t="s">
-        <v>745</v>
-      </c>
-      <c r="B15" s="24">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="B16" s="24">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="24" t="s">
-        <v>746</v>
-      </c>
-      <c r="B17" s="24">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="24" t="s">
-        <v>747</v>
-      </c>
-      <c r="B18" s="24">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="24" t="s">
-        <v>748</v>
-      </c>
-      <c r="B19" s="24">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="24">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="24" t="s">
-        <v>749</v>
-      </c>
-      <c r="B21" s="24">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="24" t="s">
-        <v>628</v>
-      </c>
-      <c r="B22" s="24">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="B23" s="24">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="24">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="B25" s="24">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="24" t="s">
-        <v>750</v>
-      </c>
-      <c r="B26" s="24">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="24" t="s">
-        <v>737</v>
-      </c>
-      <c r="B27" s="24">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="24" t="s">
-        <v>751</v>
-      </c>
-      <c r="B28" s="24">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="B29" s="24">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" s="24" t="s">
-        <v>752</v>
-      </c>
-      <c r="B30" s="24">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" s="24" t="s">
-        <v>753</v>
-      </c>
-      <c r="B31" s="24">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" s="24" t="s">
-        <v>754</v>
-      </c>
-      <c r="B32" s="24">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" s="24">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="B34" s="24">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35" s="24">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="24" t="s">
-        <v>755</v>
-      </c>
-      <c r="B36" s="24">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="B37" s="24">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="B38" s="24">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="B39" s="24">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="B40" s="24">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="B41" s="24">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="B42" s="24">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" s="24" t="s">
-        <v>756</v>
-      </c>
-      <c r="B43" s="24">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" s="24" t="s">
-        <v>757</v>
-      </c>
-      <c r="B44" s="24">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" s="24" t="s">
-        <v>758</v>
-      </c>
-      <c r="B45" s="24">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" s="24" t="s">
-        <v>759</v>
-      </c>
-      <c r="B46" s="24">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" s="24" t="s">
-        <v>760</v>
-      </c>
-      <c r="B47" s="24">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" s="24" t="s">
-        <v>761</v>
-      </c>
-      <c r="B48" s="24">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" s="24" t="s">
-        <v>423</v>
-      </c>
-      <c r="B49" s="24">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" s="24" t="s">
-        <v>762</v>
-      </c>
-      <c r="B50" s="24">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="B51" s="24">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" s="24" t="s">
-        <v>763</v>
-      </c>
-      <c r="B52" s="24">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" s="24" t="s">
-        <v>467</v>
-      </c>
-      <c r="B53" s="24">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" s="24" t="s">
-        <v>764</v>
-      </c>
-      <c r="B54" s="24">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" s="24" t="s">
-        <v>765</v>
-      </c>
-      <c r="B55" s="24">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A56" s="24" t="s">
-        <v>766</v>
-      </c>
-      <c r="B56" s="24">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" s="24" t="s">
-        <v>767</v>
-      </c>
-      <c r="B57" s="24">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="B58" s="24">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A59" s="24" t="s">
-        <v>768</v>
-      </c>
-      <c r="B59" s="24">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A60" s="24" t="s">
-        <v>414</v>
-      </c>
-      <c r="B60" s="24">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="B61" s="24">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" s="24" t="s">
-        <v>769</v>
-      </c>
-      <c r="B62" s="24">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" s="24" t="s">
-        <v>770</v>
-      </c>
-      <c r="B63" s="24">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A64" s="24" t="s">
-        <v>771</v>
-      </c>
-      <c r="B64" s="24">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A65" s="24" t="s">
-        <v>772</v>
-      </c>
-      <c r="B65" s="24">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B66" s="24">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" s="24" t="s">
-        <v>773</v>
-      </c>
-      <c r="B67" s="24">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" s="24" t="s">
-        <v>774</v>
-      </c>
-      <c r="B68" s="24">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A69" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="B69" s="24">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A70" s="24" t="s">
-        <v>775</v>
-      </c>
-      <c r="B70" s="24">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A71" s="24" t="s">
-        <v>776</v>
-      </c>
-      <c r="B71" s="24">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A72" s="24" t="s">
-        <v>777</v>
-      </c>
-      <c r="B72" s="24">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A73" s="24" t="s">
-        <v>332</v>
-      </c>
-      <c r="B73" s="24">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A74" s="24" t="s">
-        <v>778</v>
-      </c>
-      <c r="B74" s="24">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A75" s="24" t="s">
-        <v>779</v>
-      </c>
-      <c r="B75" s="24">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A76" s="24" t="s">
-        <v>780</v>
-      </c>
-      <c r="B76" s="24">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A77" s="24" t="s">
-        <v>781</v>
-      </c>
-      <c r="B77" s="24">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A78" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="B78" s="24">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A79" s="24" t="s">
-        <v>782</v>
-      </c>
-      <c r="B79" s="24">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A80" s="24" t="s">
-        <v>783</v>
-      </c>
-      <c r="B80" s="24">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A81" s="24" t="s">
-        <v>784</v>
-      </c>
-      <c r="B81" s="24">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A82" s="24" t="s">
-        <v>785</v>
-      </c>
-      <c r="B82" s="24">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A83" s="24" t="s">
-        <v>786</v>
-      </c>
-      <c r="B83" s="24">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A84" s="24" t="s">
-        <v>787</v>
-      </c>
-      <c r="B84" s="24">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A85" s="24" t="s">
-        <v>788</v>
-      </c>
-      <c r="B85" s="24">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A86" s="24" t="s">
-        <v>789</v>
-      </c>
-      <c r="B86" s="24">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A87" s="24" t="s">
-        <v>790</v>
-      </c>
-      <c r="B87" s="24">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A88" s="24" t="s">
-        <v>791</v>
-      </c>
-      <c r="B88" s="24">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A89" s="24" t="s">
-        <v>792</v>
-      </c>
-      <c r="B89" s="24">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A90" s="24" t="s">
-        <v>793</v>
-      </c>
-      <c r="B90" s="24">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A91" s="24" t="s">
-        <v>794</v>
-      </c>
-      <c r="B91" s="24">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A92" s="24" t="s">
-        <v>795</v>
-      </c>
-      <c r="B92" s="24">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A93" s="24" t="s">
-        <v>796</v>
-      </c>
-      <c r="B93" s="24">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A94" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="B94" s="24">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A95" s="24" t="s">
-        <v>365</v>
-      </c>
-      <c r="B95" s="24">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A96" s="24" t="s">
-        <v>308</v>
-      </c>
-      <c r="B96" s="24">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A97" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="B97" s="24">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A98" s="24" t="s">
-        <v>797</v>
-      </c>
-      <c r="B98" s="24">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A99" s="24" t="s">
-        <v>572</v>
-      </c>
-      <c r="B99" s="24">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A100" s="24" t="s">
-        <v>270</v>
-      </c>
-      <c r="B100" s="24">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A101" s="24" t="s">
-        <v>798</v>
-      </c>
-      <c r="B101" s="24">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A102" s="24" t="s">
-        <v>799</v>
-      </c>
-      <c r="B102" s="24">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A103" s="24" t="s">
-        <v>800</v>
-      </c>
-      <c r="B103" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A104" s="24" t="s">
-        <v>801</v>
-      </c>
-      <c r="B104" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A105" s="24" t="s">
-        <v>802</v>
-      </c>
-      <c r="B105" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A106" s="24" t="s">
-        <v>465</v>
-      </c>
-      <c r="B106" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A107" s="24" t="s">
-        <v>803</v>
-      </c>
-      <c r="B107" s="24">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A108" s="24" t="s">
-        <v>804</v>
-      </c>
-      <c r="B108" s="24">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A109" s="24" t="s">
-        <v>805</v>
-      </c>
-      <c r="B109" s="24">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A110" s="24" t="s">
-        <v>614</v>
-      </c>
-      <c r="B110" s="24">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A111" s="24" t="s">
-        <v>806</v>
-      </c>
-      <c r="B111" s="24">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A112" s="24" t="s">
-        <v>807</v>
-      </c>
-      <c r="B112" s="24">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A113" s="24" t="s">
-        <v>808</v>
-      </c>
-      <c r="B113" s="24">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A114" s="24" t="s">
-        <v>581</v>
-      </c>
-      <c r="B114" s="24">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A115" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="B115" s="24">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A116" s="24" t="s">
-        <v>809</v>
-      </c>
-      <c r="B116" s="24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A117" s="24" t="s">
-        <v>537</v>
-      </c>
-      <c r="B117" s="24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A118" s="24" t="s">
-        <v>810</v>
-      </c>
-      <c r="B118" s="24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A119" s="24" t="s">
-        <v>811</v>
-      </c>
-      <c r="B119" s="24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A120" s="24" t="s">
-        <v>812</v>
-      </c>
-      <c r="B120" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A121" s="24" t="s">
-        <v>460</v>
-      </c>
-      <c r="B121" s="24">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/Stats For Rush.xlsx
+++ b/Stats For Rush.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurtl\Desktop\statstreaks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67B47A3-FDE6-4623-AB99-628566AA4D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A92156-BE74-4894-8931-2B3DBC195106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="866" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
